--- a/Instructivo_Formularios_Junio_2026.xlsx
+++ b/Instructivo_Formularios_Junio_2026.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30026"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30131"/>
   <workbookPr codeName="ThisWorkbook" defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://arconelgobec-my.sharepoint.com/personal/ingrid_pendolema_arconel_gob_ec/Documents/7. Ejecución de costos/Repositorio/Formularios/Versión 1/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://arconelgobec-my.sharepoint.com/personal/ingrid_pendolema_arconel_gob_ec/Documents/7. Ejecución de costos/Repositorio/Formularios/Formularios_Instructivo/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="790" documentId="13_ncr:1_{FCF6FBC8-4607-4E2F-9187-96E2A78FAFC9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{25158B1A-4889-45B9-99D3-AF0AF6021CEA}"/>
+  <xr:revisionPtr revIDLastSave="802" documentId="13_ncr:1_{FCF6FBC8-4607-4E2F-9187-96E2A78FAFC9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{0574186F-21C4-4BEB-93AD-D14D3B69B6E4}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11040" xr2:uid="{23C22566-AA08-4718-B9C7-8B52305F382C}"/>
+    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{23C22566-AA08-4718-B9C7-8B52305F382C}"/>
   </bookViews>
   <sheets>
     <sheet name="Instructivo" sheetId="1" r:id="rId1"/>
@@ -819,7 +819,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="14">
+  <cellXfs count="12">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -845,20 +845,14 @@
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -1494,17 +1488,17 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{0EA1B5DC-7870-4CD4-B3EB-79CEB23C3997}">
   <sheetPr codeName="Hoja1"/>
   <dimension ref="A1:G292"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="11.42578125" defaultRowHeight="11.25" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="11.44140625" defaultRowHeight="10.8" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="23.140625" style="3" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="21.85546875" style="3" bestFit="1" customWidth="1"/>
-    <col min="3" max="5" width="11.42578125" style="3" customWidth="1"/>
-    <col min="6" max="6" width="43.42578125" style="8" customWidth="1"/>
-    <col min="7" max="7" width="43.42578125" style="3" customWidth="1"/>
-    <col min="8" max="16384" width="11.42578125" style="3"/>
+    <col min="1" max="1" width="23.109375" style="3" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="21.88671875" style="3" bestFit="1" customWidth="1"/>
+    <col min="3" max="5" width="11.44140625" style="3" customWidth="1"/>
+    <col min="6" max="6" width="43.44140625" style="8" customWidth="1"/>
+    <col min="7" max="7" width="43.44140625" style="3" customWidth="1"/>
+    <col min="8" max="16384" width="11.44140625" style="3"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:7" ht="45" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:7" ht="45" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="s">
         <v>1</v>
       </c>
@@ -1527,7 +1521,7 @@
         <v>169</v>
       </c>
     </row>
-    <row r="2" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A2" s="4" t="s">
         <v>0</v>
       </c>
@@ -1550,7 +1544,7 @@
         <v>170</v>
       </c>
     </row>
-    <row r="3" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A3" s="4" t="s">
         <v>0</v>
       </c>
@@ -1573,7 +1567,7 @@
         <v>170</v>
       </c>
     </row>
-    <row r="4" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A4" s="4" t="s">
         <v>0</v>
       </c>
@@ -1596,7 +1590,7 @@
         <v>170</v>
       </c>
     </row>
-    <row r="5" spans="1:7" ht="33.75" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:7" ht="32.4" x14ac:dyDescent="0.3">
       <c r="A5" s="4" t="s">
         <v>0</v>
       </c>
@@ -1619,7 +1613,7 @@
         <v>209</v>
       </c>
     </row>
-    <row r="6" spans="1:7" ht="56.25" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:7" ht="54" x14ac:dyDescent="0.3">
       <c r="A6" s="4" t="s">
         <v>0</v>
       </c>
@@ -1642,7 +1636,7 @@
         <v>209</v>
       </c>
     </row>
-    <row r="7" spans="1:7" ht="33.75" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:7" ht="32.4" x14ac:dyDescent="0.3">
       <c r="A7" s="4" t="s">
         <v>0</v>
       </c>
@@ -1665,7 +1659,7 @@
         <v>209</v>
       </c>
     </row>
-    <row r="8" spans="1:7" ht="45" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:7" ht="43.2" x14ac:dyDescent="0.3">
       <c r="A8" s="4" t="s">
         <v>0</v>
       </c>
@@ -1688,7 +1682,7 @@
         <v>209</v>
       </c>
     </row>
-    <row r="9" spans="1:7" ht="56.25" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:7" ht="54" x14ac:dyDescent="0.3">
       <c r="A9" s="4" t="s">
         <v>0</v>
       </c>
@@ -1711,7 +1705,7 @@
         <v>209</v>
       </c>
     </row>
-    <row r="10" spans="1:7" ht="45" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:7" ht="32.4" x14ac:dyDescent="0.3">
       <c r="A10" s="4" t="s">
         <v>0</v>
       </c>
@@ -1734,7 +1728,7 @@
         <v>209</v>
       </c>
     </row>
-    <row r="11" spans="1:7" ht="45" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:7" ht="32.4" x14ac:dyDescent="0.3">
       <c r="A11" s="4" t="s">
         <v>0</v>
       </c>
@@ -1757,7 +1751,7 @@
         <v>209</v>
       </c>
     </row>
-    <row r="12" spans="1:7" ht="67.5" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:7" ht="54" x14ac:dyDescent="0.3">
       <c r="A12" s="4" t="s">
         <v>0</v>
       </c>
@@ -1780,7 +1774,7 @@
         <v>209</v>
       </c>
     </row>
-    <row r="13" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A13" s="4" t="s">
         <v>0</v>
       </c>
@@ -1803,7 +1797,7 @@
         <v>182</v>
       </c>
     </row>
-    <row r="14" spans="1:7" ht="56.25" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:7" ht="54" x14ac:dyDescent="0.3">
       <c r="A14" s="4" t="s">
         <v>22</v>
       </c>
@@ -1826,7 +1820,7 @@
         <v>173</v>
       </c>
     </row>
-    <row r="15" spans="1:7" ht="22.5" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:7" ht="21.6" x14ac:dyDescent="0.3">
       <c r="A15" s="4" t="s">
         <v>22</v>
       </c>
@@ -1849,7 +1843,7 @@
         <v>184</v>
       </c>
     </row>
-    <row r="16" spans="1:7" ht="33.75" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:7" ht="21.6" x14ac:dyDescent="0.3">
       <c r="A16" s="4" t="s">
         <v>22</v>
       </c>
@@ -1872,7 +1866,7 @@
         <v>179</v>
       </c>
     </row>
-    <row r="17" spans="1:7" ht="22.5" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:7" ht="21.6" x14ac:dyDescent="0.3">
       <c r="A17" s="4" t="s">
         <v>22</v>
       </c>
@@ -1895,7 +1889,7 @@
         <v>173</v>
       </c>
     </row>
-    <row r="18" spans="1:7" ht="33.75" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:7" ht="21.6" x14ac:dyDescent="0.3">
       <c r="A18" s="4" t="s">
         <v>22</v>
       </c>
@@ -1918,7 +1912,7 @@
         <v>173</v>
       </c>
     </row>
-    <row r="19" spans="1:7" ht="33.75" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:7" ht="21.6" x14ac:dyDescent="0.3">
       <c r="A19" s="4" t="s">
         <v>22</v>
       </c>
@@ -1941,7 +1935,7 @@
         <v>173</v>
       </c>
     </row>
-    <row r="20" spans="1:7" ht="33.75" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:7" ht="32.4" x14ac:dyDescent="0.3">
       <c r="A20" s="4" t="s">
         <v>22</v>
       </c>
@@ -1964,7 +1958,7 @@
         <v>209</v>
       </c>
     </row>
-    <row r="21" spans="1:7" ht="56.25" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:7" ht="54" x14ac:dyDescent="0.3">
       <c r="A21" s="4" t="s">
         <v>22</v>
       </c>
@@ -1987,7 +1981,7 @@
         <v>209</v>
       </c>
     </row>
-    <row r="22" spans="1:7" ht="33.75" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:7" ht="32.4" x14ac:dyDescent="0.3">
       <c r="A22" s="4" t="s">
         <v>22</v>
       </c>
@@ -2010,7 +2004,7 @@
         <v>209</v>
       </c>
     </row>
-    <row r="23" spans="1:7" ht="45" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:7" ht="43.2" x14ac:dyDescent="0.3">
       <c r="A23" s="4" t="s">
         <v>22</v>
       </c>
@@ -2033,7 +2027,7 @@
         <v>209</v>
       </c>
     </row>
-    <row r="24" spans="1:7" ht="56.25" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:7" ht="54" x14ac:dyDescent="0.3">
       <c r="A24" s="4" t="s">
         <v>22</v>
       </c>
@@ -2056,7 +2050,7 @@
         <v>209</v>
       </c>
     </row>
-    <row r="25" spans="1:7" ht="45" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:7" ht="32.4" x14ac:dyDescent="0.3">
       <c r="A25" s="4" t="s">
         <v>22</v>
       </c>
@@ -2079,7 +2073,7 @@
         <v>209</v>
       </c>
     </row>
-    <row r="26" spans="1:7" ht="45" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:7" ht="32.4" x14ac:dyDescent="0.3">
       <c r="A26" s="4" t="s">
         <v>22</v>
       </c>
@@ -2102,7 +2096,7 @@
         <v>209</v>
       </c>
     </row>
-    <row r="27" spans="1:7" ht="56.25" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:7" ht="54" x14ac:dyDescent="0.3">
       <c r="A27" s="4" t="s">
         <v>76</v>
       </c>
@@ -2125,7 +2119,7 @@
         <v>173</v>
       </c>
     </row>
-    <row r="28" spans="1:7" ht="45" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:7" ht="43.2" x14ac:dyDescent="0.3">
       <c r="A28" s="4" t="s">
         <v>76</v>
       </c>
@@ -2148,7 +2142,7 @@
         <v>173</v>
       </c>
     </row>
-    <row r="29" spans="1:7" ht="56.25" x14ac:dyDescent="0.25">
+    <row r="29" spans="1:7" ht="54" x14ac:dyDescent="0.3">
       <c r="A29" s="4" t="s">
         <v>76</v>
       </c>
@@ -2171,7 +2165,7 @@
         <v>173</v>
       </c>
     </row>
-    <row r="30" spans="1:7" ht="78.75" x14ac:dyDescent="0.25">
+    <row r="30" spans="1:7" ht="64.8" x14ac:dyDescent="0.3">
       <c r="A30" s="4" t="s">
         <v>76</v>
       </c>
@@ -2194,7 +2188,7 @@
         <v>176</v>
       </c>
     </row>
-    <row r="31" spans="1:7" ht="56.25" x14ac:dyDescent="0.25">
+    <row r="31" spans="1:7" ht="54" x14ac:dyDescent="0.3">
       <c r="A31" s="4" t="s">
         <v>76</v>
       </c>
@@ -2217,7 +2211,7 @@
         <v>187</v>
       </c>
     </row>
-    <row r="32" spans="1:7" ht="56.25" x14ac:dyDescent="0.25">
+    <row r="32" spans="1:7" ht="54" x14ac:dyDescent="0.3">
       <c r="A32" s="4" t="s">
         <v>76</v>
       </c>
@@ -2240,7 +2234,7 @@
         <v>173</v>
       </c>
     </row>
-    <row r="33" spans="1:7" ht="22.5" x14ac:dyDescent="0.25">
+    <row r="33" spans="1:7" ht="21.6" x14ac:dyDescent="0.3">
       <c r="A33" s="4" t="s">
         <v>76</v>
       </c>
@@ -2263,7 +2257,7 @@
         <v>188</v>
       </c>
     </row>
-    <row r="34" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="34" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A34" s="4" t="s">
         <v>76</v>
       </c>
@@ -2286,7 +2280,7 @@
         <v>188</v>
       </c>
     </row>
-    <row r="35" spans="1:7" ht="22.5" x14ac:dyDescent="0.25">
+    <row r="35" spans="1:7" ht="21.6" x14ac:dyDescent="0.3">
       <c r="A35" s="4" t="s">
         <v>76</v>
       </c>
@@ -2309,7 +2303,7 @@
         <v>188</v>
       </c>
     </row>
-    <row r="36" spans="1:7" ht="67.5" x14ac:dyDescent="0.25">
+    <row r="36" spans="1:7" ht="64.8" x14ac:dyDescent="0.3">
       <c r="A36" s="4" t="s">
         <v>76</v>
       </c>
@@ -2332,7 +2326,7 @@
         <v>188</v>
       </c>
     </row>
-    <row r="37" spans="1:7" ht="67.5" x14ac:dyDescent="0.25">
+    <row r="37" spans="1:7" ht="64.8" x14ac:dyDescent="0.3">
       <c r="A37" s="4" t="s">
         <v>76</v>
       </c>
@@ -2355,7 +2349,7 @@
         <v>188</v>
       </c>
     </row>
-    <row r="38" spans="1:7" ht="67.5" x14ac:dyDescent="0.25">
+    <row r="38" spans="1:7" ht="64.8" x14ac:dyDescent="0.3">
       <c r="A38" s="4" t="s">
         <v>76</v>
       </c>
@@ -2378,7 +2372,7 @@
         <v>188</v>
       </c>
     </row>
-    <row r="39" spans="1:7" ht="45" x14ac:dyDescent="0.25">
+    <row r="39" spans="1:7" ht="43.2" x14ac:dyDescent="0.3">
       <c r="A39" s="4" t="s">
         <v>76</v>
       </c>
@@ -2401,7 +2395,7 @@
         <v>173</v>
       </c>
     </row>
-    <row r="40" spans="1:7" ht="67.5" x14ac:dyDescent="0.25">
+    <row r="40" spans="1:7" ht="64.8" x14ac:dyDescent="0.3">
       <c r="A40" s="4" t="s">
         <v>76</v>
       </c>
@@ -2424,7 +2418,7 @@
         <v>173</v>
       </c>
     </row>
-    <row r="41" spans="1:7" ht="45" x14ac:dyDescent="0.25">
+    <row r="41" spans="1:7" ht="43.2" x14ac:dyDescent="0.3">
       <c r="A41" s="4" t="s">
         <v>76</v>
       </c>
@@ -2447,7 +2441,7 @@
         <v>173</v>
       </c>
     </row>
-    <row r="42" spans="1:7" ht="45" x14ac:dyDescent="0.25">
+    <row r="42" spans="1:7" ht="32.4" x14ac:dyDescent="0.3">
       <c r="A42" s="4" t="s">
         <v>76</v>
       </c>
@@ -2470,7 +2464,7 @@
         <v>173</v>
       </c>
     </row>
-    <row r="43" spans="1:7" ht="56.25" x14ac:dyDescent="0.25">
+    <row r="43" spans="1:7" ht="54" x14ac:dyDescent="0.3">
       <c r="A43" s="4" t="s">
         <v>76</v>
       </c>
@@ -2493,7 +2487,7 @@
         <v>173</v>
       </c>
     </row>
-    <row r="44" spans="1:7" ht="56.25" x14ac:dyDescent="0.25">
+    <row r="44" spans="1:7" ht="43.2" x14ac:dyDescent="0.3">
       <c r="A44" s="4" t="s">
         <v>76</v>
       </c>
@@ -2516,7 +2510,7 @@
         <v>199</v>
       </c>
     </row>
-    <row r="45" spans="1:7" ht="56.25" x14ac:dyDescent="0.25">
+    <row r="45" spans="1:7" ht="54" x14ac:dyDescent="0.3">
       <c r="A45" s="4" t="s">
         <v>76</v>
       </c>
@@ -2539,7 +2533,7 @@
         <v>170</v>
       </c>
     </row>
-    <row r="46" spans="1:7" ht="33.75" x14ac:dyDescent="0.25">
+    <row r="46" spans="1:7" ht="21.6" x14ac:dyDescent="0.3">
       <c r="A46" s="4" t="s">
         <v>76</v>
       </c>
@@ -2562,7 +2556,7 @@
         <v>203</v>
       </c>
     </row>
-    <row r="47" spans="1:7" ht="22.5" x14ac:dyDescent="0.25">
+    <row r="47" spans="1:7" ht="21.6" x14ac:dyDescent="0.3">
       <c r="A47" s="4" t="s">
         <v>76</v>
       </c>
@@ -2585,7 +2579,7 @@
         <v>205</v>
       </c>
     </row>
-    <row r="48" spans="1:7" ht="33.75" x14ac:dyDescent="0.25">
+    <row r="48" spans="1:7" ht="32.4" x14ac:dyDescent="0.3">
       <c r="A48" s="4" t="s">
         <v>76</v>
       </c>
@@ -2608,7 +2602,7 @@
         <v>207</v>
       </c>
     </row>
-    <row r="49" spans="1:7" ht="33.75" x14ac:dyDescent="0.25">
+    <row r="49" spans="1:7" ht="32.4" x14ac:dyDescent="0.3">
       <c r="A49" s="4" t="s">
         <v>76</v>
       </c>
@@ -2631,7 +2625,7 @@
         <v>209</v>
       </c>
     </row>
-    <row r="50" spans="1:7" ht="33.75" x14ac:dyDescent="0.25">
+    <row r="50" spans="1:7" ht="32.4" x14ac:dyDescent="0.3">
       <c r="A50" s="4" t="s">
         <v>76</v>
       </c>
@@ -2654,7 +2648,7 @@
         <v>209</v>
       </c>
     </row>
-    <row r="51" spans="1:7" ht="45" x14ac:dyDescent="0.25">
+    <row r="51" spans="1:7" ht="43.2" x14ac:dyDescent="0.3">
       <c r="A51" s="4" t="s">
         <v>76</v>
       </c>
@@ -2677,7 +2671,7 @@
         <v>209</v>
       </c>
     </row>
-    <row r="52" spans="1:7" ht="33.75" x14ac:dyDescent="0.25">
+    <row r="52" spans="1:7" ht="32.4" x14ac:dyDescent="0.3">
       <c r="A52" s="4" t="s">
         <v>76</v>
       </c>
@@ -2700,7 +2694,7 @@
         <v>209</v>
       </c>
     </row>
-    <row r="53" spans="1:7" ht="33.75" x14ac:dyDescent="0.25">
+    <row r="53" spans="1:7" ht="32.4" x14ac:dyDescent="0.3">
       <c r="A53" s="4" t="s">
         <v>76</v>
       </c>
@@ -2723,7 +2717,7 @@
         <v>209</v>
       </c>
     </row>
-    <row r="54" spans="1:7" ht="56.25" x14ac:dyDescent="0.25">
+    <row r="54" spans="1:7" ht="54" x14ac:dyDescent="0.3">
       <c r="A54" s="4" t="s">
         <v>76</v>
       </c>
@@ -2746,7 +2740,7 @@
         <v>209</v>
       </c>
     </row>
-    <row r="55" spans="1:7" ht="33.75" x14ac:dyDescent="0.25">
+    <row r="55" spans="1:7" ht="32.4" x14ac:dyDescent="0.3">
       <c r="A55" s="4" t="s">
         <v>76</v>
       </c>
@@ -2769,7 +2763,7 @@
         <v>209</v>
       </c>
     </row>
-    <row r="56" spans="1:7" ht="45" x14ac:dyDescent="0.25">
+    <row r="56" spans="1:7" ht="43.2" x14ac:dyDescent="0.3">
       <c r="A56" s="4" t="s">
         <v>76</v>
       </c>
@@ -2792,7 +2786,7 @@
         <v>209</v>
       </c>
     </row>
-    <row r="57" spans="1:7" ht="56.25" x14ac:dyDescent="0.25">
+    <row r="57" spans="1:7" ht="54" x14ac:dyDescent="0.3">
       <c r="A57" s="4" t="s">
         <v>76</v>
       </c>
@@ -2815,7 +2809,7 @@
         <v>209</v>
       </c>
     </row>
-    <row r="58" spans="1:7" ht="45" x14ac:dyDescent="0.25">
+    <row r="58" spans="1:7" ht="32.4" x14ac:dyDescent="0.3">
       <c r="A58" s="4" t="s">
         <v>76</v>
       </c>
@@ -2838,7 +2832,7 @@
         <v>209</v>
       </c>
     </row>
-    <row r="59" spans="1:7" ht="45" x14ac:dyDescent="0.25">
+    <row r="59" spans="1:7" ht="32.4" x14ac:dyDescent="0.3">
       <c r="A59" s="4" t="s">
         <v>76</v>
       </c>
@@ -2861,7 +2855,7 @@
         <v>209</v>
       </c>
     </row>
-    <row r="60" spans="1:7" ht="67.5" x14ac:dyDescent="0.25">
+    <row r="60" spans="1:7" ht="54" x14ac:dyDescent="0.3">
       <c r="A60" s="4" t="s">
         <v>76</v>
       </c>
@@ -2884,7 +2878,7 @@
         <v>209</v>
       </c>
     </row>
-    <row r="61" spans="1:7" ht="22.5" x14ac:dyDescent="0.25">
+    <row r="61" spans="1:7" ht="21.6" x14ac:dyDescent="0.3">
       <c r="A61" s="4" t="s">
         <v>76</v>
       </c>
@@ -2907,7 +2901,7 @@
         <v>214</v>
       </c>
     </row>
-    <row r="62" spans="1:7" ht="22.5" x14ac:dyDescent="0.25">
+    <row r="62" spans="1:7" ht="21.6" x14ac:dyDescent="0.3">
       <c r="A62" s="4" t="s">
         <v>76</v>
       </c>
@@ -2930,7 +2924,7 @@
         <v>214</v>
       </c>
     </row>
-    <row r="63" spans="1:7" ht="45" x14ac:dyDescent="0.25">
+    <row r="63" spans="1:7" ht="32.4" x14ac:dyDescent="0.3">
       <c r="A63" s="4" t="s">
         <v>76</v>
       </c>
@@ -2953,7 +2947,7 @@
         <v>214</v>
       </c>
     </row>
-    <row r="64" spans="1:7" ht="33.75" x14ac:dyDescent="0.25">
+    <row r="64" spans="1:7" ht="32.4" x14ac:dyDescent="0.3">
       <c r="A64" s="4" t="s">
         <v>76</v>
       </c>
@@ -2976,7 +2970,7 @@
         <v>214</v>
       </c>
     </row>
-    <row r="65" spans="1:7" ht="33.75" x14ac:dyDescent="0.25">
+    <row r="65" spans="1:7" ht="32.4" x14ac:dyDescent="0.3">
       <c r="A65" s="4" t="s">
         <v>76</v>
       </c>
@@ -2999,7 +2993,7 @@
         <v>214</v>
       </c>
     </row>
-    <row r="66" spans="1:7" ht="33.75" x14ac:dyDescent="0.25">
+    <row r="66" spans="1:7" ht="32.4" x14ac:dyDescent="0.3">
       <c r="A66" s="4" t="s">
         <v>76</v>
       </c>
@@ -3022,7 +3016,7 @@
         <v>214</v>
       </c>
     </row>
-    <row r="67" spans="1:7" ht="22.5" x14ac:dyDescent="0.25">
+    <row r="67" spans="1:7" ht="21.6" x14ac:dyDescent="0.3">
       <c r="A67" s="4" t="s">
         <v>76</v>
       </c>
@@ -3045,7 +3039,7 @@
         <v>214</v>
       </c>
     </row>
-    <row r="68" spans="1:7" ht="33.75" x14ac:dyDescent="0.25">
+    <row r="68" spans="1:7" ht="21.6" x14ac:dyDescent="0.3">
       <c r="A68" s="4" t="s">
         <v>76</v>
       </c>
@@ -3068,7 +3062,7 @@
         <v>214</v>
       </c>
     </row>
-    <row r="69" spans="1:7" ht="33.75" x14ac:dyDescent="0.25">
+    <row r="69" spans="1:7" ht="32.4" x14ac:dyDescent="0.3">
       <c r="A69" s="4" t="s">
         <v>76</v>
       </c>
@@ -3091,7 +3085,7 @@
         <v>214</v>
       </c>
     </row>
-    <row r="70" spans="1:7" ht="33.75" x14ac:dyDescent="0.25">
+    <row r="70" spans="1:7" ht="21.6" x14ac:dyDescent="0.3">
       <c r="A70" s="4" t="s">
         <v>76</v>
       </c>
@@ -3114,7 +3108,7 @@
         <v>214</v>
       </c>
     </row>
-    <row r="71" spans="1:7" ht="22.5" x14ac:dyDescent="0.25">
+    <row r="71" spans="1:7" ht="21.6" x14ac:dyDescent="0.3">
       <c r="A71" s="4" t="s">
         <v>76</v>
       </c>
@@ -3137,7 +3131,7 @@
         <v>214</v>
       </c>
     </row>
-    <row r="72" spans="1:7" ht="22.5" x14ac:dyDescent="0.25">
+    <row r="72" spans="1:7" ht="21.6" x14ac:dyDescent="0.3">
       <c r="A72" s="4" t="s">
         <v>76</v>
       </c>
@@ -3160,7 +3154,7 @@
         <v>214</v>
       </c>
     </row>
-    <row r="73" spans="1:7" ht="22.5" x14ac:dyDescent="0.25">
+    <row r="73" spans="1:7" ht="21.6" x14ac:dyDescent="0.3">
       <c r="A73" s="4" t="s">
         <v>76</v>
       </c>
@@ -3183,7 +3177,7 @@
         <v>214</v>
       </c>
     </row>
-    <row r="74" spans="1:7" ht="22.5" x14ac:dyDescent="0.25">
+    <row r="74" spans="1:7" ht="21.6" x14ac:dyDescent="0.3">
       <c r="A74" s="4" t="s">
         <v>76</v>
       </c>
@@ -3206,7 +3200,7 @@
         <v>214</v>
       </c>
     </row>
-    <row r="75" spans="1:7" ht="33.75" x14ac:dyDescent="0.25">
+    <row r="75" spans="1:7" ht="32.4" x14ac:dyDescent="0.3">
       <c r="A75" s="4" t="s">
         <v>76</v>
       </c>
@@ -3229,7 +3223,7 @@
         <v>214</v>
       </c>
     </row>
-    <row r="76" spans="1:7" ht="22.5" x14ac:dyDescent="0.25">
+    <row r="76" spans="1:7" ht="21.6" x14ac:dyDescent="0.3">
       <c r="A76" s="4" t="s">
         <v>76</v>
       </c>
@@ -3252,7 +3246,7 @@
         <v>214</v>
       </c>
     </row>
-    <row r="77" spans="1:7" ht="33.75" x14ac:dyDescent="0.25">
+    <row r="77" spans="1:7" ht="32.4" x14ac:dyDescent="0.3">
       <c r="A77" s="4" t="s">
         <v>76</v>
       </c>
@@ -3275,7 +3269,7 @@
         <v>214</v>
       </c>
     </row>
-    <row r="78" spans="1:7" ht="22.5" x14ac:dyDescent="0.25">
+    <row r="78" spans="1:7" ht="21.6" x14ac:dyDescent="0.3">
       <c r="A78" s="4" t="s">
         <v>76</v>
       </c>
@@ -3298,7 +3292,7 @@
         <v>214</v>
       </c>
     </row>
-    <row r="79" spans="1:7" ht="22.5" x14ac:dyDescent="0.25">
+    <row r="79" spans="1:7" ht="21.6" x14ac:dyDescent="0.3">
       <c r="A79" s="4" t="s">
         <v>76</v>
       </c>
@@ -3321,7 +3315,7 @@
         <v>214</v>
       </c>
     </row>
-    <row r="80" spans="1:7" ht="22.5" x14ac:dyDescent="0.25">
+    <row r="80" spans="1:7" ht="21.6" x14ac:dyDescent="0.3">
       <c r="A80" s="4" t="s">
         <v>76</v>
       </c>
@@ -3344,7 +3338,7 @@
         <v>214</v>
       </c>
     </row>
-    <row r="81" spans="1:7" ht="22.5" x14ac:dyDescent="0.25">
+    <row r="81" spans="1:7" ht="21.6" x14ac:dyDescent="0.3">
       <c r="A81" s="4" t="s">
         <v>76</v>
       </c>
@@ -3367,7 +3361,7 @@
         <v>214</v>
       </c>
     </row>
-    <row r="82" spans="1:7" ht="22.5" x14ac:dyDescent="0.25">
+    <row r="82" spans="1:7" ht="21.6" x14ac:dyDescent="0.3">
       <c r="A82" s="4" t="s">
         <v>76</v>
       </c>
@@ -3390,7 +3384,7 @@
         <v>214</v>
       </c>
     </row>
-    <row r="83" spans="1:7" ht="33.75" x14ac:dyDescent="0.25">
+    <row r="83" spans="1:7" ht="32.4" x14ac:dyDescent="0.3">
       <c r="A83" s="4" t="s">
         <v>76</v>
       </c>
@@ -3413,7 +3407,7 @@
         <v>214</v>
       </c>
     </row>
-    <row r="84" spans="1:7" ht="22.5" x14ac:dyDescent="0.25">
+    <row r="84" spans="1:7" ht="21.6" x14ac:dyDescent="0.3">
       <c r="A84" s="4" t="s">
         <v>76</v>
       </c>
@@ -3436,7 +3430,7 @@
         <v>214</v>
       </c>
     </row>
-    <row r="85" spans="1:7" ht="22.5" x14ac:dyDescent="0.25">
+    <row r="85" spans="1:7" ht="21.6" x14ac:dyDescent="0.3">
       <c r="A85" s="4" t="s">
         <v>76</v>
       </c>
@@ -3459,7 +3453,7 @@
         <v>214</v>
       </c>
     </row>
-    <row r="86" spans="1:7" ht="22.5" x14ac:dyDescent="0.25">
+    <row r="86" spans="1:7" ht="21.6" x14ac:dyDescent="0.3">
       <c r="A86" s="4" t="s">
         <v>76</v>
       </c>
@@ -3482,7 +3476,7 @@
         <v>214</v>
       </c>
     </row>
-    <row r="87" spans="1:7" ht="33.75" x14ac:dyDescent="0.25">
+    <row r="87" spans="1:7" ht="21.6" x14ac:dyDescent="0.3">
       <c r="A87" s="4" t="s">
         <v>76</v>
       </c>
@@ -3505,7 +3499,7 @@
         <v>214</v>
       </c>
     </row>
-    <row r="88" spans="1:7" ht="33.75" x14ac:dyDescent="0.25">
+    <row r="88" spans="1:7" ht="21.6" x14ac:dyDescent="0.3">
       <c r="A88" s="4" t="s">
         <v>76</v>
       </c>
@@ -3528,7 +3522,7 @@
         <v>214</v>
       </c>
     </row>
-    <row r="89" spans="1:7" ht="45" x14ac:dyDescent="0.25">
+    <row r="89" spans="1:7" ht="43.2" x14ac:dyDescent="0.3">
       <c r="A89" s="4" t="s">
         <v>76</v>
       </c>
@@ -3551,7 +3545,7 @@
         <v>173</v>
       </c>
     </row>
-    <row r="90" spans="1:7" ht="45" x14ac:dyDescent="0.25">
+    <row r="90" spans="1:7" ht="43.2" x14ac:dyDescent="0.3">
       <c r="A90" s="4" t="s">
         <v>76</v>
       </c>
@@ -3574,7 +3568,7 @@
         <v>217</v>
       </c>
     </row>
-    <row r="91" spans="1:7" ht="45" x14ac:dyDescent="0.25">
+    <row r="91" spans="1:7" ht="43.2" x14ac:dyDescent="0.3">
       <c r="A91" s="4" t="s">
         <v>76</v>
       </c>
@@ -3597,7 +3591,7 @@
         <v>217</v>
       </c>
     </row>
-    <row r="92" spans="1:7" ht="33.75" x14ac:dyDescent="0.25">
+    <row r="92" spans="1:7" ht="32.4" x14ac:dyDescent="0.3">
       <c r="A92" s="4" t="s">
         <v>76</v>
       </c>
@@ -3620,7 +3614,7 @@
         <v>220</v>
       </c>
     </row>
-    <row r="93" spans="1:7" ht="33.75" x14ac:dyDescent="0.25">
+    <row r="93" spans="1:7" ht="32.4" x14ac:dyDescent="0.3">
       <c r="A93" s="4" t="s">
         <v>76</v>
       </c>
@@ -3643,7 +3637,7 @@
         <v>220</v>
       </c>
     </row>
-    <row r="94" spans="1:7" ht="22.5" x14ac:dyDescent="0.25">
+    <row r="94" spans="1:7" ht="21.6" x14ac:dyDescent="0.3">
       <c r="A94" s="4" t="s">
         <v>76</v>
       </c>
@@ -3666,7 +3660,7 @@
         <v>213</v>
       </c>
     </row>
-    <row r="95" spans="1:7" ht="56.25" x14ac:dyDescent="0.25">
+    <row r="95" spans="1:7" ht="54" x14ac:dyDescent="0.3">
       <c r="A95" s="4" t="s">
         <v>82</v>
       </c>
@@ -3689,7 +3683,7 @@
         <v>173</v>
       </c>
     </row>
-    <row r="96" spans="1:7" ht="45" x14ac:dyDescent="0.25">
+    <row r="96" spans="1:7" ht="43.2" x14ac:dyDescent="0.3">
       <c r="A96" s="4" t="s">
         <v>82</v>
       </c>
@@ -3712,7 +3706,7 @@
         <v>173</v>
       </c>
     </row>
-    <row r="97" spans="1:7" ht="78.75" x14ac:dyDescent="0.25">
+    <row r="97" spans="1:7" ht="64.8" x14ac:dyDescent="0.3">
       <c r="A97" s="4" t="s">
         <v>82</v>
       </c>
@@ -3735,7 +3729,7 @@
         <v>176</v>
       </c>
     </row>
-    <row r="98" spans="1:7" ht="22.5" x14ac:dyDescent="0.25">
+    <row r="98" spans="1:7" ht="21.6" x14ac:dyDescent="0.3">
       <c r="A98" s="4" t="s">
         <v>82</v>
       </c>
@@ -3758,7 +3752,7 @@
         <v>188</v>
       </c>
     </row>
-    <row r="99" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="99" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A99" s="4" t="s">
         <v>82</v>
       </c>
@@ -3781,7 +3775,7 @@
         <v>188</v>
       </c>
     </row>
-    <row r="100" spans="1:7" ht="22.5" x14ac:dyDescent="0.25">
+    <row r="100" spans="1:7" ht="21.6" x14ac:dyDescent="0.3">
       <c r="A100" s="4" t="s">
         <v>82</v>
       </c>
@@ -3804,7 +3798,7 @@
         <v>188</v>
       </c>
     </row>
-    <row r="101" spans="1:7" ht="67.5" x14ac:dyDescent="0.25">
+    <row r="101" spans="1:7" ht="64.8" x14ac:dyDescent="0.3">
       <c r="A101" s="4" t="s">
         <v>82</v>
       </c>
@@ -3827,7 +3821,7 @@
         <v>188</v>
       </c>
     </row>
-    <row r="102" spans="1:7" ht="67.5" x14ac:dyDescent="0.25">
+    <row r="102" spans="1:7" ht="64.8" x14ac:dyDescent="0.3">
       <c r="A102" s="4" t="s">
         <v>82</v>
       </c>
@@ -3850,7 +3844,7 @@
         <v>188</v>
       </c>
     </row>
-    <row r="103" spans="1:7" ht="67.5" x14ac:dyDescent="0.25">
+    <row r="103" spans="1:7" ht="64.8" x14ac:dyDescent="0.3">
       <c r="A103" s="4" t="s">
         <v>82</v>
       </c>
@@ -3873,7 +3867,7 @@
         <v>188</v>
       </c>
     </row>
-    <row r="104" spans="1:7" ht="45" x14ac:dyDescent="0.25">
+    <row r="104" spans="1:7" ht="43.2" x14ac:dyDescent="0.3">
       <c r="A104" s="4" t="s">
         <v>82</v>
       </c>
@@ -3896,7 +3890,7 @@
         <v>173</v>
       </c>
     </row>
-    <row r="105" spans="1:7" ht="67.5" x14ac:dyDescent="0.25">
+    <row r="105" spans="1:7" ht="64.8" x14ac:dyDescent="0.3">
       <c r="A105" s="4" t="s">
         <v>82</v>
       </c>
@@ -3919,7 +3913,7 @@
         <v>173</v>
       </c>
     </row>
-    <row r="106" spans="1:7" ht="45" x14ac:dyDescent="0.25">
+    <row r="106" spans="1:7" ht="32.4" x14ac:dyDescent="0.3">
       <c r="A106" s="4" t="s">
         <v>82</v>
       </c>
@@ -3942,7 +3936,7 @@
         <v>173</v>
       </c>
     </row>
-    <row r="107" spans="1:7" ht="56.25" x14ac:dyDescent="0.25">
+    <row r="107" spans="1:7" ht="54" x14ac:dyDescent="0.3">
       <c r="A107" s="4" t="s">
         <v>82</v>
       </c>
@@ -3965,7 +3959,7 @@
         <v>173</v>
       </c>
     </row>
-    <row r="108" spans="1:7" ht="56.25" x14ac:dyDescent="0.25">
+    <row r="108" spans="1:7" ht="43.2" x14ac:dyDescent="0.3">
       <c r="A108" s="4" t="s">
         <v>82</v>
       </c>
@@ -3988,7 +3982,7 @@
         <v>199</v>
       </c>
     </row>
-    <row r="109" spans="1:7" ht="56.25" x14ac:dyDescent="0.25">
+    <row r="109" spans="1:7" ht="54" x14ac:dyDescent="0.3">
       <c r="A109" s="4" t="s">
         <v>82</v>
       </c>
@@ -4011,7 +4005,7 @@
         <v>170</v>
       </c>
     </row>
-    <row r="110" spans="1:7" ht="33.75" x14ac:dyDescent="0.25">
+    <row r="110" spans="1:7" ht="21.6" x14ac:dyDescent="0.3">
       <c r="A110" s="4" t="s">
         <v>82</v>
       </c>
@@ -4034,7 +4028,7 @@
         <v>203</v>
       </c>
     </row>
-    <row r="111" spans="1:7" ht="22.5" x14ac:dyDescent="0.25">
+    <row r="111" spans="1:7" ht="21.6" x14ac:dyDescent="0.3">
       <c r="A111" s="4" t="s">
         <v>82</v>
       </c>
@@ -4057,7 +4051,7 @@
         <v>205</v>
       </c>
     </row>
-    <row r="112" spans="1:7" ht="33.75" x14ac:dyDescent="0.25">
+    <row r="112" spans="1:7" ht="32.4" x14ac:dyDescent="0.3">
       <c r="A112" s="4" t="s">
         <v>82</v>
       </c>
@@ -4080,7 +4074,7 @@
         <v>207</v>
       </c>
     </row>
-    <row r="113" spans="1:7" ht="33.75" x14ac:dyDescent="0.25">
+    <row r="113" spans="1:7" ht="32.4" x14ac:dyDescent="0.3">
       <c r="A113" s="4" t="s">
         <v>82</v>
       </c>
@@ -4103,7 +4097,7 @@
         <v>209</v>
       </c>
     </row>
-    <row r="114" spans="1:7" ht="45" x14ac:dyDescent="0.25">
+    <row r="114" spans="1:7" ht="43.2" x14ac:dyDescent="0.3">
       <c r="A114" s="4" t="s">
         <v>82</v>
       </c>
@@ -4126,7 +4120,7 @@
         <v>209</v>
       </c>
     </row>
-    <row r="115" spans="1:7" ht="33.75" x14ac:dyDescent="0.25">
+    <row r="115" spans="1:7" ht="32.4" x14ac:dyDescent="0.3">
       <c r="A115" s="4" t="s">
         <v>82</v>
       </c>
@@ -4149,7 +4143,7 @@
         <v>209</v>
       </c>
     </row>
-    <row r="116" spans="1:7" ht="33.75" x14ac:dyDescent="0.25">
+    <row r="116" spans="1:7" ht="32.4" x14ac:dyDescent="0.3">
       <c r="A116" s="4" t="s">
         <v>82</v>
       </c>
@@ -4172,7 +4166,7 @@
         <v>209</v>
       </c>
     </row>
-    <row r="117" spans="1:7" ht="56.25" x14ac:dyDescent="0.25">
+    <row r="117" spans="1:7" ht="54" x14ac:dyDescent="0.3">
       <c r="A117" s="4" t="s">
         <v>82</v>
       </c>
@@ -4195,7 +4189,7 @@
         <v>209</v>
       </c>
     </row>
-    <row r="118" spans="1:7" ht="33.75" x14ac:dyDescent="0.25">
+    <row r="118" spans="1:7" ht="32.4" x14ac:dyDescent="0.3">
       <c r="A118" s="4" t="s">
         <v>82</v>
       </c>
@@ -4218,7 +4212,7 @@
         <v>209</v>
       </c>
     </row>
-    <row r="119" spans="1:7" ht="45" x14ac:dyDescent="0.25">
+    <row r="119" spans="1:7" ht="43.2" x14ac:dyDescent="0.3">
       <c r="A119" s="4" t="s">
         <v>82</v>
       </c>
@@ -4241,7 +4235,7 @@
         <v>209</v>
       </c>
     </row>
-    <row r="120" spans="1:7" ht="56.25" x14ac:dyDescent="0.25">
+    <row r="120" spans="1:7" ht="54" x14ac:dyDescent="0.3">
       <c r="A120" s="4" t="s">
         <v>82</v>
       </c>
@@ -4264,7 +4258,7 @@
         <v>209</v>
       </c>
     </row>
-    <row r="121" spans="1:7" ht="45" x14ac:dyDescent="0.25">
+    <row r="121" spans="1:7" ht="32.4" x14ac:dyDescent="0.3">
       <c r="A121" s="4" t="s">
         <v>82</v>
       </c>
@@ -4287,7 +4281,7 @@
         <v>209</v>
       </c>
     </row>
-    <row r="122" spans="1:7" ht="45" x14ac:dyDescent="0.25">
+    <row r="122" spans="1:7" ht="32.4" x14ac:dyDescent="0.3">
       <c r="A122" s="4" t="s">
         <v>82</v>
       </c>
@@ -4310,7 +4304,7 @@
         <v>209</v>
       </c>
     </row>
-    <row r="123" spans="1:7" ht="67.5" x14ac:dyDescent="0.25">
+    <row r="123" spans="1:7" ht="54" x14ac:dyDescent="0.3">
       <c r="A123" s="4" t="s">
         <v>82</v>
       </c>
@@ -4333,7 +4327,7 @@
         <v>209</v>
       </c>
     </row>
-    <row r="124" spans="1:7" ht="33.75" x14ac:dyDescent="0.25">
+    <row r="124" spans="1:7" ht="32.4" x14ac:dyDescent="0.3">
       <c r="A124" s="4" t="s">
         <v>82</v>
       </c>
@@ -4356,7 +4350,7 @@
         <v>209</v>
       </c>
     </row>
-    <row r="125" spans="1:7" ht="33.75" x14ac:dyDescent="0.25">
+    <row r="125" spans="1:7" ht="32.4" x14ac:dyDescent="0.3">
       <c r="A125" s="4" t="s">
         <v>82</v>
       </c>
@@ -4379,7 +4373,7 @@
         <v>209</v>
       </c>
     </row>
-    <row r="126" spans="1:7" ht="45" x14ac:dyDescent="0.25">
+    <row r="126" spans="1:7" ht="32.4" x14ac:dyDescent="0.3">
       <c r="A126" s="4" t="s">
         <v>82</v>
       </c>
@@ -4402,7 +4396,7 @@
         <v>209</v>
       </c>
     </row>
-    <row r="127" spans="1:7" ht="33.75" x14ac:dyDescent="0.25">
+    <row r="127" spans="1:7" ht="32.4" x14ac:dyDescent="0.3">
       <c r="A127" s="4" t="s">
         <v>82</v>
       </c>
@@ -4425,7 +4419,7 @@
         <v>209</v>
       </c>
     </row>
-    <row r="128" spans="1:7" ht="33.75" x14ac:dyDescent="0.25">
+    <row r="128" spans="1:7" ht="32.4" x14ac:dyDescent="0.3">
       <c r="A128" s="4" t="s">
         <v>82</v>
       </c>
@@ -4448,7 +4442,7 @@
         <v>209</v>
       </c>
     </row>
-    <row r="129" spans="1:7" ht="33.75" x14ac:dyDescent="0.25">
+    <row r="129" spans="1:7" ht="32.4" x14ac:dyDescent="0.3">
       <c r="A129" s="4" t="s">
         <v>82</v>
       </c>
@@ -4471,7 +4465,7 @@
         <v>209</v>
       </c>
     </row>
-    <row r="130" spans="1:7" ht="33.75" x14ac:dyDescent="0.25">
+    <row r="130" spans="1:7" ht="32.4" x14ac:dyDescent="0.3">
       <c r="A130" s="4" t="s">
         <v>82</v>
       </c>
@@ -4494,7 +4488,7 @@
         <v>209</v>
       </c>
     </row>
-    <row r="131" spans="1:7" ht="33.75" x14ac:dyDescent="0.25">
+    <row r="131" spans="1:7" ht="32.4" x14ac:dyDescent="0.3">
       <c r="A131" s="4" t="s">
         <v>82</v>
       </c>
@@ -4517,7 +4511,7 @@
         <v>209</v>
       </c>
     </row>
-    <row r="132" spans="1:7" ht="33.75" x14ac:dyDescent="0.25">
+    <row r="132" spans="1:7" ht="32.4" x14ac:dyDescent="0.3">
       <c r="A132" s="4" t="s">
         <v>82</v>
       </c>
@@ -4540,7 +4534,7 @@
         <v>209</v>
       </c>
     </row>
-    <row r="133" spans="1:7" ht="33.75" x14ac:dyDescent="0.25">
+    <row r="133" spans="1:7" ht="32.4" x14ac:dyDescent="0.3">
       <c r="A133" s="4" t="s">
         <v>82</v>
       </c>
@@ -4563,7 +4557,7 @@
         <v>209</v>
       </c>
     </row>
-    <row r="134" spans="1:7" ht="33.75" x14ac:dyDescent="0.25">
+    <row r="134" spans="1:7" ht="32.4" x14ac:dyDescent="0.3">
       <c r="A134" s="4" t="s">
         <v>82</v>
       </c>
@@ -4586,7 +4580,7 @@
         <v>209</v>
       </c>
     </row>
-    <row r="135" spans="1:7" ht="33.75" x14ac:dyDescent="0.25">
+    <row r="135" spans="1:7" ht="32.4" x14ac:dyDescent="0.3">
       <c r="A135" s="4" t="s">
         <v>82</v>
       </c>
@@ -4609,7 +4603,7 @@
         <v>209</v>
       </c>
     </row>
-    <row r="136" spans="1:7" ht="33.75" x14ac:dyDescent="0.25">
+    <row r="136" spans="1:7" ht="32.4" x14ac:dyDescent="0.3">
       <c r="A136" s="4" t="s">
         <v>82</v>
       </c>
@@ -4632,7 +4626,7 @@
         <v>209</v>
       </c>
     </row>
-    <row r="137" spans="1:7" ht="33.75" x14ac:dyDescent="0.25">
+    <row r="137" spans="1:7" ht="32.4" x14ac:dyDescent="0.3">
       <c r="A137" s="4" t="s">
         <v>82</v>
       </c>
@@ -4655,7 +4649,7 @@
         <v>209</v>
       </c>
     </row>
-    <row r="138" spans="1:7" ht="33.75" x14ac:dyDescent="0.25">
+    <row r="138" spans="1:7" ht="32.4" x14ac:dyDescent="0.3">
       <c r="A138" s="4" t="s">
         <v>82</v>
       </c>
@@ -4678,7 +4672,7 @@
         <v>209</v>
       </c>
     </row>
-    <row r="139" spans="1:7" ht="33.75" x14ac:dyDescent="0.25">
+    <row r="139" spans="1:7" ht="32.4" x14ac:dyDescent="0.3">
       <c r="A139" s="4" t="s">
         <v>82</v>
       </c>
@@ -4701,7 +4695,7 @@
         <v>209</v>
       </c>
     </row>
-    <row r="140" spans="1:7" ht="33.75" x14ac:dyDescent="0.25">
+    <row r="140" spans="1:7" ht="32.4" x14ac:dyDescent="0.3">
       <c r="A140" s="4" t="s">
         <v>82</v>
       </c>
@@ -4724,7 +4718,7 @@
         <v>209</v>
       </c>
     </row>
-    <row r="141" spans="1:7" ht="33.75" x14ac:dyDescent="0.25">
+    <row r="141" spans="1:7" ht="32.4" x14ac:dyDescent="0.3">
       <c r="A141" s="4" t="s">
         <v>82</v>
       </c>
@@ -4747,7 +4741,7 @@
         <v>209</v>
       </c>
     </row>
-    <row r="142" spans="1:7" ht="33.75" x14ac:dyDescent="0.25">
+    <row r="142" spans="1:7" ht="32.4" x14ac:dyDescent="0.3">
       <c r="A142" s="4" t="s">
         <v>82</v>
       </c>
@@ -4770,7 +4764,7 @@
         <v>209</v>
       </c>
     </row>
-    <row r="143" spans="1:7" ht="33.75" x14ac:dyDescent="0.25">
+    <row r="143" spans="1:7" ht="32.4" x14ac:dyDescent="0.3">
       <c r="A143" s="4" t="s">
         <v>82</v>
       </c>
@@ -4793,7 +4787,7 @@
         <v>209</v>
       </c>
     </row>
-    <row r="144" spans="1:7" ht="33.75" x14ac:dyDescent="0.25">
+    <row r="144" spans="1:7" ht="32.4" x14ac:dyDescent="0.3">
       <c r="A144" s="4" t="s">
         <v>82</v>
       </c>
@@ -4816,7 +4810,7 @@
         <v>209</v>
       </c>
     </row>
-    <row r="145" spans="1:7" ht="33.75" x14ac:dyDescent="0.25">
+    <row r="145" spans="1:7" ht="32.4" x14ac:dyDescent="0.3">
       <c r="A145" s="4" t="s">
         <v>82</v>
       </c>
@@ -4839,7 +4833,7 @@
         <v>209</v>
       </c>
     </row>
-    <row r="146" spans="1:7" ht="33.75" x14ac:dyDescent="0.25">
+    <row r="146" spans="1:7" ht="32.4" x14ac:dyDescent="0.3">
       <c r="A146" s="4" t="s">
         <v>82</v>
       </c>
@@ -4862,7 +4856,7 @@
         <v>209</v>
       </c>
     </row>
-    <row r="147" spans="1:7" ht="33.75" x14ac:dyDescent="0.25">
+    <row r="147" spans="1:7" ht="32.4" x14ac:dyDescent="0.3">
       <c r="A147" s="4" t="s">
         <v>82</v>
       </c>
@@ -4885,7 +4879,7 @@
         <v>209</v>
       </c>
     </row>
-    <row r="148" spans="1:7" ht="33.75" x14ac:dyDescent="0.25">
+    <row r="148" spans="1:7" ht="32.4" x14ac:dyDescent="0.3">
       <c r="A148" s="4" t="s">
         <v>82</v>
       </c>
@@ -4908,7 +4902,7 @@
         <v>209</v>
       </c>
     </row>
-    <row r="149" spans="1:7" ht="33.75" x14ac:dyDescent="0.25">
+    <row r="149" spans="1:7" ht="32.4" x14ac:dyDescent="0.3">
       <c r="A149" s="4" t="s">
         <v>82</v>
       </c>
@@ -4931,7 +4925,7 @@
         <v>209</v>
       </c>
     </row>
-    <row r="150" spans="1:7" ht="33.75" x14ac:dyDescent="0.25">
+    <row r="150" spans="1:7" ht="32.4" x14ac:dyDescent="0.3">
       <c r="A150" s="4" t="s">
         <v>82</v>
       </c>
@@ -4954,7 +4948,7 @@
         <v>209</v>
       </c>
     </row>
-    <row r="151" spans="1:7" ht="33.75" x14ac:dyDescent="0.25">
+    <row r="151" spans="1:7" ht="32.4" x14ac:dyDescent="0.3">
       <c r="A151" s="4" t="s">
         <v>82</v>
       </c>
@@ -4977,7 +4971,7 @@
         <v>209</v>
       </c>
     </row>
-    <row r="152" spans="1:7" ht="45" x14ac:dyDescent="0.25">
+    <row r="152" spans="1:7" ht="43.2" x14ac:dyDescent="0.3">
       <c r="A152" s="4" t="s">
         <v>82</v>
       </c>
@@ -5000,7 +4994,7 @@
         <v>173</v>
       </c>
     </row>
-    <row r="153" spans="1:7" ht="45" x14ac:dyDescent="0.25">
+    <row r="153" spans="1:7" ht="43.2" x14ac:dyDescent="0.3">
       <c r="A153" s="4" t="s">
         <v>82</v>
       </c>
@@ -5023,7 +5017,7 @@
         <v>217</v>
       </c>
     </row>
-    <row r="154" spans="1:7" ht="45" x14ac:dyDescent="0.25">
+    <row r="154" spans="1:7" ht="43.2" x14ac:dyDescent="0.3">
       <c r="A154" s="4" t="s">
         <v>82</v>
       </c>
@@ -5046,7 +5040,7 @@
         <v>217</v>
       </c>
     </row>
-    <row r="155" spans="1:7" ht="33.75" x14ac:dyDescent="0.25">
+    <row r="155" spans="1:7" ht="32.4" x14ac:dyDescent="0.3">
       <c r="A155" s="4" t="s">
         <v>82</v>
       </c>
@@ -5057,7 +5051,7 @@
         <v>5</v>
       </c>
       <c r="D155" s="4" t="s">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="E155" s="4" t="s">
         <v>78</v>
@@ -5069,7 +5063,7 @@
         <v>220</v>
       </c>
     </row>
-    <row r="156" spans="1:7" ht="33.75" x14ac:dyDescent="0.25">
+    <row r="156" spans="1:7" ht="32.4" x14ac:dyDescent="0.3">
       <c r="A156" s="4" t="s">
         <v>82</v>
       </c>
@@ -5080,7 +5074,7 @@
         <v>5</v>
       </c>
       <c r="D156" s="4" t="s">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="E156" s="4" t="s">
         <v>78</v>
@@ -5092,7 +5086,7 @@
         <v>220</v>
       </c>
     </row>
-    <row r="157" spans="1:7" ht="22.5" x14ac:dyDescent="0.25">
+    <row r="157" spans="1:7" ht="21.6" x14ac:dyDescent="0.3">
       <c r="A157" s="4" t="s">
         <v>82</v>
       </c>
@@ -5115,7 +5109,7 @@
         <v>213</v>
       </c>
     </row>
-    <row r="158" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="158" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A158" s="4" t="s">
         <v>83</v>
       </c>
@@ -5138,7 +5132,7 @@
         <v>170</v>
       </c>
     </row>
-    <row r="159" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="159" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A159" s="4" t="s">
         <v>83</v>
       </c>
@@ -5161,7 +5155,7 @@
         <v>170</v>
       </c>
     </row>
-    <row r="160" spans="1:7" ht="33.75" x14ac:dyDescent="0.25">
+    <row r="160" spans="1:7" ht="32.4" x14ac:dyDescent="0.3">
       <c r="A160" s="4" t="s">
         <v>83</v>
       </c>
@@ -5184,7 +5178,7 @@
         <v>209</v>
       </c>
     </row>
-    <row r="161" spans="1:7" ht="56.25" x14ac:dyDescent="0.25">
+    <row r="161" spans="1:7" ht="54" x14ac:dyDescent="0.3">
       <c r="A161" s="4" t="s">
         <v>83</v>
       </c>
@@ -5207,7 +5201,7 @@
         <v>209</v>
       </c>
     </row>
-    <row r="162" spans="1:7" ht="33.75" x14ac:dyDescent="0.25">
+    <row r="162" spans="1:7" ht="32.4" x14ac:dyDescent="0.3">
       <c r="A162" s="4" t="s">
         <v>83</v>
       </c>
@@ -5230,7 +5224,7 @@
         <v>209</v>
       </c>
     </row>
-    <row r="163" spans="1:7" ht="45" x14ac:dyDescent="0.25">
+    <row r="163" spans="1:7" ht="43.2" x14ac:dyDescent="0.3">
       <c r="A163" s="4" t="s">
         <v>83</v>
       </c>
@@ -5253,7 +5247,7 @@
         <v>209</v>
       </c>
     </row>
-    <row r="164" spans="1:7" ht="56.25" x14ac:dyDescent="0.25">
+    <row r="164" spans="1:7" ht="54" x14ac:dyDescent="0.3">
       <c r="A164" s="4" t="s">
         <v>83</v>
       </c>
@@ -5276,7 +5270,7 @@
         <v>209</v>
       </c>
     </row>
-    <row r="165" spans="1:7" ht="45" x14ac:dyDescent="0.25">
+    <row r="165" spans="1:7" ht="32.4" x14ac:dyDescent="0.3">
       <c r="A165" s="4" t="s">
         <v>83</v>
       </c>
@@ -5299,7 +5293,7 @@
         <v>209</v>
       </c>
     </row>
-    <row r="166" spans="1:7" ht="45" x14ac:dyDescent="0.25">
+    <row r="166" spans="1:7" ht="32.4" x14ac:dyDescent="0.3">
       <c r="A166" s="4" t="s">
         <v>83</v>
       </c>
@@ -5322,7 +5316,7 @@
         <v>209</v>
       </c>
     </row>
-    <row r="167" spans="1:7" ht="67.5" x14ac:dyDescent="0.25">
+    <row r="167" spans="1:7" ht="54" x14ac:dyDescent="0.3">
       <c r="A167" s="4" t="s">
         <v>83</v>
       </c>
@@ -5345,7 +5339,7 @@
         <v>209</v>
       </c>
     </row>
-    <row r="168" spans="1:7" ht="56.25" x14ac:dyDescent="0.25">
+    <row r="168" spans="1:7" ht="54" x14ac:dyDescent="0.3">
       <c r="A168" s="4" t="s">
         <v>84</v>
       </c>
@@ -5368,7 +5362,7 @@
         <v>173</v>
       </c>
     </row>
-    <row r="169" spans="1:7" ht="22.5" x14ac:dyDescent="0.25">
+    <row r="169" spans="1:7" ht="21.6" x14ac:dyDescent="0.3">
       <c r="A169" s="4" t="s">
         <v>84</v>
       </c>
@@ -5391,7 +5385,7 @@
         <v>184</v>
       </c>
     </row>
-    <row r="170" spans="1:7" ht="33.75" x14ac:dyDescent="0.25">
+    <row r="170" spans="1:7" ht="21.6" x14ac:dyDescent="0.3">
       <c r="A170" s="4" t="s">
         <v>84</v>
       </c>
@@ -5414,7 +5408,7 @@
         <v>179</v>
       </c>
     </row>
-    <row r="171" spans="1:7" ht="33.75" x14ac:dyDescent="0.25">
+    <row r="171" spans="1:7" ht="21.6" x14ac:dyDescent="0.3">
       <c r="A171" s="4" t="s">
         <v>84</v>
       </c>
@@ -5437,7 +5431,7 @@
         <v>173</v>
       </c>
     </row>
-    <row r="172" spans="1:7" ht="33.75" x14ac:dyDescent="0.25">
+    <row r="172" spans="1:7" ht="21.6" x14ac:dyDescent="0.3">
       <c r="A172" s="4" t="s">
         <v>84</v>
       </c>
@@ -5460,7 +5454,7 @@
         <v>173</v>
       </c>
     </row>
-    <row r="173" spans="1:7" ht="33.75" x14ac:dyDescent="0.25">
+    <row r="173" spans="1:7" ht="32.4" x14ac:dyDescent="0.3">
       <c r="A173" s="4" t="s">
         <v>84</v>
       </c>
@@ -5483,7 +5477,7 @@
         <v>209</v>
       </c>
     </row>
-    <row r="174" spans="1:7" ht="56.25" x14ac:dyDescent="0.25">
+    <row r="174" spans="1:7" ht="54" x14ac:dyDescent="0.3">
       <c r="A174" s="4" t="s">
         <v>84</v>
       </c>
@@ -5506,7 +5500,7 @@
         <v>209</v>
       </c>
     </row>
-    <row r="175" spans="1:7" ht="33.75" x14ac:dyDescent="0.25">
+    <row r="175" spans="1:7" ht="32.4" x14ac:dyDescent="0.3">
       <c r="A175" s="4" t="s">
         <v>84</v>
       </c>
@@ -5529,7 +5523,7 @@
         <v>209</v>
       </c>
     </row>
-    <row r="176" spans="1:7" ht="45" x14ac:dyDescent="0.25">
+    <row r="176" spans="1:7" ht="43.2" x14ac:dyDescent="0.3">
       <c r="A176" s="4" t="s">
         <v>84</v>
       </c>
@@ -5552,7 +5546,7 @@
         <v>209</v>
       </c>
     </row>
-    <row r="177" spans="1:7" ht="56.25" x14ac:dyDescent="0.25">
+    <row r="177" spans="1:7" ht="54" x14ac:dyDescent="0.3">
       <c r="A177" s="4" t="s">
         <v>84</v>
       </c>
@@ -5575,7 +5569,7 @@
         <v>209</v>
       </c>
     </row>
-    <row r="178" spans="1:7" ht="45" x14ac:dyDescent="0.25">
+    <row r="178" spans="1:7" ht="32.4" x14ac:dyDescent="0.3">
       <c r="A178" s="4" t="s">
         <v>84</v>
       </c>
@@ -5598,7 +5592,7 @@
         <v>209</v>
       </c>
     </row>
-    <row r="179" spans="1:7" ht="45" x14ac:dyDescent="0.25">
+    <row r="179" spans="1:7" ht="32.4" x14ac:dyDescent="0.3">
       <c r="A179" s="4" t="s">
         <v>84</v>
       </c>
@@ -5621,7 +5615,7 @@
         <v>209</v>
       </c>
     </row>
-    <row r="180" spans="1:7" ht="56.25" x14ac:dyDescent="0.25">
+    <row r="180" spans="1:7" ht="54" x14ac:dyDescent="0.3">
       <c r="A180" s="4" t="s">
         <v>98</v>
       </c>
@@ -5644,7 +5638,7 @@
         <v>173</v>
       </c>
     </row>
-    <row r="181" spans="1:7" ht="45" x14ac:dyDescent="0.25">
+    <row r="181" spans="1:7" ht="43.2" x14ac:dyDescent="0.3">
       <c r="A181" s="4" t="s">
         <v>98</v>
       </c>
@@ -5667,7 +5661,7 @@
         <v>173</v>
       </c>
     </row>
-    <row r="182" spans="1:7" ht="56.25" x14ac:dyDescent="0.25">
+    <row r="182" spans="1:7" ht="54" x14ac:dyDescent="0.3">
       <c r="A182" s="4" t="s">
         <v>98</v>
       </c>
@@ -5690,7 +5684,7 @@
         <v>173</v>
       </c>
     </row>
-    <row r="183" spans="1:7" ht="78.75" x14ac:dyDescent="0.25">
+    <row r="183" spans="1:7" ht="64.8" x14ac:dyDescent="0.3">
       <c r="A183" s="4" t="s">
         <v>98</v>
       </c>
@@ -5713,7 +5707,7 @@
         <v>176</v>
       </c>
     </row>
-    <row r="184" spans="1:7" ht="56.25" x14ac:dyDescent="0.25">
+    <row r="184" spans="1:7" ht="54" x14ac:dyDescent="0.3">
       <c r="A184" s="4" t="s">
         <v>98</v>
       </c>
@@ -5736,7 +5730,7 @@
         <v>187</v>
       </c>
     </row>
-    <row r="185" spans="1:7" ht="56.25" x14ac:dyDescent="0.25">
+    <row r="185" spans="1:7" ht="43.2" x14ac:dyDescent="0.3">
       <c r="A185" s="4" t="s">
         <v>98</v>
       </c>
@@ -5759,7 +5753,7 @@
         <v>173</v>
       </c>
     </row>
-    <row r="186" spans="1:7" ht="22.5" x14ac:dyDescent="0.25">
+    <row r="186" spans="1:7" ht="21.6" x14ac:dyDescent="0.3">
       <c r="A186" s="4" t="s">
         <v>98</v>
       </c>
@@ -5782,7 +5776,7 @@
         <v>188</v>
       </c>
     </row>
-    <row r="187" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="187" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A187" s="4" t="s">
         <v>98</v>
       </c>
@@ -5805,7 +5799,7 @@
         <v>188</v>
       </c>
     </row>
-    <row r="188" spans="1:7" ht="22.5" x14ac:dyDescent="0.25">
+    <row r="188" spans="1:7" ht="21.6" x14ac:dyDescent="0.3">
       <c r="A188" s="4" t="s">
         <v>98</v>
       </c>
@@ -5828,7 +5822,7 @@
         <v>188</v>
       </c>
     </row>
-    <row r="189" spans="1:7" ht="67.5" x14ac:dyDescent="0.25">
+    <row r="189" spans="1:7" ht="64.8" x14ac:dyDescent="0.3">
       <c r="A189" s="4" t="s">
         <v>98</v>
       </c>
@@ -5851,7 +5845,7 @@
         <v>188</v>
       </c>
     </row>
-    <row r="190" spans="1:7" ht="67.5" x14ac:dyDescent="0.25">
+    <row r="190" spans="1:7" ht="64.8" x14ac:dyDescent="0.3">
       <c r="A190" s="4" t="s">
         <v>98</v>
       </c>
@@ -5874,7 +5868,7 @@
         <v>188</v>
       </c>
     </row>
-    <row r="191" spans="1:7" ht="67.5" x14ac:dyDescent="0.25">
+    <row r="191" spans="1:7" ht="64.8" x14ac:dyDescent="0.3">
       <c r="A191" s="4" t="s">
         <v>98</v>
       </c>
@@ -5897,7 +5891,7 @@
         <v>188</v>
       </c>
     </row>
-    <row r="192" spans="1:7" ht="45" x14ac:dyDescent="0.25">
+    <row r="192" spans="1:7" ht="32.4" x14ac:dyDescent="0.3">
       <c r="A192" s="4" t="s">
         <v>98</v>
       </c>
@@ -5920,7 +5914,7 @@
         <v>173</v>
       </c>
     </row>
-    <row r="193" spans="1:7" ht="56.25" x14ac:dyDescent="0.25">
+    <row r="193" spans="1:7" ht="54" x14ac:dyDescent="0.3">
       <c r="A193" s="4" t="s">
         <v>98</v>
       </c>
@@ -5943,7 +5937,7 @@
         <v>173</v>
       </c>
     </row>
-    <row r="194" spans="1:7" ht="56.25" x14ac:dyDescent="0.25">
+    <row r="194" spans="1:7" ht="43.2" x14ac:dyDescent="0.3">
       <c r="A194" s="4" t="s">
         <v>98</v>
       </c>
@@ -5966,7 +5960,7 @@
         <v>199</v>
       </c>
     </row>
-    <row r="195" spans="1:7" ht="56.25" x14ac:dyDescent="0.25">
+    <row r="195" spans="1:7" ht="54" x14ac:dyDescent="0.3">
       <c r="A195" s="4" t="s">
         <v>98</v>
       </c>
@@ -5989,7 +5983,7 @@
         <v>170</v>
       </c>
     </row>
-    <row r="196" spans="1:7" ht="33.75" x14ac:dyDescent="0.25">
+    <row r="196" spans="1:7" ht="21.6" x14ac:dyDescent="0.3">
       <c r="A196" s="4" t="s">
         <v>98</v>
       </c>
@@ -6012,7 +6006,7 @@
         <v>203</v>
       </c>
     </row>
-    <row r="197" spans="1:7" ht="22.5" x14ac:dyDescent="0.25">
+    <row r="197" spans="1:7" ht="21.6" x14ac:dyDescent="0.3">
       <c r="A197" s="4" t="s">
         <v>98</v>
       </c>
@@ -6035,7 +6029,7 @@
         <v>205</v>
       </c>
     </row>
-    <row r="198" spans="1:7" ht="33.75" x14ac:dyDescent="0.25">
+    <row r="198" spans="1:7" ht="32.4" x14ac:dyDescent="0.3">
       <c r="A198" s="4" t="s">
         <v>98</v>
       </c>
@@ -6058,7 +6052,7 @@
         <v>207</v>
       </c>
     </row>
-    <row r="199" spans="1:7" ht="33.75" x14ac:dyDescent="0.25">
+    <row r="199" spans="1:7" ht="32.4" x14ac:dyDescent="0.3">
       <c r="A199" s="4" t="s">
         <v>98</v>
       </c>
@@ -6081,7 +6075,7 @@
         <v>209</v>
       </c>
     </row>
-    <row r="200" spans="1:7" ht="33.75" x14ac:dyDescent="0.25">
+    <row r="200" spans="1:7" ht="32.4" x14ac:dyDescent="0.3">
       <c r="A200" s="4" t="s">
         <v>98</v>
       </c>
@@ -6104,7 +6098,7 @@
         <v>209</v>
       </c>
     </row>
-    <row r="201" spans="1:7" ht="45" x14ac:dyDescent="0.25">
+    <row r="201" spans="1:7" ht="43.2" x14ac:dyDescent="0.3">
       <c r="A201" s="4" t="s">
         <v>98</v>
       </c>
@@ -6127,7 +6121,7 @@
         <v>209</v>
       </c>
     </row>
-    <row r="202" spans="1:7" ht="33.75" x14ac:dyDescent="0.25">
+    <row r="202" spans="1:7" ht="32.4" x14ac:dyDescent="0.3">
       <c r="A202" s="4" t="s">
         <v>98</v>
       </c>
@@ -6150,7 +6144,7 @@
         <v>209</v>
       </c>
     </row>
-    <row r="203" spans="1:7" ht="33.75" x14ac:dyDescent="0.25">
+    <row r="203" spans="1:7" ht="32.4" x14ac:dyDescent="0.3">
       <c r="A203" s="4" t="s">
         <v>98</v>
       </c>
@@ -6173,7 +6167,7 @@
         <v>209</v>
       </c>
     </row>
-    <row r="204" spans="1:7" ht="56.25" x14ac:dyDescent="0.25">
+    <row r="204" spans="1:7" ht="54" x14ac:dyDescent="0.3">
       <c r="A204" s="4" t="s">
         <v>98</v>
       </c>
@@ -6196,7 +6190,7 @@
         <v>209</v>
       </c>
     </row>
-    <row r="205" spans="1:7" ht="33.75" x14ac:dyDescent="0.25">
+    <row r="205" spans="1:7" ht="32.4" x14ac:dyDescent="0.3">
       <c r="A205" s="4" t="s">
         <v>98</v>
       </c>
@@ -6219,7 +6213,7 @@
         <v>209</v>
       </c>
     </row>
-    <row r="206" spans="1:7" ht="45" x14ac:dyDescent="0.25">
+    <row r="206" spans="1:7" ht="43.2" x14ac:dyDescent="0.3">
       <c r="A206" s="4" t="s">
         <v>98</v>
       </c>
@@ -6242,7 +6236,7 @@
         <v>209</v>
       </c>
     </row>
-    <row r="207" spans="1:7" ht="56.25" x14ac:dyDescent="0.25">
+    <row r="207" spans="1:7" ht="54" x14ac:dyDescent="0.3">
       <c r="A207" s="4" t="s">
         <v>98</v>
       </c>
@@ -6265,7 +6259,7 @@
         <v>209</v>
       </c>
     </row>
-    <row r="208" spans="1:7" ht="45" x14ac:dyDescent="0.25">
+    <row r="208" spans="1:7" ht="32.4" x14ac:dyDescent="0.3">
       <c r="A208" s="4" t="s">
         <v>98</v>
       </c>
@@ -6288,7 +6282,7 @@
         <v>209</v>
       </c>
     </row>
-    <row r="209" spans="1:7" ht="45" x14ac:dyDescent="0.25">
+    <row r="209" spans="1:7" ht="32.4" x14ac:dyDescent="0.3">
       <c r="A209" s="4" t="s">
         <v>98</v>
       </c>
@@ -6311,7 +6305,7 @@
         <v>209</v>
       </c>
     </row>
-    <row r="210" spans="1:7" ht="67.5" x14ac:dyDescent="0.25">
+    <row r="210" spans="1:7" ht="54" x14ac:dyDescent="0.3">
       <c r="A210" s="4" t="s">
         <v>98</v>
       </c>
@@ -6334,7 +6328,7 @@
         <v>209</v>
       </c>
     </row>
-    <row r="211" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="211" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A211" s="4" t="s">
         <v>98</v>
       </c>
@@ -6357,7 +6351,7 @@
         <v>213</v>
       </c>
     </row>
-    <row r="212" spans="1:7" ht="33.75" x14ac:dyDescent="0.25">
+    <row r="212" spans="1:7" ht="32.4" x14ac:dyDescent="0.3">
       <c r="A212" s="4" t="s">
         <v>98</v>
       </c>
@@ -6380,7 +6374,7 @@
         <v>209</v>
       </c>
     </row>
-    <row r="213" spans="1:7" ht="33.75" x14ac:dyDescent="0.25">
+    <row r="213" spans="1:7" ht="32.4" x14ac:dyDescent="0.3">
       <c r="A213" s="4" t="s">
         <v>98</v>
       </c>
@@ -6403,7 +6397,7 @@
         <v>220</v>
       </c>
     </row>
-    <row r="214" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="214" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A214" s="4" t="s">
         <v>98</v>
       </c>
@@ -6426,7 +6420,7 @@
         <v>213</v>
       </c>
     </row>
-    <row r="215" spans="1:7" ht="33.75" x14ac:dyDescent="0.25">
+    <row r="215" spans="1:7" ht="32.4" x14ac:dyDescent="0.3">
       <c r="A215" s="4" t="s">
         <v>98</v>
       </c>
@@ -6449,7 +6443,7 @@
         <v>209</v>
       </c>
     </row>
-    <row r="216" spans="1:7" ht="33.75" x14ac:dyDescent="0.25">
+    <row r="216" spans="1:7" ht="32.4" x14ac:dyDescent="0.3">
       <c r="A216" s="4" t="s">
         <v>98</v>
       </c>
@@ -6472,7 +6466,7 @@
         <v>220</v>
       </c>
     </row>
-    <row r="217" spans="1:7" ht="33.75" x14ac:dyDescent="0.25">
+    <row r="217" spans="1:7" ht="32.4" x14ac:dyDescent="0.3">
       <c r="A217" s="4" t="s">
         <v>98</v>
       </c>
@@ -6495,7 +6489,7 @@
         <v>220</v>
       </c>
     </row>
-    <row r="218" spans="1:7" ht="33.75" x14ac:dyDescent="0.25">
+    <row r="218" spans="1:7" ht="32.4" x14ac:dyDescent="0.3">
       <c r="A218" s="4" t="s">
         <v>98</v>
       </c>
@@ -6518,7 +6512,7 @@
         <v>220</v>
       </c>
     </row>
-    <row r="219" spans="1:7" ht="33.75" x14ac:dyDescent="0.25">
+    <row r="219" spans="1:7" ht="32.4" x14ac:dyDescent="0.3">
       <c r="A219" s="4" t="s">
         <v>98</v>
       </c>
@@ -6541,7 +6535,7 @@
         <v>220</v>
       </c>
     </row>
-    <row r="220" spans="1:7" ht="33.75" x14ac:dyDescent="0.25">
+    <row r="220" spans="1:7" ht="32.4" x14ac:dyDescent="0.3">
       <c r="A220" s="4" t="s">
         <v>98</v>
       </c>
@@ -6564,7 +6558,7 @@
         <v>220</v>
       </c>
     </row>
-    <row r="221" spans="1:7" ht="33.75" x14ac:dyDescent="0.25">
+    <row r="221" spans="1:7" ht="32.4" x14ac:dyDescent="0.3">
       <c r="A221" s="4" t="s">
         <v>98</v>
       </c>
@@ -6587,7 +6581,7 @@
         <v>220</v>
       </c>
     </row>
-    <row r="222" spans="1:7" ht="33.75" x14ac:dyDescent="0.25">
+    <row r="222" spans="1:7" ht="32.4" x14ac:dyDescent="0.3">
       <c r="A222" s="4" t="s">
         <v>98</v>
       </c>
@@ -6610,7 +6604,7 @@
         <v>220</v>
       </c>
     </row>
-    <row r="223" spans="1:7" ht="22.5" x14ac:dyDescent="0.25">
+    <row r="223" spans="1:7" ht="21.6" x14ac:dyDescent="0.3">
       <c r="A223" s="4" t="s">
         <v>98</v>
       </c>
@@ -6633,7 +6627,7 @@
         <v>213</v>
       </c>
     </row>
-    <row r="224" spans="1:7" ht="56.25" x14ac:dyDescent="0.25">
+    <row r="224" spans="1:7" ht="54" x14ac:dyDescent="0.3">
       <c r="A224" s="4" t="s">
         <v>99</v>
       </c>
@@ -6656,7 +6650,7 @@
         <v>173</v>
       </c>
     </row>
-    <row r="225" spans="1:7" ht="45" x14ac:dyDescent="0.25">
+    <row r="225" spans="1:7" ht="43.2" x14ac:dyDescent="0.3">
       <c r="A225" s="4" t="s">
         <v>99</v>
       </c>
@@ -6679,7 +6673,7 @@
         <v>173</v>
       </c>
     </row>
-    <row r="226" spans="1:7" ht="78.75" x14ac:dyDescent="0.25">
+    <row r="226" spans="1:7" ht="64.8" x14ac:dyDescent="0.3">
       <c r="A226" s="4" t="s">
         <v>99</v>
       </c>
@@ -6702,7 +6696,7 @@
         <v>176</v>
       </c>
     </row>
-    <row r="227" spans="1:7" ht="22.5" x14ac:dyDescent="0.25">
+    <row r="227" spans="1:7" ht="21.6" x14ac:dyDescent="0.3">
       <c r="A227" s="4" t="s">
         <v>99</v>
       </c>
@@ -6725,7 +6719,7 @@
         <v>188</v>
       </c>
     </row>
-    <row r="228" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="228" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A228" s="4" t="s">
         <v>99</v>
       </c>
@@ -6748,7 +6742,7 @@
         <v>188</v>
       </c>
     </row>
-    <row r="229" spans="1:7" ht="22.5" x14ac:dyDescent="0.25">
+    <row r="229" spans="1:7" ht="21.6" x14ac:dyDescent="0.3">
       <c r="A229" s="4" t="s">
         <v>99</v>
       </c>
@@ -6771,7 +6765,7 @@
         <v>188</v>
       </c>
     </row>
-    <row r="230" spans="1:7" ht="67.5" x14ac:dyDescent="0.25">
+    <row r="230" spans="1:7" ht="64.8" x14ac:dyDescent="0.3">
       <c r="A230" s="4" t="s">
         <v>99</v>
       </c>
@@ -6794,7 +6788,7 @@
         <v>188</v>
       </c>
     </row>
-    <row r="231" spans="1:7" ht="67.5" x14ac:dyDescent="0.25">
+    <row r="231" spans="1:7" ht="64.8" x14ac:dyDescent="0.3">
       <c r="A231" s="4" t="s">
         <v>99</v>
       </c>
@@ -6817,7 +6811,7 @@
         <v>188</v>
       </c>
     </row>
-    <row r="232" spans="1:7" ht="67.5" x14ac:dyDescent="0.25">
+    <row r="232" spans="1:7" ht="64.8" x14ac:dyDescent="0.3">
       <c r="A232" s="4" t="s">
         <v>99</v>
       </c>
@@ -6840,7 +6834,7 @@
         <v>188</v>
       </c>
     </row>
-    <row r="233" spans="1:7" ht="45" x14ac:dyDescent="0.25">
+    <row r="233" spans="1:7" ht="32.4" x14ac:dyDescent="0.3">
       <c r="A233" s="4" t="s">
         <v>99</v>
       </c>
@@ -6863,7 +6857,7 @@
         <v>173</v>
       </c>
     </row>
-    <row r="234" spans="1:7" ht="56.25" x14ac:dyDescent="0.25">
+    <row r="234" spans="1:7" ht="54" x14ac:dyDescent="0.3">
       <c r="A234" s="4" t="s">
         <v>99</v>
       </c>
@@ -6886,7 +6880,7 @@
         <v>173</v>
       </c>
     </row>
-    <row r="235" spans="1:7" ht="56.25" x14ac:dyDescent="0.25">
+    <row r="235" spans="1:7" ht="43.2" x14ac:dyDescent="0.3">
       <c r="A235" s="4" t="s">
         <v>99</v>
       </c>
@@ -6909,7 +6903,7 @@
         <v>199</v>
       </c>
     </row>
-    <row r="236" spans="1:7" ht="56.25" x14ac:dyDescent="0.25">
+    <row r="236" spans="1:7" ht="54" x14ac:dyDescent="0.3">
       <c r="A236" s="4" t="s">
         <v>99</v>
       </c>
@@ -6932,7 +6926,7 @@
         <v>170</v>
       </c>
     </row>
-    <row r="237" spans="1:7" ht="33.75" x14ac:dyDescent="0.25">
+    <row r="237" spans="1:7" ht="21.6" x14ac:dyDescent="0.3">
       <c r="A237" s="4" t="s">
         <v>99</v>
       </c>
@@ -6955,7 +6949,7 @@
         <v>203</v>
       </c>
     </row>
-    <row r="238" spans="1:7" ht="22.5" x14ac:dyDescent="0.25">
+    <row r="238" spans="1:7" ht="21.6" x14ac:dyDescent="0.3">
       <c r="A238" s="4" t="s">
         <v>99</v>
       </c>
@@ -6978,7 +6972,7 @@
         <v>205</v>
       </c>
     </row>
-    <row r="239" spans="1:7" ht="33.75" x14ac:dyDescent="0.25">
+    <row r="239" spans="1:7" ht="32.4" x14ac:dyDescent="0.3">
       <c r="A239" s="4" t="s">
         <v>99</v>
       </c>
@@ -7001,7 +6995,7 @@
         <v>207</v>
       </c>
     </row>
-    <row r="240" spans="1:7" ht="33.75" x14ac:dyDescent="0.25">
+    <row r="240" spans="1:7" ht="32.4" x14ac:dyDescent="0.3">
       <c r="A240" s="4" t="s">
         <v>99</v>
       </c>
@@ -7024,7 +7018,7 @@
         <v>209</v>
       </c>
     </row>
-    <row r="241" spans="1:7" ht="45" x14ac:dyDescent="0.25">
+    <row r="241" spans="1:7" ht="43.2" x14ac:dyDescent="0.3">
       <c r="A241" s="4" t="s">
         <v>99</v>
       </c>
@@ -7047,7 +7041,7 @@
         <v>209</v>
       </c>
     </row>
-    <row r="242" spans="1:7" ht="33.75" x14ac:dyDescent="0.25">
+    <row r="242" spans="1:7" ht="32.4" x14ac:dyDescent="0.3">
       <c r="A242" s="4" t="s">
         <v>99</v>
       </c>
@@ -7070,7 +7064,7 @@
         <v>209</v>
       </c>
     </row>
-    <row r="243" spans="1:7" ht="33.75" x14ac:dyDescent="0.25">
+    <row r="243" spans="1:7" ht="32.4" x14ac:dyDescent="0.3">
       <c r="A243" s="4" t="s">
         <v>99</v>
       </c>
@@ -7093,7 +7087,7 @@
         <v>209</v>
       </c>
     </row>
-    <row r="244" spans="1:7" ht="56.25" x14ac:dyDescent="0.25">
+    <row r="244" spans="1:7" ht="54" x14ac:dyDescent="0.3">
       <c r="A244" s="4" t="s">
         <v>99</v>
       </c>
@@ -7116,7 +7110,7 @@
         <v>209</v>
       </c>
     </row>
-    <row r="245" spans="1:7" ht="33.75" x14ac:dyDescent="0.25">
+    <row r="245" spans="1:7" ht="32.4" x14ac:dyDescent="0.3">
       <c r="A245" s="4" t="s">
         <v>99</v>
       </c>
@@ -7139,7 +7133,7 @@
         <v>209</v>
       </c>
     </row>
-    <row r="246" spans="1:7" ht="45" x14ac:dyDescent="0.25">
+    <row r="246" spans="1:7" ht="43.2" x14ac:dyDescent="0.3">
       <c r="A246" s="4" t="s">
         <v>99</v>
       </c>
@@ -7162,7 +7156,7 @@
         <v>209</v>
       </c>
     </row>
-    <row r="247" spans="1:7" ht="56.25" x14ac:dyDescent="0.25">
+    <row r="247" spans="1:7" ht="54" x14ac:dyDescent="0.3">
       <c r="A247" s="4" t="s">
         <v>99</v>
       </c>
@@ -7185,7 +7179,7 @@
         <v>209</v>
       </c>
     </row>
-    <row r="248" spans="1:7" ht="45" x14ac:dyDescent="0.25">
+    <row r="248" spans="1:7" ht="32.4" x14ac:dyDescent="0.3">
       <c r="A248" s="4" t="s">
         <v>99</v>
       </c>
@@ -7208,7 +7202,7 @@
         <v>209</v>
       </c>
     </row>
-    <row r="249" spans="1:7" ht="45" x14ac:dyDescent="0.25">
+    <row r="249" spans="1:7" ht="32.4" x14ac:dyDescent="0.3">
       <c r="A249" s="4" t="s">
         <v>99</v>
       </c>
@@ -7231,7 +7225,7 @@
         <v>209</v>
       </c>
     </row>
-    <row r="250" spans="1:7" ht="67.5" x14ac:dyDescent="0.25">
+    <row r="250" spans="1:7" ht="54" x14ac:dyDescent="0.3">
       <c r="A250" s="4" t="s">
         <v>99</v>
       </c>
@@ -7254,7 +7248,7 @@
         <v>209</v>
       </c>
     </row>
-    <row r="251" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="251" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A251" s="4" t="s">
         <v>99</v>
       </c>
@@ -7277,7 +7271,7 @@
         <v>213</v>
       </c>
     </row>
-    <row r="252" spans="1:7" ht="22.5" x14ac:dyDescent="0.25">
+    <row r="252" spans="1:7" ht="21.6" x14ac:dyDescent="0.3">
       <c r="A252" s="4" t="s">
         <v>99</v>
       </c>
@@ -7300,7 +7294,7 @@
         <v>213</v>
       </c>
     </row>
-    <row r="253" spans="1:7" ht="33.75" x14ac:dyDescent="0.25">
+    <row r="253" spans="1:7" ht="32.4" x14ac:dyDescent="0.3">
       <c r="A253" s="4" t="s">
         <v>99</v>
       </c>
@@ -7323,7 +7317,7 @@
         <v>220</v>
       </c>
     </row>
-    <row r="254" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="254" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A254" s="4" t="s">
         <v>99</v>
       </c>
@@ -7346,7 +7340,7 @@
         <v>213</v>
       </c>
     </row>
-    <row r="255" spans="1:7" ht="22.5" x14ac:dyDescent="0.25">
+    <row r="255" spans="1:7" ht="21.6" x14ac:dyDescent="0.3">
       <c r="A255" s="4" t="s">
         <v>99</v>
       </c>
@@ -7369,7 +7363,7 @@
         <v>213</v>
       </c>
     </row>
-    <row r="256" spans="1:7" ht="33.75" x14ac:dyDescent="0.25">
+    <row r="256" spans="1:7" ht="32.4" x14ac:dyDescent="0.3">
       <c r="A256" s="4" t="s">
         <v>99</v>
       </c>
@@ -7392,7 +7386,7 @@
         <v>220</v>
       </c>
     </row>
-    <row r="257" spans="1:7" ht="33.75" x14ac:dyDescent="0.25">
+    <row r="257" spans="1:7" ht="32.4" x14ac:dyDescent="0.3">
       <c r="A257" s="4" t="s">
         <v>99</v>
       </c>
@@ -7415,7 +7409,7 @@
         <v>220</v>
       </c>
     </row>
-    <row r="258" spans="1:7" ht="33.75" x14ac:dyDescent="0.25">
+    <row r="258" spans="1:7" ht="32.4" x14ac:dyDescent="0.3">
       <c r="A258" s="4" t="s">
         <v>99</v>
       </c>
@@ -7438,7 +7432,7 @@
         <v>220</v>
       </c>
     </row>
-    <row r="259" spans="1:7" ht="33.75" x14ac:dyDescent="0.25">
+    <row r="259" spans="1:7" ht="32.4" x14ac:dyDescent="0.3">
       <c r="A259" s="4" t="s">
         <v>99</v>
       </c>
@@ -7461,7 +7455,7 @@
         <v>220</v>
       </c>
     </row>
-    <row r="260" spans="1:7" ht="33.75" x14ac:dyDescent="0.25">
+    <row r="260" spans="1:7" ht="32.4" x14ac:dyDescent="0.3">
       <c r="A260" s="4" t="s">
         <v>99</v>
       </c>
@@ -7484,7 +7478,7 @@
         <v>220</v>
       </c>
     </row>
-    <row r="261" spans="1:7" ht="33.75" x14ac:dyDescent="0.25">
+    <row r="261" spans="1:7" ht="32.4" x14ac:dyDescent="0.3">
       <c r="A261" s="4" t="s">
         <v>99</v>
       </c>
@@ -7507,7 +7501,7 @@
         <v>220</v>
       </c>
     </row>
-    <row r="262" spans="1:7" ht="33.75" x14ac:dyDescent="0.25">
+    <row r="262" spans="1:7" ht="32.4" x14ac:dyDescent="0.3">
       <c r="A262" s="4" t="s">
         <v>99</v>
       </c>
@@ -7530,7 +7524,7 @@
         <v>220</v>
       </c>
     </row>
-    <row r="263" spans="1:7" ht="22.5" x14ac:dyDescent="0.25">
+    <row r="263" spans="1:7" ht="21.6" x14ac:dyDescent="0.3">
       <c r="A263" s="4" t="s">
         <v>99</v>
       </c>
@@ -7553,11 +7547,11 @@
         <v>213</v>
       </c>
     </row>
-    <row r="264" spans="1:7" ht="56.25" x14ac:dyDescent="0.25">
-      <c r="A264" s="11" t="s">
+    <row r="264" spans="1:7" ht="54" x14ac:dyDescent="0.3">
+      <c r="A264" s="4" t="s">
         <v>224</v>
       </c>
-      <c r="B264" s="11" t="s">
+      <c r="B264" s="4" t="s">
         <v>10</v>
       </c>
       <c r="C264" s="4" t="s">
@@ -7576,34 +7570,34 @@
         <v>173</v>
       </c>
     </row>
-    <row r="265" spans="1:7" ht="22.5" x14ac:dyDescent="0.25">
-      <c r="A265" s="11" t="s">
+    <row r="265" spans="1:7" ht="21.6" x14ac:dyDescent="0.3">
+      <c r="A265" s="4" t="s">
         <v>224</v>
       </c>
-      <c r="B265" s="11" t="s">
+      <c r="B265" s="4" t="s">
         <v>225</v>
       </c>
-      <c r="C265" s="11" t="s">
-        <v>5</v>
-      </c>
-      <c r="D265" s="11" t="s">
-        <v>5</v>
-      </c>
-      <c r="E265" s="11" t="s">
+      <c r="C265" s="4" t="s">
+        <v>5</v>
+      </c>
+      <c r="D265" s="4" t="s">
+        <v>5</v>
+      </c>
+      <c r="E265" s="4" t="s">
         <v>8</v>
       </c>
-      <c r="F265" s="12" t="s">
+      <c r="F265" s="5" t="s">
         <v>226</v>
       </c>
-      <c r="G265" s="12" t="s">
+      <c r="G265" s="5" t="s">
         <v>173</v>
       </c>
     </row>
-    <row r="266" spans="1:7" ht="45" x14ac:dyDescent="0.25">
-      <c r="A266" s="11" t="s">
+    <row r="266" spans="1:7" ht="43.2" x14ac:dyDescent="0.3">
+      <c r="A266" s="4" t="s">
         <v>224</v>
       </c>
-      <c r="B266" s="11" t="s">
+      <c r="B266" s="4" t="s">
         <v>23</v>
       </c>
       <c r="C266" s="4" t="s">
@@ -7622,40 +7616,40 @@
         <v>173</v>
       </c>
     </row>
-    <row r="267" spans="1:7" ht="22.5" x14ac:dyDescent="0.25">
-      <c r="A267" s="11" t="s">
+    <row r="267" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A267" s="4" t="s">
         <v>224</v>
       </c>
-      <c r="B267" s="11" t="s">
+      <c r="B267" s="4" t="s">
         <v>222</v>
       </c>
-      <c r="C267" s="11" t="s">
-        <v>5</v>
-      </c>
-      <c r="D267" s="11" t="s">
-        <v>5</v>
-      </c>
-      <c r="E267" s="11" t="s">
+      <c r="C267" s="4" t="s">
+        <v>5</v>
+      </c>
+      <c r="D267" s="4" t="s">
+        <v>5</v>
+      </c>
+      <c r="E267" s="4" t="s">
         <v>8</v>
       </c>
-      <c r="F267" s="12" t="s">
+      <c r="F267" s="5" t="s">
         <v>227</v>
       </c>
-      <c r="G267" s="12" t="s">
+      <c r="G267" s="5" t="s">
         <v>173</v>
       </c>
     </row>
-    <row r="268" spans="1:7" ht="22.5" x14ac:dyDescent="0.25">
-      <c r="A268" s="11" t="s">
+    <row r="268" spans="1:7" ht="21.6" x14ac:dyDescent="0.3">
+      <c r="A268" s="4" t="s">
         <v>224</v>
       </c>
-      <c r="B268" s="11" t="s">
+      <c r="B268" s="4" t="s">
         <v>86</v>
       </c>
-      <c r="C268" s="11" t="s">
-        <v>5</v>
-      </c>
-      <c r="D268" s="11" t="s">
+      <c r="C268" s="4" t="s">
+        <v>5</v>
+      </c>
+      <c r="D268" s="4" t="s">
         <v>5</v>
       </c>
       <c r="E268" s="4" t="s">
@@ -7668,11 +7662,11 @@
         <v>188</v>
       </c>
     </row>
-    <row r="269" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A269" s="11" t="s">
+    <row r="269" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A269" s="4" t="s">
         <v>224</v>
       </c>
-      <c r="B269" s="11" t="s">
+      <c r="B269" s="4" t="s">
         <v>26</v>
       </c>
       <c r="C269" s="4" t="s">
@@ -7691,11 +7685,11 @@
         <v>188</v>
       </c>
     </row>
-    <row r="270" spans="1:7" ht="22.5" x14ac:dyDescent="0.25">
-      <c r="A270" s="11" t="s">
+    <row r="270" spans="1:7" ht="21.6" x14ac:dyDescent="0.3">
+      <c r="A270" s="4" t="s">
         <v>224</v>
       </c>
-      <c r="B270" s="11" t="s">
+      <c r="B270" s="4" t="s">
         <v>27</v>
       </c>
       <c r="C270" s="4" t="s">
@@ -7714,11 +7708,11 @@
         <v>188</v>
       </c>
     </row>
-    <row r="271" spans="1:7" ht="67.5" x14ac:dyDescent="0.25">
-      <c r="A271" s="11" t="s">
+    <row r="271" spans="1:7" ht="64.8" x14ac:dyDescent="0.3">
+      <c r="A271" s="4" t="s">
         <v>224</v>
       </c>
-      <c r="B271" s="11" t="s">
+      <c r="B271" s="4" t="s">
         <v>28</v>
       </c>
       <c r="C271" s="4" t="s">
@@ -7737,11 +7731,11 @@
         <v>188</v>
       </c>
     </row>
-    <row r="272" spans="1:7" ht="67.5" x14ac:dyDescent="0.25">
-      <c r="A272" s="11" t="s">
+    <row r="272" spans="1:7" ht="64.8" x14ac:dyDescent="0.3">
+      <c r="A272" s="4" t="s">
         <v>224</v>
       </c>
-      <c r="B272" s="11" t="s">
+      <c r="B272" s="4" t="s">
         <v>29</v>
       </c>
       <c r="C272" s="4" t="s">
@@ -7760,11 +7754,11 @@
         <v>188</v>
       </c>
     </row>
-    <row r="273" spans="1:7" ht="67.5" x14ac:dyDescent="0.25">
-      <c r="A273" s="11" t="s">
+    <row r="273" spans="1:7" ht="64.8" x14ac:dyDescent="0.3">
+      <c r="A273" s="4" t="s">
         <v>224</v>
       </c>
-      <c r="B273" s="11" t="s">
+      <c r="B273" s="4" t="s">
         <v>30</v>
       </c>
       <c r="C273" s="4" t="s">
@@ -7783,11 +7777,11 @@
         <v>188</v>
       </c>
     </row>
-    <row r="274" spans="1:7" ht="45" x14ac:dyDescent="0.25">
-      <c r="A274" s="11" t="s">
+    <row r="274" spans="1:7" ht="32.4" x14ac:dyDescent="0.3">
+      <c r="A274" s="4" t="s">
         <v>224</v>
       </c>
-      <c r="B274" s="11" t="s">
+      <c r="B274" s="4" t="s">
         <v>31</v>
       </c>
       <c r="C274" s="4" t="s">
@@ -7806,11 +7800,11 @@
         <v>173</v>
       </c>
     </row>
-    <row r="275" spans="1:7" ht="56.25" x14ac:dyDescent="0.25">
-      <c r="A275" s="11" t="s">
+    <row r="275" spans="1:7" ht="54" x14ac:dyDescent="0.3">
+      <c r="A275" s="4" t="s">
         <v>224</v>
       </c>
-      <c r="B275" s="11" t="s">
+      <c r="B275" s="4" t="s">
         <v>87</v>
       </c>
       <c r="C275" s="4" t="s">
@@ -7829,11 +7823,11 @@
         <v>173</v>
       </c>
     </row>
-    <row r="276" spans="1:7" ht="56.25" x14ac:dyDescent="0.25">
-      <c r="A276" s="11" t="s">
+    <row r="276" spans="1:7" ht="43.2" x14ac:dyDescent="0.3">
+      <c r="A276" s="4" t="s">
         <v>224</v>
       </c>
-      <c r="B276" s="11" t="s">
+      <c r="B276" s="4" t="s">
         <v>32</v>
       </c>
       <c r="C276" s="4" t="s">
@@ -7852,11 +7846,11 @@
         <v>199</v>
       </c>
     </row>
-    <row r="277" spans="1:7" ht="56.25" x14ac:dyDescent="0.25">
-      <c r="A277" s="11" t="s">
+    <row r="277" spans="1:7" ht="54" x14ac:dyDescent="0.3">
+      <c r="A277" s="4" t="s">
         <v>224</v>
       </c>
-      <c r="B277" s="11" t="s">
+      <c r="B277" s="4" t="s">
         <v>33</v>
       </c>
       <c r="C277" s="4" t="s">
@@ -7875,11 +7869,11 @@
         <v>170</v>
       </c>
     </row>
-    <row r="278" spans="1:7" ht="33.75" x14ac:dyDescent="0.25">
-      <c r="A278" s="11" t="s">
+    <row r="278" spans="1:7" ht="21.6" x14ac:dyDescent="0.3">
+      <c r="A278" s="4" t="s">
         <v>224</v>
       </c>
-      <c r="B278" s="11" t="s">
+      <c r="B278" s="4" t="s">
         <v>34</v>
       </c>
       <c r="C278" s="4" t="s">
@@ -7898,11 +7892,11 @@
         <v>203</v>
       </c>
     </row>
-    <row r="279" spans="1:7" ht="22.5" x14ac:dyDescent="0.25">
-      <c r="A279" s="11" t="s">
+    <row r="279" spans="1:7" ht="21.6" x14ac:dyDescent="0.3">
+      <c r="A279" s="4" t="s">
         <v>224</v>
       </c>
-      <c r="B279" s="11" t="s">
+      <c r="B279" s="4" t="s">
         <v>35</v>
       </c>
       <c r="C279" s="4" t="s">
@@ -7921,11 +7915,11 @@
         <v>205</v>
       </c>
     </row>
-    <row r="280" spans="1:7" ht="33.75" x14ac:dyDescent="0.25">
-      <c r="A280" s="11" t="s">
+    <row r="280" spans="1:7" ht="32.4" x14ac:dyDescent="0.3">
+      <c r="A280" s="4" t="s">
         <v>224</v>
       </c>
-      <c r="B280" s="11" t="s">
+      <c r="B280" s="4" t="s">
         <v>36</v>
       </c>
       <c r="C280" s="4" t="s">
@@ -7944,11 +7938,11 @@
         <v>207</v>
       </c>
     </row>
-    <row r="281" spans="1:7" ht="33.75" x14ac:dyDescent="0.25">
-      <c r="A281" s="11" t="s">
+    <row r="281" spans="1:7" ht="32.4" x14ac:dyDescent="0.3">
+      <c r="A281" s="4" t="s">
         <v>224</v>
       </c>
-      <c r="B281" s="11" t="s">
+      <c r="B281" s="4" t="s">
         <v>38</v>
       </c>
       <c r="C281" s="4" t="s">
@@ -7967,11 +7961,11 @@
         <v>209</v>
       </c>
     </row>
-    <row r="282" spans="1:7" ht="45" x14ac:dyDescent="0.25">
-      <c r="A282" s="11" t="s">
+    <row r="282" spans="1:7" ht="43.2" x14ac:dyDescent="0.3">
+      <c r="A282" s="4" t="s">
         <v>224</v>
       </c>
-      <c r="B282" s="11" t="s">
+      <c r="B282" s="4" t="s">
         <v>39</v>
       </c>
       <c r="C282" s="4" t="s">
@@ -7990,11 +7984,11 @@
         <v>209</v>
       </c>
     </row>
-    <row r="283" spans="1:7" ht="33.75" x14ac:dyDescent="0.25">
-      <c r="A283" s="11" t="s">
+    <row r="283" spans="1:7" ht="32.4" x14ac:dyDescent="0.3">
+      <c r="A283" s="4" t="s">
         <v>224</v>
       </c>
-      <c r="B283" s="11" t="s">
+      <c r="B283" s="4" t="s">
         <v>223</v>
       </c>
       <c r="C283" s="4" t="s">
@@ -8013,11 +8007,11 @@
         <v>209</v>
       </c>
     </row>
-    <row r="284" spans="1:7" ht="33.75" x14ac:dyDescent="0.25">
-      <c r="A284" s="11" t="s">
+    <row r="284" spans="1:7" ht="32.4" x14ac:dyDescent="0.3">
+      <c r="A284" s="4" t="s">
         <v>224</v>
       </c>
-      <c r="B284" s="11" t="s">
+      <c r="B284" s="4" t="s">
         <v>16</v>
       </c>
       <c r="C284" s="4" t="s">
@@ -8036,11 +8030,11 @@
         <v>209</v>
       </c>
     </row>
-    <row r="285" spans="1:7" ht="56.25" x14ac:dyDescent="0.25">
-      <c r="A285" s="11" t="s">
+    <row r="285" spans="1:7" ht="54" x14ac:dyDescent="0.3">
+      <c r="A285" s="4" t="s">
         <v>224</v>
       </c>
-      <c r="B285" s="11" t="s">
+      <c r="B285" s="4" t="s">
         <v>17</v>
       </c>
       <c r="C285" s="4" t="s">
@@ -8059,11 +8053,11 @@
         <v>209</v>
       </c>
     </row>
-    <row r="286" spans="1:7" ht="33.75" x14ac:dyDescent="0.25">
-      <c r="A286" s="11" t="s">
+    <row r="286" spans="1:7" ht="32.4" x14ac:dyDescent="0.3">
+      <c r="A286" s="4" t="s">
         <v>224</v>
       </c>
-      <c r="B286" s="11" t="s">
+      <c r="B286" s="4" t="s">
         <v>18</v>
       </c>
       <c r="C286" s="4" t="s">
@@ -8082,11 +8076,11 @@
         <v>209</v>
       </c>
     </row>
-    <row r="287" spans="1:7" ht="45" x14ac:dyDescent="0.25">
-      <c r="A287" s="11" t="s">
+    <row r="287" spans="1:7" ht="43.2" x14ac:dyDescent="0.3">
+      <c r="A287" s="4" t="s">
         <v>224</v>
       </c>
-      <c r="B287" s="11" t="s">
+      <c r="B287" s="4" t="s">
         <v>19</v>
       </c>
       <c r="C287" s="4" t="s">
@@ -8105,11 +8099,11 @@
         <v>209</v>
       </c>
     </row>
-    <row r="288" spans="1:7" ht="56.25" x14ac:dyDescent="0.25">
-      <c r="A288" s="11" t="s">
+    <row r="288" spans="1:7" ht="54" x14ac:dyDescent="0.3">
+      <c r="A288" s="4" t="s">
         <v>224</v>
       </c>
-      <c r="B288" s="11" t="s">
+      <c r="B288" s="4" t="s">
         <v>20</v>
       </c>
       <c r="C288" s="4" t="s">
@@ -8128,11 +8122,11 @@
         <v>209</v>
       </c>
     </row>
-    <row r="289" spans="1:7" ht="45" x14ac:dyDescent="0.25">
-      <c r="A289" s="11" t="s">
+    <row r="289" spans="1:7" ht="32.4" x14ac:dyDescent="0.3">
+      <c r="A289" s="4" t="s">
         <v>224</v>
       </c>
-      <c r="B289" s="11" t="s">
+      <c r="B289" s="4" t="s">
         <v>21</v>
       </c>
       <c r="C289" s="4" t="s">
@@ -8151,11 +8145,11 @@
         <v>209</v>
       </c>
     </row>
-    <row r="290" spans="1:7" ht="45" x14ac:dyDescent="0.25">
-      <c r="A290" s="11" t="s">
+    <row r="290" spans="1:7" ht="32.4" x14ac:dyDescent="0.3">
+      <c r="A290" s="4" t="s">
         <v>224</v>
       </c>
-      <c r="B290" s="11" t="s">
+      <c r="B290" s="4" t="s">
         <v>221</v>
       </c>
       <c r="C290" s="4" t="s">
@@ -8174,11 +8168,11 @@
         <v>209</v>
       </c>
     </row>
-    <row r="291" spans="1:7" ht="67.5" x14ac:dyDescent="0.25">
-      <c r="A291" s="11" t="s">
+    <row r="291" spans="1:7" ht="54" x14ac:dyDescent="0.3">
+      <c r="A291" s="4" t="s">
         <v>224</v>
       </c>
-      <c r="B291" s="11" t="s">
+      <c r="B291" s="4" t="s">
         <v>41</v>
       </c>
       <c r="C291" s="4" t="s">
@@ -8197,11 +8191,11 @@
         <v>209</v>
       </c>
     </row>
-    <row r="292" spans="1:7" ht="22.5" x14ac:dyDescent="0.25">
-      <c r="A292" s="11" t="s">
+    <row r="292" spans="1:7" ht="21.6" x14ac:dyDescent="0.3">
+      <c r="A292" s="4" t="s">
         <v>224</v>
       </c>
-      <c r="B292" s="13" t="s">
+      <c r="B292" s="9" t="s">
         <v>74</v>
       </c>
       <c r="C292" s="4" t="s">
@@ -8233,67 +8227,67 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{2AE6CAE7-325B-4FFE-A096-050724C542D5}">
   <sheetPr codeName="Hoja2"/>
   <dimension ref="A1:K4"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <sheetData>
-    <row r="1" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A1" s="9" t="s">
+    <row r="1" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A1" s="10" t="s">
         <v>160</v>
       </c>
-      <c r="B1" s="9"/>
-      <c r="C1" s="9"/>
-      <c r="D1" s="9"/>
-      <c r="E1" s="9"/>
-      <c r="F1" s="9"/>
-      <c r="G1" s="9"/>
-      <c r="H1" s="9"/>
-      <c r="I1" s="9"/>
-      <c r="J1" s="9"/>
-      <c r="K1" s="9"/>
-    </row>
-    <row r="2" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A2" s="9" t="s">
+      <c r="B1" s="10"/>
+      <c r="C1" s="10"/>
+      <c r="D1" s="10"/>
+      <c r="E1" s="10"/>
+      <c r="F1" s="10"/>
+      <c r="G1" s="10"/>
+      <c r="H1" s="10"/>
+      <c r="I1" s="10"/>
+      <c r="J1" s="10"/>
+      <c r="K1" s="10"/>
+    </row>
+    <row r="2" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A2" s="10" t="s">
         <v>161</v>
       </c>
-      <c r="B2" s="9"/>
-      <c r="C2" s="9"/>
-      <c r="D2" s="9"/>
-      <c r="E2" s="9"/>
-      <c r="F2" s="9"/>
-      <c r="G2" s="9"/>
-      <c r="H2" s="9"/>
-      <c r="I2" s="9"/>
-      <c r="J2" s="9"/>
-      <c r="K2" s="9"/>
-    </row>
-    <row r="3" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A3" s="10" t="s">
+      <c r="B2" s="10"/>
+      <c r="C2" s="10"/>
+      <c r="D2" s="10"/>
+      <c r="E2" s="10"/>
+      <c r="F2" s="10"/>
+      <c r="G2" s="10"/>
+      <c r="H2" s="10"/>
+      <c r="I2" s="10"/>
+      <c r="J2" s="10"/>
+      <c r="K2" s="10"/>
+    </row>
+    <row r="3" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A3" s="11" t="s">
         <v>162</v>
       </c>
-      <c r="B3" s="10"/>
-      <c r="C3" s="10"/>
-      <c r="D3" s="10"/>
-      <c r="E3" s="10"/>
-      <c r="F3" s="10"/>
-      <c r="G3" s="10"/>
-      <c r="H3" s="10"/>
-      <c r="I3" s="10"/>
-      <c r="J3" s="10"/>
-      <c r="K3" s="10"/>
-    </row>
-    <row r="4" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A4" s="10" t="s">
+      <c r="B3" s="11"/>
+      <c r="C3" s="11"/>
+      <c r="D3" s="11"/>
+      <c r="E3" s="11"/>
+      <c r="F3" s="11"/>
+      <c r="G3" s="11"/>
+      <c r="H3" s="11"/>
+      <c r="I3" s="11"/>
+      <c r="J3" s="11"/>
+      <c r="K3" s="11"/>
+    </row>
+    <row r="4" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A4" s="11" t="s">
         <v>163</v>
       </c>
-      <c r="B4" s="10"/>
-      <c r="C4" s="10"/>
-      <c r="D4" s="10"/>
-      <c r="E4" s="10"/>
-      <c r="F4" s="10"/>
-      <c r="G4" s="10"/>
-      <c r="H4" s="10"/>
-      <c r="I4" s="10"/>
-      <c r="J4" s="10"/>
-      <c r="K4" s="10"/>
+      <c r="B4" s="11"/>
+      <c r="C4" s="11"/>
+      <c r="D4" s="11"/>
+      <c r="E4" s="11"/>
+      <c r="F4" s="11"/>
+      <c r="G4" s="11"/>
+      <c r="H4" s="11"/>
+      <c r="I4" s="11"/>
+      <c r="J4" s="11"/>
+      <c r="K4" s="11"/>
     </row>
   </sheetData>
   <mergeCells count="4">

--- a/Instructivo_Formularios_Junio_2026.xlsx
+++ b/Instructivo_Formularios_Junio_2026.xlsx
@@ -2,42 +2,31 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
   <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30131"/>
-  <workbookPr codeName="ThisWorkbook" defaultThemeVersion="202300"/>
+  <workbookPr codeName="ThisWorkbook"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://arconelgobec-my.sharepoint.com/personal/ingrid_pendolema_arconel_gob_ec/Documents/7. Ejecución de costos/Repositorio/Formularios/Formularios_Instructivo/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\william.boconzaca\Downloads\I\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="802" documentId="13_ncr:1_{FCF6FBC8-4607-4E2F-9187-96E2A78FAFC9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{0574186F-21C4-4BEB-93AD-D14D3B69B6E4}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0CDD5727-3B59-4C81-A601-B3989EC27B71}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{23C22566-AA08-4718-B9C7-8B52305F382C}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11160" xr2:uid="{23C22566-AA08-4718-B9C7-8B52305F382C}"/>
   </bookViews>
   <sheets>
     <sheet name="Instructivo" sheetId="1" r:id="rId1"/>
     <sheet name="Observaciones adicionales" sheetId="2" state="hidden" r:id="rId2"/>
   </sheets>
-  <calcPr calcId="191029"/>
+  <calcPr calcId="181029"/>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
-    </ext>
-    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
-      <xcalcf:calcFeatures>
-        <xcalcf:feature name="microsoft.com:RD"/>
-        <xcalcf:feature name="microsoft.com:Single"/>
-        <xcalcf:feature name="microsoft.com:FV"/>
-        <xcalcf:feature name="microsoft.com:CNMTM"/>
-        <xcalcf:feature name="microsoft.com:LET_WF"/>
-        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
-        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
-      </xcalcf:calcFeatures>
     </ext>
   </extLst>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2048" uniqueCount="228">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2048" uniqueCount="227">
   <si>
     <t>FORM 1 GASTO AO&amp;M-C SPEE</t>
   </si>
@@ -280,9 +269,6 @@
   </si>
   <si>
     <t>aso_transmisión</t>
-  </si>
-  <si>
-    <t>am_planficado</t>
   </si>
   <si>
     <t>FORM 4 EXPANSION SPEE</t>
@@ -1488,17 +1474,17 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{0EA1B5DC-7870-4CD4-B3EB-79CEB23C3997}">
   <sheetPr codeName="Hoja1"/>
   <dimension ref="A1:G292"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="11.44140625" defaultRowHeight="10.8" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="11.42578125" defaultRowHeight="11.25" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="23.109375" style="3" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="21.88671875" style="3" bestFit="1" customWidth="1"/>
-    <col min="3" max="5" width="11.44140625" style="3" customWidth="1"/>
-    <col min="6" max="6" width="43.44140625" style="8" customWidth="1"/>
-    <col min="7" max="7" width="43.44140625" style="3" customWidth="1"/>
-    <col min="8" max="16384" width="11.44140625" style="3"/>
+    <col min="1" max="1" width="23.140625" style="3" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="21.85546875" style="3" bestFit="1" customWidth="1"/>
+    <col min="3" max="5" width="11.42578125" style="3" customWidth="1"/>
+    <col min="6" max="6" width="43.42578125" style="8" customWidth="1"/>
+    <col min="7" max="7" width="43.42578125" style="3" customWidth="1"/>
+    <col min="8" max="16384" width="11.42578125" style="3"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:7" ht="45" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:7" ht="45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
         <v>1</v>
       </c>
@@ -1509,7 +1495,7 @@
         <v>3</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>164</v>
+        <v>163</v>
       </c>
       <c r="E1" s="1" t="s">
         <v>7</v>
@@ -1518,15 +1504,15 @@
         <v>6</v>
       </c>
       <c r="G1" s="2" t="s">
-        <v>169</v>
-      </c>
-    </row>
-    <row r="2" spans="1:7" x14ac:dyDescent="0.3">
+        <v>168</v>
+      </c>
+    </row>
+    <row r="2" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A2" s="4" t="s">
         <v>0</v>
       </c>
       <c r="B2" s="4" t="s">
-        <v>166</v>
+        <v>165</v>
       </c>
       <c r="C2" s="4" t="s">
         <v>4</v>
@@ -1538,13 +1524,13 @@
         <v>8</v>
       </c>
       <c r="F2" s="5" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="G2" s="6" t="s">
-        <v>170</v>
-      </c>
-    </row>
-    <row r="3" spans="1:7" x14ac:dyDescent="0.3">
+        <v>169</v>
+      </c>
+    </row>
+    <row r="3" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A3" s="4" t="s">
         <v>0</v>
       </c>
@@ -1561,18 +1547,18 @@
         <v>8</v>
       </c>
       <c r="F3" s="5" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="G3" s="6" t="s">
-        <v>170</v>
-      </c>
-    </row>
-    <row r="4" spans="1:7" x14ac:dyDescent="0.3">
+        <v>169</v>
+      </c>
+    </row>
+    <row r="4" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A4" s="4" t="s">
         <v>0</v>
       </c>
       <c r="B4" s="4" t="s">
-        <v>165</v>
+        <v>164</v>
       </c>
       <c r="C4" s="4" t="s">
         <v>4</v>
@@ -1584,13 +1570,13 @@
         <v>9</v>
       </c>
       <c r="F4" s="5" t="s">
-        <v>167</v>
+        <v>166</v>
       </c>
       <c r="G4" s="6" t="s">
-        <v>170</v>
-      </c>
-    </row>
-    <row r="5" spans="1:7" ht="32.4" x14ac:dyDescent="0.3">
+        <v>169</v>
+      </c>
+    </row>
+    <row r="5" spans="1:7" ht="33.75" x14ac:dyDescent="0.25">
       <c r="A5" s="4" t="s">
         <v>0</v>
       </c>
@@ -1607,13 +1593,13 @@
         <v>9</v>
       </c>
       <c r="F5" s="5" t="s">
-        <v>168</v>
+        <v>167</v>
       </c>
       <c r="G5" s="5" t="s">
-        <v>209</v>
-      </c>
-    </row>
-    <row r="6" spans="1:7" ht="54" x14ac:dyDescent="0.3">
+        <v>208</v>
+      </c>
+    </row>
+    <row r="6" spans="1:7" ht="56.25" x14ac:dyDescent="0.25">
       <c r="A6" s="4" t="s">
         <v>0</v>
       </c>
@@ -1630,13 +1616,13 @@
         <v>9</v>
       </c>
       <c r="F6" s="5" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="G6" s="5" t="s">
-        <v>209</v>
-      </c>
-    </row>
-    <row r="7" spans="1:7" ht="32.4" x14ac:dyDescent="0.3">
+        <v>208</v>
+      </c>
+    </row>
+    <row r="7" spans="1:7" ht="33.75" x14ac:dyDescent="0.25">
       <c r="A7" s="4" t="s">
         <v>0</v>
       </c>
@@ -1653,13 +1639,13 @@
         <v>9</v>
       </c>
       <c r="F7" s="5" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="G7" s="5" t="s">
-        <v>209</v>
-      </c>
-    </row>
-    <row r="8" spans="1:7" ht="43.2" x14ac:dyDescent="0.3">
+        <v>208</v>
+      </c>
+    </row>
+    <row r="8" spans="1:7" ht="45" x14ac:dyDescent="0.25">
       <c r="A8" s="4" t="s">
         <v>0</v>
       </c>
@@ -1676,13 +1662,13 @@
         <v>9</v>
       </c>
       <c r="F8" s="5" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="G8" s="5" t="s">
-        <v>209</v>
-      </c>
-    </row>
-    <row r="9" spans="1:7" ht="54" x14ac:dyDescent="0.3">
+        <v>208</v>
+      </c>
+    </row>
+    <row r="9" spans="1:7" ht="56.25" x14ac:dyDescent="0.25">
       <c r="A9" s="4" t="s">
         <v>0</v>
       </c>
@@ -1699,13 +1685,13 @@
         <v>9</v>
       </c>
       <c r="F9" s="5" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="G9" s="5" t="s">
-        <v>209</v>
-      </c>
-    </row>
-    <row r="10" spans="1:7" ht="32.4" x14ac:dyDescent="0.3">
+        <v>208</v>
+      </c>
+    </row>
+    <row r="10" spans="1:7" ht="45" x14ac:dyDescent="0.25">
       <c r="A10" s="4" t="s">
         <v>0</v>
       </c>
@@ -1722,18 +1708,18 @@
         <v>9</v>
       </c>
       <c r="F10" s="5" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="G10" s="5" t="s">
-        <v>209</v>
-      </c>
-    </row>
-    <row r="11" spans="1:7" ht="32.4" x14ac:dyDescent="0.3">
+        <v>208</v>
+      </c>
+    </row>
+    <row r="11" spans="1:7" ht="45" x14ac:dyDescent="0.25">
       <c r="A11" s="4" t="s">
         <v>0</v>
       </c>
       <c r="B11" s="4" t="s">
-        <v>221</v>
+        <v>220</v>
       </c>
       <c r="C11" s="4" t="s">
         <v>5</v>
@@ -1745,13 +1731,13 @@
         <v>9</v>
       </c>
       <c r="F11" s="5" t="s">
-        <v>211</v>
+        <v>210</v>
       </c>
       <c r="G11" s="5" t="s">
-        <v>209</v>
-      </c>
-    </row>
-    <row r="12" spans="1:7" ht="54" x14ac:dyDescent="0.3">
+        <v>208</v>
+      </c>
+    </row>
+    <row r="12" spans="1:7" ht="67.5" x14ac:dyDescent="0.25">
       <c r="A12" s="4" t="s">
         <v>0</v>
       </c>
@@ -1768,36 +1754,36 @@
         <v>9</v>
       </c>
       <c r="F12" s="5" t="s">
-        <v>212</v>
+        <v>211</v>
       </c>
       <c r="G12" s="5" t="s">
-        <v>209</v>
-      </c>
-    </row>
-    <row r="13" spans="1:7" x14ac:dyDescent="0.3">
+        <v>208</v>
+      </c>
+    </row>
+    <row r="13" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A13" s="4" t="s">
         <v>0</v>
       </c>
       <c r="B13" s="4" t="s">
+        <v>179</v>
+      </c>
+      <c r="C13" s="4" t="s">
+        <v>4</v>
+      </c>
+      <c r="D13" s="4" t="s">
+        <v>5</v>
+      </c>
+      <c r="E13" s="4" t="s">
+        <v>9</v>
+      </c>
+      <c r="F13" s="5" t="s">
         <v>180</v>
       </c>
-      <c r="C13" s="4" t="s">
-        <v>4</v>
-      </c>
-      <c r="D13" s="4" t="s">
-        <v>5</v>
-      </c>
-      <c r="E13" s="4" t="s">
-        <v>9</v>
-      </c>
-      <c r="F13" s="5" t="s">
+      <c r="G13" s="6" t="s">
         <v>181</v>
       </c>
-      <c r="G13" s="6" t="s">
-        <v>182</v>
-      </c>
-    </row>
-    <row r="14" spans="1:7" ht="54" x14ac:dyDescent="0.3">
+    </row>
+    <row r="14" spans="1:7" ht="56.25" x14ac:dyDescent="0.25">
       <c r="A14" s="4" t="s">
         <v>22</v>
       </c>
@@ -1814,13 +1800,13 @@
         <v>8</v>
       </c>
       <c r="F14" s="5" t="s">
-        <v>183</v>
+        <v>182</v>
       </c>
       <c r="G14" s="5" t="s">
-        <v>173</v>
-      </c>
-    </row>
-    <row r="15" spans="1:7" ht="21.6" x14ac:dyDescent="0.3">
+        <v>172</v>
+      </c>
+    </row>
+    <row r="15" spans="1:7" ht="22.5" x14ac:dyDescent="0.25">
       <c r="A15" s="4" t="s">
         <v>22</v>
       </c>
@@ -1837,13 +1823,13 @@
         <v>78</v>
       </c>
       <c r="F15" s="5" t="s">
-        <v>171</v>
+        <v>170</v>
       </c>
       <c r="G15" s="5" t="s">
-        <v>184</v>
-      </c>
-    </row>
-    <row r="16" spans="1:7" ht="21.6" x14ac:dyDescent="0.3">
+        <v>183</v>
+      </c>
+    </row>
+    <row r="16" spans="1:7" ht="33.75" x14ac:dyDescent="0.25">
       <c r="A16" s="4" t="s">
         <v>22</v>
       </c>
@@ -1860,13 +1846,13 @@
         <v>8</v>
       </c>
       <c r="F16" s="5" t="s">
-        <v>172</v>
+        <v>171</v>
       </c>
       <c r="G16" s="5" t="s">
-        <v>179</v>
-      </c>
-    </row>
-    <row r="17" spans="1:7" ht="21.6" x14ac:dyDescent="0.3">
+        <v>178</v>
+      </c>
+    </row>
+    <row r="17" spans="1:7" ht="22.5" x14ac:dyDescent="0.25">
       <c r="A17" s="4" t="s">
         <v>22</v>
       </c>
@@ -1883,13 +1869,13 @@
         <v>8</v>
       </c>
       <c r="F17" s="5" t="s">
-        <v>185</v>
+        <v>184</v>
       </c>
       <c r="G17" s="5" t="s">
-        <v>173</v>
-      </c>
-    </row>
-    <row r="18" spans="1:7" ht="21.6" x14ac:dyDescent="0.3">
+        <v>172</v>
+      </c>
+    </row>
+    <row r="18" spans="1:7" ht="33.75" x14ac:dyDescent="0.25">
       <c r="A18" s="4" t="s">
         <v>22</v>
       </c>
@@ -1906,13 +1892,13 @@
         <v>8</v>
       </c>
       <c r="F18" s="5" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="G18" s="5" t="s">
-        <v>173</v>
-      </c>
-    </row>
-    <row r="19" spans="1:7" ht="21.6" x14ac:dyDescent="0.3">
+        <v>172</v>
+      </c>
+    </row>
+    <row r="19" spans="1:7" ht="33.75" x14ac:dyDescent="0.25">
       <c r="A19" s="4" t="s">
         <v>22</v>
       </c>
@@ -1929,13 +1915,13 @@
         <v>8</v>
       </c>
       <c r="F19" s="5" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="G19" s="5" t="s">
-        <v>173</v>
-      </c>
-    </row>
-    <row r="20" spans="1:7" ht="32.4" x14ac:dyDescent="0.3">
+        <v>172</v>
+      </c>
+    </row>
+    <row r="20" spans="1:7" ht="33.75" x14ac:dyDescent="0.25">
       <c r="A20" s="4" t="s">
         <v>22</v>
       </c>
@@ -1952,13 +1938,13 @@
         <v>9</v>
       </c>
       <c r="F20" s="5" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="G20" s="5" t="s">
-        <v>209</v>
-      </c>
-    </row>
-    <row r="21" spans="1:7" ht="54" x14ac:dyDescent="0.3">
+        <v>208</v>
+      </c>
+    </row>
+    <row r="21" spans="1:7" ht="56.25" x14ac:dyDescent="0.25">
       <c r="A21" s="4" t="s">
         <v>22</v>
       </c>
@@ -1975,13 +1961,13 @@
         <v>9</v>
       </c>
       <c r="F21" s="5" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="G21" s="5" t="s">
-        <v>209</v>
-      </c>
-    </row>
-    <row r="22" spans="1:7" ht="32.4" x14ac:dyDescent="0.3">
+        <v>208</v>
+      </c>
+    </row>
+    <row r="22" spans="1:7" ht="33.75" x14ac:dyDescent="0.25">
       <c r="A22" s="4" t="s">
         <v>22</v>
       </c>
@@ -1998,13 +1984,13 @@
         <v>9</v>
       </c>
       <c r="F22" s="5" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="G22" s="5" t="s">
-        <v>209</v>
-      </c>
-    </row>
-    <row r="23" spans="1:7" ht="43.2" x14ac:dyDescent="0.3">
+        <v>208</v>
+      </c>
+    </row>
+    <row r="23" spans="1:7" ht="45" x14ac:dyDescent="0.25">
       <c r="A23" s="4" t="s">
         <v>22</v>
       </c>
@@ -2021,13 +2007,13 @@
         <v>9</v>
       </c>
       <c r="F23" s="5" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="G23" s="5" t="s">
-        <v>209</v>
-      </c>
-    </row>
-    <row r="24" spans="1:7" ht="54" x14ac:dyDescent="0.3">
+        <v>208</v>
+      </c>
+    </row>
+    <row r="24" spans="1:7" ht="56.25" x14ac:dyDescent="0.25">
       <c r="A24" s="4" t="s">
         <v>22</v>
       </c>
@@ -2044,13 +2030,13 @@
         <v>9</v>
       </c>
       <c r="F24" s="5" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="G24" s="5" t="s">
-        <v>209</v>
-      </c>
-    </row>
-    <row r="25" spans="1:7" ht="32.4" x14ac:dyDescent="0.3">
+        <v>208</v>
+      </c>
+    </row>
+    <row r="25" spans="1:7" ht="45" x14ac:dyDescent="0.25">
       <c r="A25" s="4" t="s">
         <v>22</v>
       </c>
@@ -2067,18 +2053,18 @@
         <v>9</v>
       </c>
       <c r="F25" s="5" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="G25" s="5" t="s">
-        <v>209</v>
-      </c>
-    </row>
-    <row r="26" spans="1:7" ht="32.4" x14ac:dyDescent="0.3">
+        <v>208</v>
+      </c>
+    </row>
+    <row r="26" spans="1:7" ht="45" x14ac:dyDescent="0.25">
       <c r="A26" s="4" t="s">
         <v>22</v>
       </c>
       <c r="B26" s="4" t="s">
-        <v>221</v>
+        <v>220</v>
       </c>
       <c r="C26" s="4" t="s">
         <v>5</v>
@@ -2090,13 +2076,13 @@
         <v>9</v>
       </c>
       <c r="F26" s="5" t="s">
-        <v>211</v>
+        <v>210</v>
       </c>
       <c r="G26" s="5" t="s">
-        <v>209</v>
-      </c>
-    </row>
-    <row r="27" spans="1:7" ht="54" x14ac:dyDescent="0.3">
+        <v>208</v>
+      </c>
+    </row>
+    <row r="27" spans="1:7" ht="56.25" x14ac:dyDescent="0.25">
       <c r="A27" s="4" t="s">
         <v>76</v>
       </c>
@@ -2113,13 +2099,13 @@
         <v>8</v>
       </c>
       <c r="F27" s="5" t="s">
-        <v>183</v>
+        <v>182</v>
       </c>
       <c r="G27" s="5" t="s">
-        <v>173</v>
-      </c>
-    </row>
-    <row r="28" spans="1:7" ht="43.2" x14ac:dyDescent="0.3">
+        <v>172</v>
+      </c>
+    </row>
+    <row r="28" spans="1:7" ht="45" x14ac:dyDescent="0.25">
       <c r="A28" s="4" t="s">
         <v>76</v>
       </c>
@@ -2136,18 +2122,18 @@
         <v>8</v>
       </c>
       <c r="F28" s="5" t="s">
-        <v>186</v>
+        <v>185</v>
       </c>
       <c r="G28" s="5" t="s">
-        <v>173</v>
-      </c>
-    </row>
-    <row r="29" spans="1:7" ht="54" x14ac:dyDescent="0.3">
+        <v>172</v>
+      </c>
+    </row>
+    <row r="29" spans="1:7" ht="56.25" x14ac:dyDescent="0.25">
       <c r="A29" s="4" t="s">
         <v>76</v>
       </c>
       <c r="B29" s="4" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="C29" s="4" t="s">
         <v>5</v>
@@ -2159,13 +2145,13 @@
         <v>8</v>
       </c>
       <c r="F29" s="5" t="s">
-        <v>174</v>
+        <v>173</v>
       </c>
       <c r="G29" s="5" t="s">
-        <v>173</v>
-      </c>
-    </row>
-    <row r="30" spans="1:7" ht="64.8" x14ac:dyDescent="0.3">
+        <v>172</v>
+      </c>
+    </row>
+    <row r="30" spans="1:7" ht="78.75" x14ac:dyDescent="0.25">
       <c r="A30" s="4" t="s">
         <v>76</v>
       </c>
@@ -2182,13 +2168,13 @@
         <v>78</v>
       </c>
       <c r="F30" s="5" t="s">
+        <v>174</v>
+      </c>
+      <c r="G30" s="5" t="s">
         <v>175</v>
       </c>
-      <c r="G30" s="5" t="s">
-        <v>176</v>
-      </c>
-    </row>
-    <row r="31" spans="1:7" ht="54" x14ac:dyDescent="0.3">
+    </row>
+    <row r="31" spans="1:7" ht="56.25" x14ac:dyDescent="0.25">
       <c r="A31" s="4" t="s">
         <v>76</v>
       </c>
@@ -2205,13 +2191,13 @@
         <v>79</v>
       </c>
       <c r="F31" s="5" t="s">
-        <v>177</v>
+        <v>176</v>
       </c>
       <c r="G31" s="5" t="s">
-        <v>187</v>
-      </c>
-    </row>
-    <row r="32" spans="1:7" ht="54" x14ac:dyDescent="0.3">
+        <v>186</v>
+      </c>
+    </row>
+    <row r="32" spans="1:7" ht="56.25" x14ac:dyDescent="0.25">
       <c r="A32" s="4" t="s">
         <v>76</v>
       </c>
@@ -2228,18 +2214,18 @@
         <v>8</v>
       </c>
       <c r="F32" s="5" t="s">
-        <v>218</v>
+        <v>217</v>
       </c>
       <c r="G32" s="5" t="s">
-        <v>173</v>
-      </c>
-    </row>
-    <row r="33" spans="1:7" ht="21.6" x14ac:dyDescent="0.3">
+        <v>172</v>
+      </c>
+    </row>
+    <row r="33" spans="1:7" ht="22.5" x14ac:dyDescent="0.25">
       <c r="A33" s="4" t="s">
         <v>76</v>
       </c>
       <c r="B33" s="4" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="C33" s="4" t="s">
         <v>5</v>
@@ -2251,13 +2237,13 @@
         <v>79</v>
       </c>
       <c r="F33" s="5" t="s">
-        <v>178</v>
+        <v>177</v>
       </c>
       <c r="G33" s="5" t="s">
-        <v>188</v>
-      </c>
-    </row>
-    <row r="34" spans="1:7" x14ac:dyDescent="0.3">
+        <v>187</v>
+      </c>
+    </row>
+    <row r="34" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A34" s="4" t="s">
         <v>76</v>
       </c>
@@ -2274,13 +2260,13 @@
         <v>8</v>
       </c>
       <c r="F34" s="5" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
       <c r="G34" s="5" t="s">
-        <v>188</v>
-      </c>
-    </row>
-    <row r="35" spans="1:7" ht="21.6" x14ac:dyDescent="0.3">
+        <v>187</v>
+      </c>
+    </row>
+    <row r="35" spans="1:7" ht="22.5" x14ac:dyDescent="0.25">
       <c r="A35" s="4" t="s">
         <v>76</v>
       </c>
@@ -2297,13 +2283,13 @@
         <v>8</v>
       </c>
       <c r="F35" s="5" t="s">
-        <v>189</v>
+        <v>188</v>
       </c>
       <c r="G35" s="5" t="s">
-        <v>188</v>
-      </c>
-    </row>
-    <row r="36" spans="1:7" ht="64.8" x14ac:dyDescent="0.3">
+        <v>187</v>
+      </c>
+    </row>
+    <row r="36" spans="1:7" ht="67.5" x14ac:dyDescent="0.25">
       <c r="A36" s="4" t="s">
         <v>76</v>
       </c>
@@ -2320,13 +2306,13 @@
         <v>8</v>
       </c>
       <c r="F36" s="5" t="s">
-        <v>190</v>
+        <v>189</v>
       </c>
       <c r="G36" s="5" t="s">
-        <v>188</v>
-      </c>
-    </row>
-    <row r="37" spans="1:7" ht="64.8" x14ac:dyDescent="0.3">
+        <v>187</v>
+      </c>
+    </row>
+    <row r="37" spans="1:7" ht="67.5" x14ac:dyDescent="0.25">
       <c r="A37" s="4" t="s">
         <v>76</v>
       </c>
@@ -2343,13 +2329,13 @@
         <v>8</v>
       </c>
       <c r="F37" s="5" t="s">
-        <v>191</v>
+        <v>190</v>
       </c>
       <c r="G37" s="5" t="s">
-        <v>188</v>
-      </c>
-    </row>
-    <row r="38" spans="1:7" ht="64.8" x14ac:dyDescent="0.3">
+        <v>187</v>
+      </c>
+    </row>
+    <row r="38" spans="1:7" ht="67.5" x14ac:dyDescent="0.25">
       <c r="A38" s="4" t="s">
         <v>76</v>
       </c>
@@ -2366,13 +2352,13 @@
         <v>8</v>
       </c>
       <c r="F38" s="5" t="s">
-        <v>192</v>
+        <v>191</v>
       </c>
       <c r="G38" s="5" t="s">
-        <v>188</v>
-      </c>
-    </row>
-    <row r="39" spans="1:7" ht="43.2" x14ac:dyDescent="0.3">
+        <v>187</v>
+      </c>
+    </row>
+    <row r="39" spans="1:7" ht="45" x14ac:dyDescent="0.25">
       <c r="A39" s="4" t="s">
         <v>76</v>
       </c>
@@ -2389,13 +2375,13 @@
         <v>8</v>
       </c>
       <c r="F39" s="5" t="s">
-        <v>193</v>
+        <v>192</v>
       </c>
       <c r="G39" s="5" t="s">
-        <v>173</v>
-      </c>
-    </row>
-    <row r="40" spans="1:7" ht="64.8" x14ac:dyDescent="0.3">
+        <v>172</v>
+      </c>
+    </row>
+    <row r="40" spans="1:7" ht="67.5" x14ac:dyDescent="0.25">
       <c r="A40" s="4" t="s">
         <v>76</v>
       </c>
@@ -2412,18 +2398,18 @@
         <v>8</v>
       </c>
       <c r="F40" s="5" t="s">
-        <v>194</v>
+        <v>193</v>
       </c>
       <c r="G40" s="5" t="s">
-        <v>173</v>
-      </c>
-    </row>
-    <row r="41" spans="1:7" ht="43.2" x14ac:dyDescent="0.3">
+        <v>172</v>
+      </c>
+    </row>
+    <row r="41" spans="1:7" ht="45" x14ac:dyDescent="0.25">
       <c r="A41" s="4" t="s">
         <v>76</v>
       </c>
       <c r="B41" s="4" t="s">
-        <v>159</v>
+        <v>158</v>
       </c>
       <c r="C41" s="4" t="s">
         <v>5</v>
@@ -2435,13 +2421,13 @@
         <v>8</v>
       </c>
       <c r="F41" s="5" t="s">
-        <v>195</v>
+        <v>194</v>
       </c>
       <c r="G41" s="5" t="s">
-        <v>173</v>
-      </c>
-    </row>
-    <row r="42" spans="1:7" ht="32.4" x14ac:dyDescent="0.3">
+        <v>172</v>
+      </c>
+    </row>
+    <row r="42" spans="1:7" ht="45" x14ac:dyDescent="0.25">
       <c r="A42" s="4" t="s">
         <v>76</v>
       </c>
@@ -2458,18 +2444,18 @@
         <v>8</v>
       </c>
       <c r="F42" s="5" t="s">
-        <v>196</v>
+        <v>195</v>
       </c>
       <c r="G42" s="5" t="s">
-        <v>173</v>
-      </c>
-    </row>
-    <row r="43" spans="1:7" ht="54" x14ac:dyDescent="0.3">
+        <v>172</v>
+      </c>
+    </row>
+    <row r="43" spans="1:7" ht="56.25" x14ac:dyDescent="0.25">
       <c r="A43" s="4" t="s">
         <v>76</v>
       </c>
       <c r="B43" s="4" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="C43" s="4" t="s">
         <v>5</v>
@@ -2481,13 +2467,13 @@
         <v>8</v>
       </c>
       <c r="F43" s="5" t="s">
-        <v>197</v>
+        <v>196</v>
       </c>
       <c r="G43" s="5" t="s">
-        <v>173</v>
-      </c>
-    </row>
-    <row r="44" spans="1:7" ht="43.2" x14ac:dyDescent="0.3">
+        <v>172</v>
+      </c>
+    </row>
+    <row r="44" spans="1:7" ht="56.25" x14ac:dyDescent="0.25">
       <c r="A44" s="4" t="s">
         <v>76</v>
       </c>
@@ -2504,13 +2490,13 @@
         <v>77</v>
       </c>
       <c r="F44" s="5" t="s">
+        <v>197</v>
+      </c>
+      <c r="G44" s="5" t="s">
         <v>198</v>
       </c>
-      <c r="G44" s="5" t="s">
-        <v>199</v>
-      </c>
-    </row>
-    <row r="45" spans="1:7" ht="54" x14ac:dyDescent="0.3">
+    </row>
+    <row r="45" spans="1:7" ht="56.25" x14ac:dyDescent="0.25">
       <c r="A45" s="4" t="s">
         <v>76</v>
       </c>
@@ -2527,13 +2513,13 @@
         <v>77</v>
       </c>
       <c r="F45" s="5" t="s">
-        <v>200</v>
+        <v>199</v>
       </c>
       <c r="G45" s="5" t="s">
-        <v>170</v>
-      </c>
-    </row>
-    <row r="46" spans="1:7" ht="21.6" x14ac:dyDescent="0.3">
+        <v>169</v>
+      </c>
+    </row>
+    <row r="46" spans="1:7" ht="33.75" x14ac:dyDescent="0.25">
       <c r="A46" s="4" t="s">
         <v>76</v>
       </c>
@@ -2547,16 +2533,16 @@
         <v>4</v>
       </c>
       <c r="E46" s="4" t="s">
+        <v>200</v>
+      </c>
+      <c r="F46" s="5" t="s">
         <v>201</v>
       </c>
-      <c r="F46" s="5" t="s">
+      <c r="G46" s="5" t="s">
         <v>202</v>
       </c>
-      <c r="G46" s="5" t="s">
-        <v>203</v>
-      </c>
-    </row>
-    <row r="47" spans="1:7" ht="21.6" x14ac:dyDescent="0.3">
+    </row>
+    <row r="47" spans="1:7" ht="22.5" x14ac:dyDescent="0.25">
       <c r="A47" s="4" t="s">
         <v>76</v>
       </c>
@@ -2570,16 +2556,16 @@
         <v>5</v>
       </c>
       <c r="E47" s="4" t="s">
-        <v>201</v>
+        <v>200</v>
       </c>
       <c r="F47" s="5" t="s">
+        <v>203</v>
+      </c>
+      <c r="G47" s="5" t="s">
         <v>204</v>
       </c>
-      <c r="G47" s="5" t="s">
-        <v>205</v>
-      </c>
-    </row>
-    <row r="48" spans="1:7" ht="32.4" x14ac:dyDescent="0.3">
+    </row>
+    <row r="48" spans="1:7" ht="33.75" x14ac:dyDescent="0.25">
       <c r="A48" s="4" t="s">
         <v>76</v>
       </c>
@@ -2593,16 +2579,16 @@
         <v>4</v>
       </c>
       <c r="E48" s="4" t="s">
-        <v>201</v>
+        <v>200</v>
       </c>
       <c r="F48" s="5" t="s">
+        <v>205</v>
+      </c>
+      <c r="G48" s="5" t="s">
         <v>206</v>
       </c>
-      <c r="G48" s="5" t="s">
-        <v>207</v>
-      </c>
-    </row>
-    <row r="49" spans="1:7" ht="32.4" x14ac:dyDescent="0.3">
+    </row>
+    <row r="49" spans="1:7" ht="33.75" x14ac:dyDescent="0.25">
       <c r="A49" s="4" t="s">
         <v>76</v>
       </c>
@@ -2619,13 +2605,13 @@
         <v>9</v>
       </c>
       <c r="F49" s="5" t="s">
-        <v>208</v>
+        <v>207</v>
       </c>
       <c r="G49" s="5" t="s">
-        <v>209</v>
-      </c>
-    </row>
-    <row r="50" spans="1:7" ht="32.4" x14ac:dyDescent="0.3">
+        <v>208</v>
+      </c>
+    </row>
+    <row r="50" spans="1:7" ht="33.75" x14ac:dyDescent="0.25">
       <c r="A50" s="4" t="s">
         <v>76</v>
       </c>
@@ -2642,13 +2628,13 @@
         <v>9</v>
       </c>
       <c r="F50" s="5" t="s">
-        <v>210</v>
+        <v>209</v>
       </c>
       <c r="G50" s="5" t="s">
-        <v>209</v>
-      </c>
-    </row>
-    <row r="51" spans="1:7" ht="43.2" x14ac:dyDescent="0.3">
+        <v>208</v>
+      </c>
+    </row>
+    <row r="51" spans="1:7" ht="45" x14ac:dyDescent="0.25">
       <c r="A51" s="4" t="s">
         <v>76</v>
       </c>
@@ -2665,13 +2651,13 @@
         <v>9</v>
       </c>
       <c r="F51" s="5" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="G51" s="5" t="s">
-        <v>209</v>
-      </c>
-    </row>
-    <row r="52" spans="1:7" ht="32.4" x14ac:dyDescent="0.3">
+        <v>208</v>
+      </c>
+    </row>
+    <row r="52" spans="1:7" ht="33.75" x14ac:dyDescent="0.25">
       <c r="A52" s="4" t="s">
         <v>76</v>
       </c>
@@ -2688,13 +2674,13 @@
         <v>9</v>
       </c>
       <c r="F52" s="5" t="s">
-        <v>113</v>
+        <v>112</v>
       </c>
       <c r="G52" s="5" t="s">
-        <v>209</v>
-      </c>
-    </row>
-    <row r="53" spans="1:7" ht="32.4" x14ac:dyDescent="0.3">
+        <v>208</v>
+      </c>
+    </row>
+    <row r="53" spans="1:7" ht="33.75" x14ac:dyDescent="0.25">
       <c r="A53" s="4" t="s">
         <v>76</v>
       </c>
@@ -2711,13 +2697,13 @@
         <v>9</v>
       </c>
       <c r="F53" s="5" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="G53" s="5" t="s">
-        <v>209</v>
-      </c>
-    </row>
-    <row r="54" spans="1:7" ht="54" x14ac:dyDescent="0.3">
+        <v>208</v>
+      </c>
+    </row>
+    <row r="54" spans="1:7" ht="56.25" x14ac:dyDescent="0.25">
       <c r="A54" s="4" t="s">
         <v>76</v>
       </c>
@@ -2734,13 +2720,13 @@
         <v>9</v>
       </c>
       <c r="F54" s="5" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="G54" s="5" t="s">
-        <v>209</v>
-      </c>
-    </row>
-    <row r="55" spans="1:7" ht="32.4" x14ac:dyDescent="0.3">
+        <v>208</v>
+      </c>
+    </row>
+    <row r="55" spans="1:7" ht="33.75" x14ac:dyDescent="0.25">
       <c r="A55" s="4" t="s">
         <v>76</v>
       </c>
@@ -2757,13 +2743,13 @@
         <v>9</v>
       </c>
       <c r="F55" s="5" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="G55" s="5" t="s">
-        <v>209</v>
-      </c>
-    </row>
-    <row r="56" spans="1:7" ht="43.2" x14ac:dyDescent="0.3">
+        <v>208</v>
+      </c>
+    </row>
+    <row r="56" spans="1:7" ht="45" x14ac:dyDescent="0.25">
       <c r="A56" s="4" t="s">
         <v>76</v>
       </c>
@@ -2780,13 +2766,13 @@
         <v>9</v>
       </c>
       <c r="F56" s="5" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="G56" s="5" t="s">
-        <v>209</v>
-      </c>
-    </row>
-    <row r="57" spans="1:7" ht="54" x14ac:dyDescent="0.3">
+        <v>208</v>
+      </c>
+    </row>
+    <row r="57" spans="1:7" ht="56.25" x14ac:dyDescent="0.25">
       <c r="A57" s="4" t="s">
         <v>76</v>
       </c>
@@ -2803,13 +2789,13 @@
         <v>9</v>
       </c>
       <c r="F57" s="5" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="G57" s="5" t="s">
-        <v>209</v>
-      </c>
-    </row>
-    <row r="58" spans="1:7" ht="32.4" x14ac:dyDescent="0.3">
+        <v>208</v>
+      </c>
+    </row>
+    <row r="58" spans="1:7" ht="45" x14ac:dyDescent="0.25">
       <c r="A58" s="4" t="s">
         <v>76</v>
       </c>
@@ -2826,18 +2812,18 @@
         <v>9</v>
       </c>
       <c r="F58" s="5" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="G58" s="5" t="s">
-        <v>209</v>
-      </c>
-    </row>
-    <row r="59" spans="1:7" ht="32.4" x14ac:dyDescent="0.3">
+        <v>208</v>
+      </c>
+    </row>
+    <row r="59" spans="1:7" ht="45" x14ac:dyDescent="0.25">
       <c r="A59" s="4" t="s">
         <v>76</v>
       </c>
       <c r="B59" s="4" t="s">
-        <v>221</v>
+        <v>220</v>
       </c>
       <c r="C59" s="4" t="s">
         <v>5</v>
@@ -2849,13 +2835,13 @@
         <v>9</v>
       </c>
       <c r="F59" s="5" t="s">
-        <v>211</v>
+        <v>210</v>
       </c>
       <c r="G59" s="5" t="s">
-        <v>209</v>
-      </c>
-    </row>
-    <row r="60" spans="1:7" ht="54" x14ac:dyDescent="0.3">
+        <v>208</v>
+      </c>
+    </row>
+    <row r="60" spans="1:7" ht="67.5" x14ac:dyDescent="0.25">
       <c r="A60" s="4" t="s">
         <v>76</v>
       </c>
@@ -2872,13 +2858,13 @@
         <v>9</v>
       </c>
       <c r="F60" s="5" t="s">
-        <v>212</v>
+        <v>211</v>
       </c>
       <c r="G60" s="5" t="s">
-        <v>209</v>
-      </c>
-    </row>
-    <row r="61" spans="1:7" ht="21.6" x14ac:dyDescent="0.3">
+        <v>208</v>
+      </c>
+    </row>
+    <row r="61" spans="1:7" ht="22.5" x14ac:dyDescent="0.25">
       <c r="A61" s="4" t="s">
         <v>76</v>
       </c>
@@ -2895,13 +2881,13 @@
         <v>9</v>
       </c>
       <c r="F61" s="5" t="s">
-        <v>120</v>
+        <v>119</v>
       </c>
       <c r="G61" s="5" t="s">
-        <v>214</v>
-      </c>
-    </row>
-    <row r="62" spans="1:7" ht="21.6" x14ac:dyDescent="0.3">
+        <v>213</v>
+      </c>
+    </row>
+    <row r="62" spans="1:7" ht="22.5" x14ac:dyDescent="0.25">
       <c r="A62" s="4" t="s">
         <v>76</v>
       </c>
@@ -2918,13 +2904,13 @@
         <v>9</v>
       </c>
       <c r="F62" s="5" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
       <c r="G62" s="5" t="s">
-        <v>214</v>
-      </c>
-    </row>
-    <row r="63" spans="1:7" ht="32.4" x14ac:dyDescent="0.3">
+        <v>213</v>
+      </c>
+    </row>
+    <row r="63" spans="1:7" ht="45" x14ac:dyDescent="0.25">
       <c r="A63" s="4" t="s">
         <v>76</v>
       </c>
@@ -2941,13 +2927,13 @@
         <v>9</v>
       </c>
       <c r="F63" s="5" t="s">
-        <v>121</v>
+        <v>120</v>
       </c>
       <c r="G63" s="5" t="s">
-        <v>214</v>
-      </c>
-    </row>
-    <row r="64" spans="1:7" ht="32.4" x14ac:dyDescent="0.3">
+        <v>213</v>
+      </c>
+    </row>
+    <row r="64" spans="1:7" ht="33.75" x14ac:dyDescent="0.25">
       <c r="A64" s="4" t="s">
         <v>76</v>
       </c>
@@ -2964,13 +2950,13 @@
         <v>9</v>
       </c>
       <c r="F64" s="5" t="s">
-        <v>122</v>
+        <v>121</v>
       </c>
       <c r="G64" s="5" t="s">
-        <v>214</v>
-      </c>
-    </row>
-    <row r="65" spans="1:7" ht="32.4" x14ac:dyDescent="0.3">
+        <v>213</v>
+      </c>
+    </row>
+    <row r="65" spans="1:7" ht="33.75" x14ac:dyDescent="0.25">
       <c r="A65" s="4" t="s">
         <v>76</v>
       </c>
@@ -2987,13 +2973,13 @@
         <v>9</v>
       </c>
       <c r="F65" s="5" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="G65" s="5" t="s">
-        <v>214</v>
-      </c>
-    </row>
-    <row r="66" spans="1:7" ht="32.4" x14ac:dyDescent="0.3">
+        <v>213</v>
+      </c>
+    </row>
+    <row r="66" spans="1:7" ht="33.75" x14ac:dyDescent="0.25">
       <c r="A66" s="4" t="s">
         <v>76</v>
       </c>
@@ -3010,13 +2996,13 @@
         <v>9</v>
       </c>
       <c r="F66" s="5" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="G66" s="5" t="s">
-        <v>214</v>
-      </c>
-    </row>
-    <row r="67" spans="1:7" ht="21.6" x14ac:dyDescent="0.3">
+        <v>213</v>
+      </c>
+    </row>
+    <row r="67" spans="1:7" ht="22.5" x14ac:dyDescent="0.25">
       <c r="A67" s="4" t="s">
         <v>76</v>
       </c>
@@ -3033,13 +3019,13 @@
         <v>9</v>
       </c>
       <c r="F67" s="5" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="G67" s="5" t="s">
-        <v>214</v>
-      </c>
-    </row>
-    <row r="68" spans="1:7" ht="21.6" x14ac:dyDescent="0.3">
+        <v>213</v>
+      </c>
+    </row>
+    <row r="68" spans="1:7" ht="33.75" x14ac:dyDescent="0.25">
       <c r="A68" s="4" t="s">
         <v>76</v>
       </c>
@@ -3056,13 +3042,13 @@
         <v>9</v>
       </c>
       <c r="F68" s="5" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="G68" s="5" t="s">
-        <v>214</v>
-      </c>
-    </row>
-    <row r="69" spans="1:7" ht="32.4" x14ac:dyDescent="0.3">
+        <v>213</v>
+      </c>
+    </row>
+    <row r="69" spans="1:7" ht="33.75" x14ac:dyDescent="0.25">
       <c r="A69" s="4" t="s">
         <v>76</v>
       </c>
@@ -3079,13 +3065,13 @@
         <v>9</v>
       </c>
       <c r="F69" s="5" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="G69" s="5" t="s">
-        <v>214</v>
-      </c>
-    </row>
-    <row r="70" spans="1:7" ht="21.6" x14ac:dyDescent="0.3">
+        <v>213</v>
+      </c>
+    </row>
+    <row r="70" spans="1:7" ht="33.75" x14ac:dyDescent="0.25">
       <c r="A70" s="4" t="s">
         <v>76</v>
       </c>
@@ -3102,13 +3088,13 @@
         <v>9</v>
       </c>
       <c r="F70" s="5" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
       <c r="G70" s="5" t="s">
-        <v>214</v>
-      </c>
-    </row>
-    <row r="71" spans="1:7" ht="21.6" x14ac:dyDescent="0.3">
+        <v>213</v>
+      </c>
+    </row>
+    <row r="71" spans="1:7" ht="22.5" x14ac:dyDescent="0.25">
       <c r="A71" s="4" t="s">
         <v>76</v>
       </c>
@@ -3125,13 +3111,13 @@
         <v>9</v>
       </c>
       <c r="F71" s="5" t="s">
-        <v>128</v>
+        <v>127</v>
       </c>
       <c r="G71" s="5" t="s">
-        <v>214</v>
-      </c>
-    </row>
-    <row r="72" spans="1:7" ht="21.6" x14ac:dyDescent="0.3">
+        <v>213</v>
+      </c>
+    </row>
+    <row r="72" spans="1:7" ht="22.5" x14ac:dyDescent="0.25">
       <c r="A72" s="4" t="s">
         <v>76</v>
       </c>
@@ -3148,13 +3134,13 @@
         <v>9</v>
       </c>
       <c r="F72" s="5" t="s">
-        <v>129</v>
+        <v>128</v>
       </c>
       <c r="G72" s="5" t="s">
-        <v>214</v>
-      </c>
-    </row>
-    <row r="73" spans="1:7" ht="21.6" x14ac:dyDescent="0.3">
+        <v>213</v>
+      </c>
+    </row>
+    <row r="73" spans="1:7" ht="22.5" x14ac:dyDescent="0.25">
       <c r="A73" s="4" t="s">
         <v>76</v>
       </c>
@@ -3171,13 +3157,13 @@
         <v>9</v>
       </c>
       <c r="F73" s="5" t="s">
-        <v>130</v>
+        <v>129</v>
       </c>
       <c r="G73" s="5" t="s">
-        <v>214</v>
-      </c>
-    </row>
-    <row r="74" spans="1:7" ht="21.6" x14ac:dyDescent="0.3">
+        <v>213</v>
+      </c>
+    </row>
+    <row r="74" spans="1:7" ht="22.5" x14ac:dyDescent="0.25">
       <c r="A74" s="4" t="s">
         <v>76</v>
       </c>
@@ -3194,13 +3180,13 @@
         <v>9</v>
       </c>
       <c r="F74" s="5" t="s">
-        <v>131</v>
+        <v>130</v>
       </c>
       <c r="G74" s="5" t="s">
-        <v>214</v>
-      </c>
-    </row>
-    <row r="75" spans="1:7" ht="32.4" x14ac:dyDescent="0.3">
+        <v>213</v>
+      </c>
+    </row>
+    <row r="75" spans="1:7" ht="33.75" x14ac:dyDescent="0.25">
       <c r="A75" s="4" t="s">
         <v>76</v>
       </c>
@@ -3217,13 +3203,13 @@
         <v>9</v>
       </c>
       <c r="F75" s="5" t="s">
-        <v>132</v>
+        <v>131</v>
       </c>
       <c r="G75" s="5" t="s">
-        <v>214</v>
-      </c>
-    </row>
-    <row r="76" spans="1:7" ht="21.6" x14ac:dyDescent="0.3">
+        <v>213</v>
+      </c>
+    </row>
+    <row r="76" spans="1:7" ht="22.5" x14ac:dyDescent="0.25">
       <c r="A76" s="4" t="s">
         <v>76</v>
       </c>
@@ -3240,13 +3226,13 @@
         <v>9</v>
       </c>
       <c r="F76" s="5" t="s">
-        <v>133</v>
+        <v>132</v>
       </c>
       <c r="G76" s="5" t="s">
-        <v>214</v>
-      </c>
-    </row>
-    <row r="77" spans="1:7" ht="32.4" x14ac:dyDescent="0.3">
+        <v>213</v>
+      </c>
+    </row>
+    <row r="77" spans="1:7" ht="33.75" x14ac:dyDescent="0.25">
       <c r="A77" s="4" t="s">
         <v>76</v>
       </c>
@@ -3263,13 +3249,13 @@
         <v>9</v>
       </c>
       <c r="F77" s="5" t="s">
-        <v>134</v>
+        <v>133</v>
       </c>
       <c r="G77" s="5" t="s">
-        <v>214</v>
-      </c>
-    </row>
-    <row r="78" spans="1:7" ht="21.6" x14ac:dyDescent="0.3">
+        <v>213</v>
+      </c>
+    </row>
+    <row r="78" spans="1:7" ht="22.5" x14ac:dyDescent="0.25">
       <c r="A78" s="4" t="s">
         <v>76</v>
       </c>
@@ -3286,13 +3272,13 @@
         <v>9</v>
       </c>
       <c r="F78" s="5" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="G78" s="5" t="s">
-        <v>214</v>
-      </c>
-    </row>
-    <row r="79" spans="1:7" ht="21.6" x14ac:dyDescent="0.3">
+        <v>213</v>
+      </c>
+    </row>
+    <row r="79" spans="1:7" ht="22.5" x14ac:dyDescent="0.25">
       <c r="A79" s="4" t="s">
         <v>76</v>
       </c>
@@ -3309,13 +3295,13 @@
         <v>9</v>
       </c>
       <c r="F79" s="5" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
       <c r="G79" s="5" t="s">
-        <v>214</v>
-      </c>
-    </row>
-    <row r="80" spans="1:7" ht="21.6" x14ac:dyDescent="0.3">
+        <v>213</v>
+      </c>
+    </row>
+    <row r="80" spans="1:7" ht="22.5" x14ac:dyDescent="0.25">
       <c r="A80" s="4" t="s">
         <v>76</v>
       </c>
@@ -3332,13 +3318,13 @@
         <v>9</v>
       </c>
       <c r="F80" s="5" t="s">
-        <v>137</v>
+        <v>136</v>
       </c>
       <c r="G80" s="5" t="s">
-        <v>214</v>
-      </c>
-    </row>
-    <row r="81" spans="1:7" ht="21.6" x14ac:dyDescent="0.3">
+        <v>213</v>
+      </c>
+    </row>
+    <row r="81" spans="1:7" ht="22.5" x14ac:dyDescent="0.25">
       <c r="A81" s="4" t="s">
         <v>76</v>
       </c>
@@ -3355,13 +3341,13 @@
         <v>9</v>
       </c>
       <c r="F81" s="5" t="s">
-        <v>139</v>
+        <v>138</v>
       </c>
       <c r="G81" s="5" t="s">
-        <v>214</v>
-      </c>
-    </row>
-    <row r="82" spans="1:7" ht="21.6" x14ac:dyDescent="0.3">
+        <v>213</v>
+      </c>
+    </row>
+    <row r="82" spans="1:7" ht="22.5" x14ac:dyDescent="0.25">
       <c r="A82" s="4" t="s">
         <v>76</v>
       </c>
@@ -3378,13 +3364,13 @@
         <v>9</v>
       </c>
       <c r="F82" s="5" t="s">
-        <v>138</v>
+        <v>137</v>
       </c>
       <c r="G82" s="5" t="s">
-        <v>214</v>
-      </c>
-    </row>
-    <row r="83" spans="1:7" ht="32.4" x14ac:dyDescent="0.3">
+        <v>213</v>
+      </c>
+    </row>
+    <row r="83" spans="1:7" ht="33.75" x14ac:dyDescent="0.25">
       <c r="A83" s="4" t="s">
         <v>76</v>
       </c>
@@ -3401,13 +3387,13 @@
         <v>9</v>
       </c>
       <c r="F83" s="5" t="s">
-        <v>140</v>
+        <v>139</v>
       </c>
       <c r="G83" s="5" t="s">
-        <v>214</v>
-      </c>
-    </row>
-    <row r="84" spans="1:7" ht="21.6" x14ac:dyDescent="0.3">
+        <v>213</v>
+      </c>
+    </row>
+    <row r="84" spans="1:7" ht="22.5" x14ac:dyDescent="0.25">
       <c r="A84" s="4" t="s">
         <v>76</v>
       </c>
@@ -3424,13 +3410,13 @@
         <v>9</v>
       </c>
       <c r="F84" s="5" t="s">
-        <v>141</v>
+        <v>140</v>
       </c>
       <c r="G84" s="5" t="s">
-        <v>214</v>
-      </c>
-    </row>
-    <row r="85" spans="1:7" ht="21.6" x14ac:dyDescent="0.3">
+        <v>213</v>
+      </c>
+    </row>
+    <row r="85" spans="1:7" ht="22.5" x14ac:dyDescent="0.25">
       <c r="A85" s="4" t="s">
         <v>76</v>
       </c>
@@ -3447,13 +3433,13 @@
         <v>9</v>
       </c>
       <c r="F85" s="5" t="s">
-        <v>142</v>
+        <v>141</v>
       </c>
       <c r="G85" s="5" t="s">
-        <v>214</v>
-      </c>
-    </row>
-    <row r="86" spans="1:7" ht="21.6" x14ac:dyDescent="0.3">
+        <v>213</v>
+      </c>
+    </row>
+    <row r="86" spans="1:7" ht="22.5" x14ac:dyDescent="0.25">
       <c r="A86" s="4" t="s">
         <v>76</v>
       </c>
@@ -3470,13 +3456,13 @@
         <v>9</v>
       </c>
       <c r="F86" s="5" t="s">
-        <v>143</v>
+        <v>142</v>
       </c>
       <c r="G86" s="5" t="s">
-        <v>214</v>
-      </c>
-    </row>
-    <row r="87" spans="1:7" ht="21.6" x14ac:dyDescent="0.3">
+        <v>213</v>
+      </c>
+    </row>
+    <row r="87" spans="1:7" ht="33.75" x14ac:dyDescent="0.25">
       <c r="A87" s="4" t="s">
         <v>76</v>
       </c>
@@ -3493,13 +3479,13 @@
         <v>9</v>
       </c>
       <c r="F87" s="5" t="s">
-        <v>144</v>
+        <v>143</v>
       </c>
       <c r="G87" s="5" t="s">
-        <v>214</v>
-      </c>
-    </row>
-    <row r="88" spans="1:7" ht="21.6" x14ac:dyDescent="0.3">
+        <v>213</v>
+      </c>
+    </row>
+    <row r="88" spans="1:7" ht="33.75" x14ac:dyDescent="0.25">
       <c r="A88" s="4" t="s">
         <v>76</v>
       </c>
@@ -3516,13 +3502,13 @@
         <v>9</v>
       </c>
       <c r="F88" s="5" t="s">
-        <v>145</v>
+        <v>144</v>
       </c>
       <c r="G88" s="5" t="s">
-        <v>214</v>
-      </c>
-    </row>
-    <row r="89" spans="1:7" ht="43.2" x14ac:dyDescent="0.3">
+        <v>213</v>
+      </c>
+    </row>
+    <row r="89" spans="1:7" ht="45" x14ac:dyDescent="0.25">
       <c r="A89" s="4" t="s">
         <v>76</v>
       </c>
@@ -3539,13 +3525,13 @@
         <v>8</v>
       </c>
       <c r="F89" s="5" t="s">
-        <v>215</v>
+        <v>214</v>
       </c>
       <c r="G89" s="5" t="s">
-        <v>173</v>
-      </c>
-    </row>
-    <row r="90" spans="1:7" ht="43.2" x14ac:dyDescent="0.3">
+        <v>172</v>
+      </c>
+    </row>
+    <row r="90" spans="1:7" ht="45" x14ac:dyDescent="0.25">
       <c r="A90" s="4" t="s">
         <v>76</v>
       </c>
@@ -3559,16 +3545,16 @@
         <v>4</v>
       </c>
       <c r="E90" s="4" t="s">
-        <v>201</v>
+        <v>200</v>
       </c>
       <c r="F90" s="5" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c r="G90" s="5" t="s">
-        <v>217</v>
-      </c>
-    </row>
-    <row r="91" spans="1:7" ht="43.2" x14ac:dyDescent="0.3">
+        <v>216</v>
+      </c>
+    </row>
+    <row r="91" spans="1:7" ht="45" x14ac:dyDescent="0.25">
       <c r="A91" s="4" t="s">
         <v>76</v>
       </c>
@@ -3582,16 +3568,16 @@
         <v>4</v>
       </c>
       <c r="E91" s="4" t="s">
-        <v>201</v>
+        <v>200</v>
       </c>
       <c r="F91" s="5" t="s">
+        <v>215</v>
+      </c>
+      <c r="G91" s="5" t="s">
         <v>216</v>
       </c>
-      <c r="G91" s="5" t="s">
-        <v>217</v>
-      </c>
-    </row>
-    <row r="92" spans="1:7" ht="32.4" x14ac:dyDescent="0.3">
+    </row>
+    <row r="92" spans="1:7" ht="33.75" x14ac:dyDescent="0.25">
       <c r="A92" s="4" t="s">
         <v>76</v>
       </c>
@@ -3608,18 +3594,18 @@
         <v>78</v>
       </c>
       <c r="F92" s="5" t="s">
-        <v>147</v>
+        <v>146</v>
       </c>
       <c r="G92" s="5" t="s">
-        <v>220</v>
-      </c>
-    </row>
-    <row r="93" spans="1:7" ht="32.4" x14ac:dyDescent="0.3">
+        <v>219</v>
+      </c>
+    </row>
+    <row r="93" spans="1:7" ht="33.75" x14ac:dyDescent="0.25">
       <c r="A93" s="4" t="s">
         <v>76</v>
       </c>
       <c r="B93" s="4" t="s">
-        <v>117</v>
+        <v>116</v>
       </c>
       <c r="C93" s="4" t="s">
         <v>5</v>
@@ -3631,13 +3617,13 @@
         <v>78</v>
       </c>
       <c r="F93" s="5" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="G93" s="5" t="s">
-        <v>220</v>
-      </c>
-    </row>
-    <row r="94" spans="1:7" ht="21.6" x14ac:dyDescent="0.3">
+        <v>219</v>
+      </c>
+    </row>
+    <row r="94" spans="1:7" ht="22.5" x14ac:dyDescent="0.25">
       <c r="A94" s="4" t="s">
         <v>76</v>
       </c>
@@ -3654,15 +3640,15 @@
         <v>8</v>
       </c>
       <c r="F94" s="5" t="s">
-        <v>115</v>
+        <v>114</v>
       </c>
       <c r="G94" s="5" t="s">
-        <v>213</v>
-      </c>
-    </row>
-    <row r="95" spans="1:7" ht="54" x14ac:dyDescent="0.3">
+        <v>212</v>
+      </c>
+    </row>
+    <row r="95" spans="1:7" ht="56.25" x14ac:dyDescent="0.25">
       <c r="A95" s="4" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="B95" s="4" t="s">
         <v>10</v>
@@ -3677,15 +3663,15 @@
         <v>8</v>
       </c>
       <c r="F95" s="5" t="s">
-        <v>183</v>
+        <v>182</v>
       </c>
       <c r="G95" s="5" t="s">
-        <v>173</v>
-      </c>
-    </row>
-    <row r="96" spans="1:7" ht="43.2" x14ac:dyDescent="0.3">
+        <v>172</v>
+      </c>
+    </row>
+    <row r="96" spans="1:7" ht="45" x14ac:dyDescent="0.25">
       <c r="A96" s="4" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="B96" s="4" t="s">
         <v>23</v>
@@ -3700,15 +3686,15 @@
         <v>8</v>
       </c>
       <c r="F96" s="5" t="s">
-        <v>186</v>
+        <v>185</v>
       </c>
       <c r="G96" s="5" t="s">
-        <v>173</v>
-      </c>
-    </row>
-    <row r="97" spans="1:7" ht="64.8" x14ac:dyDescent="0.3">
+        <v>172</v>
+      </c>
+    </row>
+    <row r="97" spans="1:7" ht="78.75" x14ac:dyDescent="0.25">
       <c r="A97" s="4" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="B97" s="4" t="s">
         <v>24</v>
@@ -3723,18 +3709,18 @@
         <v>78</v>
       </c>
       <c r="F97" s="5" t="s">
+        <v>174</v>
+      </c>
+      <c r="G97" s="5" t="s">
         <v>175</v>
       </c>
-      <c r="G97" s="5" t="s">
-        <v>176</v>
-      </c>
-    </row>
-    <row r="98" spans="1:7" ht="21.6" x14ac:dyDescent="0.3">
+    </row>
+    <row r="98" spans="1:7" ht="22.5" x14ac:dyDescent="0.25">
       <c r="A98" s="4" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="B98" s="4" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="C98" s="4" t="s">
         <v>5</v>
@@ -3746,15 +3732,15 @@
         <v>79</v>
       </c>
       <c r="F98" s="5" t="s">
-        <v>178</v>
+        <v>177</v>
       </c>
       <c r="G98" s="5" t="s">
-        <v>188</v>
-      </c>
-    </row>
-    <row r="99" spans="1:7" x14ac:dyDescent="0.3">
+        <v>187</v>
+      </c>
+    </row>
+    <row r="99" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A99" s="4" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="B99" s="4" t="s">
         <v>26</v>
@@ -3769,15 +3755,15 @@
         <v>8</v>
       </c>
       <c r="F99" s="5" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
       <c r="G99" s="5" t="s">
-        <v>188</v>
-      </c>
-    </row>
-    <row r="100" spans="1:7" ht="21.6" x14ac:dyDescent="0.3">
+        <v>187</v>
+      </c>
+    </row>
+    <row r="100" spans="1:7" ht="22.5" x14ac:dyDescent="0.25">
       <c r="A100" s="4" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="B100" s="4" t="s">
         <v>27</v>
@@ -3792,15 +3778,15 @@
         <v>8</v>
       </c>
       <c r="F100" s="5" t="s">
-        <v>189</v>
+        <v>188</v>
       </c>
       <c r="G100" s="5" t="s">
-        <v>188</v>
-      </c>
-    </row>
-    <row r="101" spans="1:7" ht="64.8" x14ac:dyDescent="0.3">
+        <v>187</v>
+      </c>
+    </row>
+    <row r="101" spans="1:7" ht="67.5" x14ac:dyDescent="0.25">
       <c r="A101" s="4" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="B101" s="4" t="s">
         <v>28</v>
@@ -3815,15 +3801,15 @@
         <v>8</v>
       </c>
       <c r="F101" s="5" t="s">
-        <v>190</v>
+        <v>189</v>
       </c>
       <c r="G101" s="5" t="s">
-        <v>188</v>
-      </c>
-    </row>
-    <row r="102" spans="1:7" ht="64.8" x14ac:dyDescent="0.3">
+        <v>187</v>
+      </c>
+    </row>
+    <row r="102" spans="1:7" ht="67.5" x14ac:dyDescent="0.25">
       <c r="A102" s="4" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="B102" s="4" t="s">
         <v>29</v>
@@ -3838,15 +3824,15 @@
         <v>8</v>
       </c>
       <c r="F102" s="5" t="s">
-        <v>191</v>
+        <v>190</v>
       </c>
       <c r="G102" s="5" t="s">
-        <v>188</v>
-      </c>
-    </row>
-    <row r="103" spans="1:7" ht="64.8" x14ac:dyDescent="0.3">
+        <v>187</v>
+      </c>
+    </row>
+    <row r="103" spans="1:7" ht="67.5" x14ac:dyDescent="0.25">
       <c r="A103" s="4" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="B103" s="4" t="s">
         <v>30</v>
@@ -3861,15 +3847,15 @@
         <v>8</v>
       </c>
       <c r="F103" s="5" t="s">
-        <v>192</v>
+        <v>191</v>
       </c>
       <c r="G103" s="5" t="s">
-        <v>188</v>
-      </c>
-    </row>
-    <row r="104" spans="1:7" ht="43.2" x14ac:dyDescent="0.3">
+        <v>187</v>
+      </c>
+    </row>
+    <row r="104" spans="1:7" ht="45" x14ac:dyDescent="0.25">
       <c r="A104" s="4" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="B104" s="4" t="s">
         <v>80</v>
@@ -3884,15 +3870,15 @@
         <v>8</v>
       </c>
       <c r="F104" s="5" t="s">
-        <v>193</v>
+        <v>192</v>
       </c>
       <c r="G104" s="5" t="s">
-        <v>173</v>
-      </c>
-    </row>
-    <row r="105" spans="1:7" ht="64.8" x14ac:dyDescent="0.3">
+        <v>172</v>
+      </c>
+    </row>
+    <row r="105" spans="1:7" ht="67.5" x14ac:dyDescent="0.25">
       <c r="A105" s="4" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="B105" s="4" t="s">
         <v>13</v>
@@ -3907,15 +3893,15 @@
         <v>8</v>
       </c>
       <c r="F105" s="5" t="s">
-        <v>194</v>
+        <v>193</v>
       </c>
       <c r="G105" s="5" t="s">
-        <v>173</v>
-      </c>
-    </row>
-    <row r="106" spans="1:7" ht="32.4" x14ac:dyDescent="0.3">
+        <v>172</v>
+      </c>
+    </row>
+    <row r="106" spans="1:7" ht="45" x14ac:dyDescent="0.25">
       <c r="A106" s="4" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="B106" s="4" t="s">
         <v>31</v>
@@ -3930,18 +3916,18 @@
         <v>8</v>
       </c>
       <c r="F106" s="5" t="s">
-        <v>196</v>
+        <v>195</v>
       </c>
       <c r="G106" s="5" t="s">
-        <v>173</v>
-      </c>
-    </row>
-    <row r="107" spans="1:7" ht="54" x14ac:dyDescent="0.3">
+        <v>172</v>
+      </c>
+    </row>
+    <row r="107" spans="1:7" ht="56.25" x14ac:dyDescent="0.25">
       <c r="A107" s="4" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="B107" s="4" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="C107" s="4" t="s">
         <v>5</v>
@@ -3953,15 +3939,15 @@
         <v>8</v>
       </c>
       <c r="F107" s="5" t="s">
-        <v>197</v>
+        <v>196</v>
       </c>
       <c r="G107" s="5" t="s">
-        <v>173</v>
-      </c>
-    </row>
-    <row r="108" spans="1:7" ht="43.2" x14ac:dyDescent="0.3">
+        <v>172</v>
+      </c>
+    </row>
+    <row r="108" spans="1:7" ht="56.25" x14ac:dyDescent="0.25">
       <c r="A108" s="4" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="B108" s="4" t="s">
         <v>32</v>
@@ -3976,15 +3962,15 @@
         <v>77</v>
       </c>
       <c r="F108" s="5" t="s">
+        <v>197</v>
+      </c>
+      <c r="G108" s="5" t="s">
         <v>198</v>
       </c>
-      <c r="G108" s="5" t="s">
-        <v>199</v>
-      </c>
-    </row>
-    <row r="109" spans="1:7" ht="54" x14ac:dyDescent="0.3">
+    </row>
+    <row r="109" spans="1:7" ht="56.25" x14ac:dyDescent="0.25">
       <c r="A109" s="4" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="B109" s="4" t="s">
         <v>33</v>
@@ -3999,15 +3985,15 @@
         <v>77</v>
       </c>
       <c r="F109" s="5" t="s">
-        <v>200</v>
+        <v>199</v>
       </c>
       <c r="G109" s="5" t="s">
-        <v>170</v>
-      </c>
-    </row>
-    <row r="110" spans="1:7" ht="21.6" x14ac:dyDescent="0.3">
+        <v>169</v>
+      </c>
+    </row>
+    <row r="110" spans="1:7" ht="33.75" x14ac:dyDescent="0.25">
       <c r="A110" s="4" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="B110" s="4" t="s">
         <v>34</v>
@@ -4019,18 +4005,18 @@
         <v>4</v>
       </c>
       <c r="E110" s="4" t="s">
+        <v>200</v>
+      </c>
+      <c r="F110" s="5" t="s">
         <v>201</v>
       </c>
-      <c r="F110" s="5" t="s">
+      <c r="G110" s="5" t="s">
         <v>202</v>
       </c>
-      <c r="G110" s="5" t="s">
-        <v>203</v>
-      </c>
-    </row>
-    <row r="111" spans="1:7" ht="21.6" x14ac:dyDescent="0.3">
+    </row>
+    <row r="111" spans="1:7" ht="22.5" x14ac:dyDescent="0.25">
       <c r="A111" s="4" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="B111" s="4" t="s">
         <v>35</v>
@@ -4042,18 +4028,18 @@
         <v>5</v>
       </c>
       <c r="E111" s="4" t="s">
-        <v>201</v>
+        <v>200</v>
       </c>
       <c r="F111" s="5" t="s">
+        <v>203</v>
+      </c>
+      <c r="G111" s="5" t="s">
         <v>204</v>
       </c>
-      <c r="G111" s="5" t="s">
-        <v>205</v>
-      </c>
-    </row>
-    <row r="112" spans="1:7" ht="32.4" x14ac:dyDescent="0.3">
+    </row>
+    <row r="112" spans="1:7" ht="33.75" x14ac:dyDescent="0.25">
       <c r="A112" s="4" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="B112" s="4" t="s">
         <v>36</v>
@@ -4065,18 +4051,18 @@
         <v>4</v>
       </c>
       <c r="E112" s="4" t="s">
-        <v>201</v>
+        <v>200</v>
       </c>
       <c r="F112" s="5" t="s">
+        <v>205</v>
+      </c>
+      <c r="G112" s="5" t="s">
         <v>206</v>
       </c>
-      <c r="G112" s="5" t="s">
-        <v>207</v>
-      </c>
-    </row>
-    <row r="113" spans="1:7" ht="32.4" x14ac:dyDescent="0.3">
+    </row>
+    <row r="113" spans="1:7" ht="33.75" x14ac:dyDescent="0.25">
       <c r="A113" s="4" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="B113" s="4" t="s">
         <v>38</v>
@@ -4091,15 +4077,15 @@
         <v>9</v>
       </c>
       <c r="F113" s="5" t="s">
-        <v>114</v>
+        <v>113</v>
       </c>
       <c r="G113" s="5" t="s">
-        <v>209</v>
-      </c>
-    </row>
-    <row r="114" spans="1:7" ht="43.2" x14ac:dyDescent="0.3">
+        <v>208</v>
+      </c>
+    </row>
+    <row r="114" spans="1:7" ht="45" x14ac:dyDescent="0.25">
       <c r="A114" s="4" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="B114" s="4" t="s">
         <v>39</v>
@@ -4114,15 +4100,15 @@
         <v>9</v>
       </c>
       <c r="F114" s="5" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="G114" s="5" t="s">
-        <v>209</v>
-      </c>
-    </row>
-    <row r="115" spans="1:7" ht="32.4" x14ac:dyDescent="0.3">
+        <v>208</v>
+      </c>
+    </row>
+    <row r="115" spans="1:7" ht="33.75" x14ac:dyDescent="0.25">
       <c r="A115" s="4" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="B115" s="4" t="s">
         <v>40</v>
@@ -4137,15 +4123,15 @@
         <v>9</v>
       </c>
       <c r="F115" s="5" t="s">
-        <v>113</v>
+        <v>112</v>
       </c>
       <c r="G115" s="5" t="s">
-        <v>209</v>
-      </c>
-    </row>
-    <row r="116" spans="1:7" ht="32.4" x14ac:dyDescent="0.3">
+        <v>208</v>
+      </c>
+    </row>
+    <row r="116" spans="1:7" ht="33.75" x14ac:dyDescent="0.25">
       <c r="A116" s="4" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="B116" s="4" t="s">
         <v>16</v>
@@ -4160,15 +4146,15 @@
         <v>9</v>
       </c>
       <c r="F116" s="5" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="G116" s="5" t="s">
-        <v>209</v>
-      </c>
-    </row>
-    <row r="117" spans="1:7" ht="54" x14ac:dyDescent="0.3">
+        <v>208</v>
+      </c>
+    </row>
+    <row r="117" spans="1:7" ht="56.25" x14ac:dyDescent="0.25">
       <c r="A117" s="4" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="B117" s="4" t="s">
         <v>17</v>
@@ -4183,15 +4169,15 @@
         <v>9</v>
       </c>
       <c r="F117" s="5" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="G117" s="5" t="s">
-        <v>209</v>
-      </c>
-    </row>
-    <row r="118" spans="1:7" ht="32.4" x14ac:dyDescent="0.3">
+        <v>208</v>
+      </c>
+    </row>
+    <row r="118" spans="1:7" ht="33.75" x14ac:dyDescent="0.25">
       <c r="A118" s="4" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="B118" s="4" t="s">
         <v>18</v>
@@ -4206,15 +4192,15 @@
         <v>9</v>
       </c>
       <c r="F118" s="5" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="G118" s="5" t="s">
-        <v>209</v>
-      </c>
-    </row>
-    <row r="119" spans="1:7" ht="43.2" x14ac:dyDescent="0.3">
+        <v>208</v>
+      </c>
+    </row>
+    <row r="119" spans="1:7" ht="45" x14ac:dyDescent="0.25">
       <c r="A119" s="4" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="B119" s="4" t="s">
         <v>19</v>
@@ -4229,15 +4215,15 @@
         <v>9</v>
       </c>
       <c r="F119" s="5" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="G119" s="5" t="s">
-        <v>209</v>
-      </c>
-    </row>
-    <row r="120" spans="1:7" ht="54" x14ac:dyDescent="0.3">
+        <v>208</v>
+      </c>
+    </row>
+    <row r="120" spans="1:7" ht="56.25" x14ac:dyDescent="0.25">
       <c r="A120" s="4" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="B120" s="4" t="s">
         <v>20</v>
@@ -4252,15 +4238,15 @@
         <v>9</v>
       </c>
       <c r="F120" s="5" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="G120" s="5" t="s">
-        <v>209</v>
-      </c>
-    </row>
-    <row r="121" spans="1:7" ht="32.4" x14ac:dyDescent="0.3">
+        <v>208</v>
+      </c>
+    </row>
+    <row r="121" spans="1:7" ht="45" x14ac:dyDescent="0.25">
       <c r="A121" s="4" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="B121" s="4" t="s">
         <v>21</v>
@@ -4275,18 +4261,18 @@
         <v>9</v>
       </c>
       <c r="F121" s="5" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="G121" s="5" t="s">
-        <v>209</v>
-      </c>
-    </row>
-    <row r="122" spans="1:7" ht="32.4" x14ac:dyDescent="0.3">
+        <v>208</v>
+      </c>
+    </row>
+    <row r="122" spans="1:7" ht="45" x14ac:dyDescent="0.25">
       <c r="A122" s="4" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="B122" s="4" t="s">
-        <v>221</v>
+        <v>220</v>
       </c>
       <c r="C122" s="4" t="s">
         <v>5</v>
@@ -4298,15 +4284,15 @@
         <v>9</v>
       </c>
       <c r="F122" s="5" t="s">
-        <v>211</v>
+        <v>210</v>
       </c>
       <c r="G122" s="5" t="s">
-        <v>209</v>
-      </c>
-    </row>
-    <row r="123" spans="1:7" ht="54" x14ac:dyDescent="0.3">
+        <v>208</v>
+      </c>
+    </row>
+    <row r="123" spans="1:7" ht="67.5" x14ac:dyDescent="0.25">
       <c r="A123" s="4" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="B123" s="4" t="s">
         <v>41</v>
@@ -4321,15 +4307,15 @@
         <v>9</v>
       </c>
       <c r="F123" s="5" t="s">
-        <v>212</v>
+        <v>211</v>
       </c>
       <c r="G123" s="5" t="s">
-        <v>209</v>
-      </c>
-    </row>
-    <row r="124" spans="1:7" ht="32.4" x14ac:dyDescent="0.3">
+        <v>208</v>
+      </c>
+    </row>
+    <row r="124" spans="1:7" ht="33.75" x14ac:dyDescent="0.25">
       <c r="A124" s="4" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="B124" s="4" t="s">
         <v>42</v>
@@ -4344,15 +4330,15 @@
         <v>9</v>
       </c>
       <c r="F124" s="5" t="s">
-        <v>120</v>
+        <v>119</v>
       </c>
       <c r="G124" s="5" t="s">
-        <v>209</v>
-      </c>
-    </row>
-    <row r="125" spans="1:7" ht="32.4" x14ac:dyDescent="0.3">
+        <v>208</v>
+      </c>
+    </row>
+    <row r="125" spans="1:7" ht="33.75" x14ac:dyDescent="0.25">
       <c r="A125" s="4" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="B125" s="4" t="s">
         <v>43</v>
@@ -4367,15 +4353,15 @@
         <v>9</v>
       </c>
       <c r="F125" s="5" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
       <c r="G125" s="5" t="s">
-        <v>209</v>
-      </c>
-    </row>
-    <row r="126" spans="1:7" ht="32.4" x14ac:dyDescent="0.3">
+        <v>208</v>
+      </c>
+    </row>
+    <row r="126" spans="1:7" ht="45" x14ac:dyDescent="0.25">
       <c r="A126" s="4" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="B126" s="4" t="s">
         <v>44</v>
@@ -4390,15 +4376,15 @@
         <v>9</v>
       </c>
       <c r="F126" s="5" t="s">
-        <v>121</v>
+        <v>120</v>
       </c>
       <c r="G126" s="5" t="s">
-        <v>209</v>
-      </c>
-    </row>
-    <row r="127" spans="1:7" ht="32.4" x14ac:dyDescent="0.3">
+        <v>208</v>
+      </c>
+    </row>
+    <row r="127" spans="1:7" ht="33.75" x14ac:dyDescent="0.25">
       <c r="A127" s="4" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="B127" s="4" t="s">
         <v>45</v>
@@ -4413,15 +4399,15 @@
         <v>9</v>
       </c>
       <c r="F127" s="5" t="s">
-        <v>122</v>
+        <v>121</v>
       </c>
       <c r="G127" s="5" t="s">
-        <v>209</v>
-      </c>
-    </row>
-    <row r="128" spans="1:7" ht="32.4" x14ac:dyDescent="0.3">
+        <v>208</v>
+      </c>
+    </row>
+    <row r="128" spans="1:7" ht="33.75" x14ac:dyDescent="0.25">
       <c r="A128" s="4" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="B128" s="4" t="s">
         <v>46</v>
@@ -4436,15 +4422,15 @@
         <v>9</v>
       </c>
       <c r="F128" s="5" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="G128" s="5" t="s">
-        <v>209</v>
-      </c>
-    </row>
-    <row r="129" spans="1:7" ht="32.4" x14ac:dyDescent="0.3">
+        <v>208</v>
+      </c>
+    </row>
+    <row r="129" spans="1:7" ht="33.75" x14ac:dyDescent="0.25">
       <c r="A129" s="4" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="B129" s="4" t="s">
         <v>47</v>
@@ -4459,15 +4445,15 @@
         <v>9</v>
       </c>
       <c r="F129" s="5" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="G129" s="5" t="s">
-        <v>209</v>
-      </c>
-    </row>
-    <row r="130" spans="1:7" ht="32.4" x14ac:dyDescent="0.3">
+        <v>208</v>
+      </c>
+    </row>
+    <row r="130" spans="1:7" ht="33.75" x14ac:dyDescent="0.25">
       <c r="A130" s="4" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="B130" s="4" t="s">
         <v>48</v>
@@ -4482,15 +4468,15 @@
         <v>9</v>
       </c>
       <c r="F130" s="5" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="G130" s="5" t="s">
-        <v>209</v>
-      </c>
-    </row>
-    <row r="131" spans="1:7" ht="32.4" x14ac:dyDescent="0.3">
+        <v>208</v>
+      </c>
+    </row>
+    <row r="131" spans="1:7" ht="33.75" x14ac:dyDescent="0.25">
       <c r="A131" s="4" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="B131" s="4" t="s">
         <v>49</v>
@@ -4505,15 +4491,15 @@
         <v>9</v>
       </c>
       <c r="F131" s="5" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="G131" s="5" t="s">
-        <v>209</v>
-      </c>
-    </row>
-    <row r="132" spans="1:7" ht="32.4" x14ac:dyDescent="0.3">
+        <v>208</v>
+      </c>
+    </row>
+    <row r="132" spans="1:7" ht="33.75" x14ac:dyDescent="0.25">
       <c r="A132" s="4" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="B132" s="4" t="s">
         <v>50</v>
@@ -4528,15 +4514,15 @@
         <v>9</v>
       </c>
       <c r="F132" s="5" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="G132" s="5" t="s">
-        <v>209</v>
-      </c>
-    </row>
-    <row r="133" spans="1:7" ht="32.4" x14ac:dyDescent="0.3">
+        <v>208</v>
+      </c>
+    </row>
+    <row r="133" spans="1:7" ht="33.75" x14ac:dyDescent="0.25">
       <c r="A133" s="4" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="B133" s="4" t="s">
         <v>51</v>
@@ -4551,15 +4537,15 @@
         <v>9</v>
       </c>
       <c r="F133" s="5" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
       <c r="G133" s="5" t="s">
-        <v>209</v>
-      </c>
-    </row>
-    <row r="134" spans="1:7" ht="32.4" x14ac:dyDescent="0.3">
+        <v>208</v>
+      </c>
+    </row>
+    <row r="134" spans="1:7" ht="33.75" x14ac:dyDescent="0.25">
       <c r="A134" s="4" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="B134" s="4" t="s">
         <v>52</v>
@@ -4574,15 +4560,15 @@
         <v>9</v>
       </c>
       <c r="F134" s="5" t="s">
-        <v>128</v>
+        <v>127</v>
       </c>
       <c r="G134" s="5" t="s">
-        <v>209</v>
-      </c>
-    </row>
-    <row r="135" spans="1:7" ht="32.4" x14ac:dyDescent="0.3">
+        <v>208</v>
+      </c>
+    </row>
+    <row r="135" spans="1:7" ht="33.75" x14ac:dyDescent="0.25">
       <c r="A135" s="4" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="B135" s="4" t="s">
         <v>53</v>
@@ -4597,15 +4583,15 @@
         <v>9</v>
       </c>
       <c r="F135" s="5" t="s">
-        <v>129</v>
+        <v>128</v>
       </c>
       <c r="G135" s="5" t="s">
-        <v>209</v>
-      </c>
-    </row>
-    <row r="136" spans="1:7" ht="32.4" x14ac:dyDescent="0.3">
+        <v>208</v>
+      </c>
+    </row>
+    <row r="136" spans="1:7" ht="33.75" x14ac:dyDescent="0.25">
       <c r="A136" s="4" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="B136" s="4" t="s">
         <v>54</v>
@@ -4620,15 +4606,15 @@
         <v>9</v>
       </c>
       <c r="F136" s="5" t="s">
-        <v>130</v>
+        <v>129</v>
       </c>
       <c r="G136" s="5" t="s">
-        <v>209</v>
-      </c>
-    </row>
-    <row r="137" spans="1:7" ht="32.4" x14ac:dyDescent="0.3">
+        <v>208</v>
+      </c>
+    </row>
+    <row r="137" spans="1:7" ht="33.75" x14ac:dyDescent="0.25">
       <c r="A137" s="4" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="B137" s="4" t="s">
         <v>55</v>
@@ -4643,15 +4629,15 @@
         <v>9</v>
       </c>
       <c r="F137" s="5" t="s">
-        <v>131</v>
+        <v>130</v>
       </c>
       <c r="G137" s="5" t="s">
-        <v>209</v>
-      </c>
-    </row>
-    <row r="138" spans="1:7" ht="32.4" x14ac:dyDescent="0.3">
+        <v>208</v>
+      </c>
+    </row>
+    <row r="138" spans="1:7" ht="33.75" x14ac:dyDescent="0.25">
       <c r="A138" s="4" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="B138" s="4" t="s">
         <v>56</v>
@@ -4666,15 +4652,15 @@
         <v>9</v>
       </c>
       <c r="F138" s="5" t="s">
-        <v>132</v>
+        <v>131</v>
       </c>
       <c r="G138" s="5" t="s">
-        <v>209</v>
-      </c>
-    </row>
-    <row r="139" spans="1:7" ht="32.4" x14ac:dyDescent="0.3">
+        <v>208</v>
+      </c>
+    </row>
+    <row r="139" spans="1:7" ht="33.75" x14ac:dyDescent="0.25">
       <c r="A139" s="4" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="B139" s="4" t="s">
         <v>57</v>
@@ -4689,38 +4675,38 @@
         <v>9</v>
       </c>
       <c r="F139" s="5" t="s">
+        <v>132</v>
+      </c>
+      <c r="G139" s="5" t="s">
+        <v>208</v>
+      </c>
+    </row>
+    <row r="140" spans="1:7" ht="33.75" x14ac:dyDescent="0.25">
+      <c r="A140" s="4" t="s">
+        <v>81</v>
+      </c>
+      <c r="B140" s="4" t="s">
+        <v>58</v>
+      </c>
+      <c r="C140" s="4" t="s">
+        <v>5</v>
+      </c>
+      <c r="D140" s="4" t="s">
+        <v>4</v>
+      </c>
+      <c r="E140" s="4" t="s">
+        <v>9</v>
+      </c>
+      <c r="F140" s="5" t="s">
         <v>133</v>
       </c>
-      <c r="G139" s="5" t="s">
-        <v>209</v>
-      </c>
-    </row>
-    <row r="140" spans="1:7" ht="32.4" x14ac:dyDescent="0.3">
-      <c r="A140" s="4" t="s">
-        <v>82</v>
-      </c>
-      <c r="B140" s="4" t="s">
+      <c r="G140" s="5" t="s">
+        <v>208</v>
+      </c>
+    </row>
+    <row r="141" spans="1:7" ht="33.75" x14ac:dyDescent="0.25">
+      <c r="A141" s="4" t="s">
         <v>81</v>
-      </c>
-      <c r="C140" s="4" t="s">
-        <v>5</v>
-      </c>
-      <c r="D140" s="4" t="s">
-        <v>4</v>
-      </c>
-      <c r="E140" s="4" t="s">
-        <v>9</v>
-      </c>
-      <c r="F140" s="5" t="s">
-        <v>134</v>
-      </c>
-      <c r="G140" s="5" t="s">
-        <v>209</v>
-      </c>
-    </row>
-    <row r="141" spans="1:7" ht="32.4" x14ac:dyDescent="0.3">
-      <c r="A141" s="4" t="s">
-        <v>82</v>
       </c>
       <c r="B141" s="4" t="s">
         <v>59</v>
@@ -4735,15 +4721,15 @@
         <v>9</v>
       </c>
       <c r="F141" s="5" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="G141" s="5" t="s">
-        <v>209</v>
-      </c>
-    </row>
-    <row r="142" spans="1:7" ht="32.4" x14ac:dyDescent="0.3">
+        <v>208</v>
+      </c>
+    </row>
+    <row r="142" spans="1:7" ht="33.75" x14ac:dyDescent="0.25">
       <c r="A142" s="4" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="B142" s="4" t="s">
         <v>60</v>
@@ -4758,15 +4744,15 @@
         <v>9</v>
       </c>
       <c r="F142" s="5" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
       <c r="G142" s="5" t="s">
-        <v>209</v>
-      </c>
-    </row>
-    <row r="143" spans="1:7" ht="32.4" x14ac:dyDescent="0.3">
+        <v>208</v>
+      </c>
+    </row>
+    <row r="143" spans="1:7" ht="33.75" x14ac:dyDescent="0.25">
       <c r="A143" s="4" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="B143" s="4" t="s">
         <v>61</v>
@@ -4781,15 +4767,15 @@
         <v>9</v>
       </c>
       <c r="F143" s="5" t="s">
-        <v>137</v>
+        <v>136</v>
       </c>
       <c r="G143" s="5" t="s">
-        <v>209</v>
-      </c>
-    </row>
-    <row r="144" spans="1:7" ht="32.4" x14ac:dyDescent="0.3">
+        <v>208</v>
+      </c>
+    </row>
+    <row r="144" spans="1:7" ht="33.75" x14ac:dyDescent="0.25">
       <c r="A144" s="4" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="B144" s="4" t="s">
         <v>62</v>
@@ -4804,15 +4790,15 @@
         <v>9</v>
       </c>
       <c r="F144" s="5" t="s">
-        <v>139</v>
+        <v>138</v>
       </c>
       <c r="G144" s="5" t="s">
-        <v>209</v>
-      </c>
-    </row>
-    <row r="145" spans="1:7" ht="32.4" x14ac:dyDescent="0.3">
+        <v>208</v>
+      </c>
+    </row>
+    <row r="145" spans="1:7" ht="33.75" x14ac:dyDescent="0.25">
       <c r="A145" s="4" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="B145" s="4" t="s">
         <v>63</v>
@@ -4827,15 +4813,15 @@
         <v>9</v>
       </c>
       <c r="F145" s="5" t="s">
-        <v>138</v>
+        <v>137</v>
       </c>
       <c r="G145" s="5" t="s">
-        <v>209</v>
-      </c>
-    </row>
-    <row r="146" spans="1:7" ht="32.4" x14ac:dyDescent="0.3">
+        <v>208</v>
+      </c>
+    </row>
+    <row r="146" spans="1:7" ht="33.75" x14ac:dyDescent="0.25">
       <c r="A146" s="4" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="B146" s="4" t="s">
         <v>64</v>
@@ -4850,15 +4836,15 @@
         <v>9</v>
       </c>
       <c r="F146" s="5" t="s">
-        <v>140</v>
+        <v>139</v>
       </c>
       <c r="G146" s="5" t="s">
-        <v>209</v>
-      </c>
-    </row>
-    <row r="147" spans="1:7" ht="32.4" x14ac:dyDescent="0.3">
+        <v>208</v>
+      </c>
+    </row>
+    <row r="147" spans="1:7" ht="33.75" x14ac:dyDescent="0.25">
       <c r="A147" s="4" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="B147" s="4" t="s">
         <v>65</v>
@@ -4873,15 +4859,15 @@
         <v>9</v>
       </c>
       <c r="F147" s="5" t="s">
-        <v>141</v>
+        <v>140</v>
       </c>
       <c r="G147" s="5" t="s">
-        <v>209</v>
-      </c>
-    </row>
-    <row r="148" spans="1:7" ht="32.4" x14ac:dyDescent="0.3">
+        <v>208</v>
+      </c>
+    </row>
+    <row r="148" spans="1:7" ht="33.75" x14ac:dyDescent="0.25">
       <c r="A148" s="4" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="B148" s="4" t="s">
         <v>66</v>
@@ -4896,15 +4882,15 @@
         <v>9</v>
       </c>
       <c r="F148" s="5" t="s">
-        <v>142</v>
+        <v>141</v>
       </c>
       <c r="G148" s="5" t="s">
-        <v>209</v>
-      </c>
-    </row>
-    <row r="149" spans="1:7" ht="32.4" x14ac:dyDescent="0.3">
+        <v>208</v>
+      </c>
+    </row>
+    <row r="149" spans="1:7" ht="33.75" x14ac:dyDescent="0.25">
       <c r="A149" s="4" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="B149" s="4" t="s">
         <v>67</v>
@@ -4919,15 +4905,15 @@
         <v>9</v>
       </c>
       <c r="F149" s="5" t="s">
-        <v>143</v>
+        <v>142</v>
       </c>
       <c r="G149" s="5" t="s">
-        <v>209</v>
-      </c>
-    </row>
-    <row r="150" spans="1:7" ht="32.4" x14ac:dyDescent="0.3">
+        <v>208</v>
+      </c>
+    </row>
+    <row r="150" spans="1:7" ht="33.75" x14ac:dyDescent="0.25">
       <c r="A150" s="4" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="B150" s="4" t="s">
         <v>68</v>
@@ -4942,15 +4928,15 @@
         <v>9</v>
       </c>
       <c r="F150" s="5" t="s">
-        <v>144</v>
+        <v>143</v>
       </c>
       <c r="G150" s="5" t="s">
-        <v>209</v>
-      </c>
-    </row>
-    <row r="151" spans="1:7" ht="32.4" x14ac:dyDescent="0.3">
+        <v>208</v>
+      </c>
+    </row>
+    <row r="151" spans="1:7" ht="33.75" x14ac:dyDescent="0.25">
       <c r="A151" s="4" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="B151" s="4" t="s">
         <v>69</v>
@@ -4965,15 +4951,15 @@
         <v>9</v>
       </c>
       <c r="F151" s="5" t="s">
-        <v>145</v>
+        <v>144</v>
       </c>
       <c r="G151" s="5" t="s">
-        <v>209</v>
-      </c>
-    </row>
-    <row r="152" spans="1:7" ht="43.2" x14ac:dyDescent="0.3">
+        <v>208</v>
+      </c>
+    </row>
+    <row r="152" spans="1:7" ht="45" x14ac:dyDescent="0.25">
       <c r="A152" s="4" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="B152" s="4" t="s">
         <v>70</v>
@@ -4988,15 +4974,15 @@
         <v>8</v>
       </c>
       <c r="F152" s="5" t="s">
-        <v>215</v>
+        <v>214</v>
       </c>
       <c r="G152" s="5" t="s">
-        <v>173</v>
-      </c>
-    </row>
-    <row r="153" spans="1:7" ht="43.2" x14ac:dyDescent="0.3">
+        <v>172</v>
+      </c>
+    </row>
+    <row r="153" spans="1:7" ht="45" x14ac:dyDescent="0.25">
       <c r="A153" s="4" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="B153" s="4" t="s">
         <v>71</v>
@@ -5008,18 +4994,18 @@
         <v>4</v>
       </c>
       <c r="E153" s="4" t="s">
-        <v>201</v>
+        <v>200</v>
       </c>
       <c r="F153" s="5" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c r="G153" s="5" t="s">
-        <v>217</v>
-      </c>
-    </row>
-    <row r="154" spans="1:7" ht="43.2" x14ac:dyDescent="0.3">
+        <v>216</v>
+      </c>
+    </row>
+    <row r="154" spans="1:7" ht="45" x14ac:dyDescent="0.25">
       <c r="A154" s="4" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="B154" s="4" t="s">
         <v>72</v>
@@ -5031,18 +5017,18 @@
         <v>4</v>
       </c>
       <c r="E154" s="4" t="s">
-        <v>201</v>
+        <v>200</v>
       </c>
       <c r="F154" s="5" t="s">
+        <v>215</v>
+      </c>
+      <c r="G154" s="5" t="s">
         <v>216</v>
       </c>
-      <c r="G154" s="5" t="s">
-        <v>217</v>
-      </c>
-    </row>
-    <row r="155" spans="1:7" ht="32.4" x14ac:dyDescent="0.3">
+    </row>
+    <row r="155" spans="1:7" ht="33.75" x14ac:dyDescent="0.25">
       <c r="A155" s="4" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="B155" s="4" t="s">
         <v>73</v>
@@ -5057,18 +5043,18 @@
         <v>78</v>
       </c>
       <c r="F155" s="5" t="s">
-        <v>147</v>
+        <v>146</v>
       </c>
       <c r="G155" s="5" t="s">
-        <v>220</v>
-      </c>
-    </row>
-    <row r="156" spans="1:7" ht="32.4" x14ac:dyDescent="0.3">
+        <v>219</v>
+      </c>
+    </row>
+    <row r="156" spans="1:7" ht="33.75" x14ac:dyDescent="0.25">
       <c r="A156" s="4" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="B156" s="4" t="s">
-        <v>117</v>
+        <v>116</v>
       </c>
       <c r="C156" s="4" t="s">
         <v>5</v>
@@ -5080,15 +5066,15 @@
         <v>78</v>
       </c>
       <c r="F156" s="5" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="G156" s="5" t="s">
-        <v>220</v>
-      </c>
-    </row>
-    <row r="157" spans="1:7" ht="21.6" x14ac:dyDescent="0.3">
+        <v>219</v>
+      </c>
+    </row>
+    <row r="157" spans="1:7" ht="22.5" x14ac:dyDescent="0.25">
       <c r="A157" s="4" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="B157" s="4" t="s">
         <v>74</v>
@@ -5103,15 +5089,15 @@
         <v>8</v>
       </c>
       <c r="F157" s="5" t="s">
-        <v>115</v>
+        <v>114</v>
       </c>
       <c r="G157" s="5" t="s">
-        <v>213</v>
-      </c>
-    </row>
-    <row r="158" spans="1:7" x14ac:dyDescent="0.3">
+        <v>212</v>
+      </c>
+    </row>
+    <row r="158" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A158" s="4" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="B158" s="4" t="s">
         <v>13</v>
@@ -5126,18 +5112,18 @@
         <v>8</v>
       </c>
       <c r="F158" s="5" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="G158" s="6" t="s">
-        <v>170</v>
-      </c>
-    </row>
-    <row r="159" spans="1:7" x14ac:dyDescent="0.3">
+        <v>169</v>
+      </c>
+    </row>
+    <row r="159" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A159" s="4" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="B159" s="4" t="s">
-        <v>165</v>
+        <v>164</v>
       </c>
       <c r="C159" s="4" t="s">
         <v>4</v>
@@ -5149,15 +5135,15 @@
         <v>9</v>
       </c>
       <c r="F159" s="5" t="s">
-        <v>167</v>
+        <v>166</v>
       </c>
       <c r="G159" s="6" t="s">
-        <v>170</v>
-      </c>
-    </row>
-    <row r="160" spans="1:7" ht="32.4" x14ac:dyDescent="0.3">
+        <v>169</v>
+      </c>
+    </row>
+    <row r="160" spans="1:7" ht="33.75" x14ac:dyDescent="0.25">
       <c r="A160" s="4" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="B160" s="4" t="s">
         <v>16</v>
@@ -5172,15 +5158,15 @@
         <v>9</v>
       </c>
       <c r="F160" s="5" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="G160" s="5" t="s">
-        <v>209</v>
-      </c>
-    </row>
-    <row r="161" spans="1:7" ht="54" x14ac:dyDescent="0.3">
+        <v>208</v>
+      </c>
+    </row>
+    <row r="161" spans="1:7" ht="56.25" x14ac:dyDescent="0.25">
       <c r="A161" s="4" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="B161" s="4" t="s">
         <v>17</v>
@@ -5195,15 +5181,15 @@
         <v>9</v>
       </c>
       <c r="F161" s="5" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="G161" s="5" t="s">
-        <v>209</v>
-      </c>
-    </row>
-    <row r="162" spans="1:7" ht="32.4" x14ac:dyDescent="0.3">
+        <v>208</v>
+      </c>
+    </row>
+    <row r="162" spans="1:7" ht="33.75" x14ac:dyDescent="0.25">
       <c r="A162" s="4" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="B162" s="4" t="s">
         <v>18</v>
@@ -5218,15 +5204,15 @@
         <v>9</v>
       </c>
       <c r="F162" s="5" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="G162" s="5" t="s">
-        <v>209</v>
-      </c>
-    </row>
-    <row r="163" spans="1:7" ht="43.2" x14ac:dyDescent="0.3">
+        <v>208</v>
+      </c>
+    </row>
+    <row r="163" spans="1:7" ht="45" x14ac:dyDescent="0.25">
       <c r="A163" s="4" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="B163" s="4" t="s">
         <v>19</v>
@@ -5241,15 +5227,15 @@
         <v>9</v>
       </c>
       <c r="F163" s="5" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="G163" s="5" t="s">
-        <v>209</v>
-      </c>
-    </row>
-    <row r="164" spans="1:7" ht="54" x14ac:dyDescent="0.3">
+        <v>208</v>
+      </c>
+    </row>
+    <row r="164" spans="1:7" ht="56.25" x14ac:dyDescent="0.25">
       <c r="A164" s="4" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="B164" s="4" t="s">
         <v>20</v>
@@ -5264,15 +5250,15 @@
         <v>9</v>
       </c>
       <c r="F164" s="5" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="G164" s="5" t="s">
-        <v>209</v>
-      </c>
-    </row>
-    <row r="165" spans="1:7" ht="32.4" x14ac:dyDescent="0.3">
+        <v>208</v>
+      </c>
+    </row>
+    <row r="165" spans="1:7" ht="45" x14ac:dyDescent="0.25">
       <c r="A165" s="4" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="B165" s="4" t="s">
         <v>21</v>
@@ -5287,18 +5273,18 @@
         <v>9</v>
       </c>
       <c r="F165" s="5" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="G165" s="5" t="s">
-        <v>209</v>
-      </c>
-    </row>
-    <row r="166" spans="1:7" ht="32.4" x14ac:dyDescent="0.3">
+        <v>208</v>
+      </c>
+    </row>
+    <row r="166" spans="1:7" ht="45" x14ac:dyDescent="0.25">
       <c r="A166" s="4" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="B166" s="4" t="s">
-        <v>221</v>
+        <v>220</v>
       </c>
       <c r="C166" s="4" t="s">
         <v>5</v>
@@ -5310,15 +5296,15 @@
         <v>9</v>
       </c>
       <c r="F166" s="5" t="s">
-        <v>211</v>
+        <v>210</v>
       </c>
       <c r="G166" s="5" t="s">
-        <v>209</v>
-      </c>
-    </row>
-    <row r="167" spans="1:7" ht="54" x14ac:dyDescent="0.3">
+        <v>208</v>
+      </c>
+    </row>
+    <row r="167" spans="1:7" ht="67.5" x14ac:dyDescent="0.25">
       <c r="A167" s="4" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="B167" s="4" t="s">
         <v>41</v>
@@ -5333,15 +5319,15 @@
         <v>9</v>
       </c>
       <c r="F167" s="5" t="s">
-        <v>212</v>
+        <v>211</v>
       </c>
       <c r="G167" s="5" t="s">
-        <v>209</v>
-      </c>
-    </row>
-    <row r="168" spans="1:7" ht="54" x14ac:dyDescent="0.3">
+        <v>208</v>
+      </c>
+    </row>
+    <row r="168" spans="1:7" ht="56.25" x14ac:dyDescent="0.25">
       <c r="A168" s="4" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="B168" s="4" t="s">
         <v>10</v>
@@ -5356,15 +5342,15 @@
         <v>8</v>
       </c>
       <c r="F168" s="5" t="s">
-        <v>183</v>
+        <v>182</v>
       </c>
       <c r="G168" s="5" t="s">
-        <v>173</v>
-      </c>
-    </row>
-    <row r="169" spans="1:7" ht="21.6" x14ac:dyDescent="0.3">
+        <v>172</v>
+      </c>
+    </row>
+    <row r="169" spans="1:7" ht="22.5" x14ac:dyDescent="0.25">
       <c r="A169" s="4" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="B169" s="4" t="s">
         <v>11</v>
@@ -5379,15 +5365,15 @@
         <v>78</v>
       </c>
       <c r="F169" s="5" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="G169" s="5" t="s">
-        <v>184</v>
-      </c>
-    </row>
-    <row r="170" spans="1:7" ht="21.6" x14ac:dyDescent="0.3">
+        <v>183</v>
+      </c>
+    </row>
+    <row r="170" spans="1:7" ht="33.75" x14ac:dyDescent="0.25">
       <c r="A170" s="4" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="B170" s="4" t="s">
         <v>12</v>
@@ -5402,15 +5388,15 @@
         <v>8</v>
       </c>
       <c r="F170" s="5" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="G170" s="5" t="s">
-        <v>179</v>
-      </c>
-    </row>
-    <row r="171" spans="1:7" ht="21.6" x14ac:dyDescent="0.3">
+        <v>178</v>
+      </c>
+    </row>
+    <row r="171" spans="1:7" ht="33.75" x14ac:dyDescent="0.25">
       <c r="A171" s="4" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="B171" s="4" t="s">
         <v>14</v>
@@ -5425,15 +5411,15 @@
         <v>8</v>
       </c>
       <c r="F171" s="5" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="G171" s="5" t="s">
-        <v>173</v>
-      </c>
-    </row>
-    <row r="172" spans="1:7" ht="21.6" x14ac:dyDescent="0.3">
+        <v>172</v>
+      </c>
+    </row>
+    <row r="172" spans="1:7" ht="33.75" x14ac:dyDescent="0.25">
       <c r="A172" s="4" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="B172" s="4" t="s">
         <v>15</v>
@@ -5448,15 +5434,15 @@
         <v>8</v>
       </c>
       <c r="F172" s="5" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="G172" s="5" t="s">
-        <v>173</v>
-      </c>
-    </row>
-    <row r="173" spans="1:7" ht="32.4" x14ac:dyDescent="0.3">
+        <v>172</v>
+      </c>
+    </row>
+    <row r="173" spans="1:7" ht="33.75" x14ac:dyDescent="0.25">
       <c r="A173" s="4" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="B173" s="4" t="s">
         <v>16</v>
@@ -5471,15 +5457,15 @@
         <v>9</v>
       </c>
       <c r="F173" s="5" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="G173" s="5" t="s">
-        <v>209</v>
-      </c>
-    </row>
-    <row r="174" spans="1:7" ht="54" x14ac:dyDescent="0.3">
+        <v>208</v>
+      </c>
+    </row>
+    <row r="174" spans="1:7" ht="56.25" x14ac:dyDescent="0.25">
       <c r="A174" s="4" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="B174" s="4" t="s">
         <v>17</v>
@@ -5494,15 +5480,15 @@
         <v>9</v>
       </c>
       <c r="F174" s="5" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="G174" s="5" t="s">
-        <v>209</v>
-      </c>
-    </row>
-    <row r="175" spans="1:7" ht="32.4" x14ac:dyDescent="0.3">
+        <v>208</v>
+      </c>
+    </row>
+    <row r="175" spans="1:7" ht="33.75" x14ac:dyDescent="0.25">
       <c r="A175" s="4" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="B175" s="4" t="s">
         <v>18</v>
@@ -5517,15 +5503,15 @@
         <v>9</v>
       </c>
       <c r="F175" s="5" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="G175" s="5" t="s">
-        <v>209</v>
-      </c>
-    </row>
-    <row r="176" spans="1:7" ht="43.2" x14ac:dyDescent="0.3">
+        <v>208</v>
+      </c>
+    </row>
+    <row r="176" spans="1:7" ht="45" x14ac:dyDescent="0.25">
       <c r="A176" s="4" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="B176" s="4" t="s">
         <v>19</v>
@@ -5540,15 +5526,15 @@
         <v>9</v>
       </c>
       <c r="F176" s="5" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="G176" s="5" t="s">
-        <v>209</v>
-      </c>
-    </row>
-    <row r="177" spans="1:7" ht="54" x14ac:dyDescent="0.3">
+        <v>208</v>
+      </c>
+    </row>
+    <row r="177" spans="1:7" ht="56.25" x14ac:dyDescent="0.25">
       <c r="A177" s="4" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="B177" s="4" t="s">
         <v>20</v>
@@ -5563,15 +5549,15 @@
         <v>9</v>
       </c>
       <c r="F177" s="5" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="G177" s="5" t="s">
-        <v>209</v>
-      </c>
-    </row>
-    <row r="178" spans="1:7" ht="32.4" x14ac:dyDescent="0.3">
+        <v>208</v>
+      </c>
+    </row>
+    <row r="178" spans="1:7" ht="45" x14ac:dyDescent="0.25">
       <c r="A178" s="4" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="B178" s="4" t="s">
         <v>21</v>
@@ -5586,18 +5572,18 @@
         <v>9</v>
       </c>
       <c r="F178" s="5" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="G178" s="5" t="s">
-        <v>209</v>
-      </c>
-    </row>
-    <row r="179" spans="1:7" ht="32.4" x14ac:dyDescent="0.3">
+        <v>208</v>
+      </c>
+    </row>
+    <row r="179" spans="1:7" ht="45" x14ac:dyDescent="0.25">
       <c r="A179" s="4" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="B179" s="4" t="s">
-        <v>221</v>
+        <v>220</v>
       </c>
       <c r="C179" s="4" t="s">
         <v>5</v>
@@ -5609,15 +5595,15 @@
         <v>9</v>
       </c>
       <c r="F179" s="5" t="s">
-        <v>211</v>
+        <v>210</v>
       </c>
       <c r="G179" s="5" t="s">
-        <v>209</v>
-      </c>
-    </row>
-    <row r="180" spans="1:7" ht="54" x14ac:dyDescent="0.3">
+        <v>208</v>
+      </c>
+    </row>
+    <row r="180" spans="1:7" ht="56.25" x14ac:dyDescent="0.25">
       <c r="A180" s="4" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="B180" s="4" t="s">
         <v>10</v>
@@ -5632,15 +5618,15 @@
         <v>8</v>
       </c>
       <c r="F180" s="5" t="s">
-        <v>183</v>
+        <v>182</v>
       </c>
       <c r="G180" s="5" t="s">
-        <v>173</v>
-      </c>
-    </row>
-    <row r="181" spans="1:7" ht="43.2" x14ac:dyDescent="0.3">
+        <v>172</v>
+      </c>
+    </row>
+    <row r="181" spans="1:7" ht="45" x14ac:dyDescent="0.25">
       <c r="A181" s="4" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="B181" s="4" t="s">
         <v>23</v>
@@ -5655,18 +5641,18 @@
         <v>8</v>
       </c>
       <c r="F181" s="5" t="s">
-        <v>186</v>
+        <v>185</v>
       </c>
       <c r="G181" s="5" t="s">
-        <v>173</v>
-      </c>
-    </row>
-    <row r="182" spans="1:7" ht="54" x14ac:dyDescent="0.3">
+        <v>172</v>
+      </c>
+    </row>
+    <row r="182" spans="1:7" ht="56.25" x14ac:dyDescent="0.25">
       <c r="A182" s="4" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="B182" s="4" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="C182" s="4" t="s">
         <v>5</v>
@@ -5678,15 +5664,15 @@
         <v>8</v>
       </c>
       <c r="F182" s="5" t="s">
-        <v>174</v>
+        <v>173</v>
       </c>
       <c r="G182" s="5" t="s">
-        <v>173</v>
-      </c>
-    </row>
-    <row r="183" spans="1:7" ht="64.8" x14ac:dyDescent="0.3">
+        <v>172</v>
+      </c>
+    </row>
+    <row r="183" spans="1:7" ht="78.75" x14ac:dyDescent="0.25">
       <c r="A183" s="4" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="B183" s="4" t="s">
         <v>24</v>
@@ -5701,15 +5687,15 @@
         <v>78</v>
       </c>
       <c r="F183" s="5" t="s">
+        <v>174</v>
+      </c>
+      <c r="G183" s="5" t="s">
         <v>175</v>
       </c>
-      <c r="G183" s="5" t="s">
-        <v>176</v>
-      </c>
-    </row>
-    <row r="184" spans="1:7" ht="54" x14ac:dyDescent="0.3">
+    </row>
+    <row r="184" spans="1:7" ht="56.25" x14ac:dyDescent="0.25">
       <c r="A184" s="4" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="B184" s="4" t="s">
         <v>25</v>
@@ -5724,15 +5710,15 @@
         <v>79</v>
       </c>
       <c r="F184" s="5" t="s">
-        <v>177</v>
+        <v>176</v>
       </c>
       <c r="G184" s="5" t="s">
-        <v>187</v>
-      </c>
-    </row>
-    <row r="185" spans="1:7" ht="43.2" x14ac:dyDescent="0.3">
+        <v>186</v>
+      </c>
+    </row>
+    <row r="185" spans="1:7" ht="56.25" x14ac:dyDescent="0.25">
       <c r="A185" s="4" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="B185" s="4" t="s">
         <v>75</v>
@@ -5747,18 +5733,18 @@
         <v>8</v>
       </c>
       <c r="F185" s="5" t="s">
-        <v>219</v>
+        <v>218</v>
       </c>
       <c r="G185" s="5" t="s">
-        <v>173</v>
-      </c>
-    </row>
-    <row r="186" spans="1:7" ht="21.6" x14ac:dyDescent="0.3">
+        <v>172</v>
+      </c>
+    </row>
+    <row r="186" spans="1:7" ht="22.5" x14ac:dyDescent="0.25">
       <c r="A186" s="4" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="B186" s="4" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="C186" s="4" t="s">
         <v>5</v>
@@ -5770,15 +5756,15 @@
         <v>79</v>
       </c>
       <c r="F186" s="5" t="s">
-        <v>178</v>
+        <v>177</v>
       </c>
       <c r="G186" s="5" t="s">
-        <v>188</v>
-      </c>
-    </row>
-    <row r="187" spans="1:7" x14ac:dyDescent="0.3">
+        <v>187</v>
+      </c>
+    </row>
+    <row r="187" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A187" s="4" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="B187" s="4" t="s">
         <v>26</v>
@@ -5793,15 +5779,15 @@
         <v>8</v>
       </c>
       <c r="F187" s="5" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
       <c r="G187" s="5" t="s">
-        <v>188</v>
-      </c>
-    </row>
-    <row r="188" spans="1:7" ht="21.6" x14ac:dyDescent="0.3">
+        <v>187</v>
+      </c>
+    </row>
+    <row r="188" spans="1:7" ht="22.5" x14ac:dyDescent="0.25">
       <c r="A188" s="4" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="B188" s="4" t="s">
         <v>27</v>
@@ -5816,15 +5802,15 @@
         <v>8</v>
       </c>
       <c r="F188" s="5" t="s">
-        <v>189</v>
+        <v>188</v>
       </c>
       <c r="G188" s="5" t="s">
-        <v>188</v>
-      </c>
-    </row>
-    <row r="189" spans="1:7" ht="64.8" x14ac:dyDescent="0.3">
+        <v>187</v>
+      </c>
+    </row>
+    <row r="189" spans="1:7" ht="67.5" x14ac:dyDescent="0.25">
       <c r="A189" s="4" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="B189" s="4" t="s">
         <v>28</v>
@@ -5839,15 +5825,15 @@
         <v>8</v>
       </c>
       <c r="F189" s="5" t="s">
-        <v>190</v>
+        <v>189</v>
       </c>
       <c r="G189" s="5" t="s">
-        <v>188</v>
-      </c>
-    </row>
-    <row r="190" spans="1:7" ht="64.8" x14ac:dyDescent="0.3">
+        <v>187</v>
+      </c>
+    </row>
+    <row r="190" spans="1:7" ht="67.5" x14ac:dyDescent="0.25">
       <c r="A190" s="4" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="B190" s="4" t="s">
         <v>29</v>
@@ -5862,15 +5848,15 @@
         <v>8</v>
       </c>
       <c r="F190" s="5" t="s">
-        <v>191</v>
+        <v>190</v>
       </c>
       <c r="G190" s="5" t="s">
-        <v>188</v>
-      </c>
-    </row>
-    <row r="191" spans="1:7" ht="64.8" x14ac:dyDescent="0.3">
+        <v>187</v>
+      </c>
+    </row>
+    <row r="191" spans="1:7" ht="67.5" x14ac:dyDescent="0.25">
       <c r="A191" s="4" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="B191" s="4" t="s">
         <v>30</v>
@@ -5885,15 +5871,15 @@
         <v>8</v>
       </c>
       <c r="F191" s="5" t="s">
-        <v>192</v>
+        <v>191</v>
       </c>
       <c r="G191" s="5" t="s">
-        <v>188</v>
-      </c>
-    </row>
-    <row r="192" spans="1:7" ht="32.4" x14ac:dyDescent="0.3">
+        <v>187</v>
+      </c>
+    </row>
+    <row r="192" spans="1:7" ht="45" x14ac:dyDescent="0.25">
       <c r="A192" s="4" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="B192" s="4" t="s">
         <v>31</v>
@@ -5908,18 +5894,18 @@
         <v>8</v>
       </c>
       <c r="F192" s="5" t="s">
-        <v>196</v>
+        <v>195</v>
       </c>
       <c r="G192" s="5" t="s">
-        <v>173</v>
-      </c>
-    </row>
-    <row r="193" spans="1:7" ht="54" x14ac:dyDescent="0.3">
+        <v>172</v>
+      </c>
+    </row>
+    <row r="193" spans="1:7" ht="56.25" x14ac:dyDescent="0.25">
       <c r="A193" s="4" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="B193" s="4" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="C193" s="4" t="s">
         <v>5</v>
@@ -5931,15 +5917,15 @@
         <v>8</v>
       </c>
       <c r="F193" s="5" t="s">
-        <v>197</v>
+        <v>196</v>
       </c>
       <c r="G193" s="5" t="s">
-        <v>173</v>
-      </c>
-    </row>
-    <row r="194" spans="1:7" ht="43.2" x14ac:dyDescent="0.3">
+        <v>172</v>
+      </c>
+    </row>
+    <row r="194" spans="1:7" ht="56.25" x14ac:dyDescent="0.25">
       <c r="A194" s="4" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="B194" s="4" t="s">
         <v>32</v>
@@ -5954,15 +5940,15 @@
         <v>77</v>
       </c>
       <c r="F194" s="5" t="s">
+        <v>197</v>
+      </c>
+      <c r="G194" s="5" t="s">
         <v>198</v>
       </c>
-      <c r="G194" s="5" t="s">
-        <v>199</v>
-      </c>
-    </row>
-    <row r="195" spans="1:7" ht="54" x14ac:dyDescent="0.3">
+    </row>
+    <row r="195" spans="1:7" ht="56.25" x14ac:dyDescent="0.25">
       <c r="A195" s="4" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="B195" s="4" t="s">
         <v>33</v>
@@ -5977,15 +5963,15 @@
         <v>77</v>
       </c>
       <c r="F195" s="5" t="s">
-        <v>200</v>
+        <v>199</v>
       </c>
       <c r="G195" s="5" t="s">
-        <v>170</v>
-      </c>
-    </row>
-    <row r="196" spans="1:7" ht="21.6" x14ac:dyDescent="0.3">
+        <v>169</v>
+      </c>
+    </row>
+    <row r="196" spans="1:7" ht="33.75" x14ac:dyDescent="0.25">
       <c r="A196" s="4" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="B196" s="4" t="s">
         <v>34</v>
@@ -5997,18 +5983,18 @@
         <v>4</v>
       </c>
       <c r="E196" s="4" t="s">
+        <v>200</v>
+      </c>
+      <c r="F196" s="5" t="s">
         <v>201</v>
       </c>
-      <c r="F196" s="5" t="s">
+      <c r="G196" s="5" t="s">
         <v>202</v>
       </c>
-      <c r="G196" s="5" t="s">
-        <v>203</v>
-      </c>
-    </row>
-    <row r="197" spans="1:7" ht="21.6" x14ac:dyDescent="0.3">
+    </row>
+    <row r="197" spans="1:7" ht="22.5" x14ac:dyDescent="0.25">
       <c r="A197" s="4" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="B197" s="4" t="s">
         <v>35</v>
@@ -6020,18 +6006,18 @@
         <v>5</v>
       </c>
       <c r="E197" s="4" t="s">
-        <v>201</v>
+        <v>200</v>
       </c>
       <c r="F197" s="5" t="s">
+        <v>203</v>
+      </c>
+      <c r="G197" s="5" t="s">
         <v>204</v>
       </c>
-      <c r="G197" s="5" t="s">
-        <v>205</v>
-      </c>
-    </row>
-    <row r="198" spans="1:7" ht="32.4" x14ac:dyDescent="0.3">
+    </row>
+    <row r="198" spans="1:7" ht="33.75" x14ac:dyDescent="0.25">
       <c r="A198" s="4" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="B198" s="4" t="s">
         <v>36</v>
@@ -6043,18 +6029,18 @@
         <v>4</v>
       </c>
       <c r="E198" s="4" t="s">
-        <v>201</v>
+        <v>200</v>
       </c>
       <c r="F198" s="5" t="s">
+        <v>205</v>
+      </c>
+      <c r="G198" s="5" t="s">
         <v>206</v>
       </c>
-      <c r="G198" s="5" t="s">
-        <v>207</v>
-      </c>
-    </row>
-    <row r="199" spans="1:7" ht="32.4" x14ac:dyDescent="0.3">
+    </row>
+    <row r="199" spans="1:7" ht="33.75" x14ac:dyDescent="0.25">
       <c r="A199" s="4" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="B199" s="4" t="s">
         <v>37</v>
@@ -6069,15 +6055,15 @@
         <v>9</v>
       </c>
       <c r="F199" s="5" t="s">
-        <v>208</v>
+        <v>207</v>
       </c>
       <c r="G199" s="5" t="s">
-        <v>209</v>
-      </c>
-    </row>
-    <row r="200" spans="1:7" ht="32.4" x14ac:dyDescent="0.3">
+        <v>208</v>
+      </c>
+    </row>
+    <row r="200" spans="1:7" ht="33.75" x14ac:dyDescent="0.25">
       <c r="A200" s="4" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="B200" s="4" t="s">
         <v>38</v>
@@ -6092,15 +6078,15 @@
         <v>9</v>
       </c>
       <c r="F200" s="5" t="s">
-        <v>114</v>
+        <v>113</v>
       </c>
       <c r="G200" s="5" t="s">
-        <v>209</v>
-      </c>
-    </row>
-    <row r="201" spans="1:7" ht="43.2" x14ac:dyDescent="0.3">
+        <v>208</v>
+      </c>
+    </row>
+    <row r="201" spans="1:7" ht="45" x14ac:dyDescent="0.25">
       <c r="A201" s="4" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="B201" s="4" t="s">
         <v>39</v>
@@ -6115,15 +6101,15 @@
         <v>9</v>
       </c>
       <c r="F201" s="5" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="G201" s="5" t="s">
-        <v>209</v>
-      </c>
-    </row>
-    <row r="202" spans="1:7" ht="32.4" x14ac:dyDescent="0.3">
+        <v>208</v>
+      </c>
+    </row>
+    <row r="202" spans="1:7" ht="33.75" x14ac:dyDescent="0.25">
       <c r="A202" s="4" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="B202" s="4" t="s">
         <v>40</v>
@@ -6138,15 +6124,15 @@
         <v>9</v>
       </c>
       <c r="F202" s="5" t="s">
-        <v>113</v>
+        <v>112</v>
       </c>
       <c r="G202" s="5" t="s">
-        <v>209</v>
-      </c>
-    </row>
-    <row r="203" spans="1:7" ht="32.4" x14ac:dyDescent="0.3">
+        <v>208</v>
+      </c>
+    </row>
+    <row r="203" spans="1:7" ht="33.75" x14ac:dyDescent="0.25">
       <c r="A203" s="4" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="B203" s="4" t="s">
         <v>16</v>
@@ -6161,15 +6147,15 @@
         <v>9</v>
       </c>
       <c r="F203" s="5" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="G203" s="5" t="s">
-        <v>209</v>
-      </c>
-    </row>
-    <row r="204" spans="1:7" ht="54" x14ac:dyDescent="0.3">
+        <v>208</v>
+      </c>
+    </row>
+    <row r="204" spans="1:7" ht="56.25" x14ac:dyDescent="0.25">
       <c r="A204" s="4" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="B204" s="4" t="s">
         <v>17</v>
@@ -6184,15 +6170,15 @@
         <v>9</v>
       </c>
       <c r="F204" s="5" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="G204" s="5" t="s">
-        <v>209</v>
-      </c>
-    </row>
-    <row r="205" spans="1:7" ht="32.4" x14ac:dyDescent="0.3">
+        <v>208</v>
+      </c>
+    </row>
+    <row r="205" spans="1:7" ht="33.75" x14ac:dyDescent="0.25">
       <c r="A205" s="4" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="B205" s="4" t="s">
         <v>18</v>
@@ -6207,15 +6193,15 @@
         <v>9</v>
       </c>
       <c r="F205" s="5" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="G205" s="5" t="s">
-        <v>209</v>
-      </c>
-    </row>
-    <row r="206" spans="1:7" ht="43.2" x14ac:dyDescent="0.3">
+        <v>208</v>
+      </c>
+    </row>
+    <row r="206" spans="1:7" ht="45" x14ac:dyDescent="0.25">
       <c r="A206" s="4" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="B206" s="4" t="s">
         <v>19</v>
@@ -6230,15 +6216,15 @@
         <v>9</v>
       </c>
       <c r="F206" s="5" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="G206" s="5" t="s">
-        <v>209</v>
-      </c>
-    </row>
-    <row r="207" spans="1:7" ht="54" x14ac:dyDescent="0.3">
+        <v>208</v>
+      </c>
+    </row>
+    <row r="207" spans="1:7" ht="56.25" x14ac:dyDescent="0.25">
       <c r="A207" s="4" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="B207" s="4" t="s">
         <v>20</v>
@@ -6253,15 +6239,15 @@
         <v>9</v>
       </c>
       <c r="F207" s="5" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="G207" s="5" t="s">
-        <v>209</v>
-      </c>
-    </row>
-    <row r="208" spans="1:7" ht="32.4" x14ac:dyDescent="0.3">
+        <v>208</v>
+      </c>
+    </row>
+    <row r="208" spans="1:7" ht="45" x14ac:dyDescent="0.25">
       <c r="A208" s="4" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="B208" s="4" t="s">
         <v>21</v>
@@ -6276,18 +6262,18 @@
         <v>9</v>
       </c>
       <c r="F208" s="5" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="G208" s="5" t="s">
-        <v>209</v>
-      </c>
-    </row>
-    <row r="209" spans="1:7" ht="32.4" x14ac:dyDescent="0.3">
+        <v>208</v>
+      </c>
+    </row>
+    <row r="209" spans="1:7" ht="45" x14ac:dyDescent="0.25">
       <c r="A209" s="4" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="B209" s="4" t="s">
-        <v>221</v>
+        <v>220</v>
       </c>
       <c r="C209" s="4" t="s">
         <v>5</v>
@@ -6299,15 +6285,15 @@
         <v>9</v>
       </c>
       <c r="F209" s="5" t="s">
-        <v>211</v>
+        <v>210</v>
       </c>
       <c r="G209" s="5" t="s">
-        <v>209</v>
-      </c>
-    </row>
-    <row r="210" spans="1:7" ht="54" x14ac:dyDescent="0.3">
+        <v>208</v>
+      </c>
+    </row>
+    <row r="210" spans="1:7" ht="67.5" x14ac:dyDescent="0.25">
       <c r="A210" s="4" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="B210" s="4" t="s">
         <v>41</v>
@@ -6322,64 +6308,64 @@
         <v>9</v>
       </c>
       <c r="F210" s="5" t="s">
+        <v>211</v>
+      </c>
+      <c r="G210" s="5" t="s">
+        <v>208</v>
+      </c>
+    </row>
+    <row r="211" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A211" s="4" t="s">
+        <v>97</v>
+      </c>
+      <c r="B211" s="4" t="s">
+        <v>87</v>
+      </c>
+      <c r="C211" s="4" t="s">
+        <v>4</v>
+      </c>
+      <c r="D211" s="4" t="s">
+        <v>4</v>
+      </c>
+      <c r="E211" s="4" t="s">
+        <v>147</v>
+      </c>
+      <c r="F211" s="5" t="s">
+        <v>148</v>
+      </c>
+      <c r="G211" s="5" t="s">
         <v>212</v>
       </c>
-      <c r="G210" s="5" t="s">
-        <v>209</v>
-      </c>
-    </row>
-    <row r="211" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A211" s="4" t="s">
-        <v>98</v>
-      </c>
-      <c r="B211" s="4" t="s">
+    </row>
+    <row r="212" spans="1:7" ht="33.75" x14ac:dyDescent="0.25">
+      <c r="A212" s="4" t="s">
+        <v>97</v>
+      </c>
+      <c r="B212" s="4" t="s">
         <v>88</v>
       </c>
-      <c r="C211" s="4" t="s">
-        <v>4</v>
-      </c>
-      <c r="D211" s="4" t="s">
-        <v>4</v>
-      </c>
-      <c r="E211" s="4" t="s">
-        <v>148</v>
-      </c>
-      <c r="F211" s="5" t="s">
+      <c r="C212" s="4" t="s">
+        <v>5</v>
+      </c>
+      <c r="D212" s="4" t="s">
+        <v>4</v>
+      </c>
+      <c r="E212" s="4" t="s">
+        <v>9</v>
+      </c>
+      <c r="F212" s="5" t="s">
         <v>149</v>
       </c>
-      <c r="G211" s="5" t="s">
-        <v>213</v>
-      </c>
-    </row>
-    <row r="212" spans="1:7" ht="32.4" x14ac:dyDescent="0.3">
-      <c r="A212" s="4" t="s">
-        <v>98</v>
-      </c>
-      <c r="B212" s="4" t="s">
+      <c r="G212" s="5" t="s">
+        <v>208</v>
+      </c>
+    </row>
+    <row r="213" spans="1:7" ht="33.75" x14ac:dyDescent="0.25">
+      <c r="A213" s="4" t="s">
+        <v>97</v>
+      </c>
+      <c r="B213" s="4" t="s">
         <v>89</v>
-      </c>
-      <c r="C212" s="4" t="s">
-        <v>5</v>
-      </c>
-      <c r="D212" s="4" t="s">
-        <v>4</v>
-      </c>
-      <c r="E212" s="4" t="s">
-        <v>9</v>
-      </c>
-      <c r="F212" s="5" t="s">
-        <v>150</v>
-      </c>
-      <c r="G212" s="5" t="s">
-        <v>209</v>
-      </c>
-    </row>
-    <row r="213" spans="1:7" ht="32.4" x14ac:dyDescent="0.3">
-      <c r="A213" s="4" t="s">
-        <v>98</v>
-      </c>
-      <c r="B213" s="4" t="s">
-        <v>90</v>
       </c>
       <c r="C213" s="4" t="s">
         <v>5</v>
@@ -6391,64 +6377,64 @@
         <v>78</v>
       </c>
       <c r="F213" s="5" t="s">
-        <v>151</v>
+        <v>150</v>
       </c>
       <c r="G213" s="5" t="s">
-        <v>220</v>
-      </c>
-    </row>
-    <row r="214" spans="1:7" x14ac:dyDescent="0.3">
+        <v>219</v>
+      </c>
+    </row>
+    <row r="214" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A214" s="4" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="B214" s="4" t="s">
+        <v>90</v>
+      </c>
+      <c r="C214" s="7" t="s">
+        <v>4</v>
+      </c>
+      <c r="D214" s="4" t="s">
+        <v>4</v>
+      </c>
+      <c r="E214" s="4" t="s">
+        <v>147</v>
+      </c>
+      <c r="F214" s="5" t="s">
+        <v>155</v>
+      </c>
+      <c r="G214" s="5" t="s">
+        <v>212</v>
+      </c>
+    </row>
+    <row r="215" spans="1:7" ht="33.75" x14ac:dyDescent="0.25">
+      <c r="A215" s="4" t="s">
+        <v>97</v>
+      </c>
+      <c r="B215" s="4" t="s">
         <v>91</v>
       </c>
-      <c r="C214" s="7" t="s">
-        <v>4</v>
-      </c>
-      <c r="D214" s="4" t="s">
-        <v>4</v>
-      </c>
-      <c r="E214" s="4" t="s">
-        <v>148</v>
-      </c>
-      <c r="F214" s="5" t="s">
+      <c r="C215" s="4" t="s">
+        <v>5</v>
+      </c>
+      <c r="D215" s="4" t="s">
+        <v>4</v>
+      </c>
+      <c r="E215" s="4" t="s">
+        <v>9</v>
+      </c>
+      <c r="F215" s="5" t="s">
         <v>156</v>
       </c>
-      <c r="G214" s="5" t="s">
-        <v>213</v>
-      </c>
-    </row>
-    <row r="215" spans="1:7" ht="32.4" x14ac:dyDescent="0.3">
-      <c r="A215" s="4" t="s">
-        <v>98</v>
-      </c>
-      <c r="B215" s="4" t="s">
+      <c r="G215" s="5" t="s">
+        <v>208</v>
+      </c>
+    </row>
+    <row r="216" spans="1:7" ht="33.75" x14ac:dyDescent="0.25">
+      <c r="A216" s="4" t="s">
+        <v>97</v>
+      </c>
+      <c r="B216" s="4" t="s">
         <v>92</v>
-      </c>
-      <c r="C215" s="4" t="s">
-        <v>5</v>
-      </c>
-      <c r="D215" s="4" t="s">
-        <v>4</v>
-      </c>
-      <c r="E215" s="4" t="s">
-        <v>9</v>
-      </c>
-      <c r="F215" s="5" t="s">
-        <v>157</v>
-      </c>
-      <c r="G215" s="5" t="s">
-        <v>209</v>
-      </c>
-    </row>
-    <row r="216" spans="1:7" ht="32.4" x14ac:dyDescent="0.3">
-      <c r="A216" s="4" t="s">
-        <v>98</v>
-      </c>
-      <c r="B216" s="4" t="s">
-        <v>93</v>
       </c>
       <c r="C216" s="4" t="s">
         <v>5</v>
@@ -6460,18 +6446,18 @@
         <v>78</v>
       </c>
       <c r="F216" s="5" t="s">
-        <v>152</v>
+        <v>151</v>
       </c>
       <c r="G216" s="5" t="s">
-        <v>220</v>
-      </c>
-    </row>
-    <row r="217" spans="1:7" ht="32.4" x14ac:dyDescent="0.3">
+        <v>219</v>
+      </c>
+    </row>
+    <row r="217" spans="1:7" ht="33.75" x14ac:dyDescent="0.25">
       <c r="A217" s="4" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="B217" s="4" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="C217" s="4" t="s">
         <v>5</v>
@@ -6483,18 +6469,18 @@
         <v>78</v>
       </c>
       <c r="F217" s="5" t="s">
-        <v>155</v>
+        <v>154</v>
       </c>
       <c r="G217" s="5" t="s">
-        <v>220</v>
-      </c>
-    </row>
-    <row r="218" spans="1:7" ht="32.4" x14ac:dyDescent="0.3">
+        <v>219</v>
+      </c>
+    </row>
+    <row r="218" spans="1:7" ht="33.75" x14ac:dyDescent="0.25">
       <c r="A218" s="4" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="B218" s="4" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="C218" s="4" t="s">
         <v>5</v>
@@ -6506,18 +6492,18 @@
         <v>78</v>
       </c>
       <c r="F218" s="5" t="s">
-        <v>153</v>
+        <v>152</v>
       </c>
       <c r="G218" s="5" t="s">
-        <v>220</v>
-      </c>
-    </row>
-    <row r="219" spans="1:7" ht="32.4" x14ac:dyDescent="0.3">
+        <v>219</v>
+      </c>
+    </row>
+    <row r="219" spans="1:7" ht="33.75" x14ac:dyDescent="0.25">
       <c r="A219" s="4" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="B219" s="4" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="C219" s="4" t="s">
         <v>5</v>
@@ -6529,18 +6515,18 @@
         <v>78</v>
       </c>
       <c r="F219" s="5" t="s">
-        <v>154</v>
+        <v>153</v>
       </c>
       <c r="G219" s="5" t="s">
-        <v>220</v>
-      </c>
-    </row>
-    <row r="220" spans="1:7" ht="32.4" x14ac:dyDescent="0.3">
+        <v>219</v>
+      </c>
+    </row>
+    <row r="220" spans="1:7" ht="33.75" x14ac:dyDescent="0.25">
       <c r="A220" s="4" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="B220" s="4" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="C220" s="4" t="s">
         <v>5</v>
@@ -6552,15 +6538,15 @@
         <v>78</v>
       </c>
       <c r="F220" s="5" t="s">
-        <v>158</v>
+        <v>157</v>
       </c>
       <c r="G220" s="5" t="s">
-        <v>220</v>
-      </c>
-    </row>
-    <row r="221" spans="1:7" ht="32.4" x14ac:dyDescent="0.3">
+        <v>219</v>
+      </c>
+    </row>
+    <row r="221" spans="1:7" ht="33.75" x14ac:dyDescent="0.25">
       <c r="A221" s="4" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="B221" s="4" t="s">
         <v>73</v>
@@ -6575,18 +6561,18 @@
         <v>78</v>
       </c>
       <c r="F221" s="5" t="s">
-        <v>147</v>
+        <v>146</v>
       </c>
       <c r="G221" s="5" t="s">
-        <v>220</v>
-      </c>
-    </row>
-    <row r="222" spans="1:7" ht="32.4" x14ac:dyDescent="0.3">
+        <v>219</v>
+      </c>
+    </row>
+    <row r="222" spans="1:7" ht="33.75" x14ac:dyDescent="0.25">
       <c r="A222" s="4" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="B222" s="4" t="s">
-        <v>117</v>
+        <v>116</v>
       </c>
       <c r="C222" s="4" t="s">
         <v>5</v>
@@ -6598,15 +6584,15 @@
         <v>78</v>
       </c>
       <c r="F222" s="5" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="G222" s="5" t="s">
-        <v>220</v>
-      </c>
-    </row>
-    <row r="223" spans="1:7" ht="21.6" x14ac:dyDescent="0.3">
+        <v>219</v>
+      </c>
+    </row>
+    <row r="223" spans="1:7" ht="22.5" x14ac:dyDescent="0.25">
       <c r="A223" s="4" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="B223" s="4" t="s">
         <v>74</v>
@@ -6621,15 +6607,15 @@
         <v>8</v>
       </c>
       <c r="F223" s="5" t="s">
-        <v>115</v>
+        <v>114</v>
       </c>
       <c r="G223" s="5" t="s">
-        <v>213</v>
-      </c>
-    </row>
-    <row r="224" spans="1:7" ht="54" x14ac:dyDescent="0.3">
+        <v>212</v>
+      </c>
+    </row>
+    <row r="224" spans="1:7" ht="56.25" x14ac:dyDescent="0.25">
       <c r="A224" s="4" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="B224" s="4" t="s">
         <v>10</v>
@@ -6644,15 +6630,15 @@
         <v>8</v>
       </c>
       <c r="F224" s="5" t="s">
-        <v>183</v>
+        <v>182</v>
       </c>
       <c r="G224" s="5" t="s">
-        <v>173</v>
-      </c>
-    </row>
-    <row r="225" spans="1:7" ht="43.2" x14ac:dyDescent="0.3">
+        <v>172</v>
+      </c>
+    </row>
+    <row r="225" spans="1:7" ht="45" x14ac:dyDescent="0.25">
       <c r="A225" s="4" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="B225" s="4" t="s">
         <v>23</v>
@@ -6667,15 +6653,15 @@
         <v>8</v>
       </c>
       <c r="F225" s="5" t="s">
-        <v>186</v>
+        <v>185</v>
       </c>
       <c r="G225" s="5" t="s">
-        <v>173</v>
-      </c>
-    </row>
-    <row r="226" spans="1:7" ht="64.8" x14ac:dyDescent="0.3">
+        <v>172</v>
+      </c>
+    </row>
+    <row r="226" spans="1:7" ht="78.75" x14ac:dyDescent="0.25">
       <c r="A226" s="4" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="B226" s="4" t="s">
         <v>24</v>
@@ -6690,18 +6676,18 @@
         <v>78</v>
       </c>
       <c r="F226" s="5" t="s">
+        <v>174</v>
+      </c>
+      <c r="G226" s="5" t="s">
         <v>175</v>
       </c>
-      <c r="G226" s="5" t="s">
-        <v>176</v>
-      </c>
-    </row>
-    <row r="227" spans="1:7" ht="21.6" x14ac:dyDescent="0.3">
+    </row>
+    <row r="227" spans="1:7" ht="22.5" x14ac:dyDescent="0.25">
       <c r="A227" s="4" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="B227" s="4" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="C227" s="4" t="s">
         <v>5</v>
@@ -6713,15 +6699,15 @@
         <v>79</v>
       </c>
       <c r="F227" s="5" t="s">
-        <v>178</v>
+        <v>177</v>
       </c>
       <c r="G227" s="5" t="s">
-        <v>188</v>
-      </c>
-    </row>
-    <row r="228" spans="1:7" x14ac:dyDescent="0.3">
+        <v>187</v>
+      </c>
+    </row>
+    <row r="228" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A228" s="4" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="B228" s="4" t="s">
         <v>26</v>
@@ -6736,15 +6722,15 @@
         <v>8</v>
       </c>
       <c r="F228" s="5" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
       <c r="G228" s="5" t="s">
-        <v>188</v>
-      </c>
-    </row>
-    <row r="229" spans="1:7" ht="21.6" x14ac:dyDescent="0.3">
+        <v>187</v>
+      </c>
+    </row>
+    <row r="229" spans="1:7" ht="22.5" x14ac:dyDescent="0.25">
       <c r="A229" s="4" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="B229" s="4" t="s">
         <v>27</v>
@@ -6759,15 +6745,15 @@
         <v>8</v>
       </c>
       <c r="F229" s="5" t="s">
-        <v>189</v>
+        <v>188</v>
       </c>
       <c r="G229" s="5" t="s">
-        <v>188</v>
-      </c>
-    </row>
-    <row r="230" spans="1:7" ht="64.8" x14ac:dyDescent="0.3">
+        <v>187</v>
+      </c>
+    </row>
+    <row r="230" spans="1:7" ht="67.5" x14ac:dyDescent="0.25">
       <c r="A230" s="4" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="B230" s="4" t="s">
         <v>28</v>
@@ -6782,15 +6768,15 @@
         <v>8</v>
       </c>
       <c r="F230" s="5" t="s">
-        <v>190</v>
+        <v>189</v>
       </c>
       <c r="G230" s="5" t="s">
-        <v>188</v>
-      </c>
-    </row>
-    <row r="231" spans="1:7" ht="64.8" x14ac:dyDescent="0.3">
+        <v>187</v>
+      </c>
+    </row>
+    <row r="231" spans="1:7" ht="67.5" x14ac:dyDescent="0.25">
       <c r="A231" s="4" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="B231" s="4" t="s">
         <v>29</v>
@@ -6805,15 +6791,15 @@
         <v>8</v>
       </c>
       <c r="F231" s="5" t="s">
-        <v>191</v>
+        <v>190</v>
       </c>
       <c r="G231" s="5" t="s">
-        <v>188</v>
-      </c>
-    </row>
-    <row r="232" spans="1:7" ht="64.8" x14ac:dyDescent="0.3">
+        <v>187</v>
+      </c>
+    </row>
+    <row r="232" spans="1:7" ht="67.5" x14ac:dyDescent="0.25">
       <c r="A232" s="4" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="B232" s="4" t="s">
         <v>30</v>
@@ -6828,15 +6814,15 @@
         <v>8</v>
       </c>
       <c r="F232" s="5" t="s">
-        <v>192</v>
+        <v>191</v>
       </c>
       <c r="G232" s="5" t="s">
-        <v>188</v>
-      </c>
-    </row>
-    <row r="233" spans="1:7" ht="32.4" x14ac:dyDescent="0.3">
+        <v>187</v>
+      </c>
+    </row>
+    <row r="233" spans="1:7" ht="45" x14ac:dyDescent="0.25">
       <c r="A233" s="4" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="B233" s="4" t="s">
         <v>31</v>
@@ -6851,18 +6837,18 @@
         <v>8</v>
       </c>
       <c r="F233" s="5" t="s">
-        <v>196</v>
+        <v>195</v>
       </c>
       <c r="G233" s="5" t="s">
-        <v>173</v>
-      </c>
-    </row>
-    <row r="234" spans="1:7" ht="54" x14ac:dyDescent="0.3">
+        <v>172</v>
+      </c>
+    </row>
+    <row r="234" spans="1:7" ht="56.25" x14ac:dyDescent="0.25">
       <c r="A234" s="4" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="B234" s="4" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="C234" s="4" t="s">
         <v>5</v>
@@ -6874,15 +6860,15 @@
         <v>8</v>
       </c>
       <c r="F234" s="5" t="s">
-        <v>197</v>
+        <v>196</v>
       </c>
       <c r="G234" s="5" t="s">
-        <v>173</v>
-      </c>
-    </row>
-    <row r="235" spans="1:7" ht="43.2" x14ac:dyDescent="0.3">
+        <v>172</v>
+      </c>
+    </row>
+    <row r="235" spans="1:7" ht="56.25" x14ac:dyDescent="0.25">
       <c r="A235" s="4" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="B235" s="4" t="s">
         <v>32</v>
@@ -6897,15 +6883,15 @@
         <v>77</v>
       </c>
       <c r="F235" s="5" t="s">
+        <v>197</v>
+      </c>
+      <c r="G235" s="5" t="s">
         <v>198</v>
       </c>
-      <c r="G235" s="5" t="s">
-        <v>199</v>
-      </c>
-    </row>
-    <row r="236" spans="1:7" ht="54" x14ac:dyDescent="0.3">
+    </row>
+    <row r="236" spans="1:7" ht="56.25" x14ac:dyDescent="0.25">
       <c r="A236" s="4" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="B236" s="4" t="s">
         <v>33</v>
@@ -6920,15 +6906,15 @@
         <v>77</v>
       </c>
       <c r="F236" s="5" t="s">
-        <v>200</v>
+        <v>199</v>
       </c>
       <c r="G236" s="5" t="s">
-        <v>170</v>
-      </c>
-    </row>
-    <row r="237" spans="1:7" ht="21.6" x14ac:dyDescent="0.3">
+        <v>169</v>
+      </c>
+    </row>
+    <row r="237" spans="1:7" ht="33.75" x14ac:dyDescent="0.25">
       <c r="A237" s="4" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="B237" s="4" t="s">
         <v>34</v>
@@ -6940,18 +6926,18 @@
         <v>4</v>
       </c>
       <c r="E237" s="4" t="s">
+        <v>200</v>
+      </c>
+      <c r="F237" s="5" t="s">
         <v>201</v>
       </c>
-      <c r="F237" s="5" t="s">
+      <c r="G237" s="5" t="s">
         <v>202</v>
       </c>
-      <c r="G237" s="5" t="s">
-        <v>203</v>
-      </c>
-    </row>
-    <row r="238" spans="1:7" ht="21.6" x14ac:dyDescent="0.3">
+    </row>
+    <row r="238" spans="1:7" ht="22.5" x14ac:dyDescent="0.25">
       <c r="A238" s="4" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="B238" s="4" t="s">
         <v>35</v>
@@ -6963,18 +6949,18 @@
         <v>5</v>
       </c>
       <c r="E238" s="4" t="s">
-        <v>201</v>
+        <v>200</v>
       </c>
       <c r="F238" s="5" t="s">
+        <v>203</v>
+      </c>
+      <c r="G238" s="5" t="s">
         <v>204</v>
       </c>
-      <c r="G238" s="5" t="s">
-        <v>205</v>
-      </c>
-    </row>
-    <row r="239" spans="1:7" ht="32.4" x14ac:dyDescent="0.3">
+    </row>
+    <row r="239" spans="1:7" ht="33.75" x14ac:dyDescent="0.25">
       <c r="A239" s="4" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="B239" s="4" t="s">
         <v>36</v>
@@ -6986,18 +6972,18 @@
         <v>4</v>
       </c>
       <c r="E239" s="4" t="s">
-        <v>201</v>
+        <v>200</v>
       </c>
       <c r="F239" s="5" t="s">
+        <v>205</v>
+      </c>
+      <c r="G239" s="5" t="s">
         <v>206</v>
       </c>
-      <c r="G239" s="5" t="s">
-        <v>207</v>
-      </c>
-    </row>
-    <row r="240" spans="1:7" ht="32.4" x14ac:dyDescent="0.3">
+    </row>
+    <row r="240" spans="1:7" ht="33.75" x14ac:dyDescent="0.25">
       <c r="A240" s="4" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="B240" s="4" t="s">
         <v>38</v>
@@ -7012,15 +6998,15 @@
         <v>9</v>
       </c>
       <c r="F240" s="5" t="s">
-        <v>114</v>
+        <v>113</v>
       </c>
       <c r="G240" s="5" t="s">
-        <v>209</v>
-      </c>
-    </row>
-    <row r="241" spans="1:7" ht="43.2" x14ac:dyDescent="0.3">
+        <v>208</v>
+      </c>
+    </row>
+    <row r="241" spans="1:7" ht="45" x14ac:dyDescent="0.25">
       <c r="A241" s="4" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="B241" s="4" t="s">
         <v>39</v>
@@ -7035,15 +7021,15 @@
         <v>9</v>
       </c>
       <c r="F241" s="5" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="G241" s="5" t="s">
-        <v>209</v>
-      </c>
-    </row>
-    <row r="242" spans="1:7" ht="32.4" x14ac:dyDescent="0.3">
+        <v>208</v>
+      </c>
+    </row>
+    <row r="242" spans="1:7" ht="33.75" x14ac:dyDescent="0.25">
       <c r="A242" s="4" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="B242" s="4" t="s">
         <v>40</v>
@@ -7058,15 +7044,15 @@
         <v>9</v>
       </c>
       <c r="F242" s="5" t="s">
-        <v>113</v>
+        <v>112</v>
       </c>
       <c r="G242" s="5" t="s">
-        <v>209</v>
-      </c>
-    </row>
-    <row r="243" spans="1:7" ht="32.4" x14ac:dyDescent="0.3">
+        <v>208</v>
+      </c>
+    </row>
+    <row r="243" spans="1:7" ht="33.75" x14ac:dyDescent="0.25">
       <c r="A243" s="4" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="B243" s="4" t="s">
         <v>16</v>
@@ -7081,15 +7067,15 @@
         <v>9</v>
       </c>
       <c r="F243" s="5" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="G243" s="5" t="s">
-        <v>209</v>
-      </c>
-    </row>
-    <row r="244" spans="1:7" ht="54" x14ac:dyDescent="0.3">
+        <v>208</v>
+      </c>
+    </row>
+    <row r="244" spans="1:7" ht="56.25" x14ac:dyDescent="0.25">
       <c r="A244" s="4" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="B244" s="4" t="s">
         <v>17</v>
@@ -7104,15 +7090,15 @@
         <v>9</v>
       </c>
       <c r="F244" s="5" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="G244" s="5" t="s">
-        <v>209</v>
-      </c>
-    </row>
-    <row r="245" spans="1:7" ht="32.4" x14ac:dyDescent="0.3">
+        <v>208</v>
+      </c>
+    </row>
+    <row r="245" spans="1:7" ht="33.75" x14ac:dyDescent="0.25">
       <c r="A245" s="4" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="B245" s="4" t="s">
         <v>18</v>
@@ -7127,15 +7113,15 @@
         <v>9</v>
       </c>
       <c r="F245" s="5" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="G245" s="5" t="s">
-        <v>209</v>
-      </c>
-    </row>
-    <row r="246" spans="1:7" ht="43.2" x14ac:dyDescent="0.3">
+        <v>208</v>
+      </c>
+    </row>
+    <row r="246" spans="1:7" ht="45" x14ac:dyDescent="0.25">
       <c r="A246" s="4" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="B246" s="4" t="s">
         <v>19</v>
@@ -7150,15 +7136,15 @@
         <v>9</v>
       </c>
       <c r="F246" s="5" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="G246" s="5" t="s">
-        <v>209</v>
-      </c>
-    </row>
-    <row r="247" spans="1:7" ht="54" x14ac:dyDescent="0.3">
+        <v>208</v>
+      </c>
+    </row>
+    <row r="247" spans="1:7" ht="56.25" x14ac:dyDescent="0.25">
       <c r="A247" s="4" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="B247" s="4" t="s">
         <v>20</v>
@@ -7173,15 +7159,15 @@
         <v>9</v>
       </c>
       <c r="F247" s="5" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="G247" s="5" t="s">
-        <v>209</v>
-      </c>
-    </row>
-    <row r="248" spans="1:7" ht="32.4" x14ac:dyDescent="0.3">
+        <v>208</v>
+      </c>
+    </row>
+    <row r="248" spans="1:7" ht="45" x14ac:dyDescent="0.25">
       <c r="A248" s="4" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="B248" s="4" t="s">
         <v>21</v>
@@ -7196,18 +7182,18 @@
         <v>9</v>
       </c>
       <c r="F248" s="5" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="G248" s="5" t="s">
-        <v>209</v>
-      </c>
-    </row>
-    <row r="249" spans="1:7" ht="32.4" x14ac:dyDescent="0.3">
+        <v>208</v>
+      </c>
+    </row>
+    <row r="249" spans="1:7" ht="45" x14ac:dyDescent="0.25">
       <c r="A249" s="4" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="B249" s="4" t="s">
-        <v>221</v>
+        <v>220</v>
       </c>
       <c r="C249" s="4" t="s">
         <v>5</v>
@@ -7219,15 +7205,15 @@
         <v>9</v>
       </c>
       <c r="F249" s="5" t="s">
-        <v>211</v>
+        <v>210</v>
       </c>
       <c r="G249" s="5" t="s">
-        <v>209</v>
-      </c>
-    </row>
-    <row r="250" spans="1:7" ht="54" x14ac:dyDescent="0.3">
+        <v>208</v>
+      </c>
+    </row>
+    <row r="250" spans="1:7" ht="67.5" x14ac:dyDescent="0.25">
       <c r="A250" s="4" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="B250" s="4" t="s">
         <v>41</v>
@@ -7242,41 +7228,41 @@
         <v>9</v>
       </c>
       <c r="F250" s="5" t="s">
+        <v>211</v>
+      </c>
+      <c r="G250" s="5" t="s">
+        <v>208</v>
+      </c>
+    </row>
+    <row r="251" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A251" s="4" t="s">
+        <v>98</v>
+      </c>
+      <c r="B251" s="4" t="s">
+        <v>87</v>
+      </c>
+      <c r="C251" s="4" t="s">
+        <v>5</v>
+      </c>
+      <c r="D251" s="4" t="s">
+        <v>4</v>
+      </c>
+      <c r="E251" s="4" t="s">
+        <v>147</v>
+      </c>
+      <c r="F251" s="5" t="s">
+        <v>148</v>
+      </c>
+      <c r="G251" s="5" t="s">
         <v>212</v>
       </c>
-      <c r="G250" s="5" t="s">
-        <v>209</v>
-      </c>
-    </row>
-    <row r="251" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A251" s="4" t="s">
-        <v>99</v>
-      </c>
-      <c r="B251" s="4" t="s">
+    </row>
+    <row r="252" spans="1:7" ht="22.5" x14ac:dyDescent="0.25">
+      <c r="A252" s="4" t="s">
+        <v>98</v>
+      </c>
+      <c r="B252" s="4" t="s">
         <v>88</v>
-      </c>
-      <c r="C251" s="4" t="s">
-        <v>5</v>
-      </c>
-      <c r="D251" s="4" t="s">
-        <v>4</v>
-      </c>
-      <c r="E251" s="4" t="s">
-        <v>148</v>
-      </c>
-      <c r="F251" s="5" t="s">
-        <v>149</v>
-      </c>
-      <c r="G251" s="5" t="s">
-        <v>213</v>
-      </c>
-    </row>
-    <row r="252" spans="1:7" ht="21.6" x14ac:dyDescent="0.3">
-      <c r="A252" s="4" t="s">
-        <v>99</v>
-      </c>
-      <c r="B252" s="4" t="s">
-        <v>89</v>
       </c>
       <c r="C252" s="4" t="s">
         <v>5</v>
@@ -7288,18 +7274,18 @@
         <v>79</v>
       </c>
       <c r="F252" s="5" t="s">
-        <v>150</v>
+        <v>149</v>
       </c>
       <c r="G252" s="5" t="s">
-        <v>213</v>
-      </c>
-    </row>
-    <row r="253" spans="1:7" ht="32.4" x14ac:dyDescent="0.3">
+        <v>212</v>
+      </c>
+    </row>
+    <row r="253" spans="1:7" ht="33.75" x14ac:dyDescent="0.25">
       <c r="A253" s="4" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="B253" s="4" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="C253" s="4" t="s">
         <v>5</v>
@@ -7311,41 +7297,41 @@
         <v>78</v>
       </c>
       <c r="F253" s="5" t="s">
-        <v>151</v>
+        <v>150</v>
       </c>
       <c r="G253" s="5" t="s">
-        <v>220</v>
-      </c>
-    </row>
-    <row r="254" spans="1:7" x14ac:dyDescent="0.3">
+        <v>219</v>
+      </c>
+    </row>
+    <row r="254" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A254" s="4" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="B254" s="4" t="s">
+        <v>90</v>
+      </c>
+      <c r="C254" s="4" t="s">
+        <v>5</v>
+      </c>
+      <c r="D254" s="4" t="s">
+        <v>4</v>
+      </c>
+      <c r="E254" s="4" t="s">
+        <v>147</v>
+      </c>
+      <c r="F254" s="5" t="s">
+        <v>155</v>
+      </c>
+      <c r="G254" s="5" t="s">
+        <v>212</v>
+      </c>
+    </row>
+    <row r="255" spans="1:7" ht="22.5" x14ac:dyDescent="0.25">
+      <c r="A255" s="4" t="s">
+        <v>98</v>
+      </c>
+      <c r="B255" s="4" t="s">
         <v>91</v>
-      </c>
-      <c r="C254" s="4" t="s">
-        <v>5</v>
-      </c>
-      <c r="D254" s="4" t="s">
-        <v>4</v>
-      </c>
-      <c r="E254" s="4" t="s">
-        <v>148</v>
-      </c>
-      <c r="F254" s="5" t="s">
-        <v>156</v>
-      </c>
-      <c r="G254" s="5" t="s">
-        <v>213</v>
-      </c>
-    </row>
-    <row r="255" spans="1:7" ht="21.6" x14ac:dyDescent="0.3">
-      <c r="A255" s="4" t="s">
-        <v>99</v>
-      </c>
-      <c r="B255" s="4" t="s">
-        <v>92</v>
       </c>
       <c r="C255" s="4" t="s">
         <v>5</v>
@@ -7357,18 +7343,18 @@
         <v>79</v>
       </c>
       <c r="F255" s="5" t="s">
-        <v>157</v>
+        <v>156</v>
       </c>
       <c r="G255" s="5" t="s">
-        <v>213</v>
-      </c>
-    </row>
-    <row r="256" spans="1:7" ht="32.4" x14ac:dyDescent="0.3">
+        <v>212</v>
+      </c>
+    </row>
+    <row r="256" spans="1:7" ht="33.75" x14ac:dyDescent="0.25">
       <c r="A256" s="4" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="B256" s="4" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="C256" s="4" t="s">
         <v>5</v>
@@ -7380,18 +7366,18 @@
         <v>78</v>
       </c>
       <c r="F256" s="5" t="s">
-        <v>152</v>
+        <v>151</v>
       </c>
       <c r="G256" s="5" t="s">
-        <v>220</v>
-      </c>
-    </row>
-    <row r="257" spans="1:7" ht="32.4" x14ac:dyDescent="0.3">
+        <v>219</v>
+      </c>
+    </row>
+    <row r="257" spans="1:7" ht="33.75" x14ac:dyDescent="0.25">
       <c r="A257" s="4" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="B257" s="4" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="C257" s="4" t="s">
         <v>5</v>
@@ -7403,18 +7389,18 @@
         <v>78</v>
       </c>
       <c r="F257" s="5" t="s">
-        <v>155</v>
+        <v>154</v>
       </c>
       <c r="G257" s="5" t="s">
-        <v>220</v>
-      </c>
-    </row>
-    <row r="258" spans="1:7" ht="32.4" x14ac:dyDescent="0.3">
+        <v>219</v>
+      </c>
+    </row>
+    <row r="258" spans="1:7" ht="33.75" x14ac:dyDescent="0.25">
       <c r="A258" s="4" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="B258" s="4" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="C258" s="4" t="s">
         <v>5</v>
@@ -7426,18 +7412,18 @@
         <v>78</v>
       </c>
       <c r="F258" s="5" t="s">
-        <v>153</v>
+        <v>152</v>
       </c>
       <c r="G258" s="5" t="s">
-        <v>220</v>
-      </c>
-    </row>
-    <row r="259" spans="1:7" ht="32.4" x14ac:dyDescent="0.3">
+        <v>219</v>
+      </c>
+    </row>
+    <row r="259" spans="1:7" ht="33.75" x14ac:dyDescent="0.25">
       <c r="A259" s="4" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="B259" s="4" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="C259" s="4" t="s">
         <v>5</v>
@@ -7449,18 +7435,18 @@
         <v>78</v>
       </c>
       <c r="F259" s="5" t="s">
-        <v>154</v>
+        <v>153</v>
       </c>
       <c r="G259" s="5" t="s">
-        <v>220</v>
-      </c>
-    </row>
-    <row r="260" spans="1:7" ht="32.4" x14ac:dyDescent="0.3">
+        <v>219</v>
+      </c>
+    </row>
+    <row r="260" spans="1:7" ht="33.75" x14ac:dyDescent="0.25">
       <c r="A260" s="4" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="B260" s="4" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="C260" s="4" t="s">
         <v>5</v>
@@ -7472,15 +7458,15 @@
         <v>78</v>
       </c>
       <c r="F260" s="5" t="s">
-        <v>158</v>
+        <v>157</v>
       </c>
       <c r="G260" s="5" t="s">
-        <v>220</v>
-      </c>
-    </row>
-    <row r="261" spans="1:7" ht="32.4" x14ac:dyDescent="0.3">
+        <v>219</v>
+      </c>
+    </row>
+    <row r="261" spans="1:7" ht="33.75" x14ac:dyDescent="0.25">
       <c r="A261" s="4" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="B261" s="4" t="s">
         <v>73</v>
@@ -7495,18 +7481,18 @@
         <v>78</v>
       </c>
       <c r="F261" s="5" t="s">
-        <v>147</v>
+        <v>146</v>
       </c>
       <c r="G261" s="5" t="s">
-        <v>220</v>
-      </c>
-    </row>
-    <row r="262" spans="1:7" ht="32.4" x14ac:dyDescent="0.3">
+        <v>219</v>
+      </c>
+    </row>
+    <row r="262" spans="1:7" ht="33.75" x14ac:dyDescent="0.25">
       <c r="A262" s="4" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="B262" s="4" t="s">
-        <v>117</v>
+        <v>116</v>
       </c>
       <c r="C262" s="4" t="s">
         <v>5</v>
@@ -7518,15 +7504,15 @@
         <v>78</v>
       </c>
       <c r="F262" s="5" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="G262" s="5" t="s">
-        <v>220</v>
-      </c>
-    </row>
-    <row r="263" spans="1:7" ht="21.6" x14ac:dyDescent="0.3">
+        <v>219</v>
+      </c>
+    </row>
+    <row r="263" spans="1:7" ht="22.5" x14ac:dyDescent="0.25">
       <c r="A263" s="4" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="B263" s="4" t="s">
         <v>74</v>
@@ -7541,15 +7527,15 @@
         <v>8</v>
       </c>
       <c r="F263" s="5" t="s">
-        <v>115</v>
+        <v>114</v>
       </c>
       <c r="G263" s="5" t="s">
-        <v>213</v>
-      </c>
-    </row>
-    <row r="264" spans="1:7" ht="54" x14ac:dyDescent="0.3">
+        <v>212</v>
+      </c>
+    </row>
+    <row r="264" spans="1:7" ht="56.25" x14ac:dyDescent="0.25">
       <c r="A264" s="4" t="s">
-        <v>224</v>
+        <v>223</v>
       </c>
       <c r="B264" s="4" t="s">
         <v>10</v>
@@ -7564,18 +7550,18 @@
         <v>8</v>
       </c>
       <c r="F264" s="5" t="s">
-        <v>183</v>
+        <v>182</v>
       </c>
       <c r="G264" s="5" t="s">
-        <v>173</v>
-      </c>
-    </row>
-    <row r="265" spans="1:7" ht="21.6" x14ac:dyDescent="0.3">
+        <v>172</v>
+      </c>
+    </row>
+    <row r="265" spans="1:7" ht="22.5" x14ac:dyDescent="0.25">
       <c r="A265" s="4" t="s">
+        <v>223</v>
+      </c>
+      <c r="B265" s="4" t="s">
         <v>224</v>
-      </c>
-      <c r="B265" s="4" t="s">
-        <v>225</v>
       </c>
       <c r="C265" s="4" t="s">
         <v>5</v>
@@ -7587,15 +7573,15 @@
         <v>8</v>
       </c>
       <c r="F265" s="5" t="s">
-        <v>226</v>
+        <v>225</v>
       </c>
       <c r="G265" s="5" t="s">
-        <v>173</v>
-      </c>
-    </row>
-    <row r="266" spans="1:7" ht="43.2" x14ac:dyDescent="0.3">
+        <v>172</v>
+      </c>
+    </row>
+    <row r="266" spans="1:7" ht="45" x14ac:dyDescent="0.25">
       <c r="A266" s="4" t="s">
-        <v>224</v>
+        <v>223</v>
       </c>
       <c r="B266" s="4" t="s">
         <v>23</v>
@@ -7610,18 +7596,18 @@
         <v>8</v>
       </c>
       <c r="F266" s="5" t="s">
-        <v>186</v>
+        <v>185</v>
       </c>
       <c r="G266" s="5" t="s">
-        <v>173</v>
-      </c>
-    </row>
-    <row r="267" spans="1:7" x14ac:dyDescent="0.3">
+        <v>172</v>
+      </c>
+    </row>
+    <row r="267" spans="1:7" ht="22.5" x14ac:dyDescent="0.25">
       <c r="A267" s="4" t="s">
-        <v>224</v>
+        <v>223</v>
       </c>
       <c r="B267" s="4" t="s">
-        <v>222</v>
+        <v>221</v>
       </c>
       <c r="C267" s="4" t="s">
         <v>5</v>
@@ -7633,18 +7619,18 @@
         <v>8</v>
       </c>
       <c r="F267" s="5" t="s">
-        <v>227</v>
+        <v>226</v>
       </c>
       <c r="G267" s="5" t="s">
-        <v>173</v>
-      </c>
-    </row>
-    <row r="268" spans="1:7" ht="21.6" x14ac:dyDescent="0.3">
+        <v>172</v>
+      </c>
+    </row>
+    <row r="268" spans="1:7" ht="22.5" x14ac:dyDescent="0.25">
       <c r="A268" s="4" t="s">
-        <v>224</v>
+        <v>223</v>
       </c>
       <c r="B268" s="4" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="C268" s="4" t="s">
         <v>5</v>
@@ -7656,15 +7642,15 @@
         <v>79</v>
       </c>
       <c r="F268" s="5" t="s">
-        <v>178</v>
+        <v>177</v>
       </c>
       <c r="G268" s="5" t="s">
-        <v>188</v>
-      </c>
-    </row>
-    <row r="269" spans="1:7" x14ac:dyDescent="0.3">
+        <v>187</v>
+      </c>
+    </row>
+    <row r="269" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A269" s="4" t="s">
-        <v>224</v>
+        <v>223</v>
       </c>
       <c r="B269" s="4" t="s">
         <v>26</v>
@@ -7679,15 +7665,15 @@
         <v>8</v>
       </c>
       <c r="F269" s="5" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
       <c r="G269" s="5" t="s">
-        <v>188</v>
-      </c>
-    </row>
-    <row r="270" spans="1:7" ht="21.6" x14ac:dyDescent="0.3">
+        <v>187</v>
+      </c>
+    </row>
+    <row r="270" spans="1:7" ht="22.5" x14ac:dyDescent="0.25">
       <c r="A270" s="4" t="s">
-        <v>224</v>
+        <v>223</v>
       </c>
       <c r="B270" s="4" t="s">
         <v>27</v>
@@ -7702,15 +7688,15 @@
         <v>8</v>
       </c>
       <c r="F270" s="5" t="s">
-        <v>189</v>
+        <v>188</v>
       </c>
       <c r="G270" s="5" t="s">
-        <v>188</v>
-      </c>
-    </row>
-    <row r="271" spans="1:7" ht="64.8" x14ac:dyDescent="0.3">
+        <v>187</v>
+      </c>
+    </row>
+    <row r="271" spans="1:7" ht="67.5" x14ac:dyDescent="0.25">
       <c r="A271" s="4" t="s">
-        <v>224</v>
+        <v>223</v>
       </c>
       <c r="B271" s="4" t="s">
         <v>28</v>
@@ -7725,15 +7711,15 @@
         <v>8</v>
       </c>
       <c r="F271" s="5" t="s">
-        <v>190</v>
+        <v>189</v>
       </c>
       <c r="G271" s="5" t="s">
-        <v>188</v>
-      </c>
-    </row>
-    <row r="272" spans="1:7" ht="64.8" x14ac:dyDescent="0.3">
+        <v>187</v>
+      </c>
+    </row>
+    <row r="272" spans="1:7" ht="67.5" x14ac:dyDescent="0.25">
       <c r="A272" s="4" t="s">
-        <v>224</v>
+        <v>223</v>
       </c>
       <c r="B272" s="4" t="s">
         <v>29</v>
@@ -7748,15 +7734,15 @@
         <v>8</v>
       </c>
       <c r="F272" s="5" t="s">
-        <v>191</v>
+        <v>190</v>
       </c>
       <c r="G272" s="5" t="s">
-        <v>188</v>
-      </c>
-    </row>
-    <row r="273" spans="1:7" ht="64.8" x14ac:dyDescent="0.3">
+        <v>187</v>
+      </c>
+    </row>
+    <row r="273" spans="1:7" ht="67.5" x14ac:dyDescent="0.25">
       <c r="A273" s="4" t="s">
-        <v>224</v>
+        <v>223</v>
       </c>
       <c r="B273" s="4" t="s">
         <v>30</v>
@@ -7771,15 +7757,15 @@
         <v>8</v>
       </c>
       <c r="F273" s="5" t="s">
-        <v>192</v>
+        <v>191</v>
       </c>
       <c r="G273" s="5" t="s">
-        <v>188</v>
-      </c>
-    </row>
-    <row r="274" spans="1:7" ht="32.4" x14ac:dyDescent="0.3">
+        <v>187</v>
+      </c>
+    </row>
+    <row r="274" spans="1:7" ht="45" x14ac:dyDescent="0.25">
       <c r="A274" s="4" t="s">
-        <v>224</v>
+        <v>223</v>
       </c>
       <c r="B274" s="4" t="s">
         <v>31</v>
@@ -7794,18 +7780,18 @@
         <v>8</v>
       </c>
       <c r="F274" s="5" t="s">
-        <v>196</v>
+        <v>195</v>
       </c>
       <c r="G274" s="5" t="s">
-        <v>173</v>
-      </c>
-    </row>
-    <row r="275" spans="1:7" ht="54" x14ac:dyDescent="0.3">
+        <v>172</v>
+      </c>
+    </row>
+    <row r="275" spans="1:7" ht="56.25" x14ac:dyDescent="0.25">
       <c r="A275" s="4" t="s">
-        <v>224</v>
+        <v>223</v>
       </c>
       <c r="B275" s="4" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="C275" s="4" t="s">
         <v>5</v>
@@ -7817,15 +7803,15 @@
         <v>8</v>
       </c>
       <c r="F275" s="5" t="s">
-        <v>197</v>
+        <v>196</v>
       </c>
       <c r="G275" s="5" t="s">
-        <v>173</v>
-      </c>
-    </row>
-    <row r="276" spans="1:7" ht="43.2" x14ac:dyDescent="0.3">
+        <v>172</v>
+      </c>
+    </row>
+    <row r="276" spans="1:7" ht="56.25" x14ac:dyDescent="0.25">
       <c r="A276" s="4" t="s">
-        <v>224</v>
+        <v>223</v>
       </c>
       <c r="B276" s="4" t="s">
         <v>32</v>
@@ -7840,15 +7826,15 @@
         <v>77</v>
       </c>
       <c r="F276" s="5" t="s">
+        <v>197</v>
+      </c>
+      <c r="G276" s="5" t="s">
         <v>198</v>
       </c>
-      <c r="G276" s="5" t="s">
-        <v>199</v>
-      </c>
-    </row>
-    <row r="277" spans="1:7" ht="54" x14ac:dyDescent="0.3">
+    </row>
+    <row r="277" spans="1:7" ht="56.25" x14ac:dyDescent="0.25">
       <c r="A277" s="4" t="s">
-        <v>224</v>
+        <v>223</v>
       </c>
       <c r="B277" s="4" t="s">
         <v>33</v>
@@ -7863,15 +7849,15 @@
         <v>77</v>
       </c>
       <c r="F277" s="5" t="s">
-        <v>200</v>
+        <v>199</v>
       </c>
       <c r="G277" s="5" t="s">
-        <v>170</v>
-      </c>
-    </row>
-    <row r="278" spans="1:7" ht="21.6" x14ac:dyDescent="0.3">
+        <v>169</v>
+      </c>
+    </row>
+    <row r="278" spans="1:7" ht="33.75" x14ac:dyDescent="0.25">
       <c r="A278" s="4" t="s">
-        <v>224</v>
+        <v>223</v>
       </c>
       <c r="B278" s="4" t="s">
         <v>34</v>
@@ -7883,18 +7869,18 @@
         <v>4</v>
       </c>
       <c r="E278" s="4" t="s">
+        <v>200</v>
+      </c>
+      <c r="F278" s="5" t="s">
         <v>201</v>
       </c>
-      <c r="F278" s="5" t="s">
+      <c r="G278" s="5" t="s">
         <v>202</v>
       </c>
-      <c r="G278" s="5" t="s">
-        <v>203</v>
-      </c>
-    </row>
-    <row r="279" spans="1:7" ht="21.6" x14ac:dyDescent="0.3">
+    </row>
+    <row r="279" spans="1:7" ht="22.5" x14ac:dyDescent="0.25">
       <c r="A279" s="4" t="s">
-        <v>224</v>
+        <v>223</v>
       </c>
       <c r="B279" s="4" t="s">
         <v>35</v>
@@ -7906,18 +7892,18 @@
         <v>5</v>
       </c>
       <c r="E279" s="4" t="s">
-        <v>201</v>
+        <v>200</v>
       </c>
       <c r="F279" s="5" t="s">
+        <v>203</v>
+      </c>
+      <c r="G279" s="5" t="s">
         <v>204</v>
       </c>
-      <c r="G279" s="5" t="s">
-        <v>205</v>
-      </c>
-    </row>
-    <row r="280" spans="1:7" ht="32.4" x14ac:dyDescent="0.3">
+    </row>
+    <row r="280" spans="1:7" ht="33.75" x14ac:dyDescent="0.25">
       <c r="A280" s="4" t="s">
-        <v>224</v>
+        <v>223</v>
       </c>
       <c r="B280" s="4" t="s">
         <v>36</v>
@@ -7929,18 +7915,18 @@
         <v>4</v>
       </c>
       <c r="E280" s="4" t="s">
-        <v>201</v>
+        <v>200</v>
       </c>
       <c r="F280" s="5" t="s">
+        <v>205</v>
+      </c>
+      <c r="G280" s="5" t="s">
         <v>206</v>
       </c>
-      <c r="G280" s="5" t="s">
-        <v>207</v>
-      </c>
-    </row>
-    <row r="281" spans="1:7" ht="32.4" x14ac:dyDescent="0.3">
+    </row>
+    <row r="281" spans="1:7" ht="33.75" x14ac:dyDescent="0.25">
       <c r="A281" s="4" t="s">
-        <v>224</v>
+        <v>223</v>
       </c>
       <c r="B281" s="4" t="s">
         <v>38</v>
@@ -7955,15 +7941,15 @@
         <v>9</v>
       </c>
       <c r="F281" s="5" t="s">
-        <v>114</v>
+        <v>113</v>
       </c>
       <c r="G281" s="5" t="s">
-        <v>209</v>
-      </c>
-    </row>
-    <row r="282" spans="1:7" ht="43.2" x14ac:dyDescent="0.3">
+        <v>208</v>
+      </c>
+    </row>
+    <row r="282" spans="1:7" ht="45" x14ac:dyDescent="0.25">
       <c r="A282" s="4" t="s">
-        <v>224</v>
+        <v>223</v>
       </c>
       <c r="B282" s="4" t="s">
         <v>39</v>
@@ -7978,38 +7964,38 @@
         <v>9</v>
       </c>
       <c r="F282" s="5" t="s">
+        <v>111</v>
+      </c>
+      <c r="G282" s="5" t="s">
+        <v>208</v>
+      </c>
+    </row>
+    <row r="283" spans="1:7" ht="33.75" x14ac:dyDescent="0.25">
+      <c r="A283" s="4" t="s">
+        <v>223</v>
+      </c>
+      <c r="B283" s="4" t="s">
+        <v>222</v>
+      </c>
+      <c r="C283" s="4" t="s">
+        <v>5</v>
+      </c>
+      <c r="D283" s="4" t="s">
+        <v>5</v>
+      </c>
+      <c r="E283" s="4" t="s">
+        <v>9</v>
+      </c>
+      <c r="F283" s="5" t="s">
         <v>112</v>
       </c>
-      <c r="G282" s="5" t="s">
-        <v>209</v>
-      </c>
-    </row>
-    <row r="283" spans="1:7" ht="32.4" x14ac:dyDescent="0.3">
-      <c r="A283" s="4" t="s">
-        <v>224</v>
-      </c>
-      <c r="B283" s="4" t="s">
+      <c r="G283" s="5" t="s">
+        <v>208</v>
+      </c>
+    </row>
+    <row r="284" spans="1:7" ht="33.75" x14ac:dyDescent="0.25">
+      <c r="A284" s="4" t="s">
         <v>223</v>
-      </c>
-      <c r="C283" s="4" t="s">
-        <v>5</v>
-      </c>
-      <c r="D283" s="4" t="s">
-        <v>5</v>
-      </c>
-      <c r="E283" s="4" t="s">
-        <v>9</v>
-      </c>
-      <c r="F283" s="5" t="s">
-        <v>113</v>
-      </c>
-      <c r="G283" s="5" t="s">
-        <v>209</v>
-      </c>
-    </row>
-    <row r="284" spans="1:7" ht="32.4" x14ac:dyDescent="0.3">
-      <c r="A284" s="4" t="s">
-        <v>224</v>
       </c>
       <c r="B284" s="4" t="s">
         <v>16</v>
@@ -8024,15 +8010,15 @@
         <v>9</v>
       </c>
       <c r="F284" s="5" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="G284" s="5" t="s">
-        <v>209</v>
-      </c>
-    </row>
-    <row r="285" spans="1:7" ht="54" x14ac:dyDescent="0.3">
+        <v>208</v>
+      </c>
+    </row>
+    <row r="285" spans="1:7" ht="56.25" x14ac:dyDescent="0.25">
       <c r="A285" s="4" t="s">
-        <v>224</v>
+        <v>223</v>
       </c>
       <c r="B285" s="4" t="s">
         <v>17</v>
@@ -8047,15 +8033,15 @@
         <v>9</v>
       </c>
       <c r="F285" s="5" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="G285" s="5" t="s">
-        <v>209</v>
-      </c>
-    </row>
-    <row r="286" spans="1:7" ht="32.4" x14ac:dyDescent="0.3">
+        <v>208</v>
+      </c>
+    </row>
+    <row r="286" spans="1:7" ht="33.75" x14ac:dyDescent="0.25">
       <c r="A286" s="4" t="s">
-        <v>224</v>
+        <v>223</v>
       </c>
       <c r="B286" s="4" t="s">
         <v>18</v>
@@ -8070,15 +8056,15 @@
         <v>9</v>
       </c>
       <c r="F286" s="5" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="G286" s="5" t="s">
-        <v>209</v>
-      </c>
-    </row>
-    <row r="287" spans="1:7" ht="43.2" x14ac:dyDescent="0.3">
+        <v>208</v>
+      </c>
+    </row>
+    <row r="287" spans="1:7" ht="45" x14ac:dyDescent="0.25">
       <c r="A287" s="4" t="s">
-        <v>224</v>
+        <v>223</v>
       </c>
       <c r="B287" s="4" t="s">
         <v>19</v>
@@ -8093,15 +8079,15 @@
         <v>9</v>
       </c>
       <c r="F287" s="5" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="G287" s="5" t="s">
-        <v>209</v>
-      </c>
-    </row>
-    <row r="288" spans="1:7" ht="54" x14ac:dyDescent="0.3">
+        <v>208</v>
+      </c>
+    </row>
+    <row r="288" spans="1:7" ht="56.25" x14ac:dyDescent="0.25">
       <c r="A288" s="4" t="s">
-        <v>224</v>
+        <v>223</v>
       </c>
       <c r="B288" s="4" t="s">
         <v>20</v>
@@ -8116,15 +8102,15 @@
         <v>9</v>
       </c>
       <c r="F288" s="5" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="G288" s="5" t="s">
-        <v>209</v>
-      </c>
-    </row>
-    <row r="289" spans="1:7" ht="32.4" x14ac:dyDescent="0.3">
+        <v>208</v>
+      </c>
+    </row>
+    <row r="289" spans="1:7" ht="45" x14ac:dyDescent="0.25">
       <c r="A289" s="4" t="s">
-        <v>224</v>
+        <v>223</v>
       </c>
       <c r="B289" s="4" t="s">
         <v>21</v>
@@ -8139,18 +8125,18 @@
         <v>9</v>
       </c>
       <c r="F289" s="5" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="G289" s="5" t="s">
-        <v>209</v>
-      </c>
-    </row>
-    <row r="290" spans="1:7" ht="32.4" x14ac:dyDescent="0.3">
+        <v>208</v>
+      </c>
+    </row>
+    <row r="290" spans="1:7" ht="45" x14ac:dyDescent="0.25">
       <c r="A290" s="4" t="s">
-        <v>224</v>
+        <v>223</v>
       </c>
       <c r="B290" s="4" t="s">
-        <v>221</v>
+        <v>220</v>
       </c>
       <c r="C290" s="4" t="s">
         <v>5</v>
@@ -8162,15 +8148,15 @@
         <v>9</v>
       </c>
       <c r="F290" s="5" t="s">
-        <v>211</v>
+        <v>210</v>
       </c>
       <c r="G290" s="5" t="s">
-        <v>209</v>
-      </c>
-    </row>
-    <row r="291" spans="1:7" ht="54" x14ac:dyDescent="0.3">
+        <v>208</v>
+      </c>
+    </row>
+    <row r="291" spans="1:7" ht="67.5" x14ac:dyDescent="0.25">
       <c r="A291" s="4" t="s">
-        <v>224</v>
+        <v>223</v>
       </c>
       <c r="B291" s="4" t="s">
         <v>41</v>
@@ -8185,15 +8171,15 @@
         <v>9</v>
       </c>
       <c r="F291" s="5" t="s">
-        <v>212</v>
+        <v>211</v>
       </c>
       <c r="G291" s="5" t="s">
-        <v>209</v>
-      </c>
-    </row>
-    <row r="292" spans="1:7" ht="21.6" x14ac:dyDescent="0.3">
+        <v>208</v>
+      </c>
+    </row>
+    <row r="292" spans="1:7" ht="22.5" x14ac:dyDescent="0.25">
       <c r="A292" s="4" t="s">
-        <v>224</v>
+        <v>223</v>
       </c>
       <c r="B292" s="9" t="s">
         <v>74</v>
@@ -8208,10 +8194,10 @@
         <v>8</v>
       </c>
       <c r="F292" s="5" t="s">
-        <v>115</v>
+        <v>114</v>
       </c>
       <c r="G292" s="5" t="s">
-        <v>213</v>
+        <v>212</v>
       </c>
     </row>
   </sheetData>
@@ -8227,11 +8213,11 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{2AE6CAE7-325B-4FFE-A096-050724C542D5}">
   <sheetPr codeName="Hoja2"/>
   <dimension ref="A1:K4"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <sheetData>
-    <row r="1" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A1" s="10" t="s">
-        <v>160</v>
+        <v>159</v>
       </c>
       <c r="B1" s="10"/>
       <c r="C1" s="10"/>
@@ -8244,9 +8230,9 @@
       <c r="J1" s="10"/>
       <c r="K1" s="10"/>
     </row>
-    <row r="2" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A2" s="10" t="s">
-        <v>161</v>
+        <v>160</v>
       </c>
       <c r="B2" s="10"/>
       <c r="C2" s="10"/>
@@ -8259,9 +8245,9 @@
       <c r="J2" s="10"/>
       <c r="K2" s="10"/>
     </row>
-    <row r="3" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A3" s="11" t="s">
-        <v>162</v>
+        <v>161</v>
       </c>
       <c r="B3" s="11"/>
       <c r="C3" s="11"/>
@@ -8274,9 +8260,9 @@
       <c r="J3" s="11"/>
       <c r="K3" s="11"/>
     </row>
-    <row r="4" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A4" s="11" t="s">
-        <v>163</v>
+        <v>162</v>
       </c>
       <c r="B4" s="11"/>
       <c r="C4" s="11"/>

--- a/Instructivo_Formularios_Junio_2026.xlsx
+++ b/Instructivo_Formularios_Junio_2026.xlsx
@@ -1,32 +1,43 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30131"/>
-  <workbookPr codeName="ThisWorkbook"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="28827"/>
+  <workbookPr codeName="ThisWorkbook" defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\william.boconzaca\Downloads\I\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://arconelgobec-my.sharepoint.com/personal/alexandra_falcon_arconel_gob_ec/Documents/Escritorio/Andrea area Comercializacion/Formatos revision de errores/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0CDD5727-3B59-4C81-A601-B3989EC27B71}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="908" documentId="13_ncr:1_{FCF6FBC8-4607-4E2F-9187-96E2A78FAFC9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{AF27E34B-68E5-4090-8F6B-B7A9B6DB87DE}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11160" xr2:uid="{23C22566-AA08-4718-B9C7-8B52305F382C}"/>
+    <workbookView xWindow="20370" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{23C22566-AA08-4718-B9C7-8B52305F382C}"/>
   </bookViews>
   <sheets>
     <sheet name="Instructivo" sheetId="1" r:id="rId1"/>
     <sheet name="Observaciones adicionales" sheetId="2" state="hidden" r:id="rId2"/>
   </sheets>
-  <calcPr calcId="181029"/>
+  <calcPr calcId="191029"/>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
+    </ext>
+    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
+      <xcalcf:calcFeatures>
+        <xcalcf:feature name="microsoft.com:RD"/>
+        <xcalcf:feature name="microsoft.com:Single"/>
+        <xcalcf:feature name="microsoft.com:FV"/>
+        <xcalcf:feature name="microsoft.com:CNMTM"/>
+        <xcalcf:feature name="microsoft.com:LET_WF"/>
+        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
+        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
+      </xcalcf:calcFeatures>
     </ext>
   </extLst>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2048" uniqueCount="227">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2047" uniqueCount="229">
   <si>
     <t>FORM 1 GASTO AO&amp;M-C SPEE</t>
   </si>
@@ -269,6 +280,9 @@
   </si>
   <si>
     <t>aso_transmisión</t>
+  </si>
+  <si>
+    <t>am_planficado</t>
   </si>
   <si>
     <t>FORM 4 EXPANSION SPEE</t>
@@ -709,6 +723,9 @@
   </si>
   <si>
     <t>Corresponde señalar el proyecto a qué tipo de servicio está determinado.</t>
+  </si>
+  <si>
+    <t>Si</t>
   </si>
 </sst>
 </file>
@@ -805,7 +822,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="12">
+  <cellXfs count="13">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -839,6 +856,9 @@
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -1495,7 +1515,7 @@
         <v>3</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>163</v>
+        <v>164</v>
       </c>
       <c r="E1" s="1" t="s">
         <v>7</v>
@@ -1504,7 +1524,7 @@
         <v>6</v>
       </c>
       <c r="G1" s="2" t="s">
-        <v>168</v>
+        <v>169</v>
       </c>
     </row>
     <row r="2" spans="1:7" x14ac:dyDescent="0.25">
@@ -1512,7 +1532,7 @@
         <v>0</v>
       </c>
       <c r="B2" s="4" t="s">
-        <v>165</v>
+        <v>166</v>
       </c>
       <c r="C2" s="4" t="s">
         <v>4</v>
@@ -1524,10 +1544,10 @@
         <v>8</v>
       </c>
       <c r="F2" s="5" t="s">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="G2" s="6" t="s">
-        <v>169</v>
+        <v>170</v>
       </c>
     </row>
     <row r="3" spans="1:7" x14ac:dyDescent="0.25">
@@ -1547,10 +1567,10 @@
         <v>8</v>
       </c>
       <c r="F3" s="5" t="s">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="G3" s="6" t="s">
-        <v>169</v>
+        <v>170</v>
       </c>
     </row>
     <row r="4" spans="1:7" x14ac:dyDescent="0.25">
@@ -1558,7 +1578,7 @@
         <v>0</v>
       </c>
       <c r="B4" s="4" t="s">
-        <v>164</v>
+        <v>165</v>
       </c>
       <c r="C4" s="4" t="s">
         <v>4</v>
@@ -1570,10 +1590,10 @@
         <v>9</v>
       </c>
       <c r="F4" s="5" t="s">
-        <v>166</v>
+        <v>167</v>
       </c>
       <c r="G4" s="6" t="s">
-        <v>169</v>
+        <v>170</v>
       </c>
     </row>
     <row r="5" spans="1:7" ht="33.75" x14ac:dyDescent="0.25">
@@ -1593,10 +1613,10 @@
         <v>9</v>
       </c>
       <c r="F5" s="5" t="s">
-        <v>167</v>
+        <v>168</v>
       </c>
       <c r="G5" s="5" t="s">
-        <v>208</v>
+        <v>209</v>
       </c>
     </row>
     <row r="6" spans="1:7" ht="56.25" x14ac:dyDescent="0.25">
@@ -1616,10 +1636,10 @@
         <v>9</v>
       </c>
       <c r="F6" s="5" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="G6" s="5" t="s">
-        <v>208</v>
+        <v>209</v>
       </c>
     </row>
     <row r="7" spans="1:7" ht="33.75" x14ac:dyDescent="0.25">
@@ -1639,10 +1659,10 @@
         <v>9</v>
       </c>
       <c r="F7" s="5" t="s">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="G7" s="5" t="s">
-        <v>208</v>
+        <v>209</v>
       </c>
     </row>
     <row r="8" spans="1:7" ht="45" x14ac:dyDescent="0.25">
@@ -1662,10 +1682,10 @@
         <v>9</v>
       </c>
       <c r="F8" s="5" t="s">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="G8" s="5" t="s">
-        <v>208</v>
+        <v>209</v>
       </c>
     </row>
     <row r="9" spans="1:7" ht="56.25" x14ac:dyDescent="0.25">
@@ -1685,10 +1705,10 @@
         <v>9</v>
       </c>
       <c r="F9" s="5" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="G9" s="5" t="s">
-        <v>208</v>
+        <v>209</v>
       </c>
     </row>
     <row r="10" spans="1:7" ht="45" x14ac:dyDescent="0.25">
@@ -1708,10 +1728,10 @@
         <v>9</v>
       </c>
       <c r="F10" s="5" t="s">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="G10" s="5" t="s">
-        <v>208</v>
+        <v>209</v>
       </c>
     </row>
     <row r="11" spans="1:7" ht="45" x14ac:dyDescent="0.25">
@@ -1719,7 +1739,7 @@
         <v>0</v>
       </c>
       <c r="B11" s="4" t="s">
-        <v>220</v>
+        <v>221</v>
       </c>
       <c r="C11" s="4" t="s">
         <v>5</v>
@@ -1731,10 +1751,10 @@
         <v>9</v>
       </c>
       <c r="F11" s="5" t="s">
-        <v>210</v>
+        <v>211</v>
       </c>
       <c r="G11" s="5" t="s">
-        <v>208</v>
+        <v>209</v>
       </c>
     </row>
     <row r="12" spans="1:7" ht="67.5" x14ac:dyDescent="0.25">
@@ -1754,10 +1774,10 @@
         <v>9</v>
       </c>
       <c r="F12" s="5" t="s">
-        <v>211</v>
+        <v>212</v>
       </c>
       <c r="G12" s="5" t="s">
-        <v>208</v>
+        <v>209</v>
       </c>
     </row>
     <row r="13" spans="1:7" x14ac:dyDescent="0.25">
@@ -1765,7 +1785,7 @@
         <v>0</v>
       </c>
       <c r="B13" s="4" t="s">
-        <v>179</v>
+        <v>180</v>
       </c>
       <c r="C13" s="4" t="s">
         <v>4</v>
@@ -1777,10 +1797,10 @@
         <v>9</v>
       </c>
       <c r="F13" s="5" t="s">
-        <v>180</v>
+        <v>181</v>
       </c>
       <c r="G13" s="6" t="s">
-        <v>181</v>
+        <v>182</v>
       </c>
     </row>
     <row r="14" spans="1:7" ht="56.25" x14ac:dyDescent="0.25">
@@ -1800,10 +1820,10 @@
         <v>8</v>
       </c>
       <c r="F14" s="5" t="s">
-        <v>182</v>
+        <v>183</v>
       </c>
       <c r="G14" s="5" t="s">
-        <v>172</v>
+        <v>173</v>
       </c>
     </row>
     <row r="15" spans="1:7" ht="22.5" x14ac:dyDescent="0.25">
@@ -1823,10 +1843,10 @@
         <v>78</v>
       </c>
       <c r="F15" s="5" t="s">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="G15" s="5" t="s">
-        <v>183</v>
+        <v>184</v>
       </c>
     </row>
     <row r="16" spans="1:7" ht="33.75" x14ac:dyDescent="0.25">
@@ -1846,10 +1866,10 @@
         <v>8</v>
       </c>
       <c r="F16" s="5" t="s">
-        <v>171</v>
+        <v>172</v>
       </c>
       <c r="G16" s="5" t="s">
-        <v>178</v>
+        <v>179</v>
       </c>
     </row>
     <row r="17" spans="1:7" ht="22.5" x14ac:dyDescent="0.25">
@@ -1869,10 +1889,10 @@
         <v>8</v>
       </c>
       <c r="F17" s="5" t="s">
-        <v>184</v>
+        <v>185</v>
       </c>
       <c r="G17" s="5" t="s">
-        <v>172</v>
+        <v>173</v>
       </c>
     </row>
     <row r="18" spans="1:7" ht="33.75" x14ac:dyDescent="0.25">
@@ -1892,10 +1912,10 @@
         <v>8</v>
       </c>
       <c r="F18" s="5" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="G18" s="5" t="s">
-        <v>172</v>
+        <v>173</v>
       </c>
     </row>
     <row r="19" spans="1:7" ht="33.75" x14ac:dyDescent="0.25">
@@ -1915,10 +1935,10 @@
         <v>8</v>
       </c>
       <c r="F19" s="5" t="s">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="G19" s="5" t="s">
-        <v>172</v>
+        <v>173</v>
       </c>
     </row>
     <row r="20" spans="1:7" ht="33.75" x14ac:dyDescent="0.25">
@@ -1938,10 +1958,10 @@
         <v>9</v>
       </c>
       <c r="F20" s="5" t="s">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="G20" s="5" t="s">
-        <v>208</v>
+        <v>209</v>
       </c>
     </row>
     <row r="21" spans="1:7" ht="56.25" x14ac:dyDescent="0.25">
@@ -1961,10 +1981,10 @@
         <v>9</v>
       </c>
       <c r="F21" s="5" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="G21" s="5" t="s">
-        <v>208</v>
+        <v>209</v>
       </c>
     </row>
     <row r="22" spans="1:7" ht="33.75" x14ac:dyDescent="0.25">
@@ -1984,10 +2004,10 @@
         <v>9</v>
       </c>
       <c r="F22" s="5" t="s">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="G22" s="5" t="s">
-        <v>208</v>
+        <v>209</v>
       </c>
     </row>
     <row r="23" spans="1:7" ht="45" x14ac:dyDescent="0.25">
@@ -2007,10 +2027,10 @@
         <v>9</v>
       </c>
       <c r="F23" s="5" t="s">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="G23" s="5" t="s">
-        <v>208</v>
+        <v>209</v>
       </c>
     </row>
     <row r="24" spans="1:7" ht="56.25" x14ac:dyDescent="0.25">
@@ -2030,10 +2050,10 @@
         <v>9</v>
       </c>
       <c r="F24" s="5" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="G24" s="5" t="s">
-        <v>208</v>
+        <v>209</v>
       </c>
     </row>
     <row r="25" spans="1:7" ht="45" x14ac:dyDescent="0.25">
@@ -2053,10 +2073,10 @@
         <v>9</v>
       </c>
       <c r="F25" s="5" t="s">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="G25" s="5" t="s">
-        <v>208</v>
+        <v>209</v>
       </c>
     </row>
     <row r="26" spans="1:7" ht="45" x14ac:dyDescent="0.25">
@@ -2064,7 +2084,7 @@
         <v>22</v>
       </c>
       <c r="B26" s="4" t="s">
-        <v>220</v>
+        <v>221</v>
       </c>
       <c r="C26" s="4" t="s">
         <v>5</v>
@@ -2076,10 +2096,10 @@
         <v>9</v>
       </c>
       <c r="F26" s="5" t="s">
-        <v>210</v>
+        <v>211</v>
       </c>
       <c r="G26" s="5" t="s">
-        <v>208</v>
+        <v>209</v>
       </c>
     </row>
     <row r="27" spans="1:7" ht="56.25" x14ac:dyDescent="0.25">
@@ -2099,10 +2119,10 @@
         <v>8</v>
       </c>
       <c r="F27" s="5" t="s">
-        <v>182</v>
+        <v>183</v>
       </c>
       <c r="G27" s="5" t="s">
-        <v>172</v>
+        <v>173</v>
       </c>
     </row>
     <row r="28" spans="1:7" ht="45" x14ac:dyDescent="0.25">
@@ -2122,10 +2142,10 @@
         <v>8</v>
       </c>
       <c r="F28" s="5" t="s">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="G28" s="5" t="s">
-        <v>172</v>
+        <v>173</v>
       </c>
     </row>
     <row r="29" spans="1:7" ht="56.25" x14ac:dyDescent="0.25">
@@ -2133,7 +2153,7 @@
         <v>76</v>
       </c>
       <c r="B29" s="4" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="C29" s="4" t="s">
         <v>5</v>
@@ -2145,10 +2165,10 @@
         <v>8</v>
       </c>
       <c r="F29" s="5" t="s">
+        <v>174</v>
+      </c>
+      <c r="G29" s="5" t="s">
         <v>173</v>
-      </c>
-      <c r="G29" s="5" t="s">
-        <v>172</v>
       </c>
     </row>
     <row r="30" spans="1:7" ht="78.75" x14ac:dyDescent="0.25">
@@ -2168,10 +2188,10 @@
         <v>78</v>
       </c>
       <c r="F30" s="5" t="s">
-        <v>174</v>
+        <v>175</v>
       </c>
       <c r="G30" s="5" t="s">
-        <v>175</v>
+        <v>176</v>
       </c>
     </row>
     <row r="31" spans="1:7" ht="56.25" x14ac:dyDescent="0.25">
@@ -2191,10 +2211,10 @@
         <v>79</v>
       </c>
       <c r="F31" s="5" t="s">
-        <v>176</v>
+        <v>177</v>
       </c>
       <c r="G31" s="5" t="s">
-        <v>186</v>
+        <v>187</v>
       </c>
     </row>
     <row r="32" spans="1:7" ht="56.25" x14ac:dyDescent="0.25">
@@ -2214,10 +2234,10 @@
         <v>8</v>
       </c>
       <c r="F32" s="5" t="s">
-        <v>217</v>
+        <v>218</v>
       </c>
       <c r="G32" s="5" t="s">
-        <v>172</v>
+        <v>173</v>
       </c>
     </row>
     <row r="33" spans="1:7" ht="22.5" x14ac:dyDescent="0.25">
@@ -2225,7 +2245,7 @@
         <v>76</v>
       </c>
       <c r="B33" s="4" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="C33" s="4" t="s">
         <v>5</v>
@@ -2237,10 +2257,10 @@
         <v>79</v>
       </c>
       <c r="F33" s="5" t="s">
-        <v>177</v>
+        <v>178</v>
       </c>
       <c r="G33" s="5" t="s">
-        <v>187</v>
+        <v>188</v>
       </c>
     </row>
     <row r="34" spans="1:7" x14ac:dyDescent="0.25">
@@ -2260,10 +2280,10 @@
         <v>8</v>
       </c>
       <c r="F34" s="5" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="G34" s="5" t="s">
-        <v>187</v>
+        <v>188</v>
       </c>
     </row>
     <row r="35" spans="1:7" ht="22.5" x14ac:dyDescent="0.25">
@@ -2283,10 +2303,10 @@
         <v>8</v>
       </c>
       <c r="F35" s="5" t="s">
+        <v>189</v>
+      </c>
+      <c r="G35" s="5" t="s">
         <v>188</v>
-      </c>
-      <c r="G35" s="5" t="s">
-        <v>187</v>
       </c>
     </row>
     <row r="36" spans="1:7" ht="67.5" x14ac:dyDescent="0.25">
@@ -2306,10 +2326,10 @@
         <v>8</v>
       </c>
       <c r="F36" s="5" t="s">
-        <v>189</v>
+        <v>190</v>
       </c>
       <c r="G36" s="5" t="s">
-        <v>187</v>
+        <v>188</v>
       </c>
     </row>
     <row r="37" spans="1:7" ht="67.5" x14ac:dyDescent="0.25">
@@ -2329,10 +2349,10 @@
         <v>8</v>
       </c>
       <c r="F37" s="5" t="s">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="G37" s="5" t="s">
-        <v>187</v>
+        <v>188</v>
       </c>
     </row>
     <row r="38" spans="1:7" ht="67.5" x14ac:dyDescent="0.25">
@@ -2352,10 +2372,10 @@
         <v>8</v>
       </c>
       <c r="F38" s="5" t="s">
-        <v>191</v>
+        <v>192</v>
       </c>
       <c r="G38" s="5" t="s">
-        <v>187</v>
+        <v>188</v>
       </c>
     </row>
     <row r="39" spans="1:7" ht="45" x14ac:dyDescent="0.25">
@@ -2375,10 +2395,10 @@
         <v>8</v>
       </c>
       <c r="F39" s="5" t="s">
-        <v>192</v>
+        <v>193</v>
       </c>
       <c r="G39" s="5" t="s">
-        <v>172</v>
+        <v>173</v>
       </c>
     </row>
     <row r="40" spans="1:7" ht="67.5" x14ac:dyDescent="0.25">
@@ -2398,10 +2418,10 @@
         <v>8</v>
       </c>
       <c r="F40" s="5" t="s">
-        <v>193</v>
+        <v>194</v>
       </c>
       <c r="G40" s="5" t="s">
-        <v>172</v>
+        <v>173</v>
       </c>
     </row>
     <row r="41" spans="1:7" ht="45" x14ac:dyDescent="0.25">
@@ -2409,7 +2429,7 @@
         <v>76</v>
       </c>
       <c r="B41" s="4" t="s">
-        <v>158</v>
+        <v>159</v>
       </c>
       <c r="C41" s="4" t="s">
         <v>5</v>
@@ -2421,10 +2441,10 @@
         <v>8</v>
       </c>
       <c r="F41" s="5" t="s">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c r="G41" s="5" t="s">
-        <v>172</v>
+        <v>173</v>
       </c>
     </row>
     <row r="42" spans="1:7" ht="45" x14ac:dyDescent="0.25">
@@ -2444,10 +2464,10 @@
         <v>8</v>
       </c>
       <c r="F42" s="5" t="s">
-        <v>195</v>
+        <v>196</v>
       </c>
       <c r="G42" s="5" t="s">
-        <v>172</v>
+        <v>173</v>
       </c>
     </row>
     <row r="43" spans="1:7" ht="56.25" x14ac:dyDescent="0.25">
@@ -2455,7 +2475,7 @@
         <v>76</v>
       </c>
       <c r="B43" s="4" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="C43" s="4" t="s">
         <v>5</v>
@@ -2467,10 +2487,10 @@
         <v>8</v>
       </c>
       <c r="F43" s="5" t="s">
-        <v>196</v>
+        <v>197</v>
       </c>
       <c r="G43" s="5" t="s">
-        <v>172</v>
+        <v>173</v>
       </c>
     </row>
     <row r="44" spans="1:7" ht="56.25" x14ac:dyDescent="0.25">
@@ -2490,10 +2510,10 @@
         <v>77</v>
       </c>
       <c r="F44" s="5" t="s">
-        <v>197</v>
+        <v>198</v>
       </c>
       <c r="G44" s="5" t="s">
-        <v>198</v>
+        <v>199</v>
       </c>
     </row>
     <row r="45" spans="1:7" ht="56.25" x14ac:dyDescent="0.25">
@@ -2513,10 +2533,10 @@
         <v>77</v>
       </c>
       <c r="F45" s="5" t="s">
-        <v>199</v>
+        <v>200</v>
       </c>
       <c r="G45" s="5" t="s">
-        <v>169</v>
+        <v>170</v>
       </c>
     </row>
     <row r="46" spans="1:7" ht="33.75" x14ac:dyDescent="0.25">
@@ -2533,13 +2553,13 @@
         <v>4</v>
       </c>
       <c r="E46" s="4" t="s">
-        <v>200</v>
+        <v>201</v>
       </c>
       <c r="F46" s="5" t="s">
-        <v>201</v>
+        <v>202</v>
       </c>
       <c r="G46" s="5" t="s">
-        <v>202</v>
+        <v>203</v>
       </c>
     </row>
     <row r="47" spans="1:7" ht="22.5" x14ac:dyDescent="0.25">
@@ -2556,13 +2576,13 @@
         <v>5</v>
       </c>
       <c r="E47" s="4" t="s">
-        <v>200</v>
+        <v>201</v>
       </c>
       <c r="F47" s="5" t="s">
-        <v>203</v>
+        <v>204</v>
       </c>
       <c r="G47" s="5" t="s">
-        <v>204</v>
+        <v>205</v>
       </c>
     </row>
     <row r="48" spans="1:7" ht="33.75" x14ac:dyDescent="0.25">
@@ -2579,13 +2599,13 @@
         <v>4</v>
       </c>
       <c r="E48" s="4" t="s">
-        <v>200</v>
+        <v>201</v>
       </c>
       <c r="F48" s="5" t="s">
-        <v>205</v>
+        <v>206</v>
       </c>
       <c r="G48" s="5" t="s">
-        <v>206</v>
+        <v>207</v>
       </c>
     </row>
     <row r="49" spans="1:7" ht="33.75" x14ac:dyDescent="0.25">
@@ -2605,10 +2625,10 @@
         <v>9</v>
       </c>
       <c r="F49" s="5" t="s">
-        <v>207</v>
+        <v>208</v>
       </c>
       <c r="G49" s="5" t="s">
-        <v>208</v>
+        <v>209</v>
       </c>
     </row>
     <row r="50" spans="1:7" ht="33.75" x14ac:dyDescent="0.25">
@@ -2628,10 +2648,10 @@
         <v>9</v>
       </c>
       <c r="F50" s="5" t="s">
-        <v>209</v>
+        <v>210</v>
       </c>
       <c r="G50" s="5" t="s">
-        <v>208</v>
+        <v>209</v>
       </c>
     </row>
     <row r="51" spans="1:7" ht="45" x14ac:dyDescent="0.25">
@@ -2651,10 +2671,10 @@
         <v>9</v>
       </c>
       <c r="F51" s="5" t="s">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="G51" s="5" t="s">
-        <v>208</v>
+        <v>209</v>
       </c>
     </row>
     <row r="52" spans="1:7" ht="33.75" x14ac:dyDescent="0.25">
@@ -2674,10 +2694,10 @@
         <v>9</v>
       </c>
       <c r="F52" s="5" t="s">
-        <v>112</v>
+        <v>113</v>
       </c>
       <c r="G52" s="5" t="s">
-        <v>208</v>
+        <v>209</v>
       </c>
     </row>
     <row r="53" spans="1:7" ht="33.75" x14ac:dyDescent="0.25">
@@ -2697,10 +2717,10 @@
         <v>9</v>
       </c>
       <c r="F53" s="5" t="s">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="G53" s="5" t="s">
-        <v>208</v>
+        <v>209</v>
       </c>
     </row>
     <row r="54" spans="1:7" ht="56.25" x14ac:dyDescent="0.25">
@@ -2720,10 +2740,10 @@
         <v>9</v>
       </c>
       <c r="F54" s="5" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="G54" s="5" t="s">
-        <v>208</v>
+        <v>209</v>
       </c>
     </row>
     <row r="55" spans="1:7" ht="33.75" x14ac:dyDescent="0.25">
@@ -2743,10 +2763,10 @@
         <v>9</v>
       </c>
       <c r="F55" s="5" t="s">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="G55" s="5" t="s">
-        <v>208</v>
+        <v>209</v>
       </c>
     </row>
     <row r="56" spans="1:7" ht="45" x14ac:dyDescent="0.25">
@@ -2766,10 +2786,10 @@
         <v>9</v>
       </c>
       <c r="F56" s="5" t="s">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="G56" s="5" t="s">
-        <v>208</v>
+        <v>209</v>
       </c>
     </row>
     <row r="57" spans="1:7" ht="56.25" x14ac:dyDescent="0.25">
@@ -2789,10 +2809,10 @@
         <v>9</v>
       </c>
       <c r="F57" s="5" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="G57" s="5" t="s">
-        <v>208</v>
+        <v>209</v>
       </c>
     </row>
     <row r="58" spans="1:7" ht="45" x14ac:dyDescent="0.25">
@@ -2812,10 +2832,10 @@
         <v>9</v>
       </c>
       <c r="F58" s="5" t="s">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="G58" s="5" t="s">
-        <v>208</v>
+        <v>209</v>
       </c>
     </row>
     <row r="59" spans="1:7" ht="45" x14ac:dyDescent="0.25">
@@ -2823,7 +2843,7 @@
         <v>76</v>
       </c>
       <c r="B59" s="4" t="s">
-        <v>220</v>
+        <v>221</v>
       </c>
       <c r="C59" s="4" t="s">
         <v>5</v>
@@ -2835,10 +2855,10 @@
         <v>9</v>
       </c>
       <c r="F59" s="5" t="s">
-        <v>210</v>
+        <v>211</v>
       </c>
       <c r="G59" s="5" t="s">
-        <v>208</v>
+        <v>209</v>
       </c>
     </row>
     <row r="60" spans="1:7" ht="67.5" x14ac:dyDescent="0.25">
@@ -2858,10 +2878,10 @@
         <v>9</v>
       </c>
       <c r="F60" s="5" t="s">
-        <v>211</v>
+        <v>212</v>
       </c>
       <c r="G60" s="5" t="s">
-        <v>208</v>
+        <v>209</v>
       </c>
     </row>
     <row r="61" spans="1:7" ht="22.5" x14ac:dyDescent="0.25">
@@ -2881,10 +2901,10 @@
         <v>9</v>
       </c>
       <c r="F61" s="5" t="s">
-        <v>119</v>
+        <v>120</v>
       </c>
       <c r="G61" s="5" t="s">
-        <v>213</v>
+        <v>214</v>
       </c>
     </row>
     <row r="62" spans="1:7" ht="22.5" x14ac:dyDescent="0.25">
@@ -2904,10 +2924,10 @@
         <v>9</v>
       </c>
       <c r="F62" s="5" t="s">
-        <v>117</v>
+        <v>118</v>
       </c>
       <c r="G62" s="5" t="s">
-        <v>213</v>
+        <v>214</v>
       </c>
     </row>
     <row r="63" spans="1:7" ht="45" x14ac:dyDescent="0.25">
@@ -2927,10 +2947,10 @@
         <v>9</v>
       </c>
       <c r="F63" s="5" t="s">
-        <v>120</v>
+        <v>121</v>
       </c>
       <c r="G63" s="5" t="s">
-        <v>213</v>
+        <v>214</v>
       </c>
     </row>
     <row r="64" spans="1:7" ht="33.75" x14ac:dyDescent="0.25">
@@ -2950,10 +2970,10 @@
         <v>9</v>
       </c>
       <c r="F64" s="5" t="s">
-        <v>121</v>
+        <v>122</v>
       </c>
       <c r="G64" s="5" t="s">
-        <v>213</v>
+        <v>214</v>
       </c>
     </row>
     <row r="65" spans="1:7" ht="33.75" x14ac:dyDescent="0.25">
@@ -2973,10 +2993,10 @@
         <v>9</v>
       </c>
       <c r="F65" s="5" t="s">
-        <v>122</v>
+        <v>123</v>
       </c>
       <c r="G65" s="5" t="s">
-        <v>213</v>
+        <v>214</v>
       </c>
     </row>
     <row r="66" spans="1:7" ht="33.75" x14ac:dyDescent="0.25">
@@ -2996,10 +3016,10 @@
         <v>9</v>
       </c>
       <c r="F66" s="5" t="s">
-        <v>123</v>
+        <v>124</v>
       </c>
       <c r="G66" s="5" t="s">
-        <v>213</v>
+        <v>214</v>
       </c>
     </row>
     <row r="67" spans="1:7" ht="22.5" x14ac:dyDescent="0.25">
@@ -3019,10 +3039,10 @@
         <v>9</v>
       </c>
       <c r="F67" s="5" t="s">
-        <v>118</v>
+        <v>119</v>
       </c>
       <c r="G67" s="5" t="s">
-        <v>213</v>
+        <v>214</v>
       </c>
     </row>
     <row r="68" spans="1:7" ht="33.75" x14ac:dyDescent="0.25">
@@ -3042,10 +3062,10 @@
         <v>9</v>
       </c>
       <c r="F68" s="5" t="s">
-        <v>124</v>
+        <v>125</v>
       </c>
       <c r="G68" s="5" t="s">
-        <v>213</v>
+        <v>214</v>
       </c>
     </row>
     <row r="69" spans="1:7" ht="33.75" x14ac:dyDescent="0.25">
@@ -3065,10 +3085,10 @@
         <v>9</v>
       </c>
       <c r="F69" s="5" t="s">
-        <v>125</v>
+        <v>126</v>
       </c>
       <c r="G69" s="5" t="s">
-        <v>213</v>
+        <v>214</v>
       </c>
     </row>
     <row r="70" spans="1:7" ht="33.75" x14ac:dyDescent="0.25">
@@ -3088,10 +3108,10 @@
         <v>9</v>
       </c>
       <c r="F70" s="5" t="s">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="G70" s="5" t="s">
-        <v>213</v>
+        <v>214</v>
       </c>
     </row>
     <row r="71" spans="1:7" ht="22.5" x14ac:dyDescent="0.25">
@@ -3111,10 +3131,10 @@
         <v>9</v>
       </c>
       <c r="F71" s="5" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="G71" s="5" t="s">
-        <v>213</v>
+        <v>214</v>
       </c>
     </row>
     <row r="72" spans="1:7" ht="22.5" x14ac:dyDescent="0.25">
@@ -3134,10 +3154,10 @@
         <v>9</v>
       </c>
       <c r="F72" s="5" t="s">
-        <v>128</v>
+        <v>129</v>
       </c>
       <c r="G72" s="5" t="s">
-        <v>213</v>
+        <v>214</v>
       </c>
     </row>
     <row r="73" spans="1:7" ht="22.5" x14ac:dyDescent="0.25">
@@ -3157,10 +3177,10 @@
         <v>9</v>
       </c>
       <c r="F73" s="5" t="s">
-        <v>129</v>
+        <v>130</v>
       </c>
       <c r="G73" s="5" t="s">
-        <v>213</v>
+        <v>214</v>
       </c>
     </row>
     <row r="74" spans="1:7" ht="22.5" x14ac:dyDescent="0.25">
@@ -3180,10 +3200,10 @@
         <v>9</v>
       </c>
       <c r="F74" s="5" t="s">
-        <v>130</v>
+        <v>131</v>
       </c>
       <c r="G74" s="5" t="s">
-        <v>213</v>
+        <v>214</v>
       </c>
     </row>
     <row r="75" spans="1:7" ht="33.75" x14ac:dyDescent="0.25">
@@ -3203,10 +3223,10 @@
         <v>9</v>
       </c>
       <c r="F75" s="5" t="s">
-        <v>131</v>
+        <v>132</v>
       </c>
       <c r="G75" s="5" t="s">
-        <v>213</v>
+        <v>214</v>
       </c>
     </row>
     <row r="76" spans="1:7" ht="22.5" x14ac:dyDescent="0.25">
@@ -3226,10 +3246,10 @@
         <v>9</v>
       </c>
       <c r="F76" s="5" t="s">
-        <v>132</v>
+        <v>133</v>
       </c>
       <c r="G76" s="5" t="s">
-        <v>213</v>
+        <v>214</v>
       </c>
     </row>
     <row r="77" spans="1:7" ht="33.75" x14ac:dyDescent="0.25">
@@ -3249,10 +3269,10 @@
         <v>9</v>
       </c>
       <c r="F77" s="5" t="s">
-        <v>133</v>
+        <v>134</v>
       </c>
       <c r="G77" s="5" t="s">
-        <v>213</v>
+        <v>214</v>
       </c>
     </row>
     <row r="78" spans="1:7" ht="22.5" x14ac:dyDescent="0.25">
@@ -3272,10 +3292,10 @@
         <v>9</v>
       </c>
       <c r="F78" s="5" t="s">
-        <v>134</v>
+        <v>135</v>
       </c>
       <c r="G78" s="5" t="s">
-        <v>213</v>
+        <v>214</v>
       </c>
     </row>
     <row r="79" spans="1:7" ht="22.5" x14ac:dyDescent="0.25">
@@ -3295,10 +3315,10 @@
         <v>9</v>
       </c>
       <c r="F79" s="5" t="s">
-        <v>135</v>
+        <v>136</v>
       </c>
       <c r="G79" s="5" t="s">
-        <v>213</v>
+        <v>214</v>
       </c>
     </row>
     <row r="80" spans="1:7" ht="22.5" x14ac:dyDescent="0.25">
@@ -3318,10 +3338,10 @@
         <v>9</v>
       </c>
       <c r="F80" s="5" t="s">
-        <v>136</v>
+        <v>137</v>
       </c>
       <c r="G80" s="5" t="s">
-        <v>213</v>
+        <v>214</v>
       </c>
     </row>
     <row r="81" spans="1:7" ht="22.5" x14ac:dyDescent="0.25">
@@ -3341,10 +3361,10 @@
         <v>9</v>
       </c>
       <c r="F81" s="5" t="s">
-        <v>138</v>
+        <v>139</v>
       </c>
       <c r="G81" s="5" t="s">
-        <v>213</v>
+        <v>214</v>
       </c>
     </row>
     <row r="82" spans="1:7" ht="22.5" x14ac:dyDescent="0.25">
@@ -3364,10 +3384,10 @@
         <v>9</v>
       </c>
       <c r="F82" s="5" t="s">
-        <v>137</v>
+        <v>138</v>
       </c>
       <c r="G82" s="5" t="s">
-        <v>213</v>
+        <v>214</v>
       </c>
     </row>
     <row r="83" spans="1:7" ht="33.75" x14ac:dyDescent="0.25">
@@ -3387,10 +3407,10 @@
         <v>9</v>
       </c>
       <c r="F83" s="5" t="s">
-        <v>139</v>
+        <v>140</v>
       </c>
       <c r="G83" s="5" t="s">
-        <v>213</v>
+        <v>214</v>
       </c>
     </row>
     <row r="84" spans="1:7" ht="22.5" x14ac:dyDescent="0.25">
@@ -3410,10 +3430,10 @@
         <v>9</v>
       </c>
       <c r="F84" s="5" t="s">
-        <v>140</v>
+        <v>141</v>
       </c>
       <c r="G84" s="5" t="s">
-        <v>213</v>
+        <v>214</v>
       </c>
     </row>
     <row r="85" spans="1:7" ht="22.5" x14ac:dyDescent="0.25">
@@ -3433,10 +3453,10 @@
         <v>9</v>
       </c>
       <c r="F85" s="5" t="s">
-        <v>141</v>
+        <v>142</v>
       </c>
       <c r="G85" s="5" t="s">
-        <v>213</v>
+        <v>214</v>
       </c>
     </row>
     <row r="86" spans="1:7" ht="22.5" x14ac:dyDescent="0.25">
@@ -3456,10 +3476,10 @@
         <v>9</v>
       </c>
       <c r="F86" s="5" t="s">
-        <v>142</v>
+        <v>143</v>
       </c>
       <c r="G86" s="5" t="s">
-        <v>213</v>
+        <v>214</v>
       </c>
     </row>
     <row r="87" spans="1:7" ht="33.75" x14ac:dyDescent="0.25">
@@ -3479,10 +3499,10 @@
         <v>9</v>
       </c>
       <c r="F87" s="5" t="s">
-        <v>143</v>
+        <v>144</v>
       </c>
       <c r="G87" s="5" t="s">
-        <v>213</v>
+        <v>214</v>
       </c>
     </row>
     <row r="88" spans="1:7" ht="33.75" x14ac:dyDescent="0.25">
@@ -3502,10 +3522,10 @@
         <v>9</v>
       </c>
       <c r="F88" s="5" t="s">
-        <v>144</v>
+        <v>145</v>
       </c>
       <c r="G88" s="5" t="s">
-        <v>213</v>
+        <v>214</v>
       </c>
     </row>
     <row r="89" spans="1:7" ht="45" x14ac:dyDescent="0.25">
@@ -3525,10 +3545,10 @@
         <v>8</v>
       </c>
       <c r="F89" s="5" t="s">
-        <v>214</v>
+        <v>215</v>
       </c>
       <c r="G89" s="5" t="s">
-        <v>172</v>
+        <v>173</v>
       </c>
     </row>
     <row r="90" spans="1:7" ht="45" x14ac:dyDescent="0.25">
@@ -3545,13 +3565,13 @@
         <v>4</v>
       </c>
       <c r="E90" s="4" t="s">
-        <v>200</v>
+        <v>201</v>
       </c>
       <c r="F90" s="5" t="s">
-        <v>145</v>
+        <v>146</v>
       </c>
       <c r="G90" s="5" t="s">
-        <v>216</v>
+        <v>217</v>
       </c>
     </row>
     <row r="91" spans="1:7" ht="45" x14ac:dyDescent="0.25">
@@ -3568,13 +3588,13 @@
         <v>4</v>
       </c>
       <c r="E91" s="4" t="s">
-        <v>200</v>
+        <v>201</v>
       </c>
       <c r="F91" s="5" t="s">
-        <v>215</v>
+        <v>216</v>
       </c>
       <c r="G91" s="5" t="s">
-        <v>216</v>
+        <v>217</v>
       </c>
     </row>
     <row r="92" spans="1:7" ht="33.75" x14ac:dyDescent="0.25">
@@ -3588,16 +3608,16 @@
         <v>5</v>
       </c>
       <c r="D92" s="4" t="s">
-        <v>4</v>
+        <v>228</v>
       </c>
       <c r="E92" s="4" t="s">
         <v>78</v>
       </c>
       <c r="F92" s="5" t="s">
-        <v>146</v>
+        <v>147</v>
       </c>
       <c r="G92" s="5" t="s">
-        <v>219</v>
+        <v>220</v>
       </c>
     </row>
     <row r="93" spans="1:7" ht="33.75" x14ac:dyDescent="0.25">
@@ -3605,22 +3625,22 @@
         <v>76</v>
       </c>
       <c r="B93" s="4" t="s">
-        <v>116</v>
+        <v>117</v>
       </c>
       <c r="C93" s="4" t="s">
         <v>5</v>
       </c>
       <c r="D93" s="4" t="s">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="E93" s="4" t="s">
         <v>78</v>
       </c>
       <c r="F93" s="5" t="s">
-        <v>115</v>
+        <v>116</v>
       </c>
       <c r="G93" s="5" t="s">
-        <v>219</v>
+        <v>220</v>
       </c>
     </row>
     <row r="94" spans="1:7" ht="22.5" x14ac:dyDescent="0.25">
@@ -3640,15 +3660,15 @@
         <v>8</v>
       </c>
       <c r="F94" s="5" t="s">
-        <v>114</v>
+        <v>115</v>
       </c>
       <c r="G94" s="5" t="s">
-        <v>212</v>
+        <v>213</v>
       </c>
     </row>
     <row r="95" spans="1:7" ht="56.25" x14ac:dyDescent="0.25">
       <c r="A95" s="4" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="B95" s="4" t="s">
         <v>10</v>
@@ -3663,15 +3683,15 @@
         <v>8</v>
       </c>
       <c r="F95" s="5" t="s">
-        <v>182</v>
+        <v>183</v>
       </c>
       <c r="G95" s="5" t="s">
-        <v>172</v>
+        <v>173</v>
       </c>
     </row>
     <row r="96" spans="1:7" ht="45" x14ac:dyDescent="0.25">
       <c r="A96" s="4" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="B96" s="4" t="s">
         <v>23</v>
@@ -3686,15 +3706,15 @@
         <v>8</v>
       </c>
       <c r="F96" s="5" t="s">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="G96" s="5" t="s">
-        <v>172</v>
-      </c>
-    </row>
-    <row r="97" spans="1:7" ht="78.75" x14ac:dyDescent="0.25">
+        <v>173</v>
+      </c>
+    </row>
+    <row r="97" spans="1:7" ht="22.5" x14ac:dyDescent="0.25">
       <c r="A97" s="4" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="B97" s="4" t="s">
         <v>24</v>
@@ -3708,19 +3728,17 @@
       <c r="E97" s="4" t="s">
         <v>78</v>
       </c>
-      <c r="F97" s="5" t="s">
-        <v>174</v>
-      </c>
-      <c r="G97" s="5" t="s">
-        <v>175</v>
-      </c>
+      <c r="F97" s="8" t="s">
+        <v>178</v>
+      </c>
+      <c r="G97" s="5"/>
     </row>
     <row r="98" spans="1:7" ht="22.5" x14ac:dyDescent="0.25">
       <c r="A98" s="4" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="B98" s="4" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="C98" s="4" t="s">
         <v>5</v>
@@ -3732,15 +3750,15 @@
         <v>79</v>
       </c>
       <c r="F98" s="5" t="s">
-        <v>177</v>
+        <v>178</v>
       </c>
       <c r="G98" s="5" t="s">
-        <v>187</v>
+        <v>188</v>
       </c>
     </row>
     <row r="99" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A99" s="4" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="B99" s="4" t="s">
         <v>26</v>
@@ -3755,15 +3773,15 @@
         <v>8</v>
       </c>
       <c r="F99" s="5" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="G99" s="5" t="s">
-        <v>187</v>
+        <v>188</v>
       </c>
     </row>
     <row r="100" spans="1:7" ht="22.5" x14ac:dyDescent="0.25">
       <c r="A100" s="4" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="B100" s="4" t="s">
         <v>27</v>
@@ -3778,15 +3796,15 @@
         <v>8</v>
       </c>
       <c r="F100" s="5" t="s">
+        <v>189</v>
+      </c>
+      <c r="G100" s="5" t="s">
         <v>188</v>
-      </c>
-      <c r="G100" s="5" t="s">
-        <v>187</v>
       </c>
     </row>
     <row r="101" spans="1:7" ht="67.5" x14ac:dyDescent="0.25">
       <c r="A101" s="4" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="B101" s="4" t="s">
         <v>28</v>
@@ -3801,15 +3819,15 @@
         <v>8</v>
       </c>
       <c r="F101" s="5" t="s">
-        <v>189</v>
+        <v>190</v>
       </c>
       <c r="G101" s="5" t="s">
-        <v>187</v>
+        <v>188</v>
       </c>
     </row>
     <row r="102" spans="1:7" ht="67.5" x14ac:dyDescent="0.25">
       <c r="A102" s="4" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="B102" s="4" t="s">
         <v>29</v>
@@ -3824,15 +3842,15 @@
         <v>8</v>
       </c>
       <c r="F102" s="5" t="s">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="G102" s="5" t="s">
-        <v>187</v>
+        <v>188</v>
       </c>
     </row>
     <row r="103" spans="1:7" ht="67.5" x14ac:dyDescent="0.25">
       <c r="A103" s="4" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="B103" s="4" t="s">
         <v>30</v>
@@ -3847,15 +3865,15 @@
         <v>8</v>
       </c>
       <c r="F103" s="5" t="s">
-        <v>191</v>
+        <v>192</v>
       </c>
       <c r="G103" s="5" t="s">
-        <v>187</v>
+        <v>188</v>
       </c>
     </row>
     <row r="104" spans="1:7" ht="45" x14ac:dyDescent="0.25">
       <c r="A104" s="4" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="B104" s="4" t="s">
         <v>80</v>
@@ -3870,15 +3888,15 @@
         <v>8</v>
       </c>
       <c r="F104" s="5" t="s">
-        <v>192</v>
+        <v>193</v>
       </c>
       <c r="G104" s="5" t="s">
-        <v>172</v>
+        <v>173</v>
       </c>
     </row>
     <row r="105" spans="1:7" ht="67.5" x14ac:dyDescent="0.25">
       <c r="A105" s="4" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="B105" s="4" t="s">
         <v>13</v>
@@ -3893,15 +3911,15 @@
         <v>8</v>
       </c>
       <c r="F105" s="5" t="s">
-        <v>193</v>
+        <v>194</v>
       </c>
       <c r="G105" s="5" t="s">
-        <v>172</v>
+        <v>173</v>
       </c>
     </row>
     <row r="106" spans="1:7" ht="45" x14ac:dyDescent="0.25">
       <c r="A106" s="4" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="B106" s="4" t="s">
         <v>31</v>
@@ -3916,18 +3934,18 @@
         <v>8</v>
       </c>
       <c r="F106" s="5" t="s">
-        <v>195</v>
+        <v>196</v>
       </c>
       <c r="G106" s="5" t="s">
-        <v>172</v>
+        <v>173</v>
       </c>
     </row>
     <row r="107" spans="1:7" ht="56.25" x14ac:dyDescent="0.25">
       <c r="A107" s="4" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="B107" s="4" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="C107" s="4" t="s">
         <v>5</v>
@@ -3939,15 +3957,15 @@
         <v>8</v>
       </c>
       <c r="F107" s="5" t="s">
-        <v>196</v>
+        <v>197</v>
       </c>
       <c r="G107" s="5" t="s">
-        <v>172</v>
+        <v>173</v>
       </c>
     </row>
     <row r="108" spans="1:7" ht="56.25" x14ac:dyDescent="0.25">
       <c r="A108" s="4" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="B108" s="4" t="s">
         <v>32</v>
@@ -3962,15 +3980,15 @@
         <v>77</v>
       </c>
       <c r="F108" s="5" t="s">
-        <v>197</v>
+        <v>198</v>
       </c>
       <c r="G108" s="5" t="s">
-        <v>198</v>
+        <v>199</v>
       </c>
     </row>
     <row r="109" spans="1:7" ht="56.25" x14ac:dyDescent="0.25">
       <c r="A109" s="4" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="B109" s="4" t="s">
         <v>33</v>
@@ -3985,15 +4003,15 @@
         <v>77</v>
       </c>
       <c r="F109" s="5" t="s">
-        <v>199</v>
+        <v>200</v>
       </c>
       <c r="G109" s="5" t="s">
-        <v>169</v>
+        <v>170</v>
       </c>
     </row>
     <row r="110" spans="1:7" ht="33.75" x14ac:dyDescent="0.25">
       <c r="A110" s="4" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="B110" s="4" t="s">
         <v>34</v>
@@ -4005,18 +4023,18 @@
         <v>4</v>
       </c>
       <c r="E110" s="4" t="s">
-        <v>200</v>
+        <v>201</v>
       </c>
       <c r="F110" s="5" t="s">
-        <v>201</v>
+        <v>202</v>
       </c>
       <c r="G110" s="5" t="s">
-        <v>202</v>
+        <v>203</v>
       </c>
     </row>
     <row r="111" spans="1:7" ht="22.5" x14ac:dyDescent="0.25">
       <c r="A111" s="4" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="B111" s="4" t="s">
         <v>35</v>
@@ -4028,18 +4046,18 @@
         <v>5</v>
       </c>
       <c r="E111" s="4" t="s">
-        <v>200</v>
+        <v>201</v>
       </c>
       <c r="F111" s="5" t="s">
-        <v>203</v>
+        <v>204</v>
       </c>
       <c r="G111" s="5" t="s">
-        <v>204</v>
+        <v>205</v>
       </c>
     </row>
     <row r="112" spans="1:7" ht="33.75" x14ac:dyDescent="0.25">
       <c r="A112" s="4" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="B112" s="4" t="s">
         <v>36</v>
@@ -4051,18 +4069,18 @@
         <v>4</v>
       </c>
       <c r="E112" s="4" t="s">
-        <v>200</v>
+        <v>201</v>
       </c>
       <c r="F112" s="5" t="s">
-        <v>205</v>
+        <v>206</v>
       </c>
       <c r="G112" s="5" t="s">
-        <v>206</v>
+        <v>207</v>
       </c>
     </row>
     <row r="113" spans="1:7" ht="33.75" x14ac:dyDescent="0.25">
       <c r="A113" s="4" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="B113" s="4" t="s">
         <v>38</v>
@@ -4077,15 +4095,15 @@
         <v>9</v>
       </c>
       <c r="F113" s="5" t="s">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="G113" s="5" t="s">
-        <v>208</v>
+        <v>209</v>
       </c>
     </row>
     <row r="114" spans="1:7" ht="45" x14ac:dyDescent="0.25">
       <c r="A114" s="4" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="B114" s="4" t="s">
         <v>39</v>
@@ -4100,15 +4118,15 @@
         <v>9</v>
       </c>
       <c r="F114" s="5" t="s">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="G114" s="5" t="s">
-        <v>208</v>
+        <v>209</v>
       </c>
     </row>
     <row r="115" spans="1:7" ht="33.75" x14ac:dyDescent="0.25">
       <c r="A115" s="4" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="B115" s="4" t="s">
         <v>40</v>
@@ -4123,15 +4141,15 @@
         <v>9</v>
       </c>
       <c r="F115" s="5" t="s">
-        <v>112</v>
+        <v>113</v>
       </c>
       <c r="G115" s="5" t="s">
-        <v>208</v>
+        <v>209</v>
       </c>
     </row>
     <row r="116" spans="1:7" ht="33.75" x14ac:dyDescent="0.25">
       <c r="A116" s="4" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="B116" s="4" t="s">
         <v>16</v>
@@ -4146,15 +4164,15 @@
         <v>9</v>
       </c>
       <c r="F116" s="5" t="s">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="G116" s="5" t="s">
-        <v>208</v>
+        <v>209</v>
       </c>
     </row>
     <row r="117" spans="1:7" ht="56.25" x14ac:dyDescent="0.25">
       <c r="A117" s="4" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="B117" s="4" t="s">
         <v>17</v>
@@ -4169,15 +4187,15 @@
         <v>9</v>
       </c>
       <c r="F117" s="5" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="G117" s="5" t="s">
-        <v>208</v>
+        <v>209</v>
       </c>
     </row>
     <row r="118" spans="1:7" ht="33.75" x14ac:dyDescent="0.25">
       <c r="A118" s="4" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="B118" s="4" t="s">
         <v>18</v>
@@ -4192,15 +4210,15 @@
         <v>9</v>
       </c>
       <c r="F118" s="5" t="s">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="G118" s="5" t="s">
-        <v>208</v>
+        <v>209</v>
       </c>
     </row>
     <row r="119" spans="1:7" ht="45" x14ac:dyDescent="0.25">
       <c r="A119" s="4" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="B119" s="4" t="s">
         <v>19</v>
@@ -4215,15 +4233,15 @@
         <v>9</v>
       </c>
       <c r="F119" s="5" t="s">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="G119" s="5" t="s">
-        <v>208</v>
+        <v>209</v>
       </c>
     </row>
     <row r="120" spans="1:7" ht="56.25" x14ac:dyDescent="0.25">
       <c r="A120" s="4" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="B120" s="4" t="s">
         <v>20</v>
@@ -4238,15 +4256,15 @@
         <v>9</v>
       </c>
       <c r="F120" s="5" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="G120" s="5" t="s">
-        <v>208</v>
+        <v>209</v>
       </c>
     </row>
     <row r="121" spans="1:7" ht="45" x14ac:dyDescent="0.25">
       <c r="A121" s="4" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="B121" s="4" t="s">
         <v>21</v>
@@ -4261,18 +4279,18 @@
         <v>9</v>
       </c>
       <c r="F121" s="5" t="s">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="G121" s="5" t="s">
-        <v>208</v>
+        <v>209</v>
       </c>
     </row>
     <row r="122" spans="1:7" ht="45" x14ac:dyDescent="0.25">
       <c r="A122" s="4" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="B122" s="4" t="s">
-        <v>220</v>
+        <v>221</v>
       </c>
       <c r="C122" s="4" t="s">
         <v>5</v>
@@ -4284,15 +4302,15 @@
         <v>9</v>
       </c>
       <c r="F122" s="5" t="s">
-        <v>210</v>
+        <v>211</v>
       </c>
       <c r="G122" s="5" t="s">
-        <v>208</v>
+        <v>209</v>
       </c>
     </row>
     <row r="123" spans="1:7" ht="67.5" x14ac:dyDescent="0.25">
       <c r="A123" s="4" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="B123" s="4" t="s">
         <v>41</v>
@@ -4307,15 +4325,15 @@
         <v>9</v>
       </c>
       <c r="F123" s="5" t="s">
-        <v>211</v>
+        <v>212</v>
       </c>
       <c r="G123" s="5" t="s">
-        <v>208</v>
+        <v>209</v>
       </c>
     </row>
     <row r="124" spans="1:7" ht="33.75" x14ac:dyDescent="0.25">
       <c r="A124" s="4" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="B124" s="4" t="s">
         <v>42</v>
@@ -4330,15 +4348,15 @@
         <v>9</v>
       </c>
       <c r="F124" s="5" t="s">
-        <v>119</v>
+        <v>120</v>
       </c>
       <c r="G124" s="5" t="s">
-        <v>208</v>
+        <v>209</v>
       </c>
     </row>
     <row r="125" spans="1:7" ht="33.75" x14ac:dyDescent="0.25">
       <c r="A125" s="4" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="B125" s="4" t="s">
         <v>43</v>
@@ -4353,15 +4371,15 @@
         <v>9</v>
       </c>
       <c r="F125" s="5" t="s">
-        <v>117</v>
+        <v>118</v>
       </c>
       <c r="G125" s="5" t="s">
-        <v>208</v>
+        <v>209</v>
       </c>
     </row>
     <row r="126" spans="1:7" ht="45" x14ac:dyDescent="0.25">
       <c r="A126" s="4" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="B126" s="4" t="s">
         <v>44</v>
@@ -4376,15 +4394,15 @@
         <v>9</v>
       </c>
       <c r="F126" s="5" t="s">
-        <v>120</v>
+        <v>121</v>
       </c>
       <c r="G126" s="5" t="s">
-        <v>208</v>
+        <v>209</v>
       </c>
     </row>
     <row r="127" spans="1:7" ht="33.75" x14ac:dyDescent="0.25">
       <c r="A127" s="4" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="B127" s="4" t="s">
         <v>45</v>
@@ -4399,15 +4417,15 @@
         <v>9</v>
       </c>
       <c r="F127" s="5" t="s">
-        <v>121</v>
+        <v>122</v>
       </c>
       <c r="G127" s="5" t="s">
-        <v>208</v>
+        <v>209</v>
       </c>
     </row>
     <row r="128" spans="1:7" ht="33.75" x14ac:dyDescent="0.25">
       <c r="A128" s="4" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="B128" s="4" t="s">
         <v>46</v>
@@ -4422,15 +4440,15 @@
         <v>9</v>
       </c>
       <c r="F128" s="5" t="s">
-        <v>122</v>
+        <v>123</v>
       </c>
       <c r="G128" s="5" t="s">
-        <v>208</v>
+        <v>209</v>
       </c>
     </row>
     <row r="129" spans="1:7" ht="33.75" x14ac:dyDescent="0.25">
       <c r="A129" s="4" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="B129" s="4" t="s">
         <v>47</v>
@@ -4445,15 +4463,15 @@
         <v>9</v>
       </c>
       <c r="F129" s="5" t="s">
-        <v>123</v>
+        <v>124</v>
       </c>
       <c r="G129" s="5" t="s">
-        <v>208</v>
+        <v>209</v>
       </c>
     </row>
     <row r="130" spans="1:7" ht="33.75" x14ac:dyDescent="0.25">
       <c r="A130" s="4" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="B130" s="4" t="s">
         <v>48</v>
@@ -4468,15 +4486,15 @@
         <v>9</v>
       </c>
       <c r="F130" s="5" t="s">
-        <v>118</v>
+        <v>119</v>
       </c>
       <c r="G130" s="5" t="s">
-        <v>208</v>
+        <v>209</v>
       </c>
     </row>
     <row r="131" spans="1:7" ht="33.75" x14ac:dyDescent="0.25">
       <c r="A131" s="4" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="B131" s="4" t="s">
         <v>49</v>
@@ -4491,15 +4509,15 @@
         <v>9</v>
       </c>
       <c r="F131" s="5" t="s">
-        <v>124</v>
+        <v>125</v>
       </c>
       <c r="G131" s="5" t="s">
-        <v>208</v>
+        <v>209</v>
       </c>
     </row>
     <row r="132" spans="1:7" ht="33.75" x14ac:dyDescent="0.25">
       <c r="A132" s="4" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="B132" s="4" t="s">
         <v>50</v>
@@ -4514,15 +4532,15 @@
         <v>9</v>
       </c>
       <c r="F132" s="5" t="s">
-        <v>125</v>
+        <v>126</v>
       </c>
       <c r="G132" s="5" t="s">
-        <v>208</v>
+        <v>209</v>
       </c>
     </row>
     <row r="133" spans="1:7" ht="33.75" x14ac:dyDescent="0.25">
       <c r="A133" s="4" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="B133" s="4" t="s">
         <v>51</v>
@@ -4537,15 +4555,15 @@
         <v>9</v>
       </c>
       <c r="F133" s="5" t="s">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="G133" s="5" t="s">
-        <v>208</v>
+        <v>209</v>
       </c>
     </row>
     <row r="134" spans="1:7" ht="33.75" x14ac:dyDescent="0.25">
       <c r="A134" s="4" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="B134" s="4" t="s">
         <v>52</v>
@@ -4560,15 +4578,15 @@
         <v>9</v>
       </c>
       <c r="F134" s="5" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="G134" s="5" t="s">
-        <v>208</v>
+        <v>209</v>
       </c>
     </row>
     <row r="135" spans="1:7" ht="33.75" x14ac:dyDescent="0.25">
       <c r="A135" s="4" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="B135" s="4" t="s">
         <v>53</v>
@@ -4583,15 +4601,15 @@
         <v>9</v>
       </c>
       <c r="F135" s="5" t="s">
-        <v>128</v>
+        <v>129</v>
       </c>
       <c r="G135" s="5" t="s">
-        <v>208</v>
+        <v>209</v>
       </c>
     </row>
     <row r="136" spans="1:7" ht="33.75" x14ac:dyDescent="0.25">
       <c r="A136" s="4" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="B136" s="4" t="s">
         <v>54</v>
@@ -4606,15 +4624,15 @@
         <v>9</v>
       </c>
       <c r="F136" s="5" t="s">
-        <v>129</v>
+        <v>130</v>
       </c>
       <c r="G136" s="5" t="s">
-        <v>208</v>
+        <v>209</v>
       </c>
     </row>
     <row r="137" spans="1:7" ht="33.75" x14ac:dyDescent="0.25">
       <c r="A137" s="4" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="B137" s="4" t="s">
         <v>55</v>
@@ -4629,15 +4647,15 @@
         <v>9</v>
       </c>
       <c r="F137" s="5" t="s">
-        <v>130</v>
+        <v>131</v>
       </c>
       <c r="G137" s="5" t="s">
-        <v>208</v>
+        <v>209</v>
       </c>
     </row>
     <row r="138" spans="1:7" ht="33.75" x14ac:dyDescent="0.25">
       <c r="A138" s="4" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="B138" s="4" t="s">
         <v>56</v>
@@ -4652,15 +4670,15 @@
         <v>9</v>
       </c>
       <c r="F138" s="5" t="s">
-        <v>131</v>
+        <v>132</v>
       </c>
       <c r="G138" s="5" t="s">
-        <v>208</v>
+        <v>209</v>
       </c>
     </row>
     <row r="139" spans="1:7" ht="33.75" x14ac:dyDescent="0.25">
       <c r="A139" s="4" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="B139" s="4" t="s">
         <v>57</v>
@@ -4675,18 +4693,18 @@
         <v>9</v>
       </c>
       <c r="F139" s="5" t="s">
-        <v>132</v>
+        <v>133</v>
       </c>
       <c r="G139" s="5" t="s">
-        <v>208</v>
+        <v>209</v>
       </c>
     </row>
     <row r="140" spans="1:7" ht="33.75" x14ac:dyDescent="0.25">
       <c r="A140" s="4" t="s">
+        <v>82</v>
+      </c>
+      <c r="B140" s="4" t="s">
         <v>81</v>
-      </c>
-      <c r="B140" s="4" t="s">
-        <v>58</v>
       </c>
       <c r="C140" s="4" t="s">
         <v>5</v>
@@ -4698,15 +4716,15 @@
         <v>9</v>
       </c>
       <c r="F140" s="5" t="s">
-        <v>133</v>
+        <v>134</v>
       </c>
       <c r="G140" s="5" t="s">
-        <v>208</v>
+        <v>209</v>
       </c>
     </row>
     <row r="141" spans="1:7" ht="33.75" x14ac:dyDescent="0.25">
       <c r="A141" s="4" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="B141" s="4" t="s">
         <v>59</v>
@@ -4721,15 +4739,15 @@
         <v>9</v>
       </c>
       <c r="F141" s="5" t="s">
-        <v>134</v>
+        <v>135</v>
       </c>
       <c r="G141" s="5" t="s">
-        <v>208</v>
+        <v>209</v>
       </c>
     </row>
     <row r="142" spans="1:7" ht="33.75" x14ac:dyDescent="0.25">
       <c r="A142" s="4" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="B142" s="4" t="s">
         <v>60</v>
@@ -4744,15 +4762,15 @@
         <v>9</v>
       </c>
       <c r="F142" s="5" t="s">
-        <v>135</v>
+        <v>136</v>
       </c>
       <c r="G142" s="5" t="s">
-        <v>208</v>
+        <v>209</v>
       </c>
     </row>
     <row r="143" spans="1:7" ht="33.75" x14ac:dyDescent="0.25">
       <c r="A143" s="4" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="B143" s="4" t="s">
         <v>61</v>
@@ -4767,15 +4785,15 @@
         <v>9</v>
       </c>
       <c r="F143" s="5" t="s">
-        <v>136</v>
+        <v>137</v>
       </c>
       <c r="G143" s="5" t="s">
-        <v>208</v>
+        <v>209</v>
       </c>
     </row>
     <row r="144" spans="1:7" ht="33.75" x14ac:dyDescent="0.25">
       <c r="A144" s="4" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="B144" s="4" t="s">
         <v>62</v>
@@ -4790,15 +4808,15 @@
         <v>9</v>
       </c>
       <c r="F144" s="5" t="s">
-        <v>138</v>
+        <v>139</v>
       </c>
       <c r="G144" s="5" t="s">
-        <v>208</v>
+        <v>209</v>
       </c>
     </row>
     <row r="145" spans="1:7" ht="33.75" x14ac:dyDescent="0.25">
       <c r="A145" s="4" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="B145" s="4" t="s">
         <v>63</v>
@@ -4813,15 +4831,15 @@
         <v>9</v>
       </c>
       <c r="F145" s="5" t="s">
-        <v>137</v>
+        <v>138</v>
       </c>
       <c r="G145" s="5" t="s">
-        <v>208</v>
+        <v>209</v>
       </c>
     </row>
     <row r="146" spans="1:7" ht="33.75" x14ac:dyDescent="0.25">
       <c r="A146" s="4" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="B146" s="4" t="s">
         <v>64</v>
@@ -4836,15 +4854,15 @@
         <v>9</v>
       </c>
       <c r="F146" s="5" t="s">
-        <v>139</v>
+        <v>140</v>
       </c>
       <c r="G146" s="5" t="s">
-        <v>208</v>
+        <v>209</v>
       </c>
     </row>
     <row r="147" spans="1:7" ht="33.75" x14ac:dyDescent="0.25">
       <c r="A147" s="4" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="B147" s="4" t="s">
         <v>65</v>
@@ -4859,15 +4877,15 @@
         <v>9</v>
       </c>
       <c r="F147" s="5" t="s">
-        <v>140</v>
+        <v>141</v>
       </c>
       <c r="G147" s="5" t="s">
-        <v>208</v>
+        <v>209</v>
       </c>
     </row>
     <row r="148" spans="1:7" ht="33.75" x14ac:dyDescent="0.25">
       <c r="A148" s="4" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="B148" s="4" t="s">
         <v>66</v>
@@ -4882,15 +4900,15 @@
         <v>9</v>
       </c>
       <c r="F148" s="5" t="s">
-        <v>141</v>
+        <v>142</v>
       </c>
       <c r="G148" s="5" t="s">
-        <v>208</v>
+        <v>209</v>
       </c>
     </row>
     <row r="149" spans="1:7" ht="33.75" x14ac:dyDescent="0.25">
       <c r="A149" s="4" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="B149" s="4" t="s">
         <v>67</v>
@@ -4905,15 +4923,15 @@
         <v>9</v>
       </c>
       <c r="F149" s="5" t="s">
-        <v>142</v>
+        <v>143</v>
       </c>
       <c r="G149" s="5" t="s">
-        <v>208</v>
+        <v>209</v>
       </c>
     </row>
     <row r="150" spans="1:7" ht="33.75" x14ac:dyDescent="0.25">
       <c r="A150" s="4" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="B150" s="4" t="s">
         <v>68</v>
@@ -4928,15 +4946,15 @@
         <v>9</v>
       </c>
       <c r="F150" s="5" t="s">
-        <v>143</v>
+        <v>144</v>
       </c>
       <c r="G150" s="5" t="s">
-        <v>208</v>
+        <v>209</v>
       </c>
     </row>
     <row r="151" spans="1:7" ht="33.75" x14ac:dyDescent="0.25">
       <c r="A151" s="4" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="B151" s="4" t="s">
         <v>69</v>
@@ -4951,15 +4969,15 @@
         <v>9</v>
       </c>
       <c r="F151" s="5" t="s">
-        <v>144</v>
+        <v>145</v>
       </c>
       <c r="G151" s="5" t="s">
-        <v>208</v>
+        <v>209</v>
       </c>
     </row>
     <row r="152" spans="1:7" ht="45" x14ac:dyDescent="0.25">
       <c r="A152" s="4" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="B152" s="4" t="s">
         <v>70</v>
@@ -4974,15 +4992,15 @@
         <v>8</v>
       </c>
       <c r="F152" s="5" t="s">
-        <v>214</v>
+        <v>215</v>
       </c>
       <c r="G152" s="5" t="s">
-        <v>172</v>
+        <v>173</v>
       </c>
     </row>
     <row r="153" spans="1:7" ht="45" x14ac:dyDescent="0.25">
       <c r="A153" s="4" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="B153" s="4" t="s">
         <v>71</v>
@@ -4994,18 +5012,18 @@
         <v>4</v>
       </c>
       <c r="E153" s="4" t="s">
-        <v>200</v>
+        <v>201</v>
       </c>
       <c r="F153" s="5" t="s">
-        <v>145</v>
+        <v>146</v>
       </c>
       <c r="G153" s="5" t="s">
-        <v>216</v>
+        <v>217</v>
       </c>
     </row>
     <row r="154" spans="1:7" ht="45" x14ac:dyDescent="0.25">
       <c r="A154" s="4" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="B154" s="4" t="s">
         <v>72</v>
@@ -5017,18 +5035,18 @@
         <v>4</v>
       </c>
       <c r="E154" s="4" t="s">
-        <v>200</v>
+        <v>201</v>
       </c>
       <c r="F154" s="5" t="s">
-        <v>215</v>
+        <v>216</v>
       </c>
       <c r="G154" s="5" t="s">
-        <v>216</v>
+        <v>217</v>
       </c>
     </row>
     <row r="155" spans="1:7" ht="33.75" x14ac:dyDescent="0.25">
       <c r="A155" s="4" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="B155" s="4" t="s">
         <v>73</v>
@@ -5036,45 +5054,45 @@
       <c r="C155" s="4" t="s">
         <v>5</v>
       </c>
-      <c r="D155" s="4" t="s">
+      <c r="D155" s="12" t="s">
         <v>5</v>
       </c>
       <c r="E155" s="4" t="s">
         <v>78</v>
       </c>
       <c r="F155" s="5" t="s">
-        <v>146</v>
+        <v>147</v>
       </c>
       <c r="G155" s="5" t="s">
-        <v>219</v>
+        <v>220</v>
       </c>
     </row>
     <row r="156" spans="1:7" ht="33.75" x14ac:dyDescent="0.25">
       <c r="A156" s="4" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="B156" s="4" t="s">
-        <v>116</v>
+        <v>117</v>
       </c>
       <c r="C156" s="4" t="s">
         <v>5</v>
       </c>
-      <c r="D156" s="4" t="s">
+      <c r="D156" s="12" t="s">
         <v>5</v>
       </c>
       <c r="E156" s="4" t="s">
         <v>78</v>
       </c>
       <c r="F156" s="5" t="s">
-        <v>115</v>
+        <v>116</v>
       </c>
       <c r="G156" s="5" t="s">
-        <v>219</v>
+        <v>220</v>
       </c>
     </row>
     <row r="157" spans="1:7" ht="22.5" x14ac:dyDescent="0.25">
       <c r="A157" s="4" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="B157" s="4" t="s">
         <v>74</v>
@@ -5089,15 +5107,15 @@
         <v>8</v>
       </c>
       <c r="F157" s="5" t="s">
-        <v>114</v>
+        <v>115</v>
       </c>
       <c r="G157" s="5" t="s">
-        <v>212</v>
+        <v>213</v>
       </c>
     </row>
     <row r="158" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A158" s="4" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="B158" s="4" t="s">
         <v>13</v>
@@ -5112,18 +5130,18 @@
         <v>8</v>
       </c>
       <c r="F158" s="5" t="s">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="G158" s="6" t="s">
-        <v>169</v>
+        <v>170</v>
       </c>
     </row>
     <row r="159" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A159" s="4" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="B159" s="4" t="s">
-        <v>164</v>
+        <v>165</v>
       </c>
       <c r="C159" s="4" t="s">
         <v>4</v>
@@ -5135,15 +5153,15 @@
         <v>9</v>
       </c>
       <c r="F159" s="5" t="s">
-        <v>166</v>
+        <v>167</v>
       </c>
       <c r="G159" s="6" t="s">
-        <v>169</v>
+        <v>170</v>
       </c>
     </row>
     <row r="160" spans="1:7" ht="33.75" x14ac:dyDescent="0.25">
       <c r="A160" s="4" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="B160" s="4" t="s">
         <v>16</v>
@@ -5158,15 +5176,15 @@
         <v>9</v>
       </c>
       <c r="F160" s="5" t="s">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="G160" s="5" t="s">
-        <v>208</v>
+        <v>209</v>
       </c>
     </row>
     <row r="161" spans="1:7" ht="56.25" x14ac:dyDescent="0.25">
       <c r="A161" s="4" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="B161" s="4" t="s">
         <v>17</v>
@@ -5181,15 +5199,15 @@
         <v>9</v>
       </c>
       <c r="F161" s="5" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="G161" s="5" t="s">
-        <v>208</v>
+        <v>209</v>
       </c>
     </row>
     <row r="162" spans="1:7" ht="33.75" x14ac:dyDescent="0.25">
       <c r="A162" s="4" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="B162" s="4" t="s">
         <v>18</v>
@@ -5204,15 +5222,15 @@
         <v>9</v>
       </c>
       <c r="F162" s="5" t="s">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="G162" s="5" t="s">
-        <v>208</v>
+        <v>209</v>
       </c>
     </row>
     <row r="163" spans="1:7" ht="45" x14ac:dyDescent="0.25">
       <c r="A163" s="4" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="B163" s="4" t="s">
         <v>19</v>
@@ -5227,15 +5245,15 @@
         <v>9</v>
       </c>
       <c r="F163" s="5" t="s">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="G163" s="5" t="s">
-        <v>208</v>
+        <v>209</v>
       </c>
     </row>
     <row r="164" spans="1:7" ht="56.25" x14ac:dyDescent="0.25">
       <c r="A164" s="4" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="B164" s="4" t="s">
         <v>20</v>
@@ -5250,15 +5268,15 @@
         <v>9</v>
       </c>
       <c r="F164" s="5" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="G164" s="5" t="s">
-        <v>208</v>
+        <v>209</v>
       </c>
     </row>
     <row r="165" spans="1:7" ht="45" x14ac:dyDescent="0.25">
       <c r="A165" s="4" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="B165" s="4" t="s">
         <v>21</v>
@@ -5273,18 +5291,18 @@
         <v>9</v>
       </c>
       <c r="F165" s="5" t="s">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="G165" s="5" t="s">
-        <v>208</v>
+        <v>209</v>
       </c>
     </row>
     <row r="166" spans="1:7" ht="45" x14ac:dyDescent="0.25">
       <c r="A166" s="4" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="B166" s="4" t="s">
-        <v>220</v>
+        <v>221</v>
       </c>
       <c r="C166" s="4" t="s">
         <v>5</v>
@@ -5296,15 +5314,15 @@
         <v>9</v>
       </c>
       <c r="F166" s="5" t="s">
-        <v>210</v>
+        <v>211</v>
       </c>
       <c r="G166" s="5" t="s">
-        <v>208</v>
+        <v>209</v>
       </c>
     </row>
     <row r="167" spans="1:7" ht="67.5" x14ac:dyDescent="0.25">
       <c r="A167" s="4" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="B167" s="4" t="s">
         <v>41</v>
@@ -5319,15 +5337,15 @@
         <v>9</v>
       </c>
       <c r="F167" s="5" t="s">
-        <v>211</v>
+        <v>212</v>
       </c>
       <c r="G167" s="5" t="s">
-        <v>208</v>
+        <v>209</v>
       </c>
     </row>
     <row r="168" spans="1:7" ht="56.25" x14ac:dyDescent="0.25">
       <c r="A168" s="4" t="s">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="B168" s="4" t="s">
         <v>10</v>
@@ -5342,15 +5360,15 @@
         <v>8</v>
       </c>
       <c r="F168" s="5" t="s">
-        <v>182</v>
+        <v>183</v>
       </c>
       <c r="G168" s="5" t="s">
-        <v>172</v>
+        <v>173</v>
       </c>
     </row>
     <row r="169" spans="1:7" ht="22.5" x14ac:dyDescent="0.25">
       <c r="A169" s="4" t="s">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="B169" s="4" t="s">
         <v>11</v>
@@ -5365,15 +5383,15 @@
         <v>78</v>
       </c>
       <c r="F169" s="5" t="s">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="G169" s="5" t="s">
-        <v>183</v>
+        <v>184</v>
       </c>
     </row>
     <row r="170" spans="1:7" ht="33.75" x14ac:dyDescent="0.25">
       <c r="A170" s="4" t="s">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="B170" s="4" t="s">
         <v>12</v>
@@ -5388,15 +5406,15 @@
         <v>8</v>
       </c>
       <c r="F170" s="5" t="s">
-        <v>107</v>
+        <v>108</v>
       </c>
       <c r="G170" s="5" t="s">
-        <v>178</v>
+        <v>179</v>
       </c>
     </row>
     <row r="171" spans="1:7" ht="33.75" x14ac:dyDescent="0.25">
       <c r="A171" s="4" t="s">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="B171" s="4" t="s">
         <v>14</v>
@@ -5411,15 +5429,15 @@
         <v>8</v>
       </c>
       <c r="F171" s="5" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="G171" s="5" t="s">
-        <v>172</v>
+        <v>173</v>
       </c>
     </row>
     <row r="172" spans="1:7" ht="33.75" x14ac:dyDescent="0.25">
       <c r="A172" s="4" t="s">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="B172" s="4" t="s">
         <v>15</v>
@@ -5434,15 +5452,15 @@
         <v>8</v>
       </c>
       <c r="F172" s="5" t="s">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="G172" s="5" t="s">
-        <v>172</v>
+        <v>173</v>
       </c>
     </row>
     <row r="173" spans="1:7" ht="33.75" x14ac:dyDescent="0.25">
       <c r="A173" s="4" t="s">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="B173" s="4" t="s">
         <v>16</v>
@@ -5457,15 +5475,15 @@
         <v>9</v>
       </c>
       <c r="F173" s="5" t="s">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="G173" s="5" t="s">
-        <v>208</v>
+        <v>209</v>
       </c>
     </row>
     <row r="174" spans="1:7" ht="56.25" x14ac:dyDescent="0.25">
       <c r="A174" s="4" t="s">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="B174" s="4" t="s">
         <v>17</v>
@@ -5480,15 +5498,15 @@
         <v>9</v>
       </c>
       <c r="F174" s="5" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="G174" s="5" t="s">
-        <v>208</v>
+        <v>209</v>
       </c>
     </row>
     <row r="175" spans="1:7" ht="33.75" x14ac:dyDescent="0.25">
       <c r="A175" s="4" t="s">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="B175" s="4" t="s">
         <v>18</v>
@@ -5503,15 +5521,15 @@
         <v>9</v>
       </c>
       <c r="F175" s="5" t="s">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="G175" s="5" t="s">
-        <v>208</v>
+        <v>209</v>
       </c>
     </row>
     <row r="176" spans="1:7" ht="45" x14ac:dyDescent="0.25">
       <c r="A176" s="4" t="s">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="B176" s="4" t="s">
         <v>19</v>
@@ -5526,15 +5544,15 @@
         <v>9</v>
       </c>
       <c r="F176" s="5" t="s">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="G176" s="5" t="s">
-        <v>208</v>
+        <v>209</v>
       </c>
     </row>
     <row r="177" spans="1:7" ht="56.25" x14ac:dyDescent="0.25">
       <c r="A177" s="4" t="s">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="B177" s="4" t="s">
         <v>20</v>
@@ -5549,15 +5567,15 @@
         <v>9</v>
       </c>
       <c r="F177" s="5" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="G177" s="5" t="s">
-        <v>208</v>
+        <v>209</v>
       </c>
     </row>
     <row r="178" spans="1:7" ht="45" x14ac:dyDescent="0.25">
       <c r="A178" s="4" t="s">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="B178" s="4" t="s">
         <v>21</v>
@@ -5572,18 +5590,18 @@
         <v>9</v>
       </c>
       <c r="F178" s="5" t="s">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="G178" s="5" t="s">
-        <v>208</v>
+        <v>209</v>
       </c>
     </row>
     <row r="179" spans="1:7" ht="45" x14ac:dyDescent="0.25">
       <c r="A179" s="4" t="s">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="B179" s="4" t="s">
-        <v>220</v>
+        <v>221</v>
       </c>
       <c r="C179" s="4" t="s">
         <v>5</v>
@@ -5595,15 +5613,15 @@
         <v>9</v>
       </c>
       <c r="F179" s="5" t="s">
-        <v>210</v>
+        <v>211</v>
       </c>
       <c r="G179" s="5" t="s">
-        <v>208</v>
+        <v>209</v>
       </c>
     </row>
     <row r="180" spans="1:7" ht="56.25" x14ac:dyDescent="0.25">
       <c r="A180" s="4" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="B180" s="4" t="s">
         <v>10</v>
@@ -5618,15 +5636,15 @@
         <v>8</v>
       </c>
       <c r="F180" s="5" t="s">
-        <v>182</v>
+        <v>183</v>
       </c>
       <c r="G180" s="5" t="s">
-        <v>172</v>
+        <v>173</v>
       </c>
     </row>
     <row r="181" spans="1:7" ht="45" x14ac:dyDescent="0.25">
       <c r="A181" s="4" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="B181" s="4" t="s">
         <v>23</v>
@@ -5641,18 +5659,18 @@
         <v>8</v>
       </c>
       <c r="F181" s="5" t="s">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="G181" s="5" t="s">
-        <v>172</v>
+        <v>173</v>
       </c>
     </row>
     <row r="182" spans="1:7" ht="56.25" x14ac:dyDescent="0.25">
       <c r="A182" s="4" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="B182" s="4" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="C182" s="4" t="s">
         <v>5</v>
@@ -5664,15 +5682,15 @@
         <v>8</v>
       </c>
       <c r="F182" s="5" t="s">
+        <v>174</v>
+      </c>
+      <c r="G182" s="5" t="s">
         <v>173</v>
-      </c>
-      <c r="G182" s="5" t="s">
-        <v>172</v>
       </c>
     </row>
     <row r="183" spans="1:7" ht="78.75" x14ac:dyDescent="0.25">
       <c r="A183" s="4" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="B183" s="4" t="s">
         <v>24</v>
@@ -5687,15 +5705,15 @@
         <v>78</v>
       </c>
       <c r="F183" s="5" t="s">
-        <v>174</v>
+        <v>175</v>
       </c>
       <c r="G183" s="5" t="s">
-        <v>175</v>
+        <v>176</v>
       </c>
     </row>
     <row r="184" spans="1:7" ht="56.25" x14ac:dyDescent="0.25">
       <c r="A184" s="4" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="B184" s="4" t="s">
         <v>25</v>
@@ -5710,15 +5728,15 @@
         <v>79</v>
       </c>
       <c r="F184" s="5" t="s">
-        <v>176</v>
+        <v>177</v>
       </c>
       <c r="G184" s="5" t="s">
-        <v>186</v>
+        <v>187</v>
       </c>
     </row>
     <row r="185" spans="1:7" ht="56.25" x14ac:dyDescent="0.25">
       <c r="A185" s="4" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="B185" s="4" t="s">
         <v>75</v>
@@ -5733,18 +5751,18 @@
         <v>8</v>
       </c>
       <c r="F185" s="5" t="s">
-        <v>218</v>
+        <v>219</v>
       </c>
       <c r="G185" s="5" t="s">
-        <v>172</v>
+        <v>173</v>
       </c>
     </row>
     <row r="186" spans="1:7" ht="22.5" x14ac:dyDescent="0.25">
       <c r="A186" s="4" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="B186" s="4" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="C186" s="4" t="s">
         <v>5</v>
@@ -5756,15 +5774,15 @@
         <v>79</v>
       </c>
       <c r="F186" s="5" t="s">
-        <v>177</v>
+        <v>178</v>
       </c>
       <c r="G186" s="5" t="s">
-        <v>187</v>
+        <v>188</v>
       </c>
     </row>
     <row r="187" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A187" s="4" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="B187" s="4" t="s">
         <v>26</v>
@@ -5779,15 +5797,15 @@
         <v>8</v>
       </c>
       <c r="F187" s="5" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="G187" s="5" t="s">
-        <v>187</v>
+        <v>188</v>
       </c>
     </row>
     <row r="188" spans="1:7" ht="22.5" x14ac:dyDescent="0.25">
       <c r="A188" s="4" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="B188" s="4" t="s">
         <v>27</v>
@@ -5802,15 +5820,15 @@
         <v>8</v>
       </c>
       <c r="F188" s="5" t="s">
+        <v>189</v>
+      </c>
+      <c r="G188" s="5" t="s">
         <v>188</v>
-      </c>
-      <c r="G188" s="5" t="s">
-        <v>187</v>
       </c>
     </row>
     <row r="189" spans="1:7" ht="67.5" x14ac:dyDescent="0.25">
       <c r="A189" s="4" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="B189" s="4" t="s">
         <v>28</v>
@@ -5825,15 +5843,15 @@
         <v>8</v>
       </c>
       <c r="F189" s="5" t="s">
-        <v>189</v>
+        <v>190</v>
       </c>
       <c r="G189" s="5" t="s">
-        <v>187</v>
+        <v>188</v>
       </c>
     </row>
     <row r="190" spans="1:7" ht="67.5" x14ac:dyDescent="0.25">
       <c r="A190" s="4" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="B190" s="4" t="s">
         <v>29</v>
@@ -5848,15 +5866,15 @@
         <v>8</v>
       </c>
       <c r="F190" s="5" t="s">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="G190" s="5" t="s">
-        <v>187</v>
+        <v>188</v>
       </c>
     </row>
     <row r="191" spans="1:7" ht="67.5" x14ac:dyDescent="0.25">
       <c r="A191" s="4" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="B191" s="4" t="s">
         <v>30</v>
@@ -5871,15 +5889,15 @@
         <v>8</v>
       </c>
       <c r="F191" s="5" t="s">
-        <v>191</v>
+        <v>192</v>
       </c>
       <c r="G191" s="5" t="s">
-        <v>187</v>
+        <v>188</v>
       </c>
     </row>
     <row r="192" spans="1:7" ht="45" x14ac:dyDescent="0.25">
       <c r="A192" s="4" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="B192" s="4" t="s">
         <v>31</v>
@@ -5894,18 +5912,18 @@
         <v>8</v>
       </c>
       <c r="F192" s="5" t="s">
-        <v>195</v>
+        <v>196</v>
       </c>
       <c r="G192" s="5" t="s">
-        <v>172</v>
+        <v>173</v>
       </c>
     </row>
     <row r="193" spans="1:7" ht="56.25" x14ac:dyDescent="0.25">
       <c r="A193" s="4" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="B193" s="4" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="C193" s="4" t="s">
         <v>5</v>
@@ -5917,15 +5935,15 @@
         <v>8</v>
       </c>
       <c r="F193" s="5" t="s">
-        <v>196</v>
+        <v>197</v>
       </c>
       <c r="G193" s="5" t="s">
-        <v>172</v>
+        <v>173</v>
       </c>
     </row>
     <row r="194" spans="1:7" ht="56.25" x14ac:dyDescent="0.25">
       <c r="A194" s="4" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="B194" s="4" t="s">
         <v>32</v>
@@ -5940,15 +5958,15 @@
         <v>77</v>
       </c>
       <c r="F194" s="5" t="s">
-        <v>197</v>
+        <v>198</v>
       </c>
       <c r="G194" s="5" t="s">
-        <v>198</v>
+        <v>199</v>
       </c>
     </row>
     <row r="195" spans="1:7" ht="56.25" x14ac:dyDescent="0.25">
       <c r="A195" s="4" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="B195" s="4" t="s">
         <v>33</v>
@@ -5963,15 +5981,15 @@
         <v>77</v>
       </c>
       <c r="F195" s="5" t="s">
-        <v>199</v>
+        <v>200</v>
       </c>
       <c r="G195" s="5" t="s">
-        <v>169</v>
+        <v>170</v>
       </c>
     </row>
     <row r="196" spans="1:7" ht="33.75" x14ac:dyDescent="0.25">
       <c r="A196" s="4" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="B196" s="4" t="s">
         <v>34</v>
@@ -5983,18 +6001,18 @@
         <v>4</v>
       </c>
       <c r="E196" s="4" t="s">
-        <v>200</v>
+        <v>201</v>
       </c>
       <c r="F196" s="5" t="s">
-        <v>201</v>
+        <v>202</v>
       </c>
       <c r="G196" s="5" t="s">
-        <v>202</v>
+        <v>203</v>
       </c>
     </row>
     <row r="197" spans="1:7" ht="22.5" x14ac:dyDescent="0.25">
       <c r="A197" s="4" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="B197" s="4" t="s">
         <v>35</v>
@@ -6006,18 +6024,18 @@
         <v>5</v>
       </c>
       <c r="E197" s="4" t="s">
-        <v>200</v>
+        <v>201</v>
       </c>
       <c r="F197" s="5" t="s">
-        <v>203</v>
+        <v>204</v>
       </c>
       <c r="G197" s="5" t="s">
-        <v>204</v>
+        <v>205</v>
       </c>
     </row>
     <row r="198" spans="1:7" ht="33.75" x14ac:dyDescent="0.25">
       <c r="A198" s="4" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="B198" s="4" t="s">
         <v>36</v>
@@ -6029,18 +6047,18 @@
         <v>4</v>
       </c>
       <c r="E198" s="4" t="s">
-        <v>200</v>
+        <v>201</v>
       </c>
       <c r="F198" s="5" t="s">
-        <v>205</v>
+        <v>206</v>
       </c>
       <c r="G198" s="5" t="s">
-        <v>206</v>
+        <v>207</v>
       </c>
     </row>
     <row r="199" spans="1:7" ht="33.75" x14ac:dyDescent="0.25">
       <c r="A199" s="4" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="B199" s="4" t="s">
         <v>37</v>
@@ -6055,15 +6073,15 @@
         <v>9</v>
       </c>
       <c r="F199" s="5" t="s">
-        <v>207</v>
+        <v>208</v>
       </c>
       <c r="G199" s="5" t="s">
-        <v>208</v>
+        <v>209</v>
       </c>
     </row>
     <row r="200" spans="1:7" ht="33.75" x14ac:dyDescent="0.25">
       <c r="A200" s="4" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="B200" s="4" t="s">
         <v>38</v>
@@ -6078,15 +6096,15 @@
         <v>9</v>
       </c>
       <c r="F200" s="5" t="s">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="G200" s="5" t="s">
-        <v>208</v>
+        <v>209</v>
       </c>
     </row>
     <row r="201" spans="1:7" ht="45" x14ac:dyDescent="0.25">
       <c r="A201" s="4" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="B201" s="4" t="s">
         <v>39</v>
@@ -6101,15 +6119,15 @@
         <v>9</v>
       </c>
       <c r="F201" s="5" t="s">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="G201" s="5" t="s">
-        <v>208</v>
+        <v>209</v>
       </c>
     </row>
     <row r="202" spans="1:7" ht="33.75" x14ac:dyDescent="0.25">
       <c r="A202" s="4" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="B202" s="4" t="s">
         <v>40</v>
@@ -6124,15 +6142,15 @@
         <v>9</v>
       </c>
       <c r="F202" s="5" t="s">
-        <v>112</v>
+        <v>113</v>
       </c>
       <c r="G202" s="5" t="s">
-        <v>208</v>
+        <v>209</v>
       </c>
     </row>
     <row r="203" spans="1:7" ht="33.75" x14ac:dyDescent="0.25">
       <c r="A203" s="4" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="B203" s="4" t="s">
         <v>16</v>
@@ -6147,15 +6165,15 @@
         <v>9</v>
       </c>
       <c r="F203" s="5" t="s">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="G203" s="5" t="s">
-        <v>208</v>
+        <v>209</v>
       </c>
     </row>
     <row r="204" spans="1:7" ht="56.25" x14ac:dyDescent="0.25">
       <c r="A204" s="4" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="B204" s="4" t="s">
         <v>17</v>
@@ -6170,15 +6188,15 @@
         <v>9</v>
       </c>
       <c r="F204" s="5" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="G204" s="5" t="s">
-        <v>208</v>
+        <v>209</v>
       </c>
     </row>
     <row r="205" spans="1:7" ht="33.75" x14ac:dyDescent="0.25">
       <c r="A205" s="4" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="B205" s="4" t="s">
         <v>18</v>
@@ -6193,15 +6211,15 @@
         <v>9</v>
       </c>
       <c r="F205" s="5" t="s">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="G205" s="5" t="s">
-        <v>208</v>
+        <v>209</v>
       </c>
     </row>
     <row r="206" spans="1:7" ht="45" x14ac:dyDescent="0.25">
       <c r="A206" s="4" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="B206" s="4" t="s">
         <v>19</v>
@@ -6216,15 +6234,15 @@
         <v>9</v>
       </c>
       <c r="F206" s="5" t="s">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="G206" s="5" t="s">
-        <v>208</v>
+        <v>209</v>
       </c>
     </row>
     <row r="207" spans="1:7" ht="56.25" x14ac:dyDescent="0.25">
       <c r="A207" s="4" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="B207" s="4" t="s">
         <v>20</v>
@@ -6239,15 +6257,15 @@
         <v>9</v>
       </c>
       <c r="F207" s="5" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="G207" s="5" t="s">
-        <v>208</v>
+        <v>209</v>
       </c>
     </row>
     <row r="208" spans="1:7" ht="45" x14ac:dyDescent="0.25">
       <c r="A208" s="4" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="B208" s="4" t="s">
         <v>21</v>
@@ -6262,18 +6280,18 @@
         <v>9</v>
       </c>
       <c r="F208" s="5" t="s">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="G208" s="5" t="s">
-        <v>208</v>
+        <v>209</v>
       </c>
     </row>
     <row r="209" spans="1:7" ht="45" x14ac:dyDescent="0.25">
       <c r="A209" s="4" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="B209" s="4" t="s">
-        <v>220</v>
+        <v>221</v>
       </c>
       <c r="C209" s="4" t="s">
         <v>5</v>
@@ -6285,15 +6303,15 @@
         <v>9</v>
       </c>
       <c r="F209" s="5" t="s">
-        <v>210</v>
+        <v>211</v>
       </c>
       <c r="G209" s="5" t="s">
-        <v>208</v>
+        <v>209</v>
       </c>
     </row>
     <row r="210" spans="1:7" ht="67.5" x14ac:dyDescent="0.25">
       <c r="A210" s="4" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="B210" s="4" t="s">
         <v>41</v>
@@ -6308,18 +6326,18 @@
         <v>9</v>
       </c>
       <c r="F210" s="5" t="s">
-        <v>211</v>
+        <v>212</v>
       </c>
       <c r="G210" s="5" t="s">
-        <v>208</v>
+        <v>209</v>
       </c>
     </row>
     <row r="211" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A211" s="4" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="B211" s="4" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="C211" s="4" t="s">
         <v>4</v>
@@ -6328,21 +6346,21 @@
         <v>4</v>
       </c>
       <c r="E211" s="4" t="s">
-        <v>147</v>
+        <v>148</v>
       </c>
       <c r="F211" s="5" t="s">
-        <v>148</v>
+        <v>149</v>
       </c>
       <c r="G211" s="5" t="s">
-        <v>212</v>
+        <v>213</v>
       </c>
     </row>
     <row r="212" spans="1:7" ht="33.75" x14ac:dyDescent="0.25">
       <c r="A212" s="4" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="B212" s="4" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="C212" s="4" t="s">
         <v>5</v>
@@ -6354,18 +6372,18 @@
         <v>9</v>
       </c>
       <c r="F212" s="5" t="s">
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="G212" s="5" t="s">
-        <v>208</v>
+        <v>209</v>
       </c>
     </row>
     <row r="213" spans="1:7" ht="33.75" x14ac:dyDescent="0.25">
       <c r="A213" s="4" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="B213" s="4" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="C213" s="4" t="s">
         <v>5</v>
@@ -6377,18 +6395,18 @@
         <v>78</v>
       </c>
       <c r="F213" s="5" t="s">
-        <v>150</v>
+        <v>151</v>
       </c>
       <c r="G213" s="5" t="s">
-        <v>219</v>
+        <v>220</v>
       </c>
     </row>
     <row r="214" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A214" s="4" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="B214" s="4" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="C214" s="7" t="s">
         <v>4</v>
@@ -6397,21 +6415,21 @@
         <v>4</v>
       </c>
       <c r="E214" s="4" t="s">
-        <v>147</v>
+        <v>148</v>
       </c>
       <c r="F214" s="5" t="s">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="G214" s="5" t="s">
-        <v>212</v>
+        <v>213</v>
       </c>
     </row>
     <row r="215" spans="1:7" ht="33.75" x14ac:dyDescent="0.25">
       <c r="A215" s="4" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="B215" s="4" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="C215" s="4" t="s">
         <v>5</v>
@@ -6423,18 +6441,18 @@
         <v>9</v>
       </c>
       <c r="F215" s="5" t="s">
-        <v>156</v>
+        <v>157</v>
       </c>
       <c r="G215" s="5" t="s">
-        <v>208</v>
+        <v>209</v>
       </c>
     </row>
     <row r="216" spans="1:7" ht="33.75" x14ac:dyDescent="0.25">
       <c r="A216" s="4" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="B216" s="4" t="s">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="C216" s="4" t="s">
         <v>5</v>
@@ -6446,18 +6464,18 @@
         <v>78</v>
       </c>
       <c r="F216" s="5" t="s">
-        <v>151</v>
+        <v>152</v>
       </c>
       <c r="G216" s="5" t="s">
-        <v>219</v>
+        <v>220</v>
       </c>
     </row>
     <row r="217" spans="1:7" ht="33.75" x14ac:dyDescent="0.25">
       <c r="A217" s="4" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="B217" s="4" t="s">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="C217" s="4" t="s">
         <v>5</v>
@@ -6469,18 +6487,18 @@
         <v>78</v>
       </c>
       <c r="F217" s="5" t="s">
-        <v>154</v>
+        <v>155</v>
       </c>
       <c r="G217" s="5" t="s">
-        <v>219</v>
+        <v>220</v>
       </c>
     </row>
     <row r="218" spans="1:7" ht="33.75" x14ac:dyDescent="0.25">
       <c r="A218" s="4" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="B218" s="4" t="s">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="C218" s="4" t="s">
         <v>5</v>
@@ -6492,18 +6510,18 @@
         <v>78</v>
       </c>
       <c r="F218" s="5" t="s">
-        <v>152</v>
+        <v>153</v>
       </c>
       <c r="G218" s="5" t="s">
-        <v>219</v>
+        <v>220</v>
       </c>
     </row>
     <row r="219" spans="1:7" ht="33.75" x14ac:dyDescent="0.25">
       <c r="A219" s="4" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="B219" s="4" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="C219" s="4" t="s">
         <v>5</v>
@@ -6515,18 +6533,18 @@
         <v>78</v>
       </c>
       <c r="F219" s="5" t="s">
-        <v>153</v>
+        <v>154</v>
       </c>
       <c r="G219" s="5" t="s">
-        <v>219</v>
+        <v>220</v>
       </c>
     </row>
     <row r="220" spans="1:7" ht="33.75" x14ac:dyDescent="0.25">
       <c r="A220" s="4" t="s">
+        <v>98</v>
+      </c>
+      <c r="B220" s="4" t="s">
         <v>97</v>
-      </c>
-      <c r="B220" s="4" t="s">
-        <v>96</v>
       </c>
       <c r="C220" s="4" t="s">
         <v>5</v>
@@ -6538,15 +6556,15 @@
         <v>78</v>
       </c>
       <c r="F220" s="5" t="s">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="G220" s="5" t="s">
-        <v>219</v>
+        <v>220</v>
       </c>
     </row>
     <row r="221" spans="1:7" ht="33.75" x14ac:dyDescent="0.25">
       <c r="A221" s="4" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="B221" s="4" t="s">
         <v>73</v>
@@ -6554,45 +6572,45 @@
       <c r="C221" s="4" t="s">
         <v>5</v>
       </c>
-      <c r="D221" s="4" t="s">
-        <v>4</v>
+      <c r="D221" s="12" t="s">
+        <v>5</v>
       </c>
       <c r="E221" s="4" t="s">
         <v>78</v>
       </c>
       <c r="F221" s="5" t="s">
-        <v>146</v>
+        <v>147</v>
       </c>
       <c r="G221" s="5" t="s">
-        <v>219</v>
+        <v>220</v>
       </c>
     </row>
     <row r="222" spans="1:7" ht="33.75" x14ac:dyDescent="0.25">
       <c r="A222" s="4" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="B222" s="4" t="s">
-        <v>116</v>
+        <v>117</v>
       </c>
       <c r="C222" s="4" t="s">
         <v>5</v>
       </c>
-      <c r="D222" s="4" t="s">
-        <v>4</v>
+      <c r="D222" s="12" t="s">
+        <v>5</v>
       </c>
       <c r="E222" s="4" t="s">
         <v>78</v>
       </c>
       <c r="F222" s="5" t="s">
-        <v>115</v>
+        <v>116</v>
       </c>
       <c r="G222" s="5" t="s">
-        <v>219</v>
+        <v>220</v>
       </c>
     </row>
     <row r="223" spans="1:7" ht="22.5" x14ac:dyDescent="0.25">
       <c r="A223" s="4" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="B223" s="4" t="s">
         <v>74</v>
@@ -6607,15 +6625,15 @@
         <v>8</v>
       </c>
       <c r="F223" s="5" t="s">
-        <v>114</v>
+        <v>115</v>
       </c>
       <c r="G223" s="5" t="s">
-        <v>212</v>
+        <v>213</v>
       </c>
     </row>
     <row r="224" spans="1:7" ht="56.25" x14ac:dyDescent="0.25">
       <c r="A224" s="4" t="s">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="B224" s="4" t="s">
         <v>10</v>
@@ -6630,15 +6648,15 @@
         <v>8</v>
       </c>
       <c r="F224" s="5" t="s">
-        <v>182</v>
+        <v>183</v>
       </c>
       <c r="G224" s="5" t="s">
-        <v>172</v>
+        <v>173</v>
       </c>
     </row>
     <row r="225" spans="1:7" ht="45" x14ac:dyDescent="0.25">
       <c r="A225" s="4" t="s">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="B225" s="4" t="s">
         <v>23</v>
@@ -6653,15 +6671,15 @@
         <v>8</v>
       </c>
       <c r="F225" s="5" t="s">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="G225" s="5" t="s">
-        <v>172</v>
+        <v>173</v>
       </c>
     </row>
     <row r="226" spans="1:7" ht="78.75" x14ac:dyDescent="0.25">
       <c r="A226" s="4" t="s">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="B226" s="4" t="s">
         <v>24</v>
@@ -6676,18 +6694,18 @@
         <v>78</v>
       </c>
       <c r="F226" s="5" t="s">
-        <v>174</v>
+        <v>175</v>
       </c>
       <c r="G226" s="5" t="s">
-        <v>175</v>
+        <v>176</v>
       </c>
     </row>
     <row r="227" spans="1:7" ht="22.5" x14ac:dyDescent="0.25">
       <c r="A227" s="4" t="s">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="B227" s="4" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="C227" s="4" t="s">
         <v>5</v>
@@ -6699,15 +6717,15 @@
         <v>79</v>
       </c>
       <c r="F227" s="5" t="s">
-        <v>177</v>
+        <v>178</v>
       </c>
       <c r="G227" s="5" t="s">
-        <v>187</v>
+        <v>188</v>
       </c>
     </row>
     <row r="228" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A228" s="4" t="s">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="B228" s="4" t="s">
         <v>26</v>
@@ -6722,15 +6740,15 @@
         <v>8</v>
       </c>
       <c r="F228" s="5" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="G228" s="5" t="s">
-        <v>187</v>
+        <v>188</v>
       </c>
     </row>
     <row r="229" spans="1:7" ht="22.5" x14ac:dyDescent="0.25">
       <c r="A229" s="4" t="s">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="B229" s="4" t="s">
         <v>27</v>
@@ -6745,15 +6763,15 @@
         <v>8</v>
       </c>
       <c r="F229" s="5" t="s">
+        <v>189</v>
+      </c>
+      <c r="G229" s="5" t="s">
         <v>188</v>
-      </c>
-      <c r="G229" s="5" t="s">
-        <v>187</v>
       </c>
     </row>
     <row r="230" spans="1:7" ht="67.5" x14ac:dyDescent="0.25">
       <c r="A230" s="4" t="s">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="B230" s="4" t="s">
         <v>28</v>
@@ -6768,15 +6786,15 @@
         <v>8</v>
       </c>
       <c r="F230" s="5" t="s">
-        <v>189</v>
+        <v>190</v>
       </c>
       <c r="G230" s="5" t="s">
-        <v>187</v>
+        <v>188</v>
       </c>
     </row>
     <row r="231" spans="1:7" ht="67.5" x14ac:dyDescent="0.25">
       <c r="A231" s="4" t="s">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="B231" s="4" t="s">
         <v>29</v>
@@ -6791,15 +6809,15 @@
         <v>8</v>
       </c>
       <c r="F231" s="5" t="s">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="G231" s="5" t="s">
-        <v>187</v>
+        <v>188</v>
       </c>
     </row>
     <row r="232" spans="1:7" ht="67.5" x14ac:dyDescent="0.25">
       <c r="A232" s="4" t="s">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="B232" s="4" t="s">
         <v>30</v>
@@ -6814,15 +6832,15 @@
         <v>8</v>
       </c>
       <c r="F232" s="5" t="s">
-        <v>191</v>
+        <v>192</v>
       </c>
       <c r="G232" s="5" t="s">
-        <v>187</v>
+        <v>188</v>
       </c>
     </row>
     <row r="233" spans="1:7" ht="45" x14ac:dyDescent="0.25">
       <c r="A233" s="4" t="s">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="B233" s="4" t="s">
         <v>31</v>
@@ -6837,18 +6855,18 @@
         <v>8</v>
       </c>
       <c r="F233" s="5" t="s">
-        <v>195</v>
+        <v>196</v>
       </c>
       <c r="G233" s="5" t="s">
-        <v>172</v>
+        <v>173</v>
       </c>
     </row>
     <row r="234" spans="1:7" ht="56.25" x14ac:dyDescent="0.25">
       <c r="A234" s="4" t="s">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="B234" s="4" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="C234" s="4" t="s">
         <v>5</v>
@@ -6860,15 +6878,15 @@
         <v>8</v>
       </c>
       <c r="F234" s="5" t="s">
-        <v>196</v>
+        <v>197</v>
       </c>
       <c r="G234" s="5" t="s">
-        <v>172</v>
+        <v>173</v>
       </c>
     </row>
     <row r="235" spans="1:7" ht="56.25" x14ac:dyDescent="0.25">
       <c r="A235" s="4" t="s">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="B235" s="4" t="s">
         <v>32</v>
@@ -6883,15 +6901,15 @@
         <v>77</v>
       </c>
       <c r="F235" s="5" t="s">
-        <v>197</v>
+        <v>198</v>
       </c>
       <c r="G235" s="5" t="s">
-        <v>198</v>
+        <v>199</v>
       </c>
     </row>
     <row r="236" spans="1:7" ht="56.25" x14ac:dyDescent="0.25">
       <c r="A236" s="4" t="s">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="B236" s="4" t="s">
         <v>33</v>
@@ -6906,15 +6924,15 @@
         <v>77</v>
       </c>
       <c r="F236" s="5" t="s">
-        <v>199</v>
+        <v>200</v>
       </c>
       <c r="G236" s="5" t="s">
-        <v>169</v>
+        <v>170</v>
       </c>
     </row>
     <row r="237" spans="1:7" ht="33.75" x14ac:dyDescent="0.25">
       <c r="A237" s="4" t="s">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="B237" s="4" t="s">
         <v>34</v>
@@ -6926,18 +6944,18 @@
         <v>4</v>
       </c>
       <c r="E237" s="4" t="s">
-        <v>200</v>
+        <v>201</v>
       </c>
       <c r="F237" s="5" t="s">
-        <v>201</v>
+        <v>202</v>
       </c>
       <c r="G237" s="5" t="s">
-        <v>202</v>
+        <v>203</v>
       </c>
     </row>
     <row r="238" spans="1:7" ht="22.5" x14ac:dyDescent="0.25">
       <c r="A238" s="4" t="s">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="B238" s="4" t="s">
         <v>35</v>
@@ -6949,18 +6967,18 @@
         <v>5</v>
       </c>
       <c r="E238" s="4" t="s">
-        <v>200</v>
+        <v>201</v>
       </c>
       <c r="F238" s="5" t="s">
-        <v>203</v>
+        <v>204</v>
       </c>
       <c r="G238" s="5" t="s">
-        <v>204</v>
+        <v>205</v>
       </c>
     </row>
     <row r="239" spans="1:7" ht="33.75" x14ac:dyDescent="0.25">
       <c r="A239" s="4" t="s">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="B239" s="4" t="s">
         <v>36</v>
@@ -6972,18 +6990,18 @@
         <v>4</v>
       </c>
       <c r="E239" s="4" t="s">
-        <v>200</v>
+        <v>201</v>
       </c>
       <c r="F239" s="5" t="s">
-        <v>205</v>
+        <v>206</v>
       </c>
       <c r="G239" s="5" t="s">
-        <v>206</v>
+        <v>207</v>
       </c>
     </row>
     <row r="240" spans="1:7" ht="33.75" x14ac:dyDescent="0.25">
       <c r="A240" s="4" t="s">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="B240" s="4" t="s">
         <v>38</v>
@@ -6998,15 +7016,15 @@
         <v>9</v>
       </c>
       <c r="F240" s="5" t="s">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="G240" s="5" t="s">
-        <v>208</v>
+        <v>209</v>
       </c>
     </row>
     <row r="241" spans="1:7" ht="45" x14ac:dyDescent="0.25">
       <c r="A241" s="4" t="s">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="B241" s="4" t="s">
         <v>39</v>
@@ -7021,15 +7039,15 @@
         <v>9</v>
       </c>
       <c r="F241" s="5" t="s">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="G241" s="5" t="s">
-        <v>208</v>
+        <v>209</v>
       </c>
     </row>
     <row r="242" spans="1:7" ht="33.75" x14ac:dyDescent="0.25">
       <c r="A242" s="4" t="s">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="B242" s="4" t="s">
         <v>40</v>
@@ -7044,15 +7062,15 @@
         <v>9</v>
       </c>
       <c r="F242" s="5" t="s">
-        <v>112</v>
+        <v>113</v>
       </c>
       <c r="G242" s="5" t="s">
-        <v>208</v>
+        <v>209</v>
       </c>
     </row>
     <row r="243" spans="1:7" ht="33.75" x14ac:dyDescent="0.25">
       <c r="A243" s="4" t="s">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="B243" s="4" t="s">
         <v>16</v>
@@ -7067,15 +7085,15 @@
         <v>9</v>
       </c>
       <c r="F243" s="5" t="s">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="G243" s="5" t="s">
-        <v>208</v>
+        <v>209</v>
       </c>
     </row>
     <row r="244" spans="1:7" ht="56.25" x14ac:dyDescent="0.25">
       <c r="A244" s="4" t="s">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="B244" s="4" t="s">
         <v>17</v>
@@ -7090,15 +7108,15 @@
         <v>9</v>
       </c>
       <c r="F244" s="5" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="G244" s="5" t="s">
-        <v>208</v>
+        <v>209</v>
       </c>
     </row>
     <row r="245" spans="1:7" ht="33.75" x14ac:dyDescent="0.25">
       <c r="A245" s="4" t="s">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="B245" s="4" t="s">
         <v>18</v>
@@ -7113,15 +7131,15 @@
         <v>9</v>
       </c>
       <c r="F245" s="5" t="s">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="G245" s="5" t="s">
-        <v>208</v>
+        <v>209</v>
       </c>
     </row>
     <row r="246" spans="1:7" ht="45" x14ac:dyDescent="0.25">
       <c r="A246" s="4" t="s">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="B246" s="4" t="s">
         <v>19</v>
@@ -7136,15 +7154,15 @@
         <v>9</v>
       </c>
       <c r="F246" s="5" t="s">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="G246" s="5" t="s">
-        <v>208</v>
+        <v>209</v>
       </c>
     </row>
     <row r="247" spans="1:7" ht="56.25" x14ac:dyDescent="0.25">
       <c r="A247" s="4" t="s">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="B247" s="4" t="s">
         <v>20</v>
@@ -7159,15 +7177,15 @@
         <v>9</v>
       </c>
       <c r="F247" s="5" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="G247" s="5" t="s">
-        <v>208</v>
+        <v>209</v>
       </c>
     </row>
     <row r="248" spans="1:7" ht="45" x14ac:dyDescent="0.25">
       <c r="A248" s="4" t="s">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="B248" s="4" t="s">
         <v>21</v>
@@ -7182,18 +7200,18 @@
         <v>9</v>
       </c>
       <c r="F248" s="5" t="s">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="G248" s="5" t="s">
-        <v>208</v>
+        <v>209</v>
       </c>
     </row>
     <row r="249" spans="1:7" ht="45" x14ac:dyDescent="0.25">
       <c r="A249" s="4" t="s">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="B249" s="4" t="s">
-        <v>220</v>
+        <v>221</v>
       </c>
       <c r="C249" s="4" t="s">
         <v>5</v>
@@ -7205,15 +7223,15 @@
         <v>9</v>
       </c>
       <c r="F249" s="5" t="s">
-        <v>210</v>
+        <v>211</v>
       </c>
       <c r="G249" s="5" t="s">
-        <v>208</v>
+        <v>209</v>
       </c>
     </row>
     <row r="250" spans="1:7" ht="67.5" x14ac:dyDescent="0.25">
       <c r="A250" s="4" t="s">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="B250" s="4" t="s">
         <v>41</v>
@@ -7228,18 +7246,18 @@
         <v>9</v>
       </c>
       <c r="F250" s="5" t="s">
-        <v>211</v>
+        <v>212</v>
       </c>
       <c r="G250" s="5" t="s">
-        <v>208</v>
+        <v>209</v>
       </c>
     </row>
     <row r="251" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A251" s="4" t="s">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="B251" s="4" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="C251" s="4" t="s">
         <v>5</v>
@@ -7248,21 +7266,21 @@
         <v>4</v>
       </c>
       <c r="E251" s="4" t="s">
-        <v>147</v>
+        <v>148</v>
       </c>
       <c r="F251" s="5" t="s">
-        <v>148</v>
+        <v>149</v>
       </c>
       <c r="G251" s="5" t="s">
-        <v>212</v>
+        <v>213</v>
       </c>
     </row>
     <row r="252" spans="1:7" ht="22.5" x14ac:dyDescent="0.25">
       <c r="A252" s="4" t="s">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="B252" s="4" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="C252" s="4" t="s">
         <v>5</v>
@@ -7274,18 +7292,18 @@
         <v>79</v>
       </c>
       <c r="F252" s="5" t="s">
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="G252" s="5" t="s">
-        <v>212</v>
+        <v>213</v>
       </c>
     </row>
     <row r="253" spans="1:7" ht="33.75" x14ac:dyDescent="0.25">
       <c r="A253" s="4" t="s">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="B253" s="4" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="C253" s="4" t="s">
         <v>5</v>
@@ -7297,18 +7315,18 @@
         <v>78</v>
       </c>
       <c r="F253" s="5" t="s">
-        <v>150</v>
+        <v>151</v>
       </c>
       <c r="G253" s="5" t="s">
-        <v>219</v>
+        <v>220</v>
       </c>
     </row>
     <row r="254" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A254" s="4" t="s">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="B254" s="4" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="C254" s="4" t="s">
         <v>5</v>
@@ -7317,21 +7335,21 @@
         <v>4</v>
       </c>
       <c r="E254" s="4" t="s">
-        <v>147</v>
+        <v>148</v>
       </c>
       <c r="F254" s="5" t="s">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="G254" s="5" t="s">
-        <v>212</v>
+        <v>213</v>
       </c>
     </row>
     <row r="255" spans="1:7" ht="22.5" x14ac:dyDescent="0.25">
       <c r="A255" s="4" t="s">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="B255" s="4" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="C255" s="4" t="s">
         <v>5</v>
@@ -7343,18 +7361,18 @@
         <v>79</v>
       </c>
       <c r="F255" s="5" t="s">
-        <v>156</v>
+        <v>157</v>
       </c>
       <c r="G255" s="5" t="s">
-        <v>212</v>
+        <v>213</v>
       </c>
     </row>
     <row r="256" spans="1:7" ht="33.75" x14ac:dyDescent="0.25">
       <c r="A256" s="4" t="s">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="B256" s="4" t="s">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="C256" s="4" t="s">
         <v>5</v>
@@ -7366,18 +7384,18 @@
         <v>78</v>
       </c>
       <c r="F256" s="5" t="s">
-        <v>151</v>
+        <v>152</v>
       </c>
       <c r="G256" s="5" t="s">
-        <v>219</v>
+        <v>220</v>
       </c>
     </row>
     <row r="257" spans="1:7" ht="33.75" x14ac:dyDescent="0.25">
       <c r="A257" s="4" t="s">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="B257" s="4" t="s">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="C257" s="4" t="s">
         <v>5</v>
@@ -7389,18 +7407,18 @@
         <v>78</v>
       </c>
       <c r="F257" s="5" t="s">
-        <v>154</v>
+        <v>155</v>
       </c>
       <c r="G257" s="5" t="s">
-        <v>219</v>
+        <v>220</v>
       </c>
     </row>
     <row r="258" spans="1:7" ht="33.75" x14ac:dyDescent="0.25">
       <c r="A258" s="4" t="s">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="B258" s="4" t="s">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="C258" s="4" t="s">
         <v>5</v>
@@ -7412,18 +7430,18 @@
         <v>78</v>
       </c>
       <c r="F258" s="5" t="s">
-        <v>152</v>
+        <v>153</v>
       </c>
       <c r="G258" s="5" t="s">
-        <v>219</v>
+        <v>220</v>
       </c>
     </row>
     <row r="259" spans="1:7" ht="33.75" x14ac:dyDescent="0.25">
       <c r="A259" s="4" t="s">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="B259" s="4" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="C259" s="4" t="s">
         <v>5</v>
@@ -7435,18 +7453,18 @@
         <v>78</v>
       </c>
       <c r="F259" s="5" t="s">
-        <v>153</v>
+        <v>154</v>
       </c>
       <c r="G259" s="5" t="s">
-        <v>219</v>
+        <v>220</v>
       </c>
     </row>
     <row r="260" spans="1:7" ht="33.75" x14ac:dyDescent="0.25">
       <c r="A260" s="4" t="s">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="B260" s="4" t="s">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="C260" s="4" t="s">
         <v>5</v>
@@ -7458,15 +7476,15 @@
         <v>78</v>
       </c>
       <c r="F260" s="5" t="s">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="G260" s="5" t="s">
-        <v>219</v>
+        <v>220</v>
       </c>
     </row>
     <row r="261" spans="1:7" ht="33.75" x14ac:dyDescent="0.25">
       <c r="A261" s="4" t="s">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="B261" s="4" t="s">
         <v>73</v>
@@ -7474,45 +7492,45 @@
       <c r="C261" s="4" t="s">
         <v>5</v>
       </c>
-      <c r="D261" s="4" t="s">
-        <v>4</v>
+      <c r="D261" s="12" t="s">
+        <v>5</v>
       </c>
       <c r="E261" s="4" t="s">
         <v>78</v>
       </c>
       <c r="F261" s="5" t="s">
-        <v>146</v>
+        <v>147</v>
       </c>
       <c r="G261" s="5" t="s">
-        <v>219</v>
+        <v>220</v>
       </c>
     </row>
     <row r="262" spans="1:7" ht="33.75" x14ac:dyDescent="0.25">
       <c r="A262" s="4" t="s">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="B262" s="4" t="s">
-        <v>116</v>
+        <v>117</v>
       </c>
       <c r="C262" s="4" t="s">
         <v>5</v>
       </c>
-      <c r="D262" s="4" t="s">
-        <v>4</v>
+      <c r="D262" s="12" t="s">
+        <v>5</v>
       </c>
       <c r="E262" s="4" t="s">
         <v>78</v>
       </c>
       <c r="F262" s="5" t="s">
-        <v>115</v>
+        <v>116</v>
       </c>
       <c r="G262" s="5" t="s">
-        <v>219</v>
+        <v>220</v>
       </c>
     </row>
     <row r="263" spans="1:7" ht="22.5" x14ac:dyDescent="0.25">
       <c r="A263" s="4" t="s">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="B263" s="4" t="s">
         <v>74</v>
@@ -7527,15 +7545,15 @@
         <v>8</v>
       </c>
       <c r="F263" s="5" t="s">
-        <v>114</v>
+        <v>115</v>
       </c>
       <c r="G263" s="5" t="s">
-        <v>212</v>
+        <v>213</v>
       </c>
     </row>
     <row r="264" spans="1:7" ht="56.25" x14ac:dyDescent="0.25">
       <c r="A264" s="4" t="s">
-        <v>223</v>
+        <v>224</v>
       </c>
       <c r="B264" s="4" t="s">
         <v>10</v>
@@ -7550,18 +7568,18 @@
         <v>8</v>
       </c>
       <c r="F264" s="5" t="s">
-        <v>182</v>
+        <v>183</v>
       </c>
       <c r="G264" s="5" t="s">
-        <v>172</v>
+        <v>173</v>
       </c>
     </row>
     <row r="265" spans="1:7" ht="22.5" x14ac:dyDescent="0.25">
       <c r="A265" s="4" t="s">
-        <v>223</v>
+        <v>224</v>
       </c>
       <c r="B265" s="4" t="s">
-        <v>224</v>
+        <v>225</v>
       </c>
       <c r="C265" s="4" t="s">
         <v>5</v>
@@ -7573,15 +7591,15 @@
         <v>8</v>
       </c>
       <c r="F265" s="5" t="s">
-        <v>225</v>
+        <v>226</v>
       </c>
       <c r="G265" s="5" t="s">
-        <v>172</v>
+        <v>173</v>
       </c>
     </row>
     <row r="266" spans="1:7" ht="45" x14ac:dyDescent="0.25">
       <c r="A266" s="4" t="s">
-        <v>223</v>
+        <v>224</v>
       </c>
       <c r="B266" s="4" t="s">
         <v>23</v>
@@ -7596,18 +7614,18 @@
         <v>8</v>
       </c>
       <c r="F266" s="5" t="s">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="G266" s="5" t="s">
-        <v>172</v>
+        <v>173</v>
       </c>
     </row>
     <row r="267" spans="1:7" ht="22.5" x14ac:dyDescent="0.25">
       <c r="A267" s="4" t="s">
-        <v>223</v>
+        <v>224</v>
       </c>
       <c r="B267" s="4" t="s">
-        <v>221</v>
+        <v>222</v>
       </c>
       <c r="C267" s="4" t="s">
         <v>5</v>
@@ -7619,18 +7637,18 @@
         <v>8</v>
       </c>
       <c r="F267" s="5" t="s">
-        <v>226</v>
+        <v>227</v>
       </c>
       <c r="G267" s="5" t="s">
-        <v>172</v>
+        <v>173</v>
       </c>
     </row>
     <row r="268" spans="1:7" ht="22.5" x14ac:dyDescent="0.25">
       <c r="A268" s="4" t="s">
-        <v>223</v>
+        <v>224</v>
       </c>
       <c r="B268" s="4" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="C268" s="4" t="s">
         <v>5</v>
@@ -7642,15 +7660,15 @@
         <v>79</v>
       </c>
       <c r="F268" s="5" t="s">
-        <v>177</v>
+        <v>178</v>
       </c>
       <c r="G268" s="5" t="s">
-        <v>187</v>
+        <v>188</v>
       </c>
     </row>
     <row r="269" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A269" s="4" t="s">
-        <v>223</v>
+        <v>224</v>
       </c>
       <c r="B269" s="4" t="s">
         <v>26</v>
@@ -7665,15 +7683,15 @@
         <v>8</v>
       </c>
       <c r="F269" s="5" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="G269" s="5" t="s">
-        <v>187</v>
+        <v>188</v>
       </c>
     </row>
     <row r="270" spans="1:7" ht="22.5" x14ac:dyDescent="0.25">
       <c r="A270" s="4" t="s">
-        <v>223</v>
+        <v>224</v>
       </c>
       <c r="B270" s="4" t="s">
         <v>27</v>
@@ -7688,15 +7706,15 @@
         <v>8</v>
       </c>
       <c r="F270" s="5" t="s">
+        <v>189</v>
+      </c>
+      <c r="G270" s="5" t="s">
         <v>188</v>
-      </c>
-      <c r="G270" s="5" t="s">
-        <v>187</v>
       </c>
     </row>
     <row r="271" spans="1:7" ht="67.5" x14ac:dyDescent="0.25">
       <c r="A271" s="4" t="s">
-        <v>223</v>
+        <v>224</v>
       </c>
       <c r="B271" s="4" t="s">
         <v>28</v>
@@ -7711,15 +7729,15 @@
         <v>8</v>
       </c>
       <c r="F271" s="5" t="s">
-        <v>189</v>
+        <v>190</v>
       </c>
       <c r="G271" s="5" t="s">
-        <v>187</v>
+        <v>188</v>
       </c>
     </row>
     <row r="272" spans="1:7" ht="67.5" x14ac:dyDescent="0.25">
       <c r="A272" s="4" t="s">
-        <v>223</v>
+        <v>224</v>
       </c>
       <c r="B272" s="4" t="s">
         <v>29</v>
@@ -7734,15 +7752,15 @@
         <v>8</v>
       </c>
       <c r="F272" s="5" t="s">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="G272" s="5" t="s">
-        <v>187</v>
+        <v>188</v>
       </c>
     </row>
     <row r="273" spans="1:7" ht="67.5" x14ac:dyDescent="0.25">
       <c r="A273" s="4" t="s">
-        <v>223</v>
+        <v>224</v>
       </c>
       <c r="B273" s="4" t="s">
         <v>30</v>
@@ -7757,15 +7775,15 @@
         <v>8</v>
       </c>
       <c r="F273" s="5" t="s">
-        <v>191</v>
+        <v>192</v>
       </c>
       <c r="G273" s="5" t="s">
-        <v>187</v>
+        <v>188</v>
       </c>
     </row>
     <row r="274" spans="1:7" ht="45" x14ac:dyDescent="0.25">
       <c r="A274" s="4" t="s">
-        <v>223</v>
+        <v>224</v>
       </c>
       <c r="B274" s="4" t="s">
         <v>31</v>
@@ -7780,18 +7798,18 @@
         <v>8</v>
       </c>
       <c r="F274" s="5" t="s">
-        <v>195</v>
+        <v>196</v>
       </c>
       <c r="G274" s="5" t="s">
-        <v>172</v>
+        <v>173</v>
       </c>
     </row>
     <row r="275" spans="1:7" ht="56.25" x14ac:dyDescent="0.25">
       <c r="A275" s="4" t="s">
-        <v>223</v>
+        <v>224</v>
       </c>
       <c r="B275" s="4" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="C275" s="4" t="s">
         <v>5</v>
@@ -7803,15 +7821,15 @@
         <v>8</v>
       </c>
       <c r="F275" s="5" t="s">
-        <v>196</v>
+        <v>197</v>
       </c>
       <c r="G275" s="5" t="s">
-        <v>172</v>
+        <v>173</v>
       </c>
     </row>
     <row r="276" spans="1:7" ht="56.25" x14ac:dyDescent="0.25">
       <c r="A276" s="4" t="s">
-        <v>223</v>
+        <v>224</v>
       </c>
       <c r="B276" s="4" t="s">
         <v>32</v>
@@ -7826,15 +7844,15 @@
         <v>77</v>
       </c>
       <c r="F276" s="5" t="s">
-        <v>197</v>
+        <v>198</v>
       </c>
       <c r="G276" s="5" t="s">
-        <v>198</v>
+        <v>199</v>
       </c>
     </row>
     <row r="277" spans="1:7" ht="56.25" x14ac:dyDescent="0.25">
       <c r="A277" s="4" t="s">
-        <v>223</v>
+        <v>224</v>
       </c>
       <c r="B277" s="4" t="s">
         <v>33</v>
@@ -7849,15 +7867,15 @@
         <v>77</v>
       </c>
       <c r="F277" s="5" t="s">
-        <v>199</v>
+        <v>200</v>
       </c>
       <c r="G277" s="5" t="s">
-        <v>169</v>
+        <v>170</v>
       </c>
     </row>
     <row r="278" spans="1:7" ht="33.75" x14ac:dyDescent="0.25">
       <c r="A278" s="4" t="s">
-        <v>223</v>
+        <v>224</v>
       </c>
       <c r="B278" s="4" t="s">
         <v>34</v>
@@ -7869,18 +7887,18 @@
         <v>4</v>
       </c>
       <c r="E278" s="4" t="s">
-        <v>200</v>
+        <v>201</v>
       </c>
       <c r="F278" s="5" t="s">
-        <v>201</v>
+        <v>202</v>
       </c>
       <c r="G278" s="5" t="s">
-        <v>202</v>
+        <v>203</v>
       </c>
     </row>
     <row r="279" spans="1:7" ht="22.5" x14ac:dyDescent="0.25">
       <c r="A279" s="4" t="s">
-        <v>223</v>
+        <v>224</v>
       </c>
       <c r="B279" s="4" t="s">
         <v>35</v>
@@ -7892,18 +7910,18 @@
         <v>5</v>
       </c>
       <c r="E279" s="4" t="s">
-        <v>200</v>
+        <v>201</v>
       </c>
       <c r="F279" s="5" t="s">
-        <v>203</v>
+        <v>204</v>
       </c>
       <c r="G279" s="5" t="s">
-        <v>204</v>
+        <v>205</v>
       </c>
     </row>
     <row r="280" spans="1:7" ht="33.75" x14ac:dyDescent="0.25">
       <c r="A280" s="4" t="s">
-        <v>223</v>
+        <v>224</v>
       </c>
       <c r="B280" s="4" t="s">
         <v>36</v>
@@ -7915,18 +7933,18 @@
         <v>4</v>
       </c>
       <c r="E280" s="4" t="s">
-        <v>200</v>
+        <v>201</v>
       </c>
       <c r="F280" s="5" t="s">
-        <v>205</v>
+        <v>206</v>
       </c>
       <c r="G280" s="5" t="s">
-        <v>206</v>
+        <v>207</v>
       </c>
     </row>
     <row r="281" spans="1:7" ht="33.75" x14ac:dyDescent="0.25">
       <c r="A281" s="4" t="s">
-        <v>223</v>
+        <v>224</v>
       </c>
       <c r="B281" s="4" t="s">
         <v>38</v>
@@ -7941,15 +7959,15 @@
         <v>9</v>
       </c>
       <c r="F281" s="5" t="s">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="G281" s="5" t="s">
-        <v>208</v>
+        <v>209</v>
       </c>
     </row>
     <row r="282" spans="1:7" ht="45" x14ac:dyDescent="0.25">
       <c r="A282" s="4" t="s">
-        <v>223</v>
+        <v>224</v>
       </c>
       <c r="B282" s="4" t="s">
         <v>39</v>
@@ -7964,19 +7982,19 @@
         <v>9</v>
       </c>
       <c r="F282" s="5" t="s">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="G282" s="5" t="s">
-        <v>208</v>
+        <v>209</v>
       </c>
     </row>
     <row r="283" spans="1:7" ht="33.75" x14ac:dyDescent="0.25">
       <c r="A283" s="4" t="s">
+        <v>224</v>
+      </c>
+      <c r="B283" s="4" t="s">
         <v>223</v>
       </c>
-      <c r="B283" s="4" t="s">
-        <v>222</v>
-      </c>
       <c r="C283" s="4" t="s">
         <v>5</v>
       </c>
@@ -7987,15 +8005,15 @@
         <v>9</v>
       </c>
       <c r="F283" s="5" t="s">
-        <v>112</v>
+        <v>113</v>
       </c>
       <c r="G283" s="5" t="s">
-        <v>208</v>
+        <v>209</v>
       </c>
     </row>
     <row r="284" spans="1:7" ht="33.75" x14ac:dyDescent="0.25">
       <c r="A284" s="4" t="s">
-        <v>223</v>
+        <v>224</v>
       </c>
       <c r="B284" s="4" t="s">
         <v>16</v>
@@ -8010,15 +8028,15 @@
         <v>9</v>
       </c>
       <c r="F284" s="5" t="s">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="G284" s="5" t="s">
-        <v>208</v>
+        <v>209</v>
       </c>
     </row>
     <row r="285" spans="1:7" ht="56.25" x14ac:dyDescent="0.25">
       <c r="A285" s="4" t="s">
-        <v>223</v>
+        <v>224</v>
       </c>
       <c r="B285" s="4" t="s">
         <v>17</v>
@@ -8033,15 +8051,15 @@
         <v>9</v>
       </c>
       <c r="F285" s="5" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="G285" s="5" t="s">
-        <v>208</v>
+        <v>209</v>
       </c>
     </row>
     <row r="286" spans="1:7" ht="33.75" x14ac:dyDescent="0.25">
       <c r="A286" s="4" t="s">
-        <v>223</v>
+        <v>224</v>
       </c>
       <c r="B286" s="4" t="s">
         <v>18</v>
@@ -8056,15 +8074,15 @@
         <v>9</v>
       </c>
       <c r="F286" s="5" t="s">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="G286" s="5" t="s">
-        <v>208</v>
+        <v>209</v>
       </c>
     </row>
     <row r="287" spans="1:7" ht="45" x14ac:dyDescent="0.25">
       <c r="A287" s="4" t="s">
-        <v>223</v>
+        <v>224</v>
       </c>
       <c r="B287" s="4" t="s">
         <v>19</v>
@@ -8079,15 +8097,15 @@
         <v>9</v>
       </c>
       <c r="F287" s="5" t="s">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="G287" s="5" t="s">
-        <v>208</v>
+        <v>209</v>
       </c>
     </row>
     <row r="288" spans="1:7" ht="56.25" x14ac:dyDescent="0.25">
       <c r="A288" s="4" t="s">
-        <v>223</v>
+        <v>224</v>
       </c>
       <c r="B288" s="4" t="s">
         <v>20</v>
@@ -8102,15 +8120,15 @@
         <v>9</v>
       </c>
       <c r="F288" s="5" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="G288" s="5" t="s">
-        <v>208</v>
+        <v>209</v>
       </c>
     </row>
     <row r="289" spans="1:7" ht="45" x14ac:dyDescent="0.25">
       <c r="A289" s="4" t="s">
-        <v>223</v>
+        <v>224</v>
       </c>
       <c r="B289" s="4" t="s">
         <v>21</v>
@@ -8125,18 +8143,18 @@
         <v>9</v>
       </c>
       <c r="F289" s="5" t="s">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="G289" s="5" t="s">
-        <v>208</v>
+        <v>209</v>
       </c>
     </row>
     <row r="290" spans="1:7" ht="45" x14ac:dyDescent="0.25">
       <c r="A290" s="4" t="s">
-        <v>223</v>
+        <v>224</v>
       </c>
       <c r="B290" s="4" t="s">
-        <v>220</v>
+        <v>221</v>
       </c>
       <c r="C290" s="4" t="s">
         <v>5</v>
@@ -8148,15 +8166,15 @@
         <v>9</v>
       </c>
       <c r="F290" s="5" t="s">
-        <v>210</v>
+        <v>211</v>
       </c>
       <c r="G290" s="5" t="s">
-        <v>208</v>
+        <v>209</v>
       </c>
     </row>
     <row r="291" spans="1:7" ht="67.5" x14ac:dyDescent="0.25">
       <c r="A291" s="4" t="s">
-        <v>223</v>
+        <v>224</v>
       </c>
       <c r="B291" s="4" t="s">
         <v>41</v>
@@ -8171,15 +8189,15 @@
         <v>9</v>
       </c>
       <c r="F291" s="5" t="s">
-        <v>211</v>
+        <v>212</v>
       </c>
       <c r="G291" s="5" t="s">
-        <v>208</v>
+        <v>209</v>
       </c>
     </row>
     <row r="292" spans="1:7" ht="22.5" x14ac:dyDescent="0.25">
       <c r="A292" s="4" t="s">
-        <v>223</v>
+        <v>224</v>
       </c>
       <c r="B292" s="9" t="s">
         <v>74</v>
@@ -8194,10 +8212,10 @@
         <v>8</v>
       </c>
       <c r="F292" s="5" t="s">
-        <v>114</v>
+        <v>115</v>
       </c>
       <c r="G292" s="5" t="s">
-        <v>212</v>
+        <v>213</v>
       </c>
     </row>
   </sheetData>
@@ -8217,7 +8235,7 @@
   <sheetData>
     <row r="1" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A1" s="10" t="s">
-        <v>159</v>
+        <v>160</v>
       </c>
       <c r="B1" s="10"/>
       <c r="C1" s="10"/>
@@ -8232,7 +8250,7 @@
     </row>
     <row r="2" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A2" s="10" t="s">
-        <v>160</v>
+        <v>161</v>
       </c>
       <c r="B2" s="10"/>
       <c r="C2" s="10"/>
@@ -8247,7 +8265,7 @@
     </row>
     <row r="3" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A3" s="11" t="s">
-        <v>161</v>
+        <v>162</v>
       </c>
       <c r="B3" s="11"/>
       <c r="C3" s="11"/>
@@ -8262,7 +8280,7 @@
     </row>
     <row r="4" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A4" s="11" t="s">
-        <v>162</v>
+        <v>163</v>
       </c>
       <c r="B4" s="11"/>
       <c r="C4" s="11"/>
